--- a/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP73" headerRowCount="1">
-  <autoFilter ref="A1:EP73"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP79" headerRowCount="1">
+  <autoFilter ref="A1:EP79"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP73"/>
+  <dimension ref="A1:EP79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1794,10 +1794,10 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="DE3" t="n">
         <v>2.25</v>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="DE4" t="n">
         <v>0.6</v>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3359,40 +3359,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
         <v>45898.75</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -3401,90 +3401,90 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>13</v>
+      </c>
+      <c r="V6" t="n">
         <v>10</v>
       </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>11</v>
-      </c>
-      <c r="U6" t="n">
-        <v>4</v>
-      </c>
-      <c r="V6" t="n">
-        <v>21</v>
-      </c>
       <c r="W6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="Z6" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE6" t="n">
-        <v>8.5</v>
+        <v>1.54</v>
       </c>
       <c r="AF6" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AO6" t="n">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AS6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AU6" t="n">
         <v>5</v>
@@ -3496,10 +3496,10 @@
         <v>1</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ6" t="n">
         <v>4</v>
@@ -3508,7 +3508,7 @@
         <v>1</v>
       </c>
       <c r="BB6" t="n">
-        <v>5069</v>
+        <v>5077</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
@@ -3529,73 +3529,73 @@
         <v>1</v>
       </c>
       <c r="BI6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ6" t="n">
         <v>2</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL6" t="n">
         <v>3</v>
       </c>
       <c r="BM6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN6" t="n">
         <v>4</v>
       </c>
-      <c r="BN6" t="n">
-        <v>3</v>
-      </c>
       <c r="BO6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ6" t="n">
         <v>1</v>
       </c>
       <c r="BR6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BS6" t="n">
         <v>2</v>
       </c>
       <c r="BT6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU6" t="n">
         <v>1</v>
       </c>
       <c r="BV6" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="BW6" t="n">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="BX6" t="n">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="BY6" t="n">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.44</v>
+        <v>1.49</v>
       </c>
       <c r="CA6" t="n">
-        <v>2.51</v>
+        <v>1.15</v>
       </c>
       <c r="CB6" t="n">
-        <v>2.95</v>
+        <v>2.64</v>
       </c>
       <c r="CC6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD6" t="n">
         <v>1</v>
       </c>
       <c r="CE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF6" t="n">
         <v>1</v>
@@ -3619,10 +3619,10 @@
         <v>1</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO6" t="n">
         <v>0</v>
@@ -3634,7 +3634,7 @@
         <v>1</v>
       </c>
       <c r="CR6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="CS6" t="n">
         <v>15</v>
@@ -3643,19 +3643,19 @@
         <v>1</v>
       </c>
       <c r="CU6" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="CV6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW6" t="n">
         <v>1</v>
       </c>
       <c r="CX6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CY6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="CZ6" t="n">
         <v>0</v>
@@ -3670,10 +3670,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="DE6" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3724,92 +3724,84 @@
         <v>0</v>
       </c>
       <c r="DV6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW6" t="n">
-        <v>39.96</v>
+        <v>40.6</v>
       </c>
       <c r="DX6" t="n">
-        <v>6.5</v>
+        <v>7.85</v>
       </c>
       <c r="DY6" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="DZ6" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA6" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EB6" t="inlineStr">
         <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EC6" t="inlineStr">
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr"/>
+      <c r="ED6" t="inlineStr"/>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="EG6" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="ED6" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EE6" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="EF6" t="inlineStr">
-        <is>
-          <t>6.90</t>
-        </is>
-      </c>
-      <c r="EG6" t="inlineStr">
-        <is>
-          <t>10.82</t>
-        </is>
-      </c>
-      <c r="EH6" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EI6" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EJ6" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="EK6" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EL6" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
       <c r="EM6" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EN6" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EO6" t="inlineStr"/>
@@ -3831,132 +3823,132 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
         <v>45898.75</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
         <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
       </c>
       <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
         <v>10</v>
       </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>21</v>
+      </c>
+      <c r="W7" t="n">
+        <v>13</v>
+      </c>
+      <c r="X7" t="n">
         <v>6</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>9</v>
-      </c>
-      <c r="T7" t="n">
-        <v>5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>13</v>
-      </c>
-      <c r="V7" t="n">
-        <v>10</v>
-      </c>
-      <c r="W7" t="n">
-        <v>15</v>
-      </c>
-      <c r="X7" t="n">
-        <v>18</v>
-      </c>
       <c r="Y7" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="Z7" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.54</v>
+        <v>8.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AO7" t="n">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AU7" t="n">
         <v>5</v>
@@ -3968,10 +3960,10 @@
         <v>1</v>
       </c>
       <c r="AX7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ7" t="n">
         <v>4</v>
@@ -3980,7 +3972,7 @@
         <v>1</v>
       </c>
       <c r="BB7" t="n">
-        <v>5077</v>
+        <v>5069</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
@@ -4001,73 +3993,73 @@
         <v>1</v>
       </c>
       <c r="BI7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM7" t="n">
         <v>4</v>
       </c>
-      <c r="BJ7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>6</v>
-      </c>
       <c r="BN7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ7" t="n">
         <v>1</v>
       </c>
       <c r="BR7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BS7" t="n">
         <v>2</v>
       </c>
       <c r="BT7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU7" t="n">
         <v>1</v>
       </c>
       <c r="BV7" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="BW7" t="n">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="BX7" t="n">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="BY7" t="n">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.49</v>
+        <v>0.44</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.15</v>
+        <v>2.51</v>
       </c>
       <c r="CB7" t="n">
-        <v>2.64</v>
+        <v>2.95</v>
       </c>
       <c r="CC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
         <v>1</v>
       </c>
       <c r="CE7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF7" t="n">
         <v>1</v>
@@ -4091,10 +4083,10 @@
         <v>1</v>
       </c>
       <c r="CM7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO7" t="n">
         <v>0</v>
@@ -4106,7 +4098,7 @@
         <v>1</v>
       </c>
       <c r="CR7" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="CS7" t="n">
         <v>15</v>
@@ -4115,19 +4107,19 @@
         <v>1</v>
       </c>
       <c r="CU7" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="CV7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW7" t="n">
         <v>1</v>
       </c>
       <c r="CX7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CY7" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="CZ7" t="n">
         <v>0</v>
@@ -4142,10 +4134,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4196,84 +4188,92 @@
         <v>0</v>
       </c>
       <c r="DV7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>40.6</v>
+        <v>39.96</v>
       </c>
       <c r="DX7" t="n">
-        <v>7.85</v>
+        <v>6.5</v>
       </c>
       <c r="DY7" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="DZ7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="EA7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EB7" t="inlineStr">
         <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EC7" t="inlineStr"/>
-      <c r="ED7" t="inlineStr"/>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EC7" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="ED7" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EJ7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EN7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EO7" t="inlineStr"/>
@@ -4609,7 +4609,7 @@
         <v>0.75</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4775,156 +4775,156 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
         <v>45899.75</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" t="n">
         <v>4</v>
       </c>
-      <c r="J9" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>11</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>8</v>
-      </c>
-      <c r="R9" t="n">
-        <v>4</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
         <v>7</v>
       </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>15</v>
-      </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X9" t="n">
         <v>7</v>
       </c>
       <c r="Y9" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="Z9" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.44</v>
+        <v>5.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.75</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AM9" t="n">
         <v>1.47</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AO9" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA9" t="n">
         <v>4</v>
       </c>
-      <c r="AV9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2</v>
-      </c>
       <c r="BB9" t="n">
-        <v>5068</v>
+        <v>5070</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
@@ -4945,115 +4945,115 @@
         <v>1</v>
       </c>
       <c r="BI9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT9" t="n">
         <v>4</v>
       </c>
-      <c r="BJ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>59</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>63</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS9" t="n">
         <v>5</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>29</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>56</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>53</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>19</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>15</v>
       </c>
       <c r="CT9" t="n">
         <v>1</v>
@@ -5062,7 +5062,7 @@
         <v>7</v>
       </c>
       <c r="CV9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CW9" t="n">
         <v>1</v>
@@ -5071,7 +5071,7 @@
         <v>6</v>
       </c>
       <c r="CY9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="CZ9" t="n">
         <v>0</v>
@@ -5086,10 +5086,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="DE9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5134,98 +5134,98 @@
         <v>1</v>
       </c>
       <c r="DT9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV9" t="b">
         <v>1</v>
       </c>
       <c r="DW9" t="n">
-        <v>42.17</v>
+        <v>36.63</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="DY9" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="DZ9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="EA9" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EB9" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
         <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EJ9" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM9" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EN9" t="inlineStr">
+        <is>
           <t>1.50</t>
-        </is>
-      </c>
-      <c r="EJ9" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="EK9" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EL9" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EM9" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EN9" t="inlineStr">
-        <is>
-          <t>1.63</t>
         </is>
       </c>
       <c r="EO9" t="inlineStr"/>
@@ -5247,156 +5247,156 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>45899.75</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>11</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="n">
         <v>7</v>
       </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L10" t="n">
-        <v>10</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>10</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
-        <v>6</v>
-      </c>
       <c r="U10" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="W10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X10" t="n">
         <v>7</v>
       </c>
       <c r="Y10" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="Z10" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
-        <v>5.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF10" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.57</v>
+        <v>6.75</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AM10" t="n">
         <v>1.47</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AO10" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB10" t="n">
-        <v>5070</v>
+        <v>5068</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
@@ -5417,64 +5417,64 @@
         <v>1</v>
       </c>
       <c r="BI10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
         <v>5</v>
       </c>
-      <c r="BK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>7</v>
-      </c>
       <c r="BN10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BO10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP10" t="n">
         <v>0</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU10" t="n">
         <v>1</v>
       </c>
       <c r="BV10" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BW10" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="BX10" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="BY10" t="n">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.91</v>
+        <v>1.86</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.14</v>
+        <v>0.99</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
@@ -5501,10 +5501,10 @@
         <v>1</v>
       </c>
       <c r="CK10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
@@ -5522,10 +5522,10 @@
         <v>1</v>
       </c>
       <c r="CR10" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="CS10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="CT10" t="n">
         <v>1</v>
@@ -5534,7 +5534,7 @@
         <v>7</v>
       </c>
       <c r="CV10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CW10" t="n">
         <v>1</v>
@@ -5543,7 +5543,7 @@
         <v>6</v>
       </c>
       <c r="CY10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CZ10" t="n">
         <v>0</v>
@@ -5558,10 +5558,10 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="DE10" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5606,98 +5606,98 @@
         <v>1</v>
       </c>
       <c r="DT10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV10" t="b">
         <v>1</v>
       </c>
       <c r="DW10" t="n">
-        <v>36.63</v>
+        <v>42.17</v>
       </c>
       <c r="DX10" t="n">
-        <v>8.67</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DY10" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="DZ10" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA10" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EB10" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EC10" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="ED10" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>7.29</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>5.33</t>
+        </is>
+      </c>
+      <c r="EG10" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr">
+        <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="EE10" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EF10" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="EG10" t="inlineStr">
-        <is>
-          <t>4.83</t>
-        </is>
-      </c>
-      <c r="EH10" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="EI10" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
       <c r="EJ10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="EK10" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EL10" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EM10" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EN10" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EO10" t="inlineStr"/>
@@ -6030,7 +6030,7 @@
         <v>50</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="DE11" t="n">
         <v>2.5</v>
@@ -6063,7 +6063,7 @@
         <v>0.93</v>
       </c>
       <c r="DO11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP11" t="b">
         <v>0</v>
@@ -6489,7 +6489,7 @@
         <v>1</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6950,10 +6950,10 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7409,7 +7409,7 @@
         <v>1.75</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -8334,10 +8334,10 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DF16" t="n">
         <v>3</v>
@@ -8367,7 +8367,7 @@
         <v>1.8</v>
       </c>
       <c r="DO16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8801,7 +8801,7 @@
         <v>1.75</v>
       </c>
       <c r="DE17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
         <v>0.99</v>
       </c>
       <c r="DO17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9262,7 +9262,7 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DE18" t="n">
         <v>2.25</v>
@@ -9867,70 +9867,70 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
         <v>45918.65277777778</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
+        <v>7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>5</v>
       </c>
-      <c r="L20" t="n">
-        <v>8</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
+        <v>10</v>
+      </c>
+      <c r="U20" t="n">
         <v>11</v>
       </c>
-      <c r="U20" t="n">
-        <v>10</v>
-      </c>
       <c r="V20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="X20" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y20" t="n">
         <v>45</v>
@@ -9941,82 +9941,82 @@
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AK20" t="n">
         <v>1.72</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.01</v>
+        <v>1.56</v>
       </c>
       <c r="AN20" t="n">
-        <v>3.22</v>
+        <v>2.2</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AU20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV20" t="n">
         <v>1</v>
       </c>
       <c r="AW20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BA20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB20" t="n">
-        <v>5125</v>
+        <v>5074</v>
       </c>
       <c r="BC20" t="n">
         <v>0</v>
@@ -10037,19 +10037,19 @@
         <v>1</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ20" t="n">
         <v>2</v>
       </c>
       <c r="BK20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BM20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN20" t="n">
         <v>6</v>
@@ -10058,55 +10058,55 @@
         <v>1</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BU20" t="n">
         <v>1</v>
       </c>
       <c r="BV20" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BW20" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="BX20" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="BY20" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="CB20" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="CC20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG20" t="n">
         <v>0</v>
@@ -10121,7 +10121,7 @@
         <v>1</v>
       </c>
       <c r="CK20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL20" t="n">
         <v>0</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="CN20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO20" t="n">
         <v>0</v>
@@ -10142,46 +10142,46 @@
         <v>1</v>
       </c>
       <c r="CR20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CS20" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="CT20" t="n">
         <v>1</v>
       </c>
       <c r="CU20" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="CV20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CW20" t="n">
         <v>1</v>
       </c>
       <c r="CX20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CY20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CZ20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DB20" t="n">
         <v>0</v>
       </c>
       <c r="DC20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DF20" t="n">
         <v>0</v>
@@ -10190,10 +10190,10 @@
         <v>0</v>
       </c>
       <c r="DH20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DJ20" t="n">
         <v>0</v>
@@ -10202,13 +10202,13 @@
         <v>0</v>
       </c>
       <c r="DL20" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="DM20" t="n">
         <v>0</v>
       </c>
       <c r="DN20" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="DO20" t="n">
         <v>8</v>
@@ -10223,10 +10223,10 @@
         <v>1</v>
       </c>
       <c r="DS20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU20" t="b">
         <v>0</v>
@@ -10252,72 +10252,72 @@
       </c>
       <c r="EA20" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EB20" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EC20" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="ED20" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EE20" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EF20" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EG20" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EH20" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EI20" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EJ20" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EK20" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EL20" t="inlineStr">
+        <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="EE20" t="inlineStr">
-        <is>
-          <t>2.98</t>
-        </is>
-      </c>
-      <c r="EF20" t="inlineStr">
-        <is>
-          <t>3.41</t>
-        </is>
-      </c>
-      <c r="EG20" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EH20" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="EI20" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EJ20" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EK20" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EL20" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
       <c r="EM20" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EN20" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EO20" t="inlineStr">
@@ -10347,70 +10347,70 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
         <v>45918.65277777778</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
         <v>5</v>
       </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
+        <v>8</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" t="n">
         <v>7</v>
       </c>
-      <c r="L21" t="n">
-        <v>9</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>6</v>
-      </c>
       <c r="T21" t="n">
+        <v>11</v>
+      </c>
+      <c r="U21" t="n">
         <v>10</v>
       </c>
-      <c r="U21" t="n">
-        <v>11</v>
-      </c>
       <c r="V21" t="n">
+        <v>13</v>
+      </c>
+      <c r="W21" t="n">
         <v>14</v>
       </c>
-      <c r="W21" t="n">
-        <v>12</v>
-      </c>
       <c r="X21" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="n">
         <v>45</v>
@@ -10421,82 +10421,82 @@
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AI21" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="AK21" t="n">
         <v>1.72</v>
       </c>
       <c r="AL21" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.56</v>
+        <v>2.01</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.2</v>
+        <v>3.22</v>
       </c>
       <c r="AO21" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.96</v>
+        <v>1.48</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AU21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BA21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB21" t="n">
-        <v>5074</v>
+        <v>5125</v>
       </c>
       <c r="BC21" t="n">
         <v>0</v>
@@ -10517,19 +10517,19 @@
         <v>1</v>
       </c>
       <c r="BI21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ21" t="n">
         <v>2</v>
       </c>
       <c r="BK21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BM21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BN21" t="n">
         <v>6</v>
@@ -10538,55 +10538,55 @@
         <v>1</v>
       </c>
       <c r="BP21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BU21" t="n">
         <v>1</v>
       </c>
       <c r="BV21" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BW21" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="BX21" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="BY21" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="CB21" t="n">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="CC21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG21" t="n">
         <v>0</v>
@@ -10601,7 +10601,7 @@
         <v>1</v>
       </c>
       <c r="CK21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL21" t="n">
         <v>0</v>
@@ -10610,7 +10610,7 @@
         <v>0</v>
       </c>
       <c r="CN21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO21" t="n">
         <v>0</v>
@@ -10622,46 +10622,46 @@
         <v>1</v>
       </c>
       <c r="CR21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CS21" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="CT21" t="n">
         <v>1</v>
       </c>
       <c r="CU21" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV21" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX21" t="n">
         <v>8</v>
       </c>
-      <c r="CV21" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW21" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX21" t="n">
-        <v>6</v>
-      </c>
       <c r="CY21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CZ21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DB21" t="n">
         <v>0</v>
       </c>
       <c r="DC21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="DE21" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10670,10 +10670,10 @@
         <v>0</v>
       </c>
       <c r="DH21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DI21" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="DJ21" t="n">
         <v>0</v>
@@ -10682,16 +10682,16 @@
         <v>0</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="DM21" t="n">
         <v>0</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="DO21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10703,10 +10703,10 @@
         <v>1</v>
       </c>
       <c r="DS21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU21" t="b">
         <v>0</v>
@@ -10732,42 +10732,42 @@
       </c>
       <c r="EA21" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="EB21" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EC21" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="ED21" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EE21" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EF21" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EG21" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EH21" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EI21" t="inlineStr">
@@ -10777,27 +10777,27 @@
       </c>
       <c r="EJ21" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EK21" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EL21" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EM21" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EN21" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EO21" t="inlineStr">
@@ -12566,7 +12566,7 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="DE25" t="n">
         <v>2.5</v>
@@ -12599,7 +12599,7 @@
         <v>1.06</v>
       </c>
       <c r="DO25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13055,7 +13055,7 @@
         <v>2.14</v>
       </c>
       <c r="DO26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13497,7 +13497,7 @@
         <v>0.25</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DF27" t="n">
         <v>0</v>
@@ -13527,7 +13527,7 @@
         <v>1.42</v>
       </c>
       <c r="DO27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP27" t="b">
         <v>0</v>
@@ -13961,7 +13961,7 @@
         <v>3</v>
       </c>
       <c r="DE28" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -15366,7 +15366,7 @@
         <v>100</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="DE31" t="n">
         <v>0.25</v>
@@ -15855,7 +15855,7 @@
         <v>2.93</v>
       </c>
       <c r="DO32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16278,7 +16278,7 @@
         <v>75</v>
       </c>
       <c r="DD33" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DE33" t="n">
         <v>1</v>
@@ -16311,7 +16311,7 @@
         <v>2.59</v>
       </c>
       <c r="DO33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16738,7 +16738,7 @@
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="DE34" t="n">
         <v>3</v>
@@ -17701,7 +17701,7 @@
         <v>0</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="DF36" t="n">
         <v>0</v>
@@ -17731,7 +17731,7 @@
         <v>2.25</v>
       </c>
       <c r="DO36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18173,7 +18173,7 @@
         <v>0.75</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DF37" t="n">
         <v>0</v>
@@ -18203,7 +18203,7 @@
         <v>2.65</v>
       </c>
       <c r="DO37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18675,7 +18675,7 @@
         <v>2.44</v>
       </c>
       <c r="DO38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19114,10 +19114,10 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DE39" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DF39" t="n">
         <v>3</v>
@@ -19147,7 +19147,7 @@
         <v>2.02</v>
       </c>
       <c r="DO39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19602,7 +19602,7 @@
         <v>50</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="DE40" t="n">
         <v>0.67</v>
@@ -20074,7 +20074,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="DE41" t="n">
         <v>2.5</v>
@@ -20107,7 +20107,7 @@
         <v>2</v>
       </c>
       <c r="DO41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20533,7 +20533,7 @@
         <v>0.75</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="DF42" t="n">
         <v>0</v>
@@ -21005,7 +21005,7 @@
         <v>3</v>
       </c>
       <c r="DE43" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DF43" t="n">
         <v>3</v>
@@ -21469,7 +21469,7 @@
         <v>1.75</v>
       </c>
       <c r="DE44" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF44" t="n">
         <v>1.5</v>
@@ -22397,7 +22397,7 @@
         <v>1</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DF46" t="n">
         <v>3</v>
@@ -22891,7 +22891,7 @@
         <v>1.84</v>
       </c>
       <c r="DO47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23851,7 +23851,7 @@
         <v>2.9</v>
       </c>
       <c r="DO49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24331,7 +24331,7 @@
         <v>2.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25238,7 +25238,7 @@
         <v>100</v>
       </c>
       <c r="DD52" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="DE52" t="n">
         <v>2.5</v>
@@ -25271,7 +25271,7 @@
         <v>3.18</v>
       </c>
       <c r="DO52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -27066,10 +27066,10 @@
         <v>67</v>
       </c>
       <c r="DD56" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DE56" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DF56" t="n">
         <v>0.33</v>
@@ -27099,7 +27099,7 @@
         <v>2.65</v>
       </c>
       <c r="DO56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27227,149 +27227,141 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
         <v>45960.72916666666</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J57" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K57" t="n">
+        <v>2</v>
+      </c>
+      <c r="L57" t="n">
+        <v>6</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
         <v>4</v>
       </c>
-      <c r="L57" t="n">
-        <v>13</v>
-      </c>
-      <c r="M57" t="n">
-        <v>2</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
+        <v>4</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
         <v>6</v>
-      </c>
-      <c r="R57" t="n">
-        <v>3</v>
-      </c>
-      <c r="S57" t="n">
-        <v>13</v>
-      </c>
-      <c r="T57" t="n">
-        <v>3</v>
-      </c>
-      <c r="U57" t="n">
-        <v>19</v>
       </c>
       <c r="V57" t="n">
         <v>6</v>
       </c>
       <c r="W57" t="n">
+        <v>14</v>
+      </c>
+      <c r="X57" t="n">
         <v>13</v>
       </c>
-      <c r="X57" t="n">
-        <v>8</v>
-      </c>
       <c r="Y57" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="Z57" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>King Abdullah Sports City</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>, Jeddah</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD57" t="n">
         <v>3</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.14</v>
+        <v>3.6</v>
       </c>
       <c r="AF57" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG57" t="n">
-        <v>11.7</v>
+        <v>1.95</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AI57" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT57" t="n">
         <v>1.4</v>
       </c>
-      <c r="AJ57" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AU57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX57" t="n">
         <v>1</v>
@@ -27381,16 +27373,16 @@
         <v>2</v>
       </c>
       <c r="BA57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB57" t="n">
-        <v>-1</v>
+        <v>5097</v>
       </c>
       <c r="BC57" t="n">
         <v>0</v>
       </c>
       <c r="BD57" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="BE57" t="n">
         <v>0</v>
@@ -27405,76 +27397,76 @@
         <v>1</v>
       </c>
       <c r="BI57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BJ57" t="n">
         <v>0</v>
       </c>
       <c r="BK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL57" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM57" t="n">
         <v>4</v>
       </c>
-      <c r="BL57" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM57" t="n">
-        <v>5</v>
-      </c>
       <c r="BN57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BO57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP57" t="n">
         <v>1</v>
       </c>
       <c r="BQ57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR57" t="n">
         <v>2</v>
       </c>
       <c r="BS57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BU57" t="n">
         <v>1</v>
       </c>
       <c r="BV57" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="BW57" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="BX57" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="BY57" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="BZ57" t="n">
-        <v>2.19</v>
+        <v>1.01</v>
       </c>
       <c r="CA57" t="n">
-        <v>0.71</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CB57" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="CC57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG57" t="n">
         <v>0</v>
@@ -27489,10 +27481,10 @@
         <v>1</v>
       </c>
       <c r="CK57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM57" t="n">
         <v>0</v>
@@ -27510,31 +27502,31 @@
         <v>1</v>
       </c>
       <c r="CR57" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS57" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU57" t="n">
         <v>13</v>
       </c>
-      <c r="CS57" t="n">
+      <c r="CV57" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX57" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY57" t="n">
         <v>10</v>
       </c>
-      <c r="CT57" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU57" t="n">
-        <v>7</v>
-      </c>
-      <c r="CV57" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW57" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX57" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY57" t="n">
-        <v>14</v>
-      </c>
       <c r="CZ57" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="DA57" t="n">
         <v>84</v>
@@ -27549,31 +27541,31 @@
         <v>1.5</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.25</v>
+        <v>2.25</v>
       </c>
       <c r="DF57" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG57" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI57" t="n">
         <v>1.67</v>
       </c>
-      <c r="DG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH57" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI57" t="n">
-        <v>1</v>
-      </c>
       <c r="DJ57" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="DK57" t="n">
         <v>17</v>
       </c>
       <c r="DL57" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="DM57" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="DN57" t="n">
         <v>2.85</v>
@@ -27588,13 +27580,13 @@
         <v>1</v>
       </c>
       <c r="DR57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU57" t="b">
         <v>0</v>
@@ -27603,87 +27595,99 @@
         <v>1</v>
       </c>
       <c r="DW57" t="n">
-        <v>32.58</v>
+        <v>29.89</v>
       </c>
       <c r="DX57" t="n">
-        <v>6</v>
+        <v>6.19</v>
       </c>
       <c r="DY57" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="DZ57" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA57" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EB57" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EC57" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="ED57" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EE57" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF57" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="EG57" t="inlineStr">
         <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="EH57" t="inlineStr"/>
-      <c r="EI57" t="inlineStr"/>
-      <c r="EJ57" t="inlineStr"/>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="EH57" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EI57" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EJ57" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
       <c r="EK57" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EL57" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EM57" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="EN57" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EO57" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EP57" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.18</t>
         </is>
       </c>
     </row>
@@ -27703,141 +27707,149 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>45960.72916666666</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
+        <v>9</v>
+      </c>
+      <c r="K58" t="n">
         <v>4</v>
       </c>
-      <c r="K58" t="n">
-        <v>2</v>
-      </c>
       <c r="L58" t="n">
+        <v>13</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
         <v>6</v>
       </c>
-      <c r="M58" t="n">
-        <v>3</v>
-      </c>
-      <c r="N58" t="n">
-        <v>3</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>4</v>
-      </c>
       <c r="R58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U58" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="V58" t="n">
         <v>6</v>
       </c>
       <c r="W58" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="X58" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y58" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="Z58" t="n">
-        <v>53</v>
-      </c>
-      <c r="AA58" t="inlineStr"/>
-      <c r="AB58" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>King Abdullah Sports City</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>, Jeddah</t>
+        </is>
+      </c>
       <c r="AC58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD58" t="n">
         <v>3</v>
       </c>
       <c r="AE58" t="n">
-        <v>3.6</v>
+        <v>1.14</v>
       </c>
       <c r="AF58" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.95</v>
+        <v>11.7</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AJ58" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AL58" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="AM58" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AN58" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AO58" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AR58" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AS58" t="n">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AU58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX58" t="n">
         <v>1</v>
@@ -27849,16 +27861,16 @@
         <v>2</v>
       </c>
       <c r="BA58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB58" t="n">
-        <v>5097</v>
+        <v>-1</v>
       </c>
       <c r="BC58" t="n">
         <v>0</v>
       </c>
       <c r="BD58" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="BE58" t="n">
         <v>0</v>
@@ -27873,76 +27885,76 @@
         <v>1</v>
       </c>
       <c r="BI58" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK58" t="n">
         <v>4</v>
       </c>
-      <c r="BJ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK58" t="n">
-        <v>0</v>
-      </c>
       <c r="BL58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BO58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP58" t="n">
         <v>1</v>
       </c>
       <c r="BQ58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR58" t="n">
         <v>2</v>
       </c>
       <c r="BS58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BU58" t="n">
         <v>1</v>
       </c>
       <c r="BV58" t="n">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="BW58" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="BX58" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="BY58" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="BZ58" t="n">
-        <v>1.01</v>
+        <v>2.19</v>
       </c>
       <c r="CA58" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="CB58" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="CC58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG58" t="n">
         <v>0</v>
@@ -27957,10 +27969,10 @@
         <v>1</v>
       </c>
       <c r="CK58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM58" t="n">
         <v>0</v>
@@ -27978,31 +27990,31 @@
         <v>1</v>
       </c>
       <c r="CR58" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CS58" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="CT58" t="n">
         <v>1</v>
       </c>
       <c r="CU58" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="CV58" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW58" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX58" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY58" t="n">
         <v>14</v>
       </c>
-      <c r="CW58" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX58" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY58" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ58" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="DA58" t="n">
         <v>84</v>
@@ -28014,40 +28026,40 @@
         <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="DE58" t="n">
-        <v>2.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF58" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="DG58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DH58" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DI58" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DJ58" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="DK58" t="n">
         <v>17</v>
       </c>
       <c r="DL58" t="n">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="DM58" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="DN58" t="n">
         <v>2.85</v>
       </c>
       <c r="DO58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28056,13 +28068,13 @@
         <v>1</v>
       </c>
       <c r="DR58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU58" t="b">
         <v>0</v>
@@ -28071,99 +28083,87 @@
         <v>1</v>
       </c>
       <c r="DW58" t="n">
-        <v>29.89</v>
+        <v>32.58</v>
       </c>
       <c r="DX58" t="n">
-        <v>6.19</v>
+        <v>6</v>
       </c>
       <c r="DY58" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="DZ58" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="EA58" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EB58" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EC58" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="ED58" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EE58" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="EF58" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="EG58" t="inlineStr">
         <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="EH58" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
-      <c r="EI58" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EJ58" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="EH58" t="inlineStr"/>
+      <c r="EI58" t="inlineStr"/>
+      <c r="EJ58" t="inlineStr"/>
       <c r="EK58" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EL58" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EM58" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EN58" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EO58" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="EP58" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
         <v>0.75</v>
       </c>
       <c r="DE59" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DF59" t="n">
         <v>0</v>
@@ -28974,7 +28974,7 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="DE60" t="n">
         <v>0.67</v>
@@ -29438,10 +29438,10 @@
         <v>50</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="DF61" t="n">
         <v>1.33</v>
@@ -29471,7 +29471,7 @@
         <v>1.4</v>
       </c>
       <c r="DO61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29921,7 +29921,7 @@
         <v>2.25</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DF62" t="n">
         <v>2</v>
@@ -30873,7 +30873,7 @@
         <v>3</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="DF64" t="n">
         <v>3</v>
@@ -31479,40 +31479,40 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45967.72916666666</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K66" t="n">
         <v>5</v>
       </c>
       <c r="L66" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -31521,101 +31521,93 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
+        <v>13</v>
+      </c>
+      <c r="T66" t="n">
         <v>6</v>
       </c>
-      <c r="T66" t="n">
-        <v>12</v>
-      </c>
       <c r="U66" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="V66" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="W66" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="X66" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Y66" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="Z66" t="n">
-        <v>66</v>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Prince Turki bin Abdul Aziz Stadium</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>, Riyadh</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.14</v>
+        <v>1.46</v>
       </c>
       <c r="AF66" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="AG66" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AJ66" t="n">
-        <v>3.34</v>
+        <v>2.12</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AL66" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AM66" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AN66" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="AO66" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AR66" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AS66" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="AU66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV66" t="n">
         <v>1</v>
@@ -31624,25 +31616,25 @@
         <v>0</v>
       </c>
       <c r="AX66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA66" t="n">
         <v>1</v>
       </c>
       <c r="BB66" t="n">
-        <v>-1</v>
+        <v>5068</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -31657,7 +31649,7 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BJ66" t="n">
         <v>2</v>
@@ -31669,64 +31661,64 @@
         <v>3</v>
       </c>
       <c r="BM66" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BN66" t="n">
         <v>4</v>
       </c>
       <c r="BO66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP66" t="n">
         <v>0</v>
       </c>
       <c r="BQ66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU66" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BV66" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="BW66" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BX66" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="BY66" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="BZ66" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="CA66" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="CB66" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="CC66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG66" t="n">
         <v>0</v>
@@ -31747,13 +31739,13 @@
         <v>0</v>
       </c>
       <c r="CM66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP66" t="n">
         <v>0</v>
@@ -31765,73 +31757,73 @@
         <v>17</v>
       </c>
       <c r="CS66" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="CT66" t="n">
         <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="CV66" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="CW66" t="n">
         <v>1</v>
       </c>
       <c r="CX66" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY66" t="n">
         <v>9</v>
       </c>
-      <c r="CY66" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ66" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="DA66" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="DB66" t="n">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="DC66" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DF66" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DG66" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="DH66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DI66" t="n">
-        <v>0.43</v>
+        <v>1.29</v>
       </c>
       <c r="DJ66" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="DK66" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="DM66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.17</v>
+        <v>2.65</v>
       </c>
       <c r="DO66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31840,10 +31832,10 @@
         <v>1</v>
       </c>
       <c r="DR66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT66" t="b">
         <v>0</v>
@@ -31852,17 +31844,17 @@
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW66" t="n">
-        <v>25.56</v>
+        <v>27.94</v>
       </c>
       <c r="DX66" t="n">
-        <v>2.71</v>
+        <v>4.87</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
@@ -31870,68 +31862,60 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA66" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EB66" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EC66" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="ED66" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
+      <c r="EA66" t="inlineStr"/>
+      <c r="EB66" t="inlineStr"/>
+      <c r="EC66" t="inlineStr"/>
+      <c r="ED66" t="inlineStr"/>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EH66" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EI66" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EJ66" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EK66" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EL66" t="inlineStr">
         <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="EM66" t="inlineStr"/>
-      <c r="EN66" t="inlineStr"/>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM66" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EN66" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
       <c r="EO66" t="inlineStr"/>
       <c r="EP66" t="inlineStr"/>
     </row>
@@ -31951,135 +31935,143 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
         <v>45967.72916666666</v>
       </c>
       <c r="G67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K67" t="n">
         <v>5</v>
       </c>
       <c r="L67" t="n">
+        <v>8</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2</v>
+      </c>
+      <c r="S67" t="n">
+        <v>6</v>
+      </c>
+      <c r="T67" t="n">
         <v>12</v>
       </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
-        <v>2</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>6</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
+      <c r="U67" t="n">
+        <v>7</v>
+      </c>
+      <c r="V67" t="n">
+        <v>14</v>
+      </c>
+      <c r="W67" t="n">
+        <v>12</v>
+      </c>
+      <c r="X67" t="n">
         <v>13</v>
       </c>
-      <c r="T67" t="n">
-        <v>6</v>
-      </c>
-      <c r="U67" t="n">
-        <v>19</v>
-      </c>
-      <c r="V67" t="n">
-        <v>6</v>
-      </c>
-      <c r="W67" t="n">
-        <v>16</v>
-      </c>
-      <c r="X67" t="n">
-        <v>6</v>
-      </c>
       <c r="Y67" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="Z67" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA67" t="inlineStr"/>
-      <c r="AB67" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Prince Turki bin Abdul Aziz Stadium</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>, Riyadh</t>
+        </is>
+      </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.46</v>
+        <v>2.14</v>
       </c>
       <c r="AF67" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="AG67" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AI67" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP67" t="n">
         <v>1.75</v>
       </c>
-      <c r="AJ67" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL67" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM67" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO67" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AP67" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AQ67" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AR67" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AS67" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="AT67" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AU67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV67" t="n">
         <v>1</v>
@@ -32088,25 +32080,25 @@
         <v>0</v>
       </c>
       <c r="AX67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA67" t="n">
         <v>1</v>
       </c>
       <c r="BB67" t="n">
-        <v>5068</v>
+        <v>-1</v>
       </c>
       <c r="BC67" t="n">
         <v>0</v>
       </c>
       <c r="BD67" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="BE67" t="n">
         <v>0</v>
@@ -32121,7 +32113,7 @@
         <v>1</v>
       </c>
       <c r="BI67" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BJ67" t="n">
         <v>2</v>
@@ -32133,64 +32125,64 @@
         <v>3</v>
       </c>
       <c r="BM67" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BN67" t="n">
         <v>4</v>
       </c>
       <c r="BO67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP67" t="n">
         <v>0</v>
       </c>
       <c r="BQ67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU67" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BV67" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="BW67" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BX67" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="BY67" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="BZ67" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="CA67" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="CB67" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="CC67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG67" t="n">
         <v>0</v>
@@ -32211,13 +32203,13 @@
         <v>0</v>
       </c>
       <c r="CM67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP67" t="n">
         <v>0</v>
@@ -32229,74 +32221,74 @@
         <v>17</v>
       </c>
       <c r="CS67" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="CT67" t="n">
         <v>1</v>
       </c>
       <c r="CU67" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="CV67" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CW67" t="n">
         <v>1</v>
       </c>
       <c r="CX67" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CY67" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ67" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA67" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB67" t="n">
+        <v>84</v>
+      </c>
+      <c r="DC67" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD67" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DE67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF67" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG67" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DH67" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI67" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DJ67" t="n">
+        <v>33</v>
+      </c>
+      <c r="DK67" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL67" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DM67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="DN67" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DO67" t="n">
         <v>9</v>
       </c>
-      <c r="CZ67" t="n">
-        <v>59</v>
-      </c>
-      <c r="DA67" t="n">
-        <v>71</v>
-      </c>
-      <c r="DB67" t="n">
-        <v>29</v>
-      </c>
-      <c r="DC67" t="n">
-        <v>59</v>
-      </c>
-      <c r="DD67" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DE67" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="DF67" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="DG67" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DH67" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI67" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="DJ67" t="n">
-        <v>42</v>
-      </c>
-      <c r="DK67" t="n">
-        <v>29</v>
-      </c>
-      <c r="DL67" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="DM67" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="DN67" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="DO67" t="n">
-        <v>8</v>
-      </c>
       <c r="DP67" t="b">
         <v>1</v>
       </c>
@@ -32304,10 +32296,10 @@
         <v>1</v>
       </c>
       <c r="DR67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT67" t="b">
         <v>0</v>
@@ -32316,17 +32308,17 @@
         <v>0</v>
       </c>
       <c r="DV67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW67" t="n">
-        <v>27.94</v>
+        <v>25.56</v>
       </c>
       <c r="DX67" t="n">
-        <v>4.87</v>
+        <v>2.71</v>
       </c>
       <c r="DY67" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="DZ67" t="inlineStr">
@@ -32334,60 +32326,68 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA67" t="inlineStr"/>
-      <c r="EB67" t="inlineStr"/>
-      <c r="EC67" t="inlineStr"/>
-      <c r="ED67" t="inlineStr"/>
+      <c r="EA67" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EB67" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EC67" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="ED67" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
       <c r="EE67" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="EF67" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EG67" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EH67" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EI67" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EJ67" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EK67" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EL67" t="inlineStr">
         <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EM67" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="EN67" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EM67" t="inlineStr"/>
+      <c r="EN67" t="inlineStr"/>
       <c r="EO67" t="inlineStr"/>
       <c r="EP67" t="inlineStr"/>
     </row>
@@ -33687,7 +33687,7 @@
         <v>2.5</v>
       </c>
       <c r="DO70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -35078,7 +35078,7 @@
         <v>67</v>
       </c>
       <c r="DD73" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="DE73" t="n">
         <v>2.5</v>
@@ -35111,7 +35111,7 @@
         <v>3.05</v>
       </c>
       <c r="DO73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35222,6 +35222,2766 @@
       </c>
       <c r="EO73" t="inlineStr"/>
       <c r="EP73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>9</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Al Hazm</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>45982.61805555555</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2</v>
+      </c>
+      <c r="I74" t="n">
+        <v>3</v>
+      </c>
+      <c r="J74" t="n">
+        <v>4</v>
+      </c>
+      <c r="K74" t="n">
+        <v>5</v>
+      </c>
+      <c r="L74" t="n">
+        <v>9</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" t="n">
+        <v>3</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>8</v>
+      </c>
+      <c r="R74" t="n">
+        <v>9</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="n">
+        <v>9</v>
+      </c>
+      <c r="U74" t="n">
+        <v>13</v>
+      </c>
+      <c r="V74" t="n">
+        <v>18</v>
+      </c>
+      <c r="W74" t="n">
+        <v>15</v>
+      </c>
+      <c r="X74" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>5089</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>88</v>
+      </c>
+      <c r="BE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ74" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK74" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM74" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN74" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV74" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW74" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX74" t="n">
+        <v>56</v>
+      </c>
+      <c r="BY74" t="n">
+        <v>44</v>
+      </c>
+      <c r="BZ74" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CA74" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CB74" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="CC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR74" t="n">
+        <v>30</v>
+      </c>
+      <c r="CS74" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU74" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV74" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX74" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY74" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ74" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA74" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB74" t="n">
+        <v>63</v>
+      </c>
+      <c r="DC74" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE74" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DF74" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG74" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH74" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI74" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DJ74" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK74" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL74" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DM74" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DN74" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="DO74" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP74" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ74" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR74" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS74" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT74" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU74" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV74" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW74" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="DX74" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="DY74" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="DZ74" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA74" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EB74" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EC74" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="ED74" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EE74" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EF74" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EG74" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EH74" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="EI74" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EJ74" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EK74" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EL74" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EM74" t="inlineStr"/>
+      <c r="EN74" t="inlineStr"/>
+      <c r="EO74" t="inlineStr"/>
+      <c r="EP74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Al Riyadh</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>45982.63541666666</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4</v>
+      </c>
+      <c r="L75" t="n">
+        <v>9</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>6</v>
+      </c>
+      <c r="R75" t="n">
+        <v>5</v>
+      </c>
+      <c r="S75" t="n">
+        <v>9</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>15</v>
+      </c>
+      <c r="V75" t="n">
+        <v>7</v>
+      </c>
+      <c r="W75" t="n">
+        <v>15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>King Abdullah Sports City</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>, Jeddah</t>
+        </is>
+      </c>
+      <c r="AC75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>5070</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI75" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV75" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW75" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX75" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY75" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ75" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CA75" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CB75" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM75" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR75" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS75" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU75" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV75" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX75" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY75" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ75" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA75" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB75" t="n">
+        <v>63</v>
+      </c>
+      <c r="DC75" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD75" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DE75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF75" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DG75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DH75" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ75" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK75" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL75" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM75" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="DN75" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="DO75" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP75" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ75" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR75" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU75" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV75" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW75" t="n">
+        <v>30.88</v>
+      </c>
+      <c r="DX75" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="DY75" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="DZ75" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="EA75" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EB75" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EC75" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="ED75" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EE75" t="inlineStr">
+        <is>
+          <t>11.27</t>
+        </is>
+      </c>
+      <c r="EF75" t="inlineStr">
+        <is>
+          <t>6.68</t>
+        </is>
+      </c>
+      <c r="EG75" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EH75" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EI75" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EJ75" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="EK75" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EL75" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EM75" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EN75" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EO75" t="inlineStr"/>
+      <c r="EP75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>9</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Al Quadisiya</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>45982.72916666666</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>10</v>
+      </c>
+      <c r="L76" t="n">
+        <v>10</v>
+      </c>
+      <c r="M76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>4</v>
+      </c>
+      <c r="R76" t="n">
+        <v>3</v>
+      </c>
+      <c r="S76" t="n">
+        <v>3</v>
+      </c>
+      <c r="T76" t="n">
+        <v>11</v>
+      </c>
+      <c r="U76" t="n">
+        <v>7</v>
+      </c>
+      <c r="V76" t="n">
+        <v>14</v>
+      </c>
+      <c r="W76" t="n">
+        <v>14</v>
+      </c>
+      <c r="X76" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>71</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>King Abdullah Sports City</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>, Jeddah</t>
+        </is>
+      </c>
+      <c r="AC76" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>5062</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ76" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL76" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS76" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV76" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW76" t="n">
+        <v>109</v>
+      </c>
+      <c r="BX76" t="n">
+        <v>73</v>
+      </c>
+      <c r="BY76" t="n">
+        <v>176</v>
+      </c>
+      <c r="BZ76" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="CA76" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CB76" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR76" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS76" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU76" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV76" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX76" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY76" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ76" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA76" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB76" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC76" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD76" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DE76" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF76" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG76" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH76" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI76" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DJ76" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK76" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL76" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DM76" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DN76" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="DO76" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP76" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ76" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR76" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS76" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT76" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU76" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV76" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW76" t="n">
+        <v>30.88</v>
+      </c>
+      <c r="DX76" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="DY76" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="DZ76" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="EA76" t="inlineStr"/>
+      <c r="EB76" t="inlineStr"/>
+      <c r="EC76" t="inlineStr"/>
+      <c r="ED76" t="inlineStr"/>
+      <c r="EE76" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="EF76" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EG76" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EH76" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="EI76" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EJ76" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EK76" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EL76" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EM76" t="inlineStr"/>
+      <c r="EN76" t="inlineStr"/>
+      <c r="EO76" t="inlineStr"/>
+      <c r="EP76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>9</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Dhamk</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Al Najma</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>45983.56944444445</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>13</v>
+      </c>
+      <c r="K77" t="n">
+        <v>6</v>
+      </c>
+      <c r="L77" t="n">
+        <v>19</v>
+      </c>
+      <c r="M77" t="n">
+        <v>5</v>
+      </c>
+      <c r="N77" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>3</v>
+      </c>
+      <c r="R77" t="n">
+        <v>1</v>
+      </c>
+      <c r="S77" t="n">
+        <v>12</v>
+      </c>
+      <c r="T77" t="n">
+        <v>8</v>
+      </c>
+      <c r="U77" t="n">
+        <v>15</v>
+      </c>
+      <c r="V77" t="n">
+        <v>9</v>
+      </c>
+      <c r="W77" t="n">
+        <v>17</v>
+      </c>
+      <c r="X77" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Dhamak Club Stadium</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>, Khamis Mushait</t>
+        </is>
+      </c>
+      <c r="AC77" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI77" t="n">
+        <v>10</v>
+      </c>
+      <c r="BJ77" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK77" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL77" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM77" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ77" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT77" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV77" t="n">
+        <v>77</v>
+      </c>
+      <c r="BW77" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX77" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY77" t="n">
+        <v>52</v>
+      </c>
+      <c r="BZ77" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CA77" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="CB77" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="CC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM77" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN77" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR77" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS77" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU77" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV77" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX77" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY77" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ77" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA77" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB77" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC77" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD77" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DE77" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ77" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL77" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DM77" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DN77" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="DO77" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV77" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW77" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="DX77" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="DY77" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="DZ77" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA77" t="inlineStr"/>
+      <c r="EB77" t="inlineStr"/>
+      <c r="EC77" t="inlineStr"/>
+      <c r="ED77" t="inlineStr"/>
+      <c r="EE77" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="EF77" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="EG77" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EH77" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="EI77" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EJ77" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EK77" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EL77" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EM77" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EN77" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EO77" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EP77" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>9</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Al Ittifaq</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Al Feiha</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>45983.60069444445</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2</v>
+      </c>
+      <c r="I78" t="n">
+        <v>5</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>8</v>
+      </c>
+      <c r="L78" t="n">
+        <v>8</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>5</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7</v>
+      </c>
+      <c r="S78" t="n">
+        <v>2</v>
+      </c>
+      <c r="T78" t="n">
+        <v>15</v>
+      </c>
+      <c r="U78" t="n">
+        <v>7</v>
+      </c>
+      <c r="V78" t="n">
+        <v>22</v>
+      </c>
+      <c r="W78" t="n">
+        <v>13</v>
+      </c>
+      <c r="X78" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>5065</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV78" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW78" t="n">
+        <v>72</v>
+      </c>
+      <c r="BX78" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY78" t="n">
+        <v>125</v>
+      </c>
+      <c r="BZ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA78" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="CB78" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="CC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR78" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS78" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU78" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV78" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX78" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY78" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ78" t="n">
+        <v>88</v>
+      </c>
+      <c r="DA78" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB78" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC78" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD78" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE78" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DF78" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG78" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH78" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI78" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DJ78" t="n">
+        <v>13</v>
+      </c>
+      <c r="DK78" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL78" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DM78" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DN78" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DO78" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW78" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="DX78" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="DY78" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="DZ78" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA78" t="inlineStr"/>
+      <c r="EB78" t="inlineStr"/>
+      <c r="EC78" t="inlineStr"/>
+      <c r="ED78" t="inlineStr"/>
+      <c r="EE78" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EF78" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EG78" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="EH78" t="inlineStr"/>
+      <c r="EI78" t="inlineStr"/>
+      <c r="EJ78" t="inlineStr"/>
+      <c r="EK78" t="inlineStr"/>
+      <c r="EL78" t="inlineStr"/>
+      <c r="EM78" t="inlineStr"/>
+      <c r="EN78" t="inlineStr"/>
+      <c r="EO78" t="inlineStr"/>
+      <c r="EP78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>9</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Al Fateh</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>45983.61111111111</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>3</v>
+      </c>
+      <c r="J79" t="n">
+        <v>8</v>
+      </c>
+      <c r="K79" t="n">
+        <v>5</v>
+      </c>
+      <c r="L79" t="n">
+        <v>13</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2</v>
+      </c>
+      <c r="N79" t="n">
+        <v>2</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>8</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" t="n">
+        <v>9</v>
+      </c>
+      <c r="T79" t="n">
+        <v>4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>17</v>
+      </c>
+      <c r="V79" t="n">
+        <v>5</v>
+      </c>
+      <c r="W79" t="n">
+        <v>9</v>
+      </c>
+      <c r="X79" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>5066</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>90</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>109</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>56</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX79" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY79" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ79" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA79" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC79" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD79" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DE79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DF79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DI79" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DJ79" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK79" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL79" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="DM79" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DN79" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="DO79" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS79" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT79" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU79" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV79" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW79" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="DX79" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="DY79" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="DZ79" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA79" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EB79" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EC79" t="inlineStr"/>
+      <c r="ED79" t="inlineStr"/>
+      <c r="EE79" t="inlineStr">
+        <is>
+          <t>12.50</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr">
+        <is>
+          <t>10.33</t>
+        </is>
+      </c>
+      <c r="EG79" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="EH79" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="EJ79" t="inlineStr"/>
+      <c r="EK79" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EL79" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EM79" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EN79" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EO79" t="inlineStr"/>
+      <c r="EP79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP79" headerRowCount="1">
-  <autoFilter ref="A1:EP79"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP82" headerRowCount="1">
+  <autoFilter ref="A1:EP82"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP79"/>
+  <dimension ref="A1:EP82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -2285,7 +2285,7 @@
         <v>1.8</v>
       </c>
       <c r="DE3" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -3359,132 +3359,132 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
         <v>45898.75</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
         <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
       </c>
       <c r="L6" t="n">
+        <v>7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
         <v>10</v>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" t="n">
+        <v>21</v>
+      </c>
+      <c r="W6" t="n">
+        <v>13</v>
+      </c>
+      <c r="X6" t="n">
         <v>6</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>9</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>13</v>
-      </c>
-      <c r="V6" t="n">
-        <v>10</v>
-      </c>
-      <c r="W6" t="n">
-        <v>15</v>
-      </c>
-      <c r="X6" t="n">
-        <v>18</v>
-      </c>
       <c r="Y6" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="Z6" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.54</v>
+        <v>8.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AO6" t="n">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AU6" t="n">
         <v>5</v>
@@ -3496,10 +3496,10 @@
         <v>1</v>
       </c>
       <c r="AX6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ6" t="n">
         <v>4</v>
@@ -3508,7 +3508,7 @@
         <v>1</v>
       </c>
       <c r="BB6" t="n">
-        <v>5077</v>
+        <v>5069</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
@@ -3529,73 +3529,73 @@
         <v>1</v>
       </c>
       <c r="BI6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM6" t="n">
         <v>4</v>
       </c>
-      <c r="BJ6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>6</v>
-      </c>
       <c r="BN6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ6" t="n">
         <v>1</v>
       </c>
       <c r="BR6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BS6" t="n">
         <v>2</v>
       </c>
       <c r="BT6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU6" t="n">
         <v>1</v>
       </c>
       <c r="BV6" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="BW6" t="n">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="BX6" t="n">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="BY6" t="n">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.49</v>
+        <v>0.44</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.15</v>
+        <v>2.51</v>
       </c>
       <c r="CB6" t="n">
-        <v>2.64</v>
+        <v>2.95</v>
       </c>
       <c r="CC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
         <v>1</v>
       </c>
       <c r="CE6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF6" t="n">
         <v>1</v>
@@ -3619,10 +3619,10 @@
         <v>1</v>
       </c>
       <c r="CM6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO6" t="n">
         <v>0</v>
@@ -3634,7 +3634,7 @@
         <v>1</v>
       </c>
       <c r="CR6" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="CS6" t="n">
         <v>15</v>
@@ -3643,19 +3643,19 @@
         <v>1</v>
       </c>
       <c r="CU6" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="CV6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CW6" t="n">
         <v>1</v>
       </c>
       <c r="CX6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CY6" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="CZ6" t="n">
         <v>0</v>
@@ -3670,10 +3670,10 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -3724,84 +3724,92 @@
         <v>0</v>
       </c>
       <c r="DV6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>40.6</v>
+        <v>39.96</v>
       </c>
       <c r="DX6" t="n">
-        <v>7.85</v>
+        <v>6.5</v>
       </c>
       <c r="DY6" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="DZ6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="EA6" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EB6" t="inlineStr">
         <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EC6" t="inlineStr"/>
-      <c r="ED6" t="inlineStr"/>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
       <c r="EE6" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="EF6" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="EG6" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EJ6" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EM6" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EN6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EO6" t="inlineStr"/>
@@ -3823,40 +3831,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
         <v>45898.75</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3865,90 +3873,90 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>13</v>
+      </c>
+      <c r="V7" t="n">
         <v>10</v>
       </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>11</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>21</v>
-      </c>
       <c r="W7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="Z7" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE7" t="n">
-        <v>8.5</v>
+        <v>1.54</v>
       </c>
       <c r="AF7" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AO7" t="n">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AS7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AU7" t="n">
         <v>5</v>
@@ -3960,10 +3968,10 @@
         <v>1</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ7" t="n">
         <v>4</v>
@@ -3972,7 +3980,7 @@
         <v>1</v>
       </c>
       <c r="BB7" t="n">
-        <v>5069</v>
+        <v>5077</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
@@ -3993,73 +4001,73 @@
         <v>1</v>
       </c>
       <c r="BI7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ7" t="n">
         <v>2</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL7" t="n">
         <v>3</v>
       </c>
       <c r="BM7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN7" t="n">
         <v>4</v>
       </c>
-      <c r="BN7" t="n">
-        <v>3</v>
-      </c>
       <c r="BO7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ7" t="n">
         <v>1</v>
       </c>
       <c r="BR7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BS7" t="n">
         <v>2</v>
       </c>
       <c r="BT7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU7" t="n">
         <v>1</v>
       </c>
       <c r="BV7" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="BW7" t="n">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="BX7" t="n">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="BY7" t="n">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.44</v>
+        <v>1.49</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.51</v>
+        <v>1.15</v>
       </c>
       <c r="CB7" t="n">
-        <v>2.95</v>
+        <v>2.64</v>
       </c>
       <c r="CC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD7" t="n">
         <v>1</v>
       </c>
       <c r="CE7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF7" t="n">
         <v>1</v>
@@ -4083,10 +4091,10 @@
         <v>1</v>
       </c>
       <c r="CM7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO7" t="n">
         <v>0</v>
@@ -4098,7 +4106,7 @@
         <v>1</v>
       </c>
       <c r="CR7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="CS7" t="n">
         <v>15</v>
@@ -4107,68 +4115,68 @@
         <v>1</v>
       </c>
       <c r="CU7" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="CV7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW7" t="n">
         <v>1</v>
       </c>
       <c r="CX7" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
         <v>9</v>
       </c>
-      <c r="CY7" t="n">
-        <v>3</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>3</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>8</v>
-      </c>
       <c r="DP7" t="b">
         <v>1</v>
       </c>
@@ -4188,92 +4196,84 @@
         <v>0</v>
       </c>
       <c r="DV7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW7" t="n">
-        <v>39.96</v>
+        <v>40.6</v>
       </c>
       <c r="DX7" t="n">
-        <v>6.5</v>
+        <v>7.85</v>
       </c>
       <c r="DY7" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="DZ7" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA7" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EB7" t="inlineStr">
         <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EC7" t="inlineStr">
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EC7" t="inlineStr"/>
+      <c r="ED7" t="inlineStr"/>
+      <c r="EE7" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="EF7" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="EG7" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EH7" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EI7" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EJ7" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EK7" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EL7" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="ED7" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EE7" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="EF7" t="inlineStr">
-        <is>
-          <t>6.90</t>
-        </is>
-      </c>
-      <c r="EG7" t="inlineStr">
-        <is>
-          <t>10.82</t>
-        </is>
-      </c>
-      <c r="EH7" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EI7" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EJ7" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="EK7" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EL7" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
       <c r="EM7" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EN7" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EO7" t="inlineStr"/>
@@ -4775,156 +4775,156 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
         <v>45899.75</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>11</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" t="n">
         <v>7</v>
       </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7</v>
-      </c>
-      <c r="L9" t="n">
-        <v>10</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>10</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="T9" t="n">
-        <v>6</v>
-      </c>
       <c r="U9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X9" t="n">
         <v>7</v>
       </c>
       <c r="Y9" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="Z9" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>5.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF9" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.57</v>
+        <v>6.75</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AM9" t="n">
         <v>1.47</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AO9" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
         <v>1</v>
       </c>
       <c r="AY9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB9" t="n">
-        <v>5070</v>
+        <v>5068</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
@@ -4945,64 +4945,64 @@
         <v>1</v>
       </c>
       <c r="BI9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
         <v>5</v>
       </c>
-      <c r="BK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>7</v>
-      </c>
       <c r="BN9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BO9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
         <v>0</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU9" t="n">
         <v>1</v>
       </c>
       <c r="BV9" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BW9" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="BX9" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="BY9" t="n">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.91</v>
+        <v>1.86</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.14</v>
+        <v>0.99</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="CC9" t="n">
         <v>0</v>
@@ -5029,10 +5029,10 @@
         <v>1</v>
       </c>
       <c r="CK9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
@@ -5050,10 +5050,10 @@
         <v>1</v>
       </c>
       <c r="CR9" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="CS9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="CT9" t="n">
         <v>1</v>
@@ -5062,7 +5062,7 @@
         <v>7</v>
       </c>
       <c r="CV9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CW9" t="n">
         <v>1</v>
@@ -5071,7 +5071,7 @@
         <v>6</v>
       </c>
       <c r="CY9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CZ9" t="n">
         <v>0</v>
@@ -5086,10 +5086,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="DE9" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5134,98 +5134,98 @@
         <v>1</v>
       </c>
       <c r="DT9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV9" t="b">
         <v>1</v>
       </c>
       <c r="DW9" t="n">
-        <v>36.63</v>
+        <v>42.17</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.67</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DY9" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="DZ9" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA9" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EB9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>7.29</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr">
+        <is>
+          <t>5.33</t>
+        </is>
+      </c>
+      <c r="EG9" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EI9" t="inlineStr">
+        <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="EE9" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EF9" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="EG9" t="inlineStr">
-        <is>
-          <t>4.83</t>
-        </is>
-      </c>
-      <c r="EH9" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="EI9" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
       <c r="EJ9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EM9" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EN9" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EO9" t="inlineStr"/>
@@ -5247,156 +5247,156 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>45899.75</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S10" t="n">
         <v>4</v>
       </c>
-      <c r="J10" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>11</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>8</v>
-      </c>
-      <c r="R10" t="n">
-        <v>4</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
         <v>7</v>
       </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>15</v>
-      </c>
       <c r="V10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X10" t="n">
         <v>7</v>
       </c>
       <c r="Y10" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="Z10" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.44</v>
+        <v>5.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.75</v>
+        <v>1.57</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AM10" t="n">
         <v>1.47</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AO10" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AU10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA10" t="n">
         <v>4</v>
       </c>
-      <c r="AV10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>2</v>
-      </c>
       <c r="BB10" t="n">
-        <v>5068</v>
+        <v>5070</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
@@ -5417,115 +5417,115 @@
         <v>1</v>
       </c>
       <c r="BI10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT10" t="n">
         <v>4</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM10" t="n">
+      <c r="BU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>59</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>63</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS10" t="n">
         <v>5</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>29</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>56</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>53</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>19</v>
-      </c>
-      <c r="CS10" t="n">
-        <v>15</v>
       </c>
       <c r="CT10" t="n">
         <v>1</v>
@@ -5534,7 +5534,7 @@
         <v>7</v>
       </c>
       <c r="CV10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CW10" t="n">
         <v>1</v>
@@ -5543,7 +5543,7 @@
         <v>6</v>
       </c>
       <c r="CY10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="CZ10" t="n">
         <v>0</v>
@@ -5558,10 +5558,10 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5606,98 +5606,98 @@
         <v>1</v>
       </c>
       <c r="DT10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV10" t="b">
         <v>1</v>
       </c>
       <c r="DW10" t="n">
-        <v>42.17</v>
+        <v>36.63</v>
       </c>
       <c r="DX10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="DY10" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="DZ10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="EA10" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EB10" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EC10" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="ED10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EE10" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EF10" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="EG10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="EH10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="EI10" t="inlineStr">
         <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EJ10" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EK10" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM10" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EN10" t="inlineStr">
+        <is>
           <t>1.50</t>
-        </is>
-      </c>
-      <c r="EJ10" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="EK10" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EL10" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EM10" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EN10" t="inlineStr">
-        <is>
-          <t>1.63</t>
         </is>
       </c>
       <c r="EO10" t="inlineStr"/>
@@ -6519,7 +6519,7 @@
         <v>2.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7439,7 +7439,7 @@
         <v>0.87</v>
       </c>
       <c r="DO14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7870,7 +7870,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DE15" t="n">
         <v>3</v>
@@ -7903,7 +7903,7 @@
         <v>0.91</v>
       </c>
       <c r="DO15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -9265,7 +9265,7 @@
         <v>0.6</v>
       </c>
       <c r="DE18" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF18" t="n">
         <v>1</v>
@@ -9295,7 +9295,7 @@
         <v>2.11</v>
       </c>
       <c r="DO18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9751,7 +9751,7 @@
         <v>1.18</v>
       </c>
       <c r="DO19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10178,7 +10178,7 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DE20" t="n">
         <v>1</v>
@@ -10211,7 +10211,7 @@
         <v>0.44</v>
       </c>
       <c r="DO20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -11171,7 +11171,7 @@
         <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11609,7 +11609,7 @@
         <v>2.5</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11639,7 +11639,7 @@
         <v>3.01</v>
       </c>
       <c r="DO23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12081,7 +12081,7 @@
         <v>1.25</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -12111,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="DO24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP24" t="b">
         <v>0</v>
@@ -12711,12 +12711,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -12726,120 +12726,120 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
+        <v>6</v>
+      </c>
+      <c r="L26" t="n">
         <v>8</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="n">
         <v>11</v>
       </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="n">
-        <v>8</v>
-      </c>
       <c r="U26" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="V26" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W26" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="X26" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Y26" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="Z26" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="AF26" t="n">
-        <v>4.35</v>
+        <v>3.6</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AM26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN26" t="n">
         <v>1.49</v>
       </c>
-      <c r="AN26" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AO26" t="n">
-        <v>2.3</v>
+        <v>3.14</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AS26" t="n">
         <v>3.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AU26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
         <v>0</v>
@@ -12851,16 +12851,16 @@
         <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>5070</v>
+        <v>-1</v>
       </c>
       <c r="BC26" t="n">
         <v>0</v>
@@ -12875,70 +12875,70 @@
         <v>-1</v>
       </c>
       <c r="BG26" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH26" t="n">
         <v>1</v>
       </c>
       <c r="BI26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BJ26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL26" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BM26" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BN26" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ26" t="n">
         <v>1</v>
       </c>
       <c r="BR26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS26" t="n">
         <v>1</v>
       </c>
       <c r="BT26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU26" t="n">
         <v>1</v>
       </c>
       <c r="BV26" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="BW26" t="n">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="BX26" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="BY26" t="n">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.16</v>
+        <v>1.55</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="CC26" t="n">
         <v>0</v>
@@ -12971,10 +12971,10 @@
         <v>0</v>
       </c>
       <c r="CM26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO26" t="n">
         <v>0</v>
@@ -12986,25 +12986,25 @@
         <v>1</v>
       </c>
       <c r="CR26" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="CS26" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="CT26" t="n">
         <v>1</v>
       </c>
       <c r="CU26" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CV26" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="CW26" t="n">
         <v>1</v>
       </c>
       <c r="CX26" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="CY26" t="n">
         <v>8</v>
@@ -13022,22 +13022,22 @@
         <v>50</v>
       </c>
       <c r="DD26" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DE26" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="DF26" t="n">
         <v>0</v>
       </c>
       <c r="DG26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DI26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DJ26" t="n">
         <v>0</v>
@@ -13049,16 +13049,16 @@
         <v>0</v>
       </c>
       <c r="DM26" t="n">
-        <v>2.14</v>
+        <v>1.42</v>
       </c>
       <c r="DN26" t="n">
-        <v>2.14</v>
+        <v>1.42</v>
       </c>
       <c r="DO26" t="n">
         <v>9</v>
       </c>
       <c r="DP26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ26" t="b">
         <v>0</v>
@@ -13096,74 +13096,58 @@
       </c>
       <c r="EA26" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EB26" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EC26" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="ED26" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EC26" t="inlineStr"/>
+      <c r="ED26" t="inlineStr"/>
       <c r="EE26" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EF26" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="EG26" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="EH26" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EI26" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EJ26" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EK26" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EL26" t="inlineStr">
         <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="EM26" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EN26" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EM26" t="inlineStr"/>
+      <c r="EN26" t="inlineStr"/>
       <c r="EO26" t="inlineStr"/>
       <c r="EP26" t="inlineStr"/>
     </row>
@@ -13183,12 +13167,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -13198,120 +13182,120 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L27" t="n">
+        <v>11</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="n">
         <v>8</v>
       </c>
-      <c r="M27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>4</v>
-      </c>
-      <c r="R27" t="n">
-        <v>4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>5</v>
-      </c>
-      <c r="T27" t="n">
-        <v>11</v>
-      </c>
       <c r="U27" t="n">
+        <v>13</v>
+      </c>
+      <c r="V27" t="n">
         <v>9</v>
       </c>
-      <c r="V27" t="n">
-        <v>15</v>
-      </c>
       <c r="W27" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="X27" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Y27" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="Z27" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="AF27" t="n">
-        <v>3.6</v>
+        <v>4.35</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.45</v>
+        <v>1.31</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.49</v>
+        <v>2.19</v>
       </c>
       <c r="AO27" t="n">
-        <v>3.14</v>
+        <v>2.3</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AS27" t="n">
         <v>3.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV27" t="n">
         <v>0</v>
@@ -13323,16 +13307,16 @@
         <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA27" t="n">
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>-1</v>
+        <v>5070</v>
       </c>
       <c r="BC27" t="n">
         <v>0</v>
@@ -13347,70 +13331,70 @@
         <v>-1</v>
       </c>
       <c r="BG27" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH27" t="n">
         <v>1</v>
       </c>
       <c r="BI27" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BJ27" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BK27" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL27" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BM27" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BN27" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BO27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ27" t="n">
         <v>1</v>
       </c>
       <c r="BR27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS27" t="n">
         <v>1</v>
       </c>
       <c r="BT27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU27" t="n">
         <v>1</v>
       </c>
       <c r="BV27" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="BW27" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="BX27" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="BY27" t="n">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.55</v>
+        <v>1.16</v>
       </c>
       <c r="CB27" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="CC27" t="n">
         <v>0</v>
@@ -13443,10 +13427,10 @@
         <v>0</v>
       </c>
       <c r="CM27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CN27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO27" t="n">
         <v>0</v>
@@ -13458,25 +13442,25 @@
         <v>1</v>
       </c>
       <c r="CR27" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS27" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU27" t="n">
         <v>19</v>
       </c>
-      <c r="CS27" t="n">
-        <v>20</v>
-      </c>
-      <c r="CT27" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU27" t="n">
-        <v>12</v>
-      </c>
       <c r="CV27" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="CW27" t="n">
         <v>1</v>
       </c>
       <c r="CX27" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="CY27" t="n">
         <v>8</v>
@@ -13494,22 +13478,22 @@
         <v>50</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="DF27" t="n">
         <v>0</v>
       </c>
       <c r="DG27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH27" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="DI27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DJ27" t="n">
         <v>0</v>
@@ -13521,16 +13505,16 @@
         <v>0</v>
       </c>
       <c r="DM27" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="DN27" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="DO27" t="n">
         <v>9</v>
       </c>
       <c r="DP27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ27" t="b">
         <v>0</v>
@@ -13568,58 +13552,74 @@
       </c>
       <c r="EA27" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EB27" t="inlineStr">
         <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="EC27" t="inlineStr"/>
-      <c r="ED27" t="inlineStr"/>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EC27" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="ED27" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
       <c r="EE27" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EF27" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="EG27" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="EH27" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EI27" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EJ27" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="EK27" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EL27" t="inlineStr">
         <is>
-          <t>2.58</t>
-        </is>
-      </c>
-      <c r="EM27" t="inlineStr"/>
-      <c r="EN27" t="inlineStr"/>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EM27" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EN27" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="EO27" t="inlineStr"/>
       <c r="EP27" t="inlineStr"/>
     </row>
@@ -13991,7 +13991,7 @@
         <v>3.72</v>
       </c>
       <c r="DO28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14463,7 +14463,7 @@
         <v>2.82</v>
       </c>
       <c r="DO29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14943,7 +14943,7 @@
         <v>2.34</v>
       </c>
       <c r="DO30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15399,7 +15399,7 @@
         <v>2.97</v>
       </c>
       <c r="DO31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16771,7 +16771,7 @@
         <v>4.3</v>
       </c>
       <c r="DO34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17221,7 +17221,7 @@
         <v>1.75</v>
       </c>
       <c r="DE35" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF35" t="n">
         <v>3</v>
@@ -17251,7 +17251,7 @@
         <v>2.37</v>
       </c>
       <c r="DO35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -19605,7 +19605,7 @@
         <v>1.8</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DF40" t="n">
         <v>2</v>
@@ -19635,7 +19635,7 @@
         <v>2.66</v>
       </c>
       <c r="DO40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20530,7 +20530,7 @@
         <v>50</v>
       </c>
       <c r="DD42" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DE42" t="n">
         <v>1.6</v>
@@ -20563,7 +20563,7 @@
         <v>1.63</v>
       </c>
       <c r="DO42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21035,7 +21035,7 @@
         <v>4.22</v>
       </c>
       <c r="DO43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21499,7 +21499,7 @@
         <v>2.13</v>
       </c>
       <c r="DO44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21930,7 +21930,7 @@
         <v>100</v>
       </c>
       <c r="DD45" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DE45" t="n">
         <v>0.5</v>
@@ -21963,7 +21963,7 @@
         <v>2.14</v>
       </c>
       <c r="DO45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22427,7 +22427,7 @@
         <v>2.57</v>
       </c>
       <c r="DO46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23371,7 +23371,7 @@
         <v>1.94</v>
       </c>
       <c r="DO48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24773,7 +24773,7 @@
         <v>1</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DF51" t="n">
         <v>1.5</v>
@@ -24803,7 +24803,7 @@
         <v>2.84</v>
       </c>
       <c r="DO51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25735,7 +25735,7 @@
         <v>2.21</v>
       </c>
       <c r="DO53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP53" t="b">
         <v>0</v>
@@ -26179,7 +26179,7 @@
         <v>2.64</v>
       </c>
       <c r="DO54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26627,7 +26627,7 @@
         <v>3.19</v>
       </c>
       <c r="DO55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27541,7 +27541,7 @@
         <v>1.5</v>
       </c>
       <c r="DE57" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF57" t="n">
         <v>3</v>
@@ -27571,7 +27571,7 @@
         <v>2.85</v>
       </c>
       <c r="DO57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28494,7 +28494,7 @@
         <v>100</v>
       </c>
       <c r="DD59" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DE59" t="n">
         <v>0.2</v>
@@ -28527,7 +28527,7 @@
         <v>2.02</v>
       </c>
       <c r="DO59" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -28977,7 +28977,7 @@
         <v>2.6</v>
       </c>
       <c r="DE60" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DF60" t="n">
         <v>2.33</v>
@@ -29007,7 +29007,7 @@
         <v>3.38</v>
       </c>
       <c r="DO60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29918,7 +29918,7 @@
         <v>84</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DE62" t="n">
         <v>1.4</v>
@@ -29951,7 +29951,7 @@
         <v>2.42</v>
       </c>
       <c r="DO62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30431,7 +30431,7 @@
         <v>3.33</v>
       </c>
       <c r="DO63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30903,7 +30903,7 @@
         <v>3.73</v>
       </c>
       <c r="DO64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31329,7 +31329,7 @@
         <v>0.25</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DF65" t="n">
         <v>0.33</v>
@@ -31359,7 +31359,7 @@
         <v>2.02</v>
       </c>
       <c r="DO65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31479,135 +31479,143 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45967.72916666666</v>
       </c>
       <c r="G66" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K66" t="n">
         <v>5</v>
       </c>
       <c r="L66" t="n">
+        <v>8</v>
+      </c>
+      <c r="M66" t="n">
+        <v>3</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1</v>
+      </c>
+      <c r="R66" t="n">
+        <v>2</v>
+      </c>
+      <c r="S66" t="n">
+        <v>6</v>
+      </c>
+      <c r="T66" t="n">
         <v>12</v>
       </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
-        <v>2</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>6</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
+      <c r="U66" t="n">
+        <v>7</v>
+      </c>
+      <c r="V66" t="n">
+        <v>14</v>
+      </c>
+      <c r="W66" t="n">
+        <v>12</v>
+      </c>
+      <c r="X66" t="n">
         <v>13</v>
       </c>
-      <c r="T66" t="n">
-        <v>6</v>
-      </c>
-      <c r="U66" t="n">
-        <v>19</v>
-      </c>
-      <c r="V66" t="n">
-        <v>6</v>
-      </c>
-      <c r="W66" t="n">
-        <v>16</v>
-      </c>
-      <c r="X66" t="n">
-        <v>6</v>
-      </c>
       <c r="Y66" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="Z66" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Prince Turki bin Abdul Aziz Stadium</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>, Riyadh</t>
+        </is>
+      </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.46</v>
+        <v>2.14</v>
       </c>
       <c r="AF66" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="AG66" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AI66" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP66" t="n">
         <v>1.75</v>
       </c>
-      <c r="AJ66" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AQ66" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AR66" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AS66" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AU66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV66" t="n">
         <v>1</v>
@@ -31616,25 +31624,25 @@
         <v>0</v>
       </c>
       <c r="AX66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA66" t="n">
         <v>1</v>
       </c>
       <c r="BB66" t="n">
-        <v>5068</v>
+        <v>-1</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -31649,7 +31657,7 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BJ66" t="n">
         <v>2</v>
@@ -31661,64 +31669,64 @@
         <v>3</v>
       </c>
       <c r="BM66" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BN66" t="n">
         <v>4</v>
       </c>
       <c r="BO66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP66" t="n">
         <v>0</v>
       </c>
       <c r="BQ66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU66" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BV66" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="BW66" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BX66" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="BY66" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="BZ66" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="CA66" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="CB66" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="CC66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG66" t="n">
         <v>0</v>
@@ -31739,13 +31747,13 @@
         <v>0</v>
       </c>
       <c r="CM66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP66" t="n">
         <v>0</v>
@@ -31757,70 +31765,70 @@
         <v>17</v>
       </c>
       <c r="CS66" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="CT66" t="n">
         <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="CV66" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CW66" t="n">
         <v>1</v>
       </c>
       <c r="CX66" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CY66" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CZ66" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="DA66" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="DB66" t="n">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="DC66" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="DD66" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DF66" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="DG66" t="n">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
       <c r="DH66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DI66" t="n">
-        <v>1.29</v>
+        <v>0.43</v>
       </c>
       <c r="DJ66" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="DK66" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="DM66" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.65</v>
+        <v>2.17</v>
       </c>
       <c r="DO66" t="n">
         <v>9</v>
@@ -31832,10 +31840,10 @@
         <v>1</v>
       </c>
       <c r="DR66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT66" t="b">
         <v>0</v>
@@ -31844,17 +31852,17 @@
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW66" t="n">
-        <v>27.94</v>
+        <v>25.56</v>
       </c>
       <c r="DX66" t="n">
-        <v>4.87</v>
+        <v>2.71</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
@@ -31862,60 +31870,68 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA66" t="inlineStr"/>
-      <c r="EB66" t="inlineStr"/>
-      <c r="EC66" t="inlineStr"/>
-      <c r="ED66" t="inlineStr"/>
+      <c r="EA66" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EB66" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EC66" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="ED66" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EH66" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EI66" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EJ66" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EK66" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EL66" t="inlineStr">
         <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EM66" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="EN66" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EM66" t="inlineStr"/>
+      <c r="EN66" t="inlineStr"/>
       <c r="EO66" t="inlineStr"/>
       <c r="EP66" t="inlineStr"/>
     </row>
@@ -31935,40 +31951,40 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
         <v>45967.72916666666</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K67" t="n">
         <v>5</v>
       </c>
       <c r="L67" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -31977,101 +31993,93 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
+        <v>13</v>
+      </c>
+      <c r="T67" t="n">
         <v>6</v>
       </c>
-      <c r="T67" t="n">
-        <v>12</v>
-      </c>
       <c r="U67" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="V67" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="W67" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="X67" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Y67" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="Z67" t="n">
-        <v>66</v>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>Prince Turki bin Abdul Aziz Stadium</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>, Riyadh</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE67" t="n">
-        <v>2.14</v>
+        <v>1.46</v>
       </c>
       <c r="AF67" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="AG67" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AJ67" t="n">
-        <v>3.34</v>
+        <v>2.12</v>
       </c>
       <c r="AK67" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AL67" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AM67" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AN67" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="AO67" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AR67" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AS67" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="AT67" t="n">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="AU67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV67" t="n">
         <v>1</v>
@@ -32080,25 +32088,25 @@
         <v>0</v>
       </c>
       <c r="AX67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA67" t="n">
         <v>1</v>
       </c>
       <c r="BB67" t="n">
-        <v>-1</v>
+        <v>5068</v>
       </c>
       <c r="BC67" t="n">
         <v>0</v>
       </c>
       <c r="BD67" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="BE67" t="n">
         <v>0</v>
@@ -32113,7 +32121,7 @@
         <v>1</v>
       </c>
       <c r="BI67" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BJ67" t="n">
         <v>2</v>
@@ -32125,64 +32133,64 @@
         <v>3</v>
       </c>
       <c r="BM67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BN67" t="n">
         <v>4</v>
       </c>
       <c r="BO67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP67" t="n">
         <v>0</v>
       </c>
       <c r="BQ67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU67" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BV67" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="BW67" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BX67" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="BY67" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="BZ67" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="CA67" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="CB67" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="CC67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG67" t="n">
         <v>0</v>
@@ -32203,13 +32211,13 @@
         <v>0</v>
       </c>
       <c r="CM67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP67" t="n">
         <v>0</v>
@@ -32221,70 +32229,70 @@
         <v>17</v>
       </c>
       <c r="CS67" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="CT67" t="n">
         <v>1</v>
       </c>
       <c r="CU67" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="CV67" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="CW67" t="n">
         <v>1</v>
       </c>
       <c r="CX67" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY67" t="n">
         <v>9</v>
       </c>
-      <c r="CY67" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ67" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="DA67" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="DB67" t="n">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="DC67" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DF67" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DG67" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="DH67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DI67" t="n">
-        <v>0.43</v>
+        <v>1.29</v>
       </c>
       <c r="DJ67" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="DK67" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="DL67" t="n">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="DM67" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="DN67" t="n">
-        <v>2.17</v>
+        <v>2.65</v>
       </c>
       <c r="DO67" t="n">
         <v>9</v>
@@ -32296,10 +32304,10 @@
         <v>1</v>
       </c>
       <c r="DR67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT67" t="b">
         <v>0</v>
@@ -32308,17 +32316,17 @@
         <v>0</v>
       </c>
       <c r="DV67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW67" t="n">
-        <v>25.56</v>
+        <v>27.94</v>
       </c>
       <c r="DX67" t="n">
-        <v>2.71</v>
+        <v>4.87</v>
       </c>
       <c r="DY67" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="DZ67" t="inlineStr">
@@ -32326,68 +32334,60 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA67" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EB67" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EC67" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="ED67" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
+      <c r="EA67" t="inlineStr"/>
+      <c r="EB67" t="inlineStr"/>
+      <c r="EC67" t="inlineStr"/>
+      <c r="ED67" t="inlineStr"/>
       <c r="EE67" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="EF67" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="EG67" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EH67" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EI67" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EJ67" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EK67" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EL67" t="inlineStr">
         <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="EM67" t="inlineStr"/>
-      <c r="EN67" t="inlineStr"/>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM67" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EN67" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
       <c r="EO67" t="inlineStr"/>
       <c r="EP67" t="inlineStr"/>
     </row>
@@ -32751,7 +32751,7 @@
         <v>1.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33223,7 +33223,7 @@
         <v>2.68</v>
       </c>
       <c r="DO69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34151,7 +34151,7 @@
         <v>3.72</v>
       </c>
       <c r="DO71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34623,7 +34623,7 @@
         <v>2.76</v>
       </c>
       <c r="DO72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -36690,13 +36690,13 @@
         <v>12</v>
       </c>
       <c r="T77" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U77" t="n">
         <v>15</v>
       </c>
       <c r="V77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W77" t="n">
         <v>17</v>
@@ -36871,10 +36871,10 @@
         <v>1.7</v>
       </c>
       <c r="CA77" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="CB77" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="CC77" t="n">
         <v>0</v>
@@ -37983,6 +37983,1410 @@
       <c r="EO79" t="inlineStr"/>
       <c r="EP79" t="inlineStr"/>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>9</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Al Akhdoud</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Al Shabab</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>45984.62847222222</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>2</v>
+      </c>
+      <c r="J80" t="n">
+        <v>3</v>
+      </c>
+      <c r="K80" t="n">
+        <v>5</v>
+      </c>
+      <c r="L80" t="n">
+        <v>8</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1</v>
+      </c>
+      <c r="N80" t="n">
+        <v>2</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>2</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="n">
+        <v>3</v>
+      </c>
+      <c r="T80" t="n">
+        <v>11</v>
+      </c>
+      <c r="U80" t="n">
+        <v>5</v>
+      </c>
+      <c r="V80" t="n">
+        <v>12</v>
+      </c>
+      <c r="W80" t="n">
+        <v>13</v>
+      </c>
+      <c r="X80" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>71</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV80" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX80" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY80" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ80" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA80" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB80" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC80" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD80" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DE80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DF80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI80" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DJ80" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK80" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL80" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DM80" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="DN80" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DO80" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU80" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV80" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW80" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="DX80" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="DY80" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="DZ80" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="EA80" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EB80" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EC80" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="ED80" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EE80" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EF80" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="EG80" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="EH80" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="EI80" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EJ80" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EK80" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EL80" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EM80" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="EN80" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EO80" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EP80" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>9</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Al Taawon</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Neom SC</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>45984.72916666666</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2</v>
+      </c>
+      <c r="J81" t="n">
+        <v>8</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>9</v>
+      </c>
+      <c r="M81" t="n">
+        <v>3</v>
+      </c>
+      <c r="N81" t="n">
+        <v>3</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>2</v>
+      </c>
+      <c r="R81" t="n">
+        <v>2</v>
+      </c>
+      <c r="S81" t="n">
+        <v>6</v>
+      </c>
+      <c r="T81" t="n">
+        <v>13</v>
+      </c>
+      <c r="U81" t="n">
+        <v>8</v>
+      </c>
+      <c r="V81" t="n">
+        <v>15</v>
+      </c>
+      <c r="W81" t="n">
+        <v>11</v>
+      </c>
+      <c r="X81" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI81" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM81" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT81" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV81" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW81" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX81" t="n">
+        <v>45</v>
+      </c>
+      <c r="BY81" t="n">
+        <v>55</v>
+      </c>
+      <c r="BZ81" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CA81" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CB81" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR81" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS81" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU81" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV81" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX81" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY81" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ81" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA81" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB81" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC81" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD81" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE81" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF81" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DG81" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DH81" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DI81" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DJ81" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK81" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL81" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DM81" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DN81" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="DO81" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP81" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ81" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU81" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV81" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW81" t="n">
+        <v>30.11</v>
+      </c>
+      <c r="DX81" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="DY81" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="DZ81" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="EA81" t="inlineStr"/>
+      <c r="EB81" t="inlineStr"/>
+      <c r="EC81" t="inlineStr"/>
+      <c r="ED81" t="inlineStr"/>
+      <c r="EE81" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EF81" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="EG81" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EH81" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="EI81" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EJ81" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EK81" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EL81" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EM81" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EN81" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EO81" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EP81" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>9</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>45984.72916666666</v>
+      </c>
+      <c r="G82" t="n">
+        <v>4</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>5</v>
+      </c>
+      <c r="J82" t="n">
+        <v>4</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" t="n">
+        <v>6</v>
+      </c>
+      <c r="M82" t="n">
+        <v>3</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>10</v>
+      </c>
+      <c r="R82" t="n">
+        <v>5</v>
+      </c>
+      <c r="S82" t="n">
+        <v>11</v>
+      </c>
+      <c r="T82" t="n">
+        <v>7</v>
+      </c>
+      <c r="U82" t="n">
+        <v>21</v>
+      </c>
+      <c r="V82" t="n">
+        <v>12</v>
+      </c>
+      <c r="W82" t="n">
+        <v>15</v>
+      </c>
+      <c r="X82" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>King Saud University Stadium</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
+        </is>
+      </c>
+      <c r="AC82" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>5069</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>88</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM82" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN82" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT82" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV82" t="n">
+        <v>47</v>
+      </c>
+      <c r="BW82" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX82" t="n">
+        <v>113</v>
+      </c>
+      <c r="BY82" t="n">
+        <v>54</v>
+      </c>
+      <c r="BZ82" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CA82" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CB82" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="CC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR82" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS82" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU82" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV82" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX82" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY82" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ82" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA82" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB82" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC82" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD82" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE82" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF82" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG82" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH82" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI82" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ82" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK82" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL82" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DM82" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DN82" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="DO82" t="n">
+        <v>9</v>
+      </c>
+      <c r="DP82" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ82" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR82" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS82" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT82" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU82" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV82" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW82" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="DX82" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="DY82" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="DZ82" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA82" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EB82" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EC82" t="inlineStr"/>
+      <c r="ED82" t="inlineStr"/>
+      <c r="EE82" t="inlineStr">
+        <is>
+          <t>14.12</t>
+        </is>
+      </c>
+      <c r="EF82" t="inlineStr">
+        <is>
+          <t>8.87</t>
+        </is>
+      </c>
+      <c r="EG82" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EH82" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EI82" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EJ82" t="inlineStr"/>
+      <c r="EK82" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EL82" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EM82" t="inlineStr"/>
+      <c r="EN82" t="inlineStr"/>
+      <c r="EO82" t="inlineStr"/>
+      <c r="EP82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP82" headerRowCount="1">
-  <autoFilter ref="A1:EP82"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP85" headerRowCount="1">
+  <autoFilter ref="A1:EP85"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP82"/>
+  <dimension ref="A1:EP85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1797,7 +1797,7 @@
         <v>0.6</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -4775,156 +4775,156 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
         <v>45899.75</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" t="n">
         <v>4</v>
       </c>
-      <c r="J9" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>11</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>8</v>
-      </c>
-      <c r="R9" t="n">
-        <v>4</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
         <v>7</v>
       </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>15</v>
-      </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X9" t="n">
         <v>7</v>
       </c>
       <c r="Y9" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="Z9" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.44</v>
+        <v>5.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.75</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AM9" t="n">
         <v>1.47</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AO9" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA9" t="n">
         <v>4</v>
       </c>
-      <c r="AV9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2</v>
-      </c>
       <c r="BB9" t="n">
-        <v>5068</v>
+        <v>5070</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
@@ -4945,115 +4945,115 @@
         <v>1</v>
       </c>
       <c r="BI9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT9" t="n">
         <v>4</v>
       </c>
-      <c r="BJ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>59</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>63</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS9" t="n">
         <v>5</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>29</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>56</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>53</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>19</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>15</v>
       </c>
       <c r="CT9" t="n">
         <v>1</v>
@@ -5062,7 +5062,7 @@
         <v>7</v>
       </c>
       <c r="CV9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CW9" t="n">
         <v>1</v>
@@ -5071,7 +5071,7 @@
         <v>6</v>
       </c>
       <c r="CY9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="CZ9" t="n">
         <v>0</v>
@@ -5086,10 +5086,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5134,98 +5134,98 @@
         <v>1</v>
       </c>
       <c r="DT9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV9" t="b">
         <v>1</v>
       </c>
       <c r="DW9" t="n">
-        <v>42.17</v>
+        <v>36.63</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="DY9" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="DZ9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="EA9" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EB9" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
         <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EJ9" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM9" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EN9" t="inlineStr">
+        <is>
           <t>1.50</t>
-        </is>
-      </c>
-      <c r="EJ9" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="EK9" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EL9" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EM9" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EN9" t="inlineStr">
-        <is>
-          <t>1.63</t>
         </is>
       </c>
       <c r="EO9" t="inlineStr"/>
@@ -5247,156 +5247,156 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>45899.75</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>11</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="n">
         <v>7</v>
       </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L10" t="n">
-        <v>10</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>10</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
-        <v>6</v>
-      </c>
       <c r="U10" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="W10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X10" t="n">
         <v>7</v>
       </c>
       <c r="Y10" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="Z10" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
-        <v>5.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF10" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.57</v>
+        <v>6.75</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AM10" t="n">
         <v>1.47</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AO10" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB10" t="n">
-        <v>5070</v>
+        <v>5068</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
@@ -5417,64 +5417,64 @@
         <v>1</v>
       </c>
       <c r="BI10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
         <v>5</v>
       </c>
-      <c r="BK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>7</v>
-      </c>
       <c r="BN10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BO10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP10" t="n">
         <v>0</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU10" t="n">
         <v>1</v>
       </c>
       <c r="BV10" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BW10" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="BX10" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="BY10" t="n">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.91</v>
+        <v>1.86</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.14</v>
+        <v>0.99</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
@@ -5501,10 +5501,10 @@
         <v>1</v>
       </c>
       <c r="CK10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
@@ -5522,10 +5522,10 @@
         <v>1</v>
       </c>
       <c r="CR10" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="CS10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="CT10" t="n">
         <v>1</v>
@@ -5534,7 +5534,7 @@
         <v>7</v>
       </c>
       <c r="CV10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CW10" t="n">
         <v>1</v>
@@ -5543,7 +5543,7 @@
         <v>6</v>
       </c>
       <c r="CY10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CZ10" t="n">
         <v>0</v>
@@ -5558,10 +5558,10 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="DE10" t="n">
-        <v>2</v>
+        <v>0.17</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5606,98 +5606,98 @@
         <v>1</v>
       </c>
       <c r="DT10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV10" t="b">
         <v>1</v>
       </c>
       <c r="DW10" t="n">
-        <v>36.63</v>
+        <v>42.17</v>
       </c>
       <c r="DX10" t="n">
-        <v>8.67</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DY10" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="DZ10" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA10" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EB10" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EC10" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="ED10" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>7.29</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>5.33</t>
+        </is>
+      </c>
+      <c r="EG10" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr">
+        <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="EE10" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EF10" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="EG10" t="inlineStr">
-        <is>
-          <t>4.83</t>
-        </is>
-      </c>
-      <c r="EH10" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="EI10" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
       <c r="EJ10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="EK10" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EL10" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EM10" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EN10" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EO10" t="inlineStr"/>
@@ -6489,7 +6489,7 @@
         <v>1</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -8798,10 +8798,10 @@
         <v>50</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
         <v>0.99</v>
       </c>
       <c r="DO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -10181,7 +10181,7 @@
         <v>2</v>
       </c>
       <c r="DE20" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="DF20" t="n">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="DD22" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="DE22" t="n">
         <v>0.25</v>
@@ -12078,7 +12078,7 @@
         <v>0</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="DE24" t="n">
         <v>0.75</v>
@@ -12711,12 +12711,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -12726,120 +12726,120 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L26" t="n">
+        <v>11</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="n">
         <v>8</v>
       </c>
-      <c r="M26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>11</v>
-      </c>
       <c r="U26" t="n">
+        <v>13</v>
+      </c>
+      <c r="V26" t="n">
         <v>9</v>
       </c>
-      <c r="V26" t="n">
-        <v>15</v>
-      </c>
       <c r="W26" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="X26" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Y26" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="Z26" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="n">
-        <v>3.6</v>
+        <v>4.35</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.45</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.49</v>
+        <v>2.19</v>
       </c>
       <c r="AO26" t="n">
-        <v>3.14</v>
+        <v>2.3</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AS26" t="n">
         <v>3.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV26" t="n">
         <v>0</v>
@@ -12851,16 +12851,16 @@
         <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA26" t="n">
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>-1</v>
+        <v>5070</v>
       </c>
       <c r="BC26" t="n">
         <v>0</v>
@@ -12875,70 +12875,70 @@
         <v>-1</v>
       </c>
       <c r="BG26" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH26" t="n">
         <v>1</v>
       </c>
       <c r="BI26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BK26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL26" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BM26" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BN26" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BO26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ26" t="n">
         <v>1</v>
       </c>
       <c r="BR26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS26" t="n">
         <v>1</v>
       </c>
       <c r="BT26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU26" t="n">
         <v>1</v>
       </c>
       <c r="BV26" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="BW26" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="BX26" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="BY26" t="n">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.55</v>
+        <v>1.16</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="CC26" t="n">
         <v>0</v>
@@ -12971,10 +12971,10 @@
         <v>0</v>
       </c>
       <c r="CM26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CN26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO26" t="n">
         <v>0</v>
@@ -12986,25 +12986,25 @@
         <v>1</v>
       </c>
       <c r="CR26" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS26" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU26" t="n">
         <v>19</v>
       </c>
-      <c r="CS26" t="n">
-        <v>20</v>
-      </c>
-      <c r="CT26" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU26" t="n">
-        <v>12</v>
-      </c>
       <c r="CV26" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="CW26" t="n">
         <v>1</v>
       </c>
       <c r="CX26" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="CY26" t="n">
         <v>8</v>
@@ -13022,22 +13022,22 @@
         <v>50</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="DF26" t="n">
         <v>0</v>
       </c>
       <c r="DG26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="DI26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DJ26" t="n">
         <v>0</v>
@@ -13049,16 +13049,16 @@
         <v>0</v>
       </c>
       <c r="DM26" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="DN26" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="DO26" t="n">
         <v>9</v>
       </c>
       <c r="DP26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ26" t="b">
         <v>0</v>
@@ -13096,58 +13096,74 @@
       </c>
       <c r="EA26" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EB26" t="inlineStr">
         <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="EC26" t="inlineStr"/>
-      <c r="ED26" t="inlineStr"/>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EC26" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="ED26" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
       <c r="EE26" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EF26" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="EG26" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="EH26" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EI26" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EJ26" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="EK26" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EL26" t="inlineStr">
         <is>
-          <t>2.58</t>
-        </is>
-      </c>
-      <c r="EM26" t="inlineStr"/>
-      <c r="EN26" t="inlineStr"/>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EM26" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EN26" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="EO26" t="inlineStr"/>
       <c r="EP26" t="inlineStr"/>
     </row>
@@ -13167,12 +13183,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -13182,120 +13198,120 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L27" t="n">
         <v>8</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="n">
         <v>11</v>
       </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="n">
-        <v>8</v>
-      </c>
       <c r="U27" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W27" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="X27" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Y27" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="Z27" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="AF27" t="n">
-        <v>4.35</v>
+        <v>3.6</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.31</v>
+        <v>2.45</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AM27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN27" t="n">
         <v>1.49</v>
       </c>
-      <c r="AN27" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AO27" t="n">
-        <v>2.3</v>
+        <v>3.14</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AS27" t="n">
         <v>3.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AU27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
         <v>0</v>
@@ -13307,16 +13323,16 @@
         <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>5070</v>
+        <v>-1</v>
       </c>
       <c r="BC27" t="n">
         <v>0</v>
@@ -13331,70 +13347,70 @@
         <v>-1</v>
       </c>
       <c r="BG27" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH27" t="n">
         <v>1</v>
       </c>
       <c r="BI27" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BJ27" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK27" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL27" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BM27" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BN27" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BO27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ27" t="n">
         <v>1</v>
       </c>
       <c r="BR27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS27" t="n">
         <v>1</v>
       </c>
       <c r="BT27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU27" t="n">
         <v>1</v>
       </c>
       <c r="BV27" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="BW27" t="n">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="BX27" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="BY27" t="n">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.16</v>
+        <v>1.55</v>
       </c>
       <c r="CB27" t="n">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="CC27" t="n">
         <v>0</v>
@@ -13427,10 +13443,10 @@
         <v>0</v>
       </c>
       <c r="CM27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO27" t="n">
         <v>0</v>
@@ -13442,25 +13458,25 @@
         <v>1</v>
       </c>
       <c r="CR27" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="CS27" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="CT27" t="n">
         <v>1</v>
       </c>
       <c r="CU27" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CV27" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="CW27" t="n">
         <v>1</v>
       </c>
       <c r="CX27" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="CY27" t="n">
         <v>8</v>
@@ -13478,22 +13494,22 @@
         <v>50</v>
       </c>
       <c r="DD27" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DE27" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="DF27" t="n">
         <v>0</v>
       </c>
       <c r="DG27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DI27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DJ27" t="n">
         <v>0</v>
@@ -13505,16 +13521,16 @@
         <v>0</v>
       </c>
       <c r="DM27" t="n">
-        <v>2.14</v>
+        <v>1.42</v>
       </c>
       <c r="DN27" t="n">
-        <v>2.14</v>
+        <v>1.42</v>
       </c>
       <c r="DO27" t="n">
         <v>9</v>
       </c>
       <c r="DP27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ27" t="b">
         <v>0</v>
@@ -13552,74 +13568,58 @@
       </c>
       <c r="EA27" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EB27" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EC27" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="ED27" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EC27" t="inlineStr"/>
+      <c r="ED27" t="inlineStr"/>
       <c r="EE27" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EF27" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="EG27" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="EH27" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EI27" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EJ27" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EK27" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EL27" t="inlineStr">
         <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="EM27" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EN27" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EM27" t="inlineStr"/>
+      <c r="EN27" t="inlineStr"/>
       <c r="EO27" t="inlineStr"/>
       <c r="EP27" t="inlineStr"/>
     </row>
@@ -16281,7 +16281,7 @@
         <v>0.6</v>
       </c>
       <c r="DE33" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="DF33" t="n">
         <v>0.5</v>
@@ -17218,7 +17218,7 @@
         <v>100</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DE35" t="n">
         <v>2</v>
@@ -17251,7 +17251,7 @@
         <v>2.37</v>
       </c>
       <c r="DO35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17731,7 +17731,7 @@
         <v>2.25</v>
       </c>
       <c r="DO36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18642,7 +18642,7 @@
         <v>25</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="DE38" t="n">
         <v>2</v>
@@ -19117,7 +19117,7 @@
         <v>1.5</v>
       </c>
       <c r="DE39" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF39" t="n">
         <v>3</v>
@@ -20533,7 +20533,7 @@
         <v>0.8</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DF42" t="n">
         <v>0</v>
@@ -22394,7 +22394,7 @@
         <v>75</v>
       </c>
       <c r="DD46" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="DE46" t="n">
         <v>1.4</v>
@@ -22858,7 +22858,7 @@
         <v>67</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DE47" t="n">
         <v>0.6</v>
@@ -23338,7 +23338,7 @@
         <v>50</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="DE48" t="n">
         <v>3</v>
@@ -24301,7 +24301,7 @@
         <v>0.75</v>
       </c>
       <c r="DE50" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="DF50" t="n">
         <v>0</v>
@@ -24770,7 +24770,7 @@
         <v>100</v>
       </c>
       <c r="DD51" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="DE51" t="n">
         <v>1.4</v>
@@ -27227,141 +27227,149 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
         <v>45960.72916666666</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
+        <v>9</v>
+      </c>
+      <c r="K57" t="n">
         <v>4</v>
       </c>
-      <c r="K57" t="n">
-        <v>2</v>
-      </c>
       <c r="L57" t="n">
+        <v>13</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
         <v>6</v>
       </c>
-      <c r="M57" t="n">
-        <v>3</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>4</v>
-      </c>
       <c r="R57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U57" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="V57" t="n">
         <v>6</v>
       </c>
       <c r="W57" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="X57" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y57" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="Z57" t="n">
-        <v>53</v>
-      </c>
-      <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>King Abdullah Sports City</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>, Jeddah</t>
+        </is>
+      </c>
       <c r="AC57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD57" t="n">
         <v>3</v>
       </c>
       <c r="AE57" t="n">
-        <v>3.6</v>
+        <v>1.14</v>
       </c>
       <c r="AF57" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.95</v>
+        <v>11.7</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AI57" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AJ57" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AL57" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="AM57" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AN57" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AO57" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AR57" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AS57" t="n">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="AT57" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AU57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX57" t="n">
         <v>1</v>
@@ -27373,16 +27381,16 @@
         <v>2</v>
       </c>
       <c r="BA57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>5097</v>
+        <v>-1</v>
       </c>
       <c r="BC57" t="n">
         <v>0</v>
       </c>
       <c r="BD57" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="BE57" t="n">
         <v>0</v>
@@ -27397,76 +27405,76 @@
         <v>1</v>
       </c>
       <c r="BI57" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK57" t="n">
         <v>4</v>
       </c>
-      <c r="BJ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK57" t="n">
-        <v>0</v>
-      </c>
       <c r="BL57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BO57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP57" t="n">
         <v>1</v>
       </c>
       <c r="BQ57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR57" t="n">
         <v>2</v>
       </c>
       <c r="BS57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BU57" t="n">
         <v>1</v>
       </c>
       <c r="BV57" t="n">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="BW57" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="BX57" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="BY57" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="BZ57" t="n">
-        <v>1.01</v>
+        <v>2.19</v>
       </c>
       <c r="CA57" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="CB57" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="CC57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG57" t="n">
         <v>0</v>
@@ -27481,10 +27489,10 @@
         <v>1</v>
       </c>
       <c r="CK57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM57" t="n">
         <v>0</v>
@@ -27502,31 +27510,31 @@
         <v>1</v>
       </c>
       <c r="CR57" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CS57" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="CT57" t="n">
         <v>1</v>
       </c>
       <c r="CU57" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="CV57" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX57" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY57" t="n">
         <v>14</v>
       </c>
-      <c r="CW57" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX57" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY57" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ57" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="DA57" t="n">
         <v>84</v>
@@ -27538,34 +27546,34 @@
         <v>100</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="DE57" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="DF57" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="DG57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DH57" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DI57" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DJ57" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="DK57" t="n">
         <v>17</v>
       </c>
       <c r="DL57" t="n">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="DM57" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="DN57" t="n">
         <v>2.85</v>
@@ -27580,13 +27588,13 @@
         <v>1</v>
       </c>
       <c r="DR57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU57" t="b">
         <v>0</v>
@@ -27595,99 +27603,87 @@
         <v>1</v>
       </c>
       <c r="DW57" t="n">
-        <v>29.89</v>
+        <v>32.58</v>
       </c>
       <c r="DX57" t="n">
-        <v>6.19</v>
+        <v>6</v>
       </c>
       <c r="DY57" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="DZ57" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="EA57" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EB57" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EC57" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="ED57" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EE57" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="EF57" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="EG57" t="inlineStr">
         <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="EH57" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
-      <c r="EI57" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EJ57" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="EH57" t="inlineStr"/>
+      <c r="EI57" t="inlineStr"/>
+      <c r="EJ57" t="inlineStr"/>
       <c r="EK57" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EL57" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EM57" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EN57" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EO57" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="EP57" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -27707,149 +27703,141 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>45960.72916666666</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K58" t="n">
+        <v>2</v>
+      </c>
+      <c r="L58" t="n">
+        <v>6</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
         <v>4</v>
       </c>
-      <c r="L58" t="n">
-        <v>13</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2</v>
-      </c>
-      <c r="N58" t="n">
-        <v>3</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
+        <v>4</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
         <v>6</v>
-      </c>
-      <c r="R58" t="n">
-        <v>3</v>
-      </c>
-      <c r="S58" t="n">
-        <v>13</v>
-      </c>
-      <c r="T58" t="n">
-        <v>3</v>
-      </c>
-      <c r="U58" t="n">
-        <v>19</v>
       </c>
       <c r="V58" t="n">
         <v>6</v>
       </c>
       <c r="W58" t="n">
+        <v>14</v>
+      </c>
+      <c r="X58" t="n">
         <v>13</v>
       </c>
-      <c r="X58" t="n">
-        <v>8</v>
-      </c>
       <c r="Y58" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="Z58" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>King Abdullah Sports City</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>, Jeddah</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD58" t="n">
         <v>3</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.14</v>
+        <v>3.6</v>
       </c>
       <c r="AF58" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG58" t="n">
-        <v>11.7</v>
+        <v>1.95</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AI58" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT58" t="n">
         <v>1.4</v>
       </c>
-      <c r="AJ58" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN58" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AO58" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AU58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX58" t="n">
         <v>1</v>
@@ -27861,16 +27849,16 @@
         <v>2</v>
       </c>
       <c r="BA58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB58" t="n">
-        <v>-1</v>
+        <v>5097</v>
       </c>
       <c r="BC58" t="n">
         <v>0</v>
       </c>
       <c r="BD58" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="BE58" t="n">
         <v>0</v>
@@ -27885,76 +27873,76 @@
         <v>1</v>
       </c>
       <c r="BI58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BJ58" t="n">
         <v>0</v>
       </c>
       <c r="BK58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL58" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM58" t="n">
         <v>4</v>
       </c>
-      <c r="BL58" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM58" t="n">
-        <v>5</v>
-      </c>
       <c r="BN58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BO58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP58" t="n">
         <v>1</v>
       </c>
       <c r="BQ58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR58" t="n">
         <v>2</v>
       </c>
       <c r="BS58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BU58" t="n">
         <v>1</v>
       </c>
       <c r="BV58" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="BW58" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="BX58" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="BY58" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="BZ58" t="n">
-        <v>2.19</v>
+        <v>1.01</v>
       </c>
       <c r="CA58" t="n">
-        <v>0.71</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CB58" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="CC58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG58" t="n">
         <v>0</v>
@@ -27969,10 +27957,10 @@
         <v>1</v>
       </c>
       <c r="CK58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM58" t="n">
         <v>0</v>
@@ -27990,31 +27978,31 @@
         <v>1</v>
       </c>
       <c r="CR58" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS58" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT58" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU58" t="n">
         <v>13</v>
       </c>
-      <c r="CS58" t="n">
+      <c r="CV58" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW58" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX58" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY58" t="n">
         <v>10</v>
       </c>
-      <c r="CT58" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU58" t="n">
-        <v>7</v>
-      </c>
-      <c r="CV58" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW58" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX58" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY58" t="n">
-        <v>14</v>
-      </c>
       <c r="CZ58" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="DA58" t="n">
         <v>84</v>
@@ -28026,34 +28014,34 @@
         <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="DF58" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG58" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI58" t="n">
         <v>1.67</v>
       </c>
-      <c r="DG58" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH58" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI58" t="n">
-        <v>1</v>
-      </c>
       <c r="DJ58" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="DK58" t="n">
         <v>17</v>
       </c>
       <c r="DL58" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="DM58" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="DN58" t="n">
         <v>2.85</v>
@@ -28068,13 +28056,13 @@
         <v>1</v>
       </c>
       <c r="DR58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU58" t="b">
         <v>0</v>
@@ -28083,87 +28071,99 @@
         <v>1</v>
       </c>
       <c r="DW58" t="n">
-        <v>32.58</v>
+        <v>29.89</v>
       </c>
       <c r="DX58" t="n">
-        <v>6</v>
+        <v>6.19</v>
       </c>
       <c r="DY58" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="DZ58" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA58" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EB58" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EC58" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="ED58" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EE58" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF58" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="EG58" t="inlineStr">
         <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="EH58" t="inlineStr"/>
-      <c r="EI58" t="inlineStr"/>
-      <c r="EJ58" t="inlineStr"/>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="EH58" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EI58" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EJ58" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
       <c r="EK58" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EL58" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EM58" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="EN58" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EO58" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EP58" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.18</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
         <v>0.8</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF59" t="n">
         <v>0</v>
@@ -29441,7 +29441,7 @@
         <v>1.6</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DF61" t="n">
         <v>1.33</v>
@@ -29471,7 +29471,7 @@
         <v>1.4</v>
       </c>
       <c r="DO61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -31479,40 +31479,40 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45967.72916666666</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K66" t="n">
         <v>5</v>
       </c>
       <c r="L66" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -31521,101 +31521,93 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
+        <v>13</v>
+      </c>
+      <c r="T66" t="n">
         <v>6</v>
       </c>
-      <c r="T66" t="n">
-        <v>12</v>
-      </c>
       <c r="U66" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="V66" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="W66" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="X66" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Y66" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="Z66" t="n">
-        <v>66</v>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Prince Turki bin Abdul Aziz Stadium</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>, Riyadh</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.14</v>
+        <v>1.46</v>
       </c>
       <c r="AF66" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="AG66" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AI66" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AJ66" t="n">
-        <v>3.34</v>
+        <v>2.12</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AL66" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AM66" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AN66" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="AO66" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AR66" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AS66" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="AU66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV66" t="n">
         <v>1</v>
@@ -31624,25 +31616,25 @@
         <v>0</v>
       </c>
       <c r="AX66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA66" t="n">
         <v>1</v>
       </c>
       <c r="BB66" t="n">
-        <v>-1</v>
+        <v>5068</v>
       </c>
       <c r="BC66" t="n">
         <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="BE66" t="n">
         <v>0</v>
@@ -31657,7 +31649,7 @@
         <v>1</v>
       </c>
       <c r="BI66" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BJ66" t="n">
         <v>2</v>
@@ -31669,64 +31661,64 @@
         <v>3</v>
       </c>
       <c r="BM66" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BN66" t="n">
         <v>4</v>
       </c>
       <c r="BO66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP66" t="n">
         <v>0</v>
       </c>
       <c r="BQ66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU66" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BV66" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="BW66" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BX66" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="BY66" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="BZ66" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="CA66" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="CB66" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="CC66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG66" t="n">
         <v>0</v>
@@ -31747,13 +31739,13 @@
         <v>0</v>
       </c>
       <c r="CM66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP66" t="n">
         <v>0</v>
@@ -31765,70 +31757,70 @@
         <v>17</v>
       </c>
       <c r="CS66" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="CT66" t="n">
         <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="CV66" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="CW66" t="n">
         <v>1</v>
       </c>
       <c r="CX66" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY66" t="n">
         <v>9</v>
       </c>
-      <c r="CY66" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ66" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="DA66" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="DB66" t="n">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="DC66" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DF66" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DG66" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="DH66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DI66" t="n">
-        <v>0.43</v>
+        <v>1.29</v>
       </c>
       <c r="DJ66" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="DK66" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="DM66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.17</v>
+        <v>2.65</v>
       </c>
       <c r="DO66" t="n">
         <v>9</v>
@@ -31840,10 +31832,10 @@
         <v>1</v>
       </c>
       <c r="DR66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT66" t="b">
         <v>0</v>
@@ -31852,17 +31844,17 @@
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW66" t="n">
-        <v>25.56</v>
+        <v>27.94</v>
       </c>
       <c r="DX66" t="n">
-        <v>2.71</v>
+        <v>4.87</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
@@ -31870,68 +31862,60 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA66" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EB66" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EC66" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="ED66" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
+      <c r="EA66" t="inlineStr"/>
+      <c r="EB66" t="inlineStr"/>
+      <c r="EC66" t="inlineStr"/>
+      <c r="ED66" t="inlineStr"/>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EH66" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EI66" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EJ66" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EK66" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EL66" t="inlineStr">
         <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="EM66" t="inlineStr"/>
-      <c r="EN66" t="inlineStr"/>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM66" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EN66" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
       <c r="EO66" t="inlineStr"/>
       <c r="EP66" t="inlineStr"/>
     </row>
@@ -31951,135 +31935,143 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
         <v>45967.72916666666</v>
       </c>
       <c r="G67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K67" t="n">
         <v>5</v>
       </c>
       <c r="L67" t="n">
+        <v>8</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2</v>
+      </c>
+      <c r="S67" t="n">
+        <v>6</v>
+      </c>
+      <c r="T67" t="n">
         <v>12</v>
       </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
-        <v>2</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>6</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
+      <c r="U67" t="n">
+        <v>7</v>
+      </c>
+      <c r="V67" t="n">
+        <v>14</v>
+      </c>
+      <c r="W67" t="n">
+        <v>12</v>
+      </c>
+      <c r="X67" t="n">
         <v>13</v>
       </c>
-      <c r="T67" t="n">
-        <v>6</v>
-      </c>
-      <c r="U67" t="n">
-        <v>19</v>
-      </c>
-      <c r="V67" t="n">
-        <v>6</v>
-      </c>
-      <c r="W67" t="n">
-        <v>16</v>
-      </c>
-      <c r="X67" t="n">
-        <v>6</v>
-      </c>
       <c r="Y67" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="Z67" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA67" t="inlineStr"/>
-      <c r="AB67" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Prince Turki bin Abdul Aziz Stadium</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>, Riyadh</t>
+        </is>
+      </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.46</v>
+        <v>2.14</v>
       </c>
       <c r="AF67" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="AG67" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AI67" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP67" t="n">
         <v>1.75</v>
       </c>
-      <c r="AJ67" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL67" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM67" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO67" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AP67" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AQ67" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AR67" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AS67" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="AT67" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AU67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV67" t="n">
         <v>1</v>
@@ -32088,25 +32080,25 @@
         <v>0</v>
       </c>
       <c r="AX67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA67" t="n">
         <v>1</v>
       </c>
       <c r="BB67" t="n">
-        <v>5068</v>
+        <v>-1</v>
       </c>
       <c r="BC67" t="n">
         <v>0</v>
       </c>
       <c r="BD67" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="BE67" t="n">
         <v>0</v>
@@ -32121,7 +32113,7 @@
         <v>1</v>
       </c>
       <c r="BI67" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BJ67" t="n">
         <v>2</v>
@@ -32133,64 +32125,64 @@
         <v>3</v>
       </c>
       <c r="BM67" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BN67" t="n">
         <v>4</v>
       </c>
       <c r="BO67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP67" t="n">
         <v>0</v>
       </c>
       <c r="BQ67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU67" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BV67" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="BW67" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BX67" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="BY67" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="BZ67" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="CA67" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="CB67" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="CC67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG67" t="n">
         <v>0</v>
@@ -32211,13 +32203,13 @@
         <v>0</v>
       </c>
       <c r="CM67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP67" t="n">
         <v>0</v>
@@ -32229,70 +32221,70 @@
         <v>17</v>
       </c>
       <c r="CS67" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="CT67" t="n">
         <v>1</v>
       </c>
       <c r="CU67" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="CV67" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CW67" t="n">
         <v>1</v>
       </c>
       <c r="CX67" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CY67" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CZ67" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="DA67" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="DB67" t="n">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="DC67" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="DD67" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DF67" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="DG67" t="n">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
       <c r="DH67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DI67" t="n">
-        <v>1.29</v>
+        <v>0.43</v>
       </c>
       <c r="DJ67" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="DK67" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="DL67" t="n">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="DM67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="DN67" t="n">
-        <v>2.65</v>
+        <v>2.17</v>
       </c>
       <c r="DO67" t="n">
         <v>9</v>
@@ -32304,10 +32296,10 @@
         <v>1</v>
       </c>
       <c r="DR67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT67" t="b">
         <v>0</v>
@@ -32316,17 +32308,17 @@
         <v>0</v>
       </c>
       <c r="DV67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW67" t="n">
-        <v>27.94</v>
+        <v>25.56</v>
       </c>
       <c r="DX67" t="n">
-        <v>4.87</v>
+        <v>2.71</v>
       </c>
       <c r="DY67" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="DZ67" t="inlineStr">
@@ -32334,60 +32326,68 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA67" t="inlineStr"/>
-      <c r="EB67" t="inlineStr"/>
-      <c r="EC67" t="inlineStr"/>
-      <c r="ED67" t="inlineStr"/>
+      <c r="EA67" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EB67" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EC67" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="ED67" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
       <c r="EE67" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="EF67" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EG67" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EH67" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EI67" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EJ67" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EK67" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EL67" t="inlineStr">
         <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EM67" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="EN67" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EM67" t="inlineStr"/>
+      <c r="EN67" t="inlineStr"/>
       <c r="EO67" t="inlineStr"/>
       <c r="EP67" t="inlineStr"/>
     </row>
@@ -32718,7 +32718,7 @@
         <v>67</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="DE68" t="n">
         <v>0.25</v>
@@ -34118,7 +34118,7 @@
         <v>100</v>
       </c>
       <c r="DD71" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="DE71" t="n">
         <v>3</v>
@@ -34593,7 +34593,7 @@
         <v>1</v>
       </c>
       <c r="DE72" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="DF72" t="n">
         <v>1</v>
@@ -35553,7 +35553,7 @@
         <v>1.5</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DF74" t="n">
         <v>2</v>
@@ -36961,7 +36961,7 @@
         <v>0.6</v>
       </c>
       <c r="DE77" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF77" t="n">
         <v>0.5</v>
@@ -37455,7 +37455,7 @@
         <v>1.69</v>
       </c>
       <c r="DO78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -39387,6 +39387,1402 @@
       <c r="EO82" t="inlineStr"/>
       <c r="EP82" t="inlineStr"/>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>11</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Al Feiha</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Al Hazm</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>46016.61805555555</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>4</v>
+      </c>
+      <c r="K83" t="n">
+        <v>4</v>
+      </c>
+      <c r="L83" t="n">
+        <v>8</v>
+      </c>
+      <c r="M83" t="n">
+        <v>2</v>
+      </c>
+      <c r="N83" t="n">
+        <v>3</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>3</v>
+      </c>
+      <c r="R83" t="n">
+        <v>2</v>
+      </c>
+      <c r="S83" t="n">
+        <v>6</v>
+      </c>
+      <c r="T83" t="n">
+        <v>7</v>
+      </c>
+      <c r="U83" t="n">
+        <v>9</v>
+      </c>
+      <c r="V83" t="n">
+        <v>9</v>
+      </c>
+      <c r="W83" t="n">
+        <v>13</v>
+      </c>
+      <c r="X83" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI83" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL83" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM83" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN83" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS83" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT83" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV83" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW83" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX83" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY83" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ83" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CA83" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB83" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP83" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR83" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS83" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU83" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV83" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW83" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX83" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY83" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ83" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA83" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB83" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC83" t="n">
+        <v>55</v>
+      </c>
+      <c r="DD83" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DE83" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF83" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG83" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DH83" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DI83" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ83" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK83" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL83" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DM83" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DN83" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="DO83" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV83" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW83" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="DX83" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="DY83" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="DZ83" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="EA83" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EB83" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EC83" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="ED83" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EE83" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="EF83" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EG83" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EH83" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="EI83" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EJ83" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EK83" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EL83" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EM83" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="EN83" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EO83" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EP83" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>11</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Al Riyadh</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Al Ittifaq</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>46016.72916666666</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2</v>
+      </c>
+      <c r="I84" t="n">
+        <v>2</v>
+      </c>
+      <c r="J84" t="n">
+        <v>2</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2</v>
+      </c>
+      <c r="L84" t="n">
+        <v>4</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>2</v>
+      </c>
+      <c r="R84" t="n">
+        <v>8</v>
+      </c>
+      <c r="S84" t="n">
+        <v>6</v>
+      </c>
+      <c r="T84" t="n">
+        <v>7</v>
+      </c>
+      <c r="U84" t="n">
+        <v>8</v>
+      </c>
+      <c r="V84" t="n">
+        <v>15</v>
+      </c>
+      <c r="W84" t="n">
+        <v>15</v>
+      </c>
+      <c r="X84" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>66</v>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>Prince Turki bin Abdul Aziz Stadium</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>, Riyadh</t>
+        </is>
+      </c>
+      <c r="AC84" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>5065</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>88</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN84" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV84" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW84" t="n">
+        <v>80</v>
+      </c>
+      <c r="BX84" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY84" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ84" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CA84" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CB84" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR84" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS84" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU84" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV84" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX84" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY84" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ84" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA84" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB84" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC84" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD84" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DE84" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF84" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG84" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH84" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DI84" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DJ84" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK84" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL84" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DM84" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DN84" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DO84" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ84" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV84" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW84" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="DX84" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="DY84" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="DZ84" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="EA84" t="inlineStr"/>
+      <c r="EB84" t="inlineStr"/>
+      <c r="EC84" t="inlineStr"/>
+      <c r="ED84" t="inlineStr"/>
+      <c r="EE84" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EF84" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="EG84" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="EH84" t="inlineStr"/>
+      <c r="EI84" t="inlineStr"/>
+      <c r="EJ84" t="inlineStr"/>
+      <c r="EK84" t="inlineStr"/>
+      <c r="EL84" t="inlineStr"/>
+      <c r="EM84" t="inlineStr"/>
+      <c r="EN84" t="inlineStr"/>
+      <c r="EO84" t="inlineStr"/>
+      <c r="EP84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>11</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Neom SC</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Al Najma</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>46016.72916666666</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" t="n">
+        <v>3</v>
+      </c>
+      <c r="J85" t="n">
+        <v>5</v>
+      </c>
+      <c r="K85" t="n">
+        <v>3</v>
+      </c>
+      <c r="L85" t="n">
+        <v>8</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" t="n">
+        <v>3</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>5</v>
+      </c>
+      <c r="R85" t="n">
+        <v>2</v>
+      </c>
+      <c r="S85" t="n">
+        <v>7</v>
+      </c>
+      <c r="T85" t="n">
+        <v>8</v>
+      </c>
+      <c r="U85" t="n">
+        <v>12</v>
+      </c>
+      <c r="V85" t="n">
+        <v>10</v>
+      </c>
+      <c r="W85" t="n">
+        <v>12</v>
+      </c>
+      <c r="X85" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>King Khalid Sport City Stadium</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>, Tabouk</t>
+        </is>
+      </c>
+      <c r="AC85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>5097</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>78</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI85" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM85" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT85" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV85" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW85" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX85" t="n">
+        <v>66</v>
+      </c>
+      <c r="BY85" t="n">
+        <v>64</v>
+      </c>
+      <c r="BZ85" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CA85" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB85" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR85" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS85" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU85" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV85" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX85" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY85" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ85" t="n">
+        <v>65</v>
+      </c>
+      <c r="DA85" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB85" t="n">
+        <v>55</v>
+      </c>
+      <c r="DC85" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD85" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DE85" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DF85" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG85" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DH85" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DI85" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DJ85" t="n">
+        <v>35</v>
+      </c>
+      <c r="DK85" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL85" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DM85" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DN85" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="DO85" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS85" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT85" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU85" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV85" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW85" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="DX85" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="DY85" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="DZ85" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA85" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EB85" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EC85" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="ED85" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EE85" t="inlineStr">
+        <is>
+          <t>9.60</t>
+        </is>
+      </c>
+      <c r="EF85" t="inlineStr">
+        <is>
+          <t>6.16</t>
+        </is>
+      </c>
+      <c r="EG85" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EH85" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EI85" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EJ85" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EK85" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EL85" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EM85" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EN85" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EO85" t="inlineStr"/>
+      <c r="EP85" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP85" headerRowCount="1">
-  <autoFilter ref="A1:EP85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP91" headerRowCount="1">
+  <autoFilter ref="A1:EP91"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP85"/>
+  <dimension ref="A1:EP91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DE5" t="n">
         <v>0.2</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4145,7 +4145,7 @@
         <v>1</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4175,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="DE8" t="n">
         <v>1.2</v>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -4775,156 +4775,156 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
         <v>45899.75</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>11</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" t="n">
         <v>7</v>
       </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7</v>
-      </c>
-      <c r="L9" t="n">
-        <v>10</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>10</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="T9" t="n">
-        <v>6</v>
-      </c>
       <c r="U9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X9" t="n">
         <v>7</v>
       </c>
       <c r="Y9" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="Z9" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>5.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF9" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.57</v>
+        <v>6.75</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AM9" t="n">
         <v>1.47</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AO9" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
         <v>1</v>
       </c>
       <c r="AY9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB9" t="n">
-        <v>5070</v>
+        <v>5068</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
@@ -4945,64 +4945,64 @@
         <v>1</v>
       </c>
       <c r="BI9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
         <v>5</v>
       </c>
-      <c r="BK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>7</v>
-      </c>
       <c r="BN9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BO9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
         <v>0</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU9" t="n">
         <v>1</v>
       </c>
       <c r="BV9" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BW9" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="BX9" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="BY9" t="n">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.91</v>
+        <v>1.86</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.14</v>
+        <v>0.99</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="CC9" t="n">
         <v>0</v>
@@ -5029,10 +5029,10 @@
         <v>1</v>
       </c>
       <c r="CK9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
@@ -5050,10 +5050,10 @@
         <v>1</v>
       </c>
       <c r="CR9" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="CS9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="CT9" t="n">
         <v>1</v>
@@ -5062,7 +5062,7 @@
         <v>7</v>
       </c>
       <c r="CV9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CW9" t="n">
         <v>1</v>
@@ -5071,7 +5071,7 @@
         <v>6</v>
       </c>
       <c r="CY9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CZ9" t="n">
         <v>0</v>
@@ -5086,10 +5086,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="DE9" t="n">
-        <v>2</v>
+        <v>0.17</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5134,98 +5134,98 @@
         <v>1</v>
       </c>
       <c r="DT9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV9" t="b">
         <v>1</v>
       </c>
       <c r="DW9" t="n">
-        <v>36.63</v>
+        <v>42.17</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.67</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DY9" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="DZ9" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA9" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EB9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>7.29</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr">
+        <is>
+          <t>5.33</t>
+        </is>
+      </c>
+      <c r="EG9" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EI9" t="inlineStr">
+        <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="EE9" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EF9" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="EG9" t="inlineStr">
-        <is>
-          <t>4.83</t>
-        </is>
-      </c>
-      <c r="EH9" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="EI9" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
       <c r="EJ9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EM9" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EN9" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EO9" t="inlineStr"/>
@@ -5247,156 +5247,156 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>45899.75</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S10" t="n">
         <v>4</v>
       </c>
-      <c r="J10" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>11</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>8</v>
-      </c>
-      <c r="R10" t="n">
-        <v>4</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
         <v>7</v>
       </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>15</v>
-      </c>
       <c r="V10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X10" t="n">
         <v>7</v>
       </c>
       <c r="Y10" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="Z10" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.44</v>
+        <v>5.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.75</v>
+        <v>1.57</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AM10" t="n">
         <v>1.47</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AO10" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AU10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA10" t="n">
         <v>4</v>
       </c>
-      <c r="AV10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>2</v>
-      </c>
       <c r="BB10" t="n">
-        <v>5068</v>
+        <v>5070</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
@@ -5417,115 +5417,115 @@
         <v>1</v>
       </c>
       <c r="BI10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT10" t="n">
         <v>4</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM10" t="n">
+      <c r="BU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>59</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>63</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS10" t="n">
         <v>5</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>29</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>56</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>53</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>19</v>
-      </c>
-      <c r="CS10" t="n">
-        <v>15</v>
       </c>
       <c r="CT10" t="n">
         <v>1</v>
@@ -5534,7 +5534,7 @@
         <v>7</v>
       </c>
       <c r="CV10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CW10" t="n">
         <v>1</v>
@@ -5543,7 +5543,7 @@
         <v>6</v>
       </c>
       <c r="CY10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="CZ10" t="n">
         <v>0</v>
@@ -5558,10 +5558,10 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.17</v>
+        <v>2</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5606,98 +5606,98 @@
         <v>1</v>
       </c>
       <c r="DT10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV10" t="b">
         <v>1</v>
       </c>
       <c r="DW10" t="n">
-        <v>42.17</v>
+        <v>36.63</v>
       </c>
       <c r="DX10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="DY10" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="DZ10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="EA10" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EB10" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EC10" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="ED10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EE10" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EF10" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="EG10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="EH10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="EI10" t="inlineStr">
         <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EJ10" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EK10" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM10" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EN10" t="inlineStr">
+        <is>
           <t>1.50</t>
-        </is>
-      </c>
-      <c r="EJ10" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="EK10" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EL10" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EM10" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EN10" t="inlineStr">
-        <is>
-          <t>1.63</t>
         </is>
       </c>
       <c r="EO10" t="inlineStr"/>
@@ -6033,7 +6033,7 @@
         <v>1.6</v>
       </c>
       <c r="DE11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -6063,7 +6063,7 @@
         <v>0.93</v>
       </c>
       <c r="DO11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP11" t="b">
         <v>0</v>
@@ -6519,7 +6519,7 @@
         <v>2.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6950,7 +6950,7 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DE13" t="n">
         <v>0.4</v>
@@ -6983,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7439,7 +7439,7 @@
         <v>0.87</v>
       </c>
       <c r="DO14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7903,7 +7903,7 @@
         <v>0.91</v>
       </c>
       <c r="DO15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8334,7 +8334,7 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DE16" t="n">
         <v>1.4</v>
@@ -8367,7 +8367,7 @@
         <v>1.8</v>
       </c>
       <c r="DO16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9295,7 +9295,7 @@
         <v>2.11</v>
       </c>
       <c r="DO18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9751,7 +9751,7 @@
         <v>1.18</v>
       </c>
       <c r="DO19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9867,70 +9867,70 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
         <v>45918.65277777778</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
         <v>5</v>
       </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
+        <v>8</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2</v>
+      </c>
+      <c r="S20" t="n">
         <v>7</v>
       </c>
-      <c r="L20" t="n">
-        <v>9</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>6</v>
-      </c>
       <c r="T20" t="n">
+        <v>11</v>
+      </c>
+      <c r="U20" t="n">
         <v>10</v>
       </c>
-      <c r="U20" t="n">
-        <v>11</v>
-      </c>
       <c r="V20" t="n">
+        <v>13</v>
+      </c>
+      <c r="W20" t="n">
         <v>14</v>
       </c>
-      <c r="W20" t="n">
-        <v>12</v>
-      </c>
       <c r="X20" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y20" t="n">
         <v>45</v>
@@ -9941,82 +9941,82 @@
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AG20" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AI20" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="AK20" t="n">
         <v>1.72</v>
       </c>
       <c r="AL20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.56</v>
+        <v>2.01</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.2</v>
+        <v>3.22</v>
       </c>
       <c r="AO20" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.96</v>
+        <v>1.48</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AU20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV20" t="n">
         <v>1</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BA20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB20" t="n">
-        <v>5074</v>
+        <v>5125</v>
       </c>
       <c r="BC20" t="n">
         <v>0</v>
@@ -10037,19 +10037,19 @@
         <v>1</v>
       </c>
       <c r="BI20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ20" t="n">
         <v>2</v>
       </c>
       <c r="BK20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BM20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BN20" t="n">
         <v>6</v>
@@ -10058,55 +10058,55 @@
         <v>1</v>
       </c>
       <c r="BP20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BU20" t="n">
         <v>1</v>
       </c>
       <c r="BV20" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BW20" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="BX20" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="BY20" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="CB20" t="n">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="CC20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG20" t="n">
         <v>0</v>
@@ -10121,7 +10121,7 @@
         <v>1</v>
       </c>
       <c r="CK20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL20" t="n">
         <v>0</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="CN20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO20" t="n">
         <v>0</v>
@@ -10142,46 +10142,46 @@
         <v>1</v>
       </c>
       <c r="CR20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CS20" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="CT20" t="n">
         <v>1</v>
       </c>
       <c r="CU20" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV20" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW20" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX20" t="n">
         <v>8</v>
       </c>
-      <c r="CV20" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW20" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX20" t="n">
-        <v>6</v>
-      </c>
       <c r="CY20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CZ20" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA20" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DB20" t="n">
         <v>0</v>
       </c>
       <c r="DC20" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="DF20" t="n">
         <v>0</v>
@@ -10190,10 +10190,10 @@
         <v>0</v>
       </c>
       <c r="DH20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DI20" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="DJ20" t="n">
         <v>0</v>
@@ -10202,16 +10202,16 @@
         <v>0</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="DM20" t="n">
         <v>0</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="DO20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10223,10 +10223,10 @@
         <v>1</v>
       </c>
       <c r="DS20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU20" t="b">
         <v>0</v>
@@ -10252,42 +10252,42 @@
       </c>
       <c r="EA20" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="EB20" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EC20" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="ED20" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EE20" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EF20" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EG20" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EH20" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EI20" t="inlineStr">
@@ -10297,27 +10297,27 @@
       </c>
       <c r="EJ20" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EK20" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EL20" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EM20" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EN20" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EO20" t="inlineStr">
@@ -10347,70 +10347,70 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
         <v>45918.65277777778</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L21" t="n">
+        <v>9</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>5</v>
       </c>
-      <c r="L21" t="n">
-        <v>8</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
+        <v>10</v>
+      </c>
+      <c r="U21" t="n">
         <v>11</v>
       </c>
-      <c r="U21" t="n">
-        <v>10</v>
-      </c>
       <c r="V21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="X21" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y21" t="n">
         <v>45</v>
@@ -10421,82 +10421,82 @@
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AK21" t="n">
         <v>1.72</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AM21" t="n">
-        <v>2.01</v>
+        <v>1.56</v>
       </c>
       <c r="AN21" t="n">
-        <v>3.22</v>
+        <v>2.2</v>
       </c>
       <c r="AO21" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AU21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BA21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB21" t="n">
-        <v>5125</v>
+        <v>5074</v>
       </c>
       <c r="BC21" t="n">
         <v>0</v>
@@ -10517,19 +10517,19 @@
         <v>1</v>
       </c>
       <c r="BI21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ21" t="n">
         <v>2</v>
       </c>
       <c r="BK21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BM21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN21" t="n">
         <v>6</v>
@@ -10538,55 +10538,55 @@
         <v>1</v>
       </c>
       <c r="BP21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BU21" t="n">
         <v>1</v>
       </c>
       <c r="BV21" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BW21" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="BX21" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="BY21" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="CB21" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="CC21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG21" t="n">
         <v>0</v>
@@ -10601,7 +10601,7 @@
         <v>1</v>
       </c>
       <c r="CK21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL21" t="n">
         <v>0</v>
@@ -10610,7 +10610,7 @@
         <v>0</v>
       </c>
       <c r="CN21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO21" t="n">
         <v>0</v>
@@ -10622,58 +10622,58 @@
         <v>1</v>
       </c>
       <c r="CR21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CS21" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="CT21" t="n">
         <v>1</v>
       </c>
       <c r="CU21" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="CV21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CW21" t="n">
         <v>1</v>
       </c>
       <c r="CX21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CY21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CZ21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DB21" t="n">
         <v>0</v>
       </c>
       <c r="DC21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DD21" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH21" t="n">
         <v>1.5</v>
       </c>
-      <c r="DE21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH21" t="n">
-        <v>0</v>
-      </c>
       <c r="DI21" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DJ21" t="n">
         <v>0</v>
@@ -10682,16 +10682,16 @@
         <v>0</v>
       </c>
       <c r="DL21" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="DM21" t="n">
         <v>0</v>
       </c>
       <c r="DN21" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="DO21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10703,10 +10703,10 @@
         <v>1</v>
       </c>
       <c r="DS21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU21" t="b">
         <v>0</v>
@@ -10732,72 +10732,72 @@
       </c>
       <c r="EA21" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EB21" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EC21" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="ED21" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EE21" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EF21" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EG21" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EH21" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EI21" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EJ21" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EK21" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EL21" t="inlineStr">
+        <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="EE21" t="inlineStr">
-        <is>
-          <t>2.98</t>
-        </is>
-      </c>
-      <c r="EF21" t="inlineStr">
-        <is>
-          <t>3.41</t>
-        </is>
-      </c>
-      <c r="EG21" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EH21" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="EI21" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EJ21" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EK21" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EL21" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
       <c r="EM21" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EN21" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EO21" t="inlineStr">
@@ -11141,7 +11141,7 @@
         <v>1.4</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11171,7 +11171,7 @@
         <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11606,10 +11606,10 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -11639,7 +11639,7 @@
         <v>3.01</v>
       </c>
       <c r="DO23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12081,7 +12081,7 @@
         <v>1.2</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -12111,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="DO24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP24" t="b">
         <v>0</v>
@@ -12599,7 +12599,7 @@
         <v>1.06</v>
       </c>
       <c r="DO25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12711,12 +12711,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -12726,120 +12726,120 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
+        <v>6</v>
+      </c>
+      <c r="L26" t="n">
         <v>8</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="n">
         <v>11</v>
       </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="n">
-        <v>8</v>
-      </c>
       <c r="U26" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="V26" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W26" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="X26" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Y26" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="Z26" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="AF26" t="n">
-        <v>4.35</v>
+        <v>3.6</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AM26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN26" t="n">
         <v>1.49</v>
       </c>
-      <c r="AN26" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AO26" t="n">
-        <v>2.3</v>
+        <v>3.14</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AS26" t="n">
         <v>3.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AU26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
         <v>0</v>
@@ -12851,16 +12851,16 @@
         <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>5070</v>
+        <v>-1</v>
       </c>
       <c r="BC26" t="n">
         <v>0</v>
@@ -12875,70 +12875,70 @@
         <v>-1</v>
       </c>
       <c r="BG26" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH26" t="n">
         <v>1</v>
       </c>
       <c r="BI26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BJ26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL26" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BM26" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BN26" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ26" t="n">
         <v>1</v>
       </c>
       <c r="BR26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS26" t="n">
         <v>1</v>
       </c>
       <c r="BT26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU26" t="n">
         <v>1</v>
       </c>
       <c r="BV26" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="BW26" t="n">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="BX26" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="BY26" t="n">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.16</v>
+        <v>1.55</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="CC26" t="n">
         <v>0</v>
@@ -12971,10 +12971,10 @@
         <v>0</v>
       </c>
       <c r="CM26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO26" t="n">
         <v>0</v>
@@ -12986,25 +12986,25 @@
         <v>1</v>
       </c>
       <c r="CR26" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="CS26" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="CT26" t="n">
         <v>1</v>
       </c>
       <c r="CU26" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CV26" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="CW26" t="n">
         <v>1</v>
       </c>
       <c r="CX26" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="CY26" t="n">
         <v>8</v>
@@ -13022,22 +13022,22 @@
         <v>50</v>
       </c>
       <c r="DD26" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DE26" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="DF26" t="n">
         <v>0</v>
       </c>
       <c r="DG26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DI26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DJ26" t="n">
         <v>0</v>
@@ -13049,16 +13049,16 @@
         <v>0</v>
       </c>
       <c r="DM26" t="n">
-        <v>2.14</v>
+        <v>1.42</v>
       </c>
       <c r="DN26" t="n">
-        <v>2.14</v>
+        <v>1.42</v>
       </c>
       <c r="DO26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ26" t="b">
         <v>0</v>
@@ -13096,74 +13096,58 @@
       </c>
       <c r="EA26" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EB26" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EC26" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="ED26" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EC26" t="inlineStr"/>
+      <c r="ED26" t="inlineStr"/>
       <c r="EE26" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EF26" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="EG26" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="EH26" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EI26" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EJ26" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EK26" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EL26" t="inlineStr">
         <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="EM26" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EN26" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EM26" t="inlineStr"/>
+      <c r="EN26" t="inlineStr"/>
       <c r="EO26" t="inlineStr"/>
       <c r="EP26" t="inlineStr"/>
     </row>
@@ -13183,12 +13167,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -13198,120 +13182,120 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L27" t="n">
+        <v>11</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="n">
         <v>8</v>
       </c>
-      <c r="M27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>4</v>
-      </c>
-      <c r="R27" t="n">
-        <v>4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>5</v>
-      </c>
-      <c r="T27" t="n">
-        <v>11</v>
-      </c>
       <c r="U27" t="n">
+        <v>13</v>
+      </c>
+      <c r="V27" t="n">
         <v>9</v>
       </c>
-      <c r="V27" t="n">
-        <v>15</v>
-      </c>
       <c r="W27" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="X27" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Y27" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="Z27" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="AF27" t="n">
-        <v>3.6</v>
+        <v>4.35</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.45</v>
+        <v>1.31</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.49</v>
+        <v>2.19</v>
       </c>
       <c r="AO27" t="n">
-        <v>3.14</v>
+        <v>2.3</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AS27" t="n">
         <v>3.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV27" t="n">
         <v>0</v>
@@ -13323,16 +13307,16 @@
         <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA27" t="n">
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>-1</v>
+        <v>5070</v>
       </c>
       <c r="BC27" t="n">
         <v>0</v>
@@ -13347,70 +13331,70 @@
         <v>-1</v>
       </c>
       <c r="BG27" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH27" t="n">
         <v>1</v>
       </c>
       <c r="BI27" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BJ27" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BK27" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL27" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BM27" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BN27" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BO27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ27" t="n">
         <v>1</v>
       </c>
       <c r="BR27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS27" t="n">
         <v>1</v>
       </c>
       <c r="BT27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU27" t="n">
         <v>1</v>
       </c>
       <c r="BV27" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="BW27" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="BX27" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="BY27" t="n">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.55</v>
+        <v>1.16</v>
       </c>
       <c r="CB27" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="CC27" t="n">
         <v>0</v>
@@ -13443,10 +13427,10 @@
         <v>0</v>
       </c>
       <c r="CM27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CN27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO27" t="n">
         <v>0</v>
@@ -13458,25 +13442,25 @@
         <v>1</v>
       </c>
       <c r="CR27" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS27" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU27" t="n">
         <v>19</v>
       </c>
-      <c r="CS27" t="n">
-        <v>20</v>
-      </c>
-      <c r="CT27" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU27" t="n">
-        <v>12</v>
-      </c>
       <c r="CV27" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="CW27" t="n">
         <v>1</v>
       </c>
       <c r="CX27" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="CY27" t="n">
         <v>8</v>
@@ -13494,22 +13478,22 @@
         <v>50</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="DF27" t="n">
         <v>0</v>
       </c>
       <c r="DG27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH27" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="DI27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DJ27" t="n">
         <v>0</v>
@@ -13521,16 +13505,16 @@
         <v>0</v>
       </c>
       <c r="DM27" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="DN27" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="DO27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ27" t="b">
         <v>0</v>
@@ -13568,58 +13552,74 @@
       </c>
       <c r="EA27" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EB27" t="inlineStr">
         <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="EC27" t="inlineStr"/>
-      <c r="ED27" t="inlineStr"/>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EC27" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="ED27" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
       <c r="EE27" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EF27" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="EG27" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="EH27" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EI27" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EJ27" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="EK27" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EL27" t="inlineStr">
         <is>
-          <t>2.58</t>
-        </is>
-      </c>
-      <c r="EM27" t="inlineStr"/>
-      <c r="EN27" t="inlineStr"/>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EM27" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EN27" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="EO27" t="inlineStr"/>
       <c r="EP27" t="inlineStr"/>
     </row>
@@ -13991,7 +13991,7 @@
         <v>3.72</v>
       </c>
       <c r="DO28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14463,7 +14463,7 @@
         <v>2.82</v>
       </c>
       <c r="DO29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14943,7 +14943,7 @@
         <v>2.34</v>
       </c>
       <c r="DO30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15366,10 +15366,10 @@
         <v>100</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF31" t="n">
         <v>2</v>
@@ -15399,7 +15399,7 @@
         <v>2.97</v>
       </c>
       <c r="DO31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15825,7 +15825,7 @@
         <v>0.25</v>
       </c>
       <c r="DE32" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="DF32" t="n">
         <v>1</v>
@@ -15855,7 +15855,7 @@
         <v>2.93</v>
       </c>
       <c r="DO32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16311,7 +16311,7 @@
         <v>2.59</v>
       </c>
       <c r="DO33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16738,7 +16738,7 @@
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DE34" t="n">
         <v>3</v>
@@ -16771,7 +16771,7 @@
         <v>4.3</v>
       </c>
       <c r="DO34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -18170,7 +18170,7 @@
         <v>100</v>
       </c>
       <c r="DD37" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="DE37" t="n">
         <v>1.4</v>
@@ -18203,7 +18203,7 @@
         <v>2.65</v>
       </c>
       <c r="DO37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18675,7 +18675,7 @@
         <v>2.44</v>
       </c>
       <c r="DO38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19114,7 +19114,7 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="DE39" t="n">
         <v>0.17</v>
@@ -19147,7 +19147,7 @@
         <v>2.02</v>
       </c>
       <c r="DO39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19605,7 +19605,7 @@
         <v>1.8</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DF40" t="n">
         <v>2</v>
@@ -19635,7 +19635,7 @@
         <v>2.66</v>
       </c>
       <c r="DO40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20107,7 +20107,7 @@
         <v>2</v>
       </c>
       <c r="DO41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20563,7 +20563,7 @@
         <v>1.63</v>
       </c>
       <c r="DO42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21035,7 +21035,7 @@
         <v>4.22</v>
       </c>
       <c r="DO43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21499,7 +21499,7 @@
         <v>2.13</v>
       </c>
       <c r="DO44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21933,7 +21933,7 @@
         <v>2</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DF45" t="n">
         <v>1.5</v>
@@ -21963,7 +21963,7 @@
         <v>2.14</v>
       </c>
       <c r="DO45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22427,7 +22427,7 @@
         <v>2.57</v>
       </c>
       <c r="DO46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22891,7 +22891,7 @@
         <v>1.84</v>
       </c>
       <c r="DO47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23371,7 +23371,7 @@
         <v>1.94</v>
       </c>
       <c r="DO48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23821,7 +23821,7 @@
         <v>0</v>
       </c>
       <c r="DE49" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="DF49" t="n">
         <v>0</v>
@@ -23851,7 +23851,7 @@
         <v>2.9</v>
       </c>
       <c r="DO49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24298,7 +24298,7 @@
         <v>75</v>
       </c>
       <c r="DD50" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="DE50" t="n">
         <v>1.4</v>
@@ -24331,7 +24331,7 @@
         <v>2.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24773,7 +24773,7 @@
         <v>1.4</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DF51" t="n">
         <v>1.5</v>
@@ -24803,7 +24803,7 @@
         <v>2.84</v>
       </c>
       <c r="DO51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25238,7 +25238,7 @@
         <v>100</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DE52" t="n">
         <v>2.5</v>
@@ -25271,7 +25271,7 @@
         <v>3.18</v>
       </c>
       <c r="DO52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25702,10 +25702,10 @@
         <v>100</v>
       </c>
       <c r="DD53" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="DE53" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF53" t="n">
         <v>3</v>
@@ -25735,7 +25735,7 @@
         <v>2.21</v>
       </c>
       <c r="DO53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP53" t="b">
         <v>0</v>
@@ -26149,7 +26149,7 @@
         <v>1</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DF54" t="n">
         <v>1</v>
@@ -26179,7 +26179,7 @@
         <v>2.64</v>
       </c>
       <c r="DO54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26627,7 +26627,7 @@
         <v>3.19</v>
       </c>
       <c r="DO55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27099,7 +27099,7 @@
         <v>2.65</v>
       </c>
       <c r="DO56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27579,7 +27579,7 @@
         <v>2.85</v>
       </c>
       <c r="DO57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28014,7 +28014,7 @@
         <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="DE58" t="n">
         <v>2</v>
@@ -28047,7 +28047,7 @@
         <v>2.85</v>
       </c>
       <c r="DO58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28527,7 +28527,7 @@
         <v>2.02</v>
       </c>
       <c r="DO59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -28974,10 +28974,10 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DE60" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DF60" t="n">
         <v>2.33</v>
@@ -29007,7 +29007,7 @@
         <v>3.38</v>
       </c>
       <c r="DO60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29951,7 +29951,7 @@
         <v>2.42</v>
       </c>
       <c r="DO62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30431,7 +30431,7 @@
         <v>3.33</v>
       </c>
       <c r="DO63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30903,7 +30903,7 @@
         <v>3.73</v>
       </c>
       <c r="DO64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31329,7 +31329,7 @@
         <v>0.25</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DF65" t="n">
         <v>0.33</v>
@@ -31359,7 +31359,7 @@
         <v>2.02</v>
       </c>
       <c r="DO65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31790,7 +31790,7 @@
         <v>59</v>
       </c>
       <c r="DD66" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="DE66" t="n">
         <v>0.6</v>
@@ -31823,7 +31823,7 @@
         <v>2.65</v>
       </c>
       <c r="DO66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32257,7 +32257,7 @@
         <v>1.4</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DF67" t="n">
         <v>2</v>
@@ -32287,7 +32287,7 @@
         <v>2.17</v>
       </c>
       <c r="DO67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32721,7 +32721,7 @@
         <v>1.2</v>
       </c>
       <c r="DE68" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF68" t="n">
         <v>0.67</v>
@@ -32751,7 +32751,7 @@
         <v>1.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33190,7 +33190,7 @@
         <v>67</v>
       </c>
       <c r="DD69" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="DE69" t="n">
         <v>3</v>
@@ -33223,7 +33223,7 @@
         <v>2.68</v>
       </c>
       <c r="DO69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33687,7 +33687,7 @@
         <v>2.5</v>
       </c>
       <c r="DO70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34151,7 +34151,7 @@
         <v>3.72</v>
       </c>
       <c r="DO71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34623,7 +34623,7 @@
         <v>2.76</v>
       </c>
       <c r="DO72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35078,10 +35078,10 @@
         <v>67</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DE73" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -35111,7 +35111,7 @@
         <v>3.05</v>
       </c>
       <c r="DO73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35550,7 +35550,7 @@
         <v>75</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="DE74" t="n">
         <v>1.5</v>
@@ -35583,7 +35583,7 @@
         <v>2.12</v>
       </c>
       <c r="DO74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36022,7 +36022,7 @@
         <v>75</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DE75" t="n">
         <v>0.2</v>
@@ -36055,7 +36055,7 @@
         <v>2.45</v>
       </c>
       <c r="DO75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36535,7 +36535,7 @@
         <v>3.13</v>
       </c>
       <c r="DO76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36991,7 +36991,7 @@
         <v>2.28</v>
       </c>
       <c r="DO77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -37850,7 +37850,7 @@
         <v>75</v>
       </c>
       <c r="DD79" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DE79" t="n">
         <v>0.4</v>
@@ -37883,7 +37883,7 @@
         <v>3.63</v>
       </c>
       <c r="DO79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -38313,7 +38313,7 @@
         <v>0.8</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DF80" t="n">
         <v>0.75</v>
@@ -38343,7 +38343,7 @@
         <v>2.38</v>
       </c>
       <c r="DO80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38479,79 +38479,87 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
         <v>45984.72916666666</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H81" t="n">
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
+        <v>4</v>
+      </c>
+      <c r="K81" t="n">
+        <v>2</v>
+      </c>
+      <c r="L81" t="n">
+        <v>6</v>
+      </c>
+      <c r="M81" t="n">
+        <v>3</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>10</v>
+      </c>
+      <c r="R81" t="n">
+        <v>5</v>
+      </c>
+      <c r="S81" t="n">
+        <v>11</v>
+      </c>
+      <c r="T81" t="n">
+        <v>7</v>
+      </c>
+      <c r="U81" t="n">
+        <v>21</v>
+      </c>
+      <c r="V81" t="n">
+        <v>12</v>
+      </c>
+      <c r="W81" t="n">
+        <v>15</v>
+      </c>
+      <c r="X81" t="n">
         <v>8</v>
       </c>
-      <c r="K81" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" t="n">
-        <v>9</v>
-      </c>
-      <c r="M81" t="n">
-        <v>3</v>
-      </c>
-      <c r="N81" t="n">
-        <v>3</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>2</v>
-      </c>
-      <c r="R81" t="n">
-        <v>2</v>
-      </c>
-      <c r="S81" t="n">
-        <v>6</v>
-      </c>
-      <c r="T81" t="n">
-        <v>13</v>
-      </c>
-      <c r="U81" t="n">
-        <v>8</v>
-      </c>
-      <c r="V81" t="n">
-        <v>15</v>
-      </c>
-      <c r="W81" t="n">
-        <v>11</v>
-      </c>
-      <c r="X81" t="n">
-        <v>16</v>
-      </c>
       <c r="Y81" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Z81" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA81" t="inlineStr"/>
-      <c r="AB81" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>King Saud University Stadium</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
+        </is>
+      </c>
       <c r="AC81" t="n">
         <v>3</v>
       </c>
@@ -38559,82 +38567,82 @@
         <v>3</v>
       </c>
       <c r="AE81" t="n">
-        <v>2.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF81" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="AG81" t="n">
-        <v>2.65</v>
+        <v>12</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="AI81" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR81" t="n">
         <v>1.73</v>
       </c>
-      <c r="AJ81" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK81" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL81" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM81" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AN81" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AO81" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AP81" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AQ81" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR81" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AS81" t="n">
-        <v>2.91</v>
+        <v>5</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.42</v>
+        <v>1.99</v>
       </c>
       <c r="AU81" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW81" t="n">
         <v>0</v>
       </c>
       <c r="AX81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY81" t="n">
         <v>1</v>
       </c>
       <c r="AZ81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB81" t="n">
-        <v>-1</v>
+        <v>5069</v>
       </c>
       <c r="BC81" t="n">
         <v>0</v>
       </c>
       <c r="BD81" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="BE81" t="n">
         <v>0</v>
@@ -38649,10 +38657,10 @@
         <v>1</v>
       </c>
       <c r="BI81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BJ81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK81" t="n">
         <v>2</v>
@@ -38661,7 +38669,7 @@
         <v>1</v>
       </c>
       <c r="BM81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BN81" t="n">
         <v>3</v>
@@ -38676,49 +38684,49 @@
         <v>2</v>
       </c>
       <c r="BR81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS81" t="n">
         <v>2</v>
       </c>
       <c r="BT81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU81" t="n">
         <v>1</v>
       </c>
       <c r="BV81" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="BW81" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BX81" t="n">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="BY81" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BZ81" t="n">
-        <v>0.91</v>
+        <v>2.36</v>
       </c>
       <c r="CA81" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CB81" t="n">
-        <v>2.21</v>
+        <v>3.68</v>
       </c>
       <c r="CC81" t="n">
         <v>0</v>
       </c>
       <c r="CD81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE81" t="n">
         <v>0</v>
       </c>
       <c r="CF81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG81" t="n">
         <v>0</v>
@@ -38745,85 +38753,85 @@
         <v>0</v>
       </c>
       <c r="CO81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ81" t="n">
         <v>1</v>
       </c>
       <c r="CR81" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CS81" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CT81" t="n">
         <v>1</v>
       </c>
       <c r="CU81" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="CV81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="CW81" t="n">
         <v>1</v>
       </c>
       <c r="CX81" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="CY81" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="CZ81" t="n">
         <v>75</v>
       </c>
       <c r="DA81" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="DB81" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="DC81" t="n">
         <v>88</v>
       </c>
       <c r="DD81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DE81" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="DF81" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="DG81" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="DH81" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="DI81" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="DJ81" t="n">
         <v>25</v>
       </c>
       <c r="DK81" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="DL81" t="n">
-        <v>1.2</v>
+        <v>2.59</v>
       </c>
       <c r="DM81" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="DN81" t="n">
-        <v>2.51</v>
+        <v>3.82</v>
       </c>
       <c r="DO81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38832,13 +38840,13 @@
         <v>1</v>
       </c>
       <c r="DR81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU81" t="b">
         <v>0</v>
@@ -38847,85 +38855,73 @@
         <v>1</v>
       </c>
       <c r="DW81" t="n">
-        <v>30.11</v>
+        <v>21.64</v>
       </c>
       <c r="DX81" t="n">
-        <v>4.86</v>
+        <v>4.03</v>
       </c>
       <c r="DY81" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="DZ81" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="EA81" t="inlineStr"/>
-      <c r="EB81" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA81" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EB81" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
       <c r="EC81" t="inlineStr"/>
       <c r="ED81" t="inlineStr"/>
       <c r="EE81" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="EF81" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="EG81" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="EH81" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EI81" t="inlineStr">
         <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EJ81" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EJ81" t="inlineStr"/>
       <c r="EK81" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EL81" t="inlineStr">
         <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="EM81" t="inlineStr">
-        <is>
-          <t>2.71</t>
-        </is>
-      </c>
-      <c r="EN81" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EO81" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EP81" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EM81" t="inlineStr"/>
+      <c r="EN81" t="inlineStr"/>
+      <c r="EO81" t="inlineStr"/>
+      <c r="EP81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -38943,87 +38939,79 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
         <v>45984.72916666666</v>
       </c>
       <c r="G82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
         <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
+        <v>9</v>
+      </c>
+      <c r="M82" t="n">
+        <v>3</v>
+      </c>
+      <c r="N82" t="n">
+        <v>3</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>2</v>
+      </c>
+      <c r="R82" t="n">
+        <v>2</v>
+      </c>
+      <c r="S82" t="n">
         <v>6</v>
       </c>
-      <c r="M82" t="n">
-        <v>3</v>
-      </c>
-      <c r="N82" t="n">
-        <v>1</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>10</v>
-      </c>
-      <c r="R82" t="n">
-        <v>5</v>
-      </c>
-      <c r="S82" t="n">
+      <c r="T82" t="n">
+        <v>13</v>
+      </c>
+      <c r="U82" t="n">
+        <v>8</v>
+      </c>
+      <c r="V82" t="n">
+        <v>15</v>
+      </c>
+      <c r="W82" t="n">
         <v>11</v>
       </c>
-      <c r="T82" t="n">
-        <v>7</v>
-      </c>
-      <c r="U82" t="n">
-        <v>21</v>
-      </c>
-      <c r="V82" t="n">
-        <v>12</v>
-      </c>
-      <c r="W82" t="n">
-        <v>15</v>
-      </c>
       <c r="X82" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y82" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="Z82" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>King Saud University Stadium</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
         <v>3</v>
       </c>
@@ -39031,82 +39019,82 @@
         <v>3</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.14</v>
+        <v>2.29</v>
       </c>
       <c r="AF82" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="AG82" t="n">
-        <v>12</v>
+        <v>2.65</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AI82" t="n">
-        <v>1.21</v>
+        <v>1.73</v>
       </c>
       <c r="AJ82" t="n">
-        <v>1.56</v>
+        <v>3</v>
       </c>
       <c r="AK82" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL82" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AM82" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AN82" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="AO82" t="n">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="AS82" t="n">
-        <v>5</v>
+        <v>2.91</v>
       </c>
       <c r="AT82" t="n">
-        <v>1.99</v>
+        <v>1.42</v>
       </c>
       <c r="AU82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW82" t="n">
         <v>0</v>
       </c>
       <c r="AX82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY82" t="n">
         <v>1</v>
       </c>
       <c r="AZ82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB82" t="n">
-        <v>5069</v>
+        <v>-1</v>
       </c>
       <c r="BC82" t="n">
         <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="BE82" t="n">
         <v>0</v>
@@ -39121,10 +39109,10 @@
         <v>1</v>
       </c>
       <c r="BI82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK82" t="n">
         <v>2</v>
@@ -39133,7 +39121,7 @@
         <v>1</v>
       </c>
       <c r="BM82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN82" t="n">
         <v>3</v>
@@ -39148,49 +39136,49 @@
         <v>2</v>
       </c>
       <c r="BR82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS82" t="n">
         <v>2</v>
       </c>
       <c r="BT82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU82" t="n">
         <v>1</v>
       </c>
       <c r="BV82" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="BW82" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="BX82" t="n">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="BY82" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="BZ82" t="n">
-        <v>2.36</v>
+        <v>0.91</v>
       </c>
       <c r="CA82" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CB82" t="n">
-        <v>3.68</v>
+        <v>2.21</v>
       </c>
       <c r="CC82" t="n">
         <v>0</v>
       </c>
       <c r="CD82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE82" t="n">
         <v>0</v>
       </c>
       <c r="CF82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG82" t="n">
         <v>0</v>
@@ -39217,85 +39205,85 @@
         <v>0</v>
       </c>
       <c r="CO82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ82" t="n">
         <v>1</v>
       </c>
       <c r="CR82" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CS82" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="CT82" t="n">
         <v>1</v>
       </c>
       <c r="CU82" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV82" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX82" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY82" t="n">
         <v>8</v>
-      </c>
-      <c r="CV82" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX82" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY82" t="n">
-        <v>14</v>
       </c>
       <c r="CZ82" t="n">
         <v>75</v>
       </c>
       <c r="DA82" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="DB82" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="DC82" t="n">
         <v>88</v>
       </c>
       <c r="DD82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="DF82" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="DG82" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="DH82" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="DI82" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="DJ82" t="n">
         <v>25</v>
       </c>
       <c r="DK82" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="DL82" t="n">
-        <v>2.59</v>
+        <v>1.2</v>
       </c>
       <c r="DM82" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="DN82" t="n">
-        <v>3.82</v>
+        <v>2.51</v>
       </c>
       <c r="DO82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39304,13 +39292,13 @@
         <v>1</v>
       </c>
       <c r="DR82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU82" t="b">
         <v>0</v>
@@ -39319,73 +39307,85 @@
         <v>1</v>
       </c>
       <c r="DW82" t="n">
-        <v>21.64</v>
+        <v>30.11</v>
       </c>
       <c r="DX82" t="n">
-        <v>4.03</v>
+        <v>4.86</v>
       </c>
       <c r="DY82" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="DZ82" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="EA82" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EB82" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="EA82" t="inlineStr"/>
+      <c r="EB82" t="inlineStr"/>
       <c r="EC82" t="inlineStr"/>
       <c r="ED82" t="inlineStr"/>
       <c r="EE82" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EF82" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EG82" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EH82" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EI82" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EJ82" t="inlineStr"/>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EJ82" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
       <c r="EK82" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EL82" t="inlineStr">
         <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="EM82" t="inlineStr"/>
-      <c r="EN82" t="inlineStr"/>
-      <c r="EO82" t="inlineStr"/>
-      <c r="EP82" t="inlineStr"/>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EM82" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EN82" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EO82" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EP82" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -39883,143 +39883,143 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
         <v>46016.72916666666</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L84" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M84" t="n">
         <v>1</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R84" t="n">
+        <v>2</v>
+      </c>
+      <c r="S84" t="n">
+        <v>7</v>
+      </c>
+      <c r="T84" t="n">
         <v>8</v>
       </c>
-      <c r="S84" t="n">
+      <c r="U84" t="n">
+        <v>12</v>
+      </c>
+      <c r="V84" t="n">
+        <v>10</v>
+      </c>
+      <c r="W84" t="n">
+        <v>12</v>
+      </c>
+      <c r="X84" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>King Khalid Sport City Stadium</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>, Tabouk</t>
+        </is>
+      </c>
+      <c r="AC84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF84" t="n">
         <v>6</v>
       </c>
-      <c r="T84" t="n">
-        <v>7</v>
-      </c>
-      <c r="U84" t="n">
-        <v>8</v>
-      </c>
-      <c r="V84" t="n">
-        <v>15</v>
-      </c>
-      <c r="W84" t="n">
-        <v>15</v>
-      </c>
-      <c r="X84" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>66</v>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>Prince Turki bin Abdul Aziz Stadium</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>, Riyadh</t>
-        </is>
-      </c>
-      <c r="AC84" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AF84" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AG84" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR84" t="n">
         <v>2.22</v>
       </c>
-      <c r="AH84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI84" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK84" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL84" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR84" t="n">
-        <v>0</v>
-      </c>
       <c r="AS84" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AU84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV84" t="n">
         <v>0</v>
@@ -40028,25 +40028,25 @@
         <v>0</v>
       </c>
       <c r="AX84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA84" t="n">
         <v>0</v>
       </c>
       <c r="BB84" t="n">
-        <v>5065</v>
+        <v>5097</v>
       </c>
       <c r="BC84" t="n">
         <v>0</v>
       </c>
       <c r="BD84" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="BE84" t="n">
         <v>0</v>
@@ -40061,7 +40061,7 @@
         <v>1</v>
       </c>
       <c r="BI84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ84" t="n">
         <v>0</v>
@@ -40070,16 +40070,16 @@
         <v>1</v>
       </c>
       <c r="BL84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BN84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP84" t="n">
         <v>1</v>
@@ -40088,49 +40088,49 @@
         <v>1</v>
       </c>
       <c r="BR84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU84" t="n">
         <v>1</v>
       </c>
       <c r="BV84" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="BW84" t="n">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="BX84" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="BY84" t="n">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="BZ84" t="n">
-        <v>0.88</v>
+        <v>1.39</v>
       </c>
       <c r="CA84" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="CB84" t="n">
-        <v>2.96</v>
+        <v>2.43</v>
       </c>
       <c r="CC84" t="n">
         <v>0</v>
       </c>
       <c r="CD84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE84" t="n">
         <v>0</v>
       </c>
       <c r="CF84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG84" t="n">
         <v>0</v>
@@ -40151,7 +40151,7 @@
         <v>0</v>
       </c>
       <c r="CM84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN84" t="n">
         <v>0</v>
@@ -40166,73 +40166,73 @@
         <v>1</v>
       </c>
       <c r="CR84" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS84" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU84" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV84" t="n">
         <v>11</v>
       </c>
-      <c r="CS84" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU84" t="n">
+      <c r="CW84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX84" t="n">
         <v>6</v>
       </c>
-      <c r="CV84" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX84" t="n">
-        <v>5</v>
-      </c>
       <c r="CY84" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="CZ84" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="DA84" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="DB84" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="DC84" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="DD84" t="n">
         <v>1.4</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.4</v>
+        <v>0.17</v>
       </c>
       <c r="DF84" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="DG84" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="DH84" t="n">
-        <v>0.89</v>
+        <v>1.56</v>
       </c>
       <c r="DI84" t="n">
-        <v>1.33</v>
+        <v>0.11</v>
       </c>
       <c r="DJ84" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="DK84" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="DL84" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="DM84" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="DN84" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="DO84" t="n">
         <v>10</v>
@@ -40244,7 +40244,7 @@
         <v>1</v>
       </c>
       <c r="DR84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS84" t="b">
         <v>0</v>
@@ -40256,50 +40256,94 @@
         <v>0</v>
       </c>
       <c r="DV84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW84" t="n">
-        <v>18.15</v>
+        <v>15.82</v>
       </c>
       <c r="DX84" t="n">
-        <v>4.4</v>
+        <v>3.69</v>
       </c>
       <c r="DY84" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="DZ84" t="inlineStr">
         <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="EA84" t="inlineStr"/>
-      <c r="EB84" t="inlineStr"/>
-      <c r="EC84" t="inlineStr"/>
-      <c r="ED84" t="inlineStr"/>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA84" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EB84" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EC84" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="ED84" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
       <c r="EE84" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="EF84" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="EG84" t="inlineStr">
         <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EH84" t="inlineStr"/>
-      <c r="EI84" t="inlineStr"/>
-      <c r="EJ84" t="inlineStr"/>
-      <c r="EK84" t="inlineStr"/>
-      <c r="EL84" t="inlineStr"/>
-      <c r="EM84" t="inlineStr"/>
-      <c r="EN84" t="inlineStr"/>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EH84" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EI84" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EJ84" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EK84" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EL84" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EM84" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EN84" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
       <c r="EO84" t="inlineStr"/>
       <c r="EP84" t="inlineStr"/>
     </row>
@@ -40319,143 +40363,143 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
         <v>46016.72916666666</v>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L85" t="n">
+        <v>4</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>2</v>
+      </c>
+      <c r="R85" t="n">
         <v>8</v>
       </c>
-      <c r="M85" t="n">
-        <v>1</v>
-      </c>
-      <c r="N85" t="n">
-        <v>3</v>
-      </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>5</v>
-      </c>
-      <c r="R85" t="n">
-        <v>2</v>
-      </c>
       <c r="S85" t="n">
+        <v>6</v>
+      </c>
+      <c r="T85" t="n">
         <v>7</v>
       </c>
-      <c r="T85" t="n">
+      <c r="U85" t="n">
         <v>8</v>
       </c>
-      <c r="U85" t="n">
-        <v>12</v>
-      </c>
       <c r="V85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W85" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X85" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y85" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="Z85" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>King Khalid Sport City Stadium</t>
+          <t>Prince Turki bin Abdul Aziz Stadium</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>, Tabouk</t>
+          <t>, Riyadh</t>
         </is>
       </c>
       <c r="AC85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.4</v>
+        <v>2.97</v>
       </c>
       <c r="AF85" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="AG85" t="n">
-        <v>10</v>
+        <v>2.22</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI85" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="AJ85" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AK85" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AL85" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AM85" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AN85" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AO85" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR85" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AS85" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT85" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AU85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV85" t="n">
         <v>0</v>
@@ -40464,25 +40508,25 @@
         <v>0</v>
       </c>
       <c r="AX85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA85" t="n">
         <v>0</v>
       </c>
       <c r="BB85" t="n">
-        <v>5097</v>
+        <v>5065</v>
       </c>
       <c r="BC85" t="n">
         <v>0</v>
       </c>
       <c r="BD85" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="BE85" t="n">
         <v>0</v>
@@ -40497,178 +40541,178 @@
         <v>1</v>
       </c>
       <c r="BI85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV85" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW85" t="n">
+        <v>80</v>
+      </c>
+      <c r="BX85" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY85" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ85" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CA85" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CB85" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR85" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS85" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU85" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV85" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX85" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY85" t="n">
         <v>4</v>
       </c>
-      <c r="BJ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL85" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM85" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN85" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR85" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT85" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV85" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW85" t="n">
-        <v>37</v>
-      </c>
-      <c r="BX85" t="n">
-        <v>66</v>
-      </c>
-      <c r="BY85" t="n">
-        <v>64</v>
-      </c>
-      <c r="BZ85" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CA85" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB85" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="CC85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR85" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS85" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU85" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV85" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX85" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY85" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ85" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="DA85" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="DB85" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="DC85" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="DD85" t="n">
         <v>1.4</v>
       </c>
       <c r="DE85" t="n">
-        <v>0.17</v>
+        <v>1.4</v>
       </c>
       <c r="DF85" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="DG85" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="DH85" t="n">
-        <v>1.56</v>
+        <v>0.89</v>
       </c>
       <c r="DI85" t="n">
-        <v>0.11</v>
+        <v>1.33</v>
       </c>
       <c r="DJ85" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="DK85" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="DL85" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="DM85" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="DN85" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="DO85" t="n">
         <v>10</v>
@@ -40680,7 +40724,7 @@
         <v>1</v>
       </c>
       <c r="DR85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS85" t="b">
         <v>0</v>
@@ -40692,96 +40736,2816 @@
         <v>0</v>
       </c>
       <c r="DV85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW85" t="n">
-        <v>15.82</v>
+        <v>18.15</v>
       </c>
       <c r="DX85" t="n">
-        <v>3.69</v>
+        <v>4.4</v>
       </c>
       <c r="DY85" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="DZ85" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="EA85" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="EB85" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="EC85" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="ED85" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="EA85" t="inlineStr"/>
+      <c r="EB85" t="inlineStr"/>
+      <c r="EC85" t="inlineStr"/>
+      <c r="ED85" t="inlineStr"/>
       <c r="EE85" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EF85" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EG85" t="inlineStr">
         <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="EH85" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="EI85" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EJ85" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="EK85" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="EL85" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EM85" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="EN85" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="EH85" t="inlineStr"/>
+      <c r="EI85" t="inlineStr"/>
+      <c r="EJ85" t="inlineStr"/>
+      <c r="EK85" t="inlineStr"/>
+      <c r="EL85" t="inlineStr"/>
+      <c r="EM85" t="inlineStr"/>
+      <c r="EN85" t="inlineStr"/>
       <c r="EO85" t="inlineStr"/>
       <c r="EP85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>11</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Al Fateh</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>46017.54513888889</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" t="n">
+        <v>3</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>9</v>
+      </c>
+      <c r="L86" t="n">
+        <v>10</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1</v>
+      </c>
+      <c r="N86" t="n">
+        <v>3</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>3</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6</v>
+      </c>
+      <c r="S86" t="n">
+        <v>3</v>
+      </c>
+      <c r="T86" t="n">
+        <v>11</v>
+      </c>
+      <c r="U86" t="n">
+        <v>6</v>
+      </c>
+      <c r="V86" t="n">
+        <v>17</v>
+      </c>
+      <c r="W86" t="n">
+        <v>12</v>
+      </c>
+      <c r="X86" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>Prince Abdullah bin Jalawi Sports City Stadium</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>, Al-Hasa</t>
+        </is>
+      </c>
+      <c r="AC86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>5064</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ86" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL86" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM86" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN86" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR86" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT86" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV86" t="n">
+        <v>14</v>
+      </c>
+      <c r="BW86" t="n">
+        <v>90</v>
+      </c>
+      <c r="BX86" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY86" t="n">
+        <v>114</v>
+      </c>
+      <c r="BZ86" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CA86" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CB86" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP86" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR86" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS86" t="n">
+        <v>31</v>
+      </c>
+      <c r="CT86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU86" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV86" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW86" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX86" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY86" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ86" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA86" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB86" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC86" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD86" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DE86" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF86" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DG86" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DH86" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DI86" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DJ86" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK86" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL86" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DM86" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DN86" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="DO86" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP86" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ86" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR86" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS86" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT86" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU86" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV86" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW86" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="DX86" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="DY86" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="DZ86" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="EA86" t="inlineStr"/>
+      <c r="EB86" t="inlineStr"/>
+      <c r="EC86" t="inlineStr"/>
+      <c r="ED86" t="inlineStr"/>
+      <c r="EE86" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EF86" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="EG86" t="inlineStr">
+        <is>
+          <t>5.18</t>
+        </is>
+      </c>
+      <c r="EH86" t="inlineStr"/>
+      <c r="EI86" t="inlineStr"/>
+      <c r="EJ86" t="inlineStr"/>
+      <c r="EK86" t="inlineStr"/>
+      <c r="EL86" t="inlineStr"/>
+      <c r="EM86" t="inlineStr"/>
+      <c r="EN86" t="inlineStr"/>
+      <c r="EO86" t="inlineStr"/>
+      <c r="EP86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>11</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Al Taawon</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>46017.625</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>2</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>12</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>12</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>3</v>
+      </c>
+      <c r="R87" t="n">
+        <v>3</v>
+      </c>
+      <c r="S87" t="n">
+        <v>9</v>
+      </c>
+      <c r="T87" t="n">
+        <v>5</v>
+      </c>
+      <c r="U87" t="n">
+        <v>12</v>
+      </c>
+      <c r="V87" t="n">
+        <v>8</v>
+      </c>
+      <c r="W87" t="n">
+        <v>9</v>
+      </c>
+      <c r="X87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>5074</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>88</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK87" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN87" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV87" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW87" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX87" t="n">
+        <v>102</v>
+      </c>
+      <c r="BY87" t="n">
+        <v>71</v>
+      </c>
+      <c r="BZ87" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CA87" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="CB87" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR87" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS87" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU87" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV87" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX87" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY87" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ87" t="n">
+        <v>88</v>
+      </c>
+      <c r="DA87" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB87" t="n">
+        <v>88</v>
+      </c>
+      <c r="DC87" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD87" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DE87" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF87" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG87" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH87" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI87" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DJ87" t="n">
+        <v>13</v>
+      </c>
+      <c r="DK87" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL87" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DM87" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DN87" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="DO87" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP87" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ87" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV87" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW87" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="DX87" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="DY87" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="DZ87" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="EA87" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EB87" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EC87" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="ED87" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EE87" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EF87" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="EG87" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EH87" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="EI87" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EJ87" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EK87" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EL87" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EM87" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EN87" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EO87" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EP87" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>11</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>46017.72916666666</v>
+      </c>
+      <c r="G88" t="n">
+        <v>3</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2</v>
+      </c>
+      <c r="I88" t="n">
+        <v>5</v>
+      </c>
+      <c r="J88" t="n">
+        <v>7</v>
+      </c>
+      <c r="K88" t="n">
+        <v>3</v>
+      </c>
+      <c r="L88" t="n">
+        <v>10</v>
+      </c>
+      <c r="M88" t="n">
+        <v>2</v>
+      </c>
+      <c r="N88" t="n">
+        <v>3</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>11</v>
+      </c>
+      <c r="R88" t="n">
+        <v>5</v>
+      </c>
+      <c r="S88" t="n">
+        <v>7</v>
+      </c>
+      <c r="T88" t="n">
+        <v>7</v>
+      </c>
+      <c r="U88" t="n">
+        <v>18</v>
+      </c>
+      <c r="V88" t="n">
+        <v>12</v>
+      </c>
+      <c r="W88" t="n">
+        <v>12</v>
+      </c>
+      <c r="X88" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr"/>
+      <c r="AC88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>5066</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>80</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI88" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK88" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM88" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN88" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP88" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS88" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV88" t="n">
+        <v>63</v>
+      </c>
+      <c r="BW88" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX88" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY88" t="n">
+        <v>76</v>
+      </c>
+      <c r="BZ88" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CA88" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CB88" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="CC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR88" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS88" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU88" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV88" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX88" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY88" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ88" t="n">
+        <v>70</v>
+      </c>
+      <c r="DA88" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB88" t="n">
+        <v>60</v>
+      </c>
+      <c r="DC88" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD88" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DE88" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DF88" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DG88" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DH88" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DI88" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DJ88" t="n">
+        <v>30</v>
+      </c>
+      <c r="DK88" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL88" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="DM88" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DN88" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="DO88" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP88" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ88" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR88" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS88" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT88" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU88" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV88" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW88" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="DX88" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="DY88" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="DZ88" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="EA88" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EB88" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EC88" t="inlineStr"/>
+      <c r="ED88" t="inlineStr"/>
+      <c r="EE88" t="inlineStr">
+        <is>
+          <t>10.60</t>
+        </is>
+      </c>
+      <c r="EF88" t="inlineStr">
+        <is>
+          <t>7.92</t>
+        </is>
+      </c>
+      <c r="EG88" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EH88" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EI88" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EJ88" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="EK88" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EL88" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EM88" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EN88" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EO88" t="inlineStr"/>
+      <c r="EP88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>11</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Al Quadisiya</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Dhamk</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>46018.54166666666</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2</v>
+      </c>
+      <c r="J89" t="n">
+        <v>18</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>18</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1</v>
+      </c>
+      <c r="N89" t="n">
+        <v>4</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>6</v>
+      </c>
+      <c r="R89" t="n">
+        <v>3</v>
+      </c>
+      <c r="S89" t="n">
+        <v>9</v>
+      </c>
+      <c r="T89" t="n">
+        <v>3</v>
+      </c>
+      <c r="U89" t="n">
+        <v>15</v>
+      </c>
+      <c r="V89" t="n">
+        <v>6</v>
+      </c>
+      <c r="W89" t="n">
+        <v>14</v>
+      </c>
+      <c r="X89" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr"/>
+      <c r="AC89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF89" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI89" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK89" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM89" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN89" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR89" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT89" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV89" t="n">
+        <v>103</v>
+      </c>
+      <c r="BW89" t="n">
+        <v>16</v>
+      </c>
+      <c r="BX89" t="n">
+        <v>132</v>
+      </c>
+      <c r="BY89" t="n">
+        <v>53</v>
+      </c>
+      <c r="BZ89" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CA89" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="CB89" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM89" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP89" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR89" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS89" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU89" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV89" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW89" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX89" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY89" t="n">
+        <v>16</v>
+      </c>
+      <c r="CZ89" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA89" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB89" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC89" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD89" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DE89" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DF89" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DG89" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH89" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DI89" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DJ89" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK89" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL89" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DM89" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="DN89" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DO89" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP89" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ89" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR89" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS89" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT89" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU89" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV89" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW89" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="DX89" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="DY89" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="DZ89" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="EA89" t="inlineStr"/>
+      <c r="EB89" t="inlineStr"/>
+      <c r="EC89" t="inlineStr"/>
+      <c r="ED89" t="inlineStr"/>
+      <c r="EE89" t="inlineStr">
+        <is>
+          <t>10.56</t>
+        </is>
+      </c>
+      <c r="EF89" t="inlineStr">
+        <is>
+          <t>6.12</t>
+        </is>
+      </c>
+      <c r="EG89" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EH89" t="inlineStr"/>
+      <c r="EI89" t="inlineStr"/>
+      <c r="EJ89" t="inlineStr"/>
+      <c r="EK89" t="inlineStr"/>
+      <c r="EL89" t="inlineStr"/>
+      <c r="EM89" t="inlineStr"/>
+      <c r="EN89" t="inlineStr"/>
+      <c r="EO89" t="inlineStr"/>
+      <c r="EP89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>11</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Al Akhdoud</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>46018.61805555555</v>
+      </c>
+      <c r="G90" t="n">
+        <v>3</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>3</v>
+      </c>
+      <c r="J90" t="n">
+        <v>8</v>
+      </c>
+      <c r="K90" t="n">
+        <v>5</v>
+      </c>
+      <c r="L90" t="n">
+        <v>13</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>5</v>
+      </c>
+      <c r="R90" t="n">
+        <v>2</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="n">
+        <v>2</v>
+      </c>
+      <c r="U90" t="n">
+        <v>15</v>
+      </c>
+      <c r="V90" t="n">
+        <v>4</v>
+      </c>
+      <c r="W90" t="n">
+        <v>11</v>
+      </c>
+      <c r="X90" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>King Saud University Stadium</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
+        </is>
+      </c>
+      <c r="AC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AQ90" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB90" t="n">
+        <v>5069</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>53</v>
+      </c>
+      <c r="BE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF90" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI90" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ90" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM90" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN90" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV90" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW90" t="n">
+        <v>18</v>
+      </c>
+      <c r="BX90" t="n">
+        <v>82</v>
+      </c>
+      <c r="BY90" t="n">
+        <v>41</v>
+      </c>
+      <c r="BZ90" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CA90" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="CB90" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN90" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP90" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR90" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS90" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU90" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV90" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CY90" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ90" t="n">
+        <v>53</v>
+      </c>
+      <c r="DA90" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB90" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC90" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD90" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE90" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF90" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG90" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DH90" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI90" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DJ90" t="n">
+        <v>48</v>
+      </c>
+      <c r="DK90" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL90" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="DM90" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="DN90" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="DO90" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP90" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ90" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR90" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV90" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW90" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="DX90" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="DY90" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="DZ90" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="EA90" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EB90" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EC90" t="inlineStr"/>
+      <c r="ED90" t="inlineStr"/>
+      <c r="EE90" t="inlineStr">
+        <is>
+          <t>19.98</t>
+        </is>
+      </c>
+      <c r="EF90" t="inlineStr">
+        <is>
+          <t>13.02</t>
+        </is>
+      </c>
+      <c r="EG90" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="EH90" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EI90" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EJ90" t="inlineStr"/>
+      <c r="EK90" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EL90" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EM90" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EN90" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EO90" t="inlineStr"/>
+      <c r="EP90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>11</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Al Shabab</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>46018.72916666666</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>2</v>
+      </c>
+      <c r="J91" t="n">
+        <v>12</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="n">
+        <v>13</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>8</v>
+      </c>
+      <c r="R91" t="n">
+        <v>4</v>
+      </c>
+      <c r="S91" t="n">
+        <v>9</v>
+      </c>
+      <c r="T91" t="n">
+        <v>2</v>
+      </c>
+      <c r="U91" t="n">
+        <v>17</v>
+      </c>
+      <c r="V91" t="n">
+        <v>6</v>
+      </c>
+      <c r="W91" t="n">
+        <v>12</v>
+      </c>
+      <c r="X91" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>King Abdullah Sports City</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>, Jeddah</t>
+        </is>
+      </c>
+      <c r="AC91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ91" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR91" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AS91" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT91" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AU91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>5070</v>
+      </c>
+      <c r="BC91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD91" t="n">
+        <v>45</v>
+      </c>
+      <c r="BE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF91" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI91" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK91" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM91" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN91" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT91" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV91" t="n">
+        <v>95</v>
+      </c>
+      <c r="BW91" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX91" t="n">
+        <v>127</v>
+      </c>
+      <c r="BY91" t="n">
+        <v>72</v>
+      </c>
+      <c r="BZ91" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CA91" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CB91" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="CC91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP91" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR91" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS91" t="n">
+        <v>9</v>
+      </c>
+      <c r="CT91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU91" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV91" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW91" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX91" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY91" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ91" t="n">
+        <v>20</v>
+      </c>
+      <c r="DA91" t="n">
+        <v>65</v>
+      </c>
+      <c r="DB91" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC91" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD91" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE91" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DF91" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG91" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH91" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DI91" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DJ91" t="n">
+        <v>80</v>
+      </c>
+      <c r="DK91" t="n">
+        <v>35</v>
+      </c>
+      <c r="DL91" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM91" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="DN91" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="DO91" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP91" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ91" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV91" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW91" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="DX91" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="DY91" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="DZ91" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA91" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EB91" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EC91" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="ED91" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EE91" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="EF91" t="inlineStr">
+        <is>
+          <t>5.06</t>
+        </is>
+      </c>
+      <c r="EG91" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EH91" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EI91" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EJ91" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EK91" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EL91" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EM91" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EN91" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EO91" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EP91" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP91" headerRowCount="1">
-  <autoFilter ref="A1:EP91"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP94" headerRowCount="1">
+  <autoFilter ref="A1:EP94"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP91"/>
+  <dimension ref="A1:EP94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1797,7 +1797,7 @@
         <v>0.6</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -3670,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DE6" t="n">
         <v>3</v>
@@ -4775,156 +4775,156 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
         <v>45899.75</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" t="n">
         <v>4</v>
       </c>
-      <c r="J9" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>11</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>8</v>
-      </c>
-      <c r="R9" t="n">
-        <v>4</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
         <v>7</v>
       </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>15</v>
-      </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X9" t="n">
         <v>7</v>
       </c>
       <c r="Y9" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="Z9" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.44</v>
+        <v>5.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.75</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AM9" t="n">
         <v>1.47</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AO9" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AU9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA9" t="n">
         <v>4</v>
       </c>
-      <c r="AV9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2</v>
-      </c>
       <c r="BB9" t="n">
-        <v>5068</v>
+        <v>5070</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
@@ -4945,115 +4945,115 @@
         <v>1</v>
       </c>
       <c r="BI9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT9" t="n">
         <v>4</v>
       </c>
-      <c r="BJ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>59</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>63</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS9" t="n">
         <v>5</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>29</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>56</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>53</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>19</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>15</v>
       </c>
       <c r="CT9" t="n">
         <v>1</v>
@@ -5062,7 +5062,7 @@
         <v>7</v>
       </c>
       <c r="CV9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CW9" t="n">
         <v>1</v>
@@ -5071,7 +5071,7 @@
         <v>6</v>
       </c>
       <c r="CY9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="CZ9" t="n">
         <v>0</v>
@@ -5086,10 +5086,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.17</v>
+        <v>2</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5134,98 +5134,98 @@
         <v>1</v>
       </c>
       <c r="DT9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV9" t="b">
         <v>1</v>
       </c>
       <c r="DW9" t="n">
-        <v>42.17</v>
+        <v>36.63</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="DY9" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="DZ9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="EA9" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EB9" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
         <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EJ9" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM9" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EN9" t="inlineStr">
+        <is>
           <t>1.50</t>
-        </is>
-      </c>
-      <c r="EJ9" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="EK9" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EL9" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EM9" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EN9" t="inlineStr">
-        <is>
-          <t>1.63</t>
         </is>
       </c>
       <c r="EO9" t="inlineStr"/>
@@ -5247,156 +5247,156 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>45899.75</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>11</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
+      </c>
+      <c r="S10" t="n">
         <v>7</v>
       </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>7</v>
-      </c>
-      <c r="L10" t="n">
-        <v>10</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>10</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
-        <v>6</v>
-      </c>
       <c r="U10" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="V10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="W10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X10" t="n">
         <v>7</v>
       </c>
       <c r="Y10" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="Z10" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
-        <v>5.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF10" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.57</v>
+        <v>6.75</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AM10" t="n">
         <v>1.47</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AO10" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB10" t="n">
-        <v>5070</v>
+        <v>5068</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
@@ -5417,64 +5417,64 @@
         <v>1</v>
       </c>
       <c r="BI10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
         <v>5</v>
       </c>
-      <c r="BK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>7</v>
-      </c>
       <c r="BN10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BO10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP10" t="n">
         <v>0</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU10" t="n">
         <v>1</v>
       </c>
       <c r="BV10" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BW10" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="BX10" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="BY10" t="n">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.91</v>
+        <v>1.86</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.14</v>
+        <v>0.99</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
@@ -5501,10 +5501,10 @@
         <v>1</v>
       </c>
       <c r="CK10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
@@ -5522,10 +5522,10 @@
         <v>1</v>
       </c>
       <c r="CR10" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="CS10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="CT10" t="n">
         <v>1</v>
@@ -5534,7 +5534,7 @@
         <v>7</v>
       </c>
       <c r="CV10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CW10" t="n">
         <v>1</v>
@@ -5543,7 +5543,7 @@
         <v>6</v>
       </c>
       <c r="CY10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CZ10" t="n">
         <v>0</v>
@@ -5558,10 +5558,10 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="DE10" t="n">
-        <v>2</v>
+        <v>0.14</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5606,98 +5606,98 @@
         <v>1</v>
       </c>
       <c r="DT10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV10" t="b">
         <v>1</v>
       </c>
       <c r="DW10" t="n">
-        <v>36.63</v>
+        <v>42.17</v>
       </c>
       <c r="DX10" t="n">
-        <v>8.67</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DY10" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="DZ10" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA10" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EB10" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EC10" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="ED10" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>7.29</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>5.33</t>
+        </is>
+      </c>
+      <c r="EG10" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr">
+        <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="EE10" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EF10" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="EG10" t="inlineStr">
-        <is>
-          <t>4.83</t>
-        </is>
-      </c>
-      <c r="EH10" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="EI10" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
       <c r="EJ10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="EK10" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EL10" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EM10" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EN10" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EO10" t="inlineStr"/>
@@ -6489,7 +6489,7 @@
         <v>1</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6953,7 +6953,7 @@
         <v>1.5</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
         <v>50</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DE14" t="n">
         <v>1.2</v>
@@ -8798,10 +8798,10 @@
         <v>50</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
         <v>0.99</v>
       </c>
       <c r="DO17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -10658,7 +10658,7 @@
         <v>50</v>
       </c>
       <c r="DD21" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DE21" t="n">
         <v>1.4</v>
@@ -13025,7 +13025,7 @@
         <v>0.25</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="DF26" t="n">
         <v>0</v>
@@ -13055,7 +13055,7 @@
         <v>1.42</v>
       </c>
       <c r="DO26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP26" t="b">
         <v>0</v>
@@ -14430,7 +14430,7 @@
         <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DE29" t="n">
         <v>3</v>
@@ -14463,7 +14463,7 @@
         <v>2.82</v>
       </c>
       <c r="DO29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -17218,7 +17218,7 @@
         <v>100</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DE35" t="n">
         <v>2</v>
@@ -19117,7 +19117,7 @@
         <v>1.2</v>
       </c>
       <c r="DE39" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF39" t="n">
         <v>3</v>
@@ -20533,7 +20533,7 @@
         <v>0.8</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF42" t="n">
         <v>0</v>
@@ -21005,7 +21005,7 @@
         <v>3</v>
       </c>
       <c r="DE43" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="DF43" t="n">
         <v>3</v>
@@ -21466,7 +21466,7 @@
         <v>75</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DE44" t="n">
         <v>0.2</v>
@@ -21499,7 +21499,7 @@
         <v>2.13</v>
       </c>
       <c r="DO44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21930,7 +21930,7 @@
         <v>100</v>
       </c>
       <c r="DD45" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DE45" t="n">
         <v>0.6</v>
@@ -22858,7 +22858,7 @@
         <v>67</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DE47" t="n">
         <v>0.6</v>
@@ -27069,7 +27069,7 @@
         <v>0.6</v>
       </c>
       <c r="DE56" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="DF56" t="n">
         <v>0.33</v>
@@ -28497,7 +28497,7 @@
         <v>0.8</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF59" t="n">
         <v>0</v>
@@ -29441,7 +29441,7 @@
         <v>1.6</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF61" t="n">
         <v>1.33</v>
@@ -29918,7 +29918,7 @@
         <v>84</v>
       </c>
       <c r="DD62" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DE62" t="n">
         <v>1.4</v>
@@ -30398,7 +30398,7 @@
         <v>67</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DE63" t="n">
         <v>2</v>
@@ -31359,7 +31359,7 @@
         <v>2.02</v>
       </c>
       <c r="DO65" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32254,7 +32254,7 @@
         <v>100</v>
       </c>
       <c r="DD67" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DE67" t="n">
         <v>0.6</v>
@@ -33223,7 +33223,7 @@
         <v>2.68</v>
       </c>
       <c r="DO69" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -35553,7 +35553,7 @@
         <v>1.2</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF74" t="n">
         <v>2</v>
@@ -36961,7 +36961,7 @@
         <v>0.6</v>
       </c>
       <c r="DE77" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF77" t="n">
         <v>0.5</v>
@@ -37853,7 +37853,7 @@
         <v>2.67</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="DF79" t="n">
         <v>2.5</v>
@@ -38479,87 +38479,79 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
         <v>45984.72916666666</v>
       </c>
       <c r="G81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L81" t="n">
+        <v>9</v>
+      </c>
+      <c r="M81" t="n">
+        <v>3</v>
+      </c>
+      <c r="N81" t="n">
+        <v>3</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>2</v>
+      </c>
+      <c r="R81" t="n">
+        <v>2</v>
+      </c>
+      <c r="S81" t="n">
         <v>6</v>
       </c>
-      <c r="M81" t="n">
-        <v>3</v>
-      </c>
-      <c r="N81" t="n">
-        <v>1</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>10</v>
-      </c>
-      <c r="R81" t="n">
-        <v>5</v>
-      </c>
-      <c r="S81" t="n">
+      <c r="T81" t="n">
+        <v>13</v>
+      </c>
+      <c r="U81" t="n">
+        <v>8</v>
+      </c>
+      <c r="V81" t="n">
+        <v>15</v>
+      </c>
+      <c r="W81" t="n">
         <v>11</v>
       </c>
-      <c r="T81" t="n">
-        <v>7</v>
-      </c>
-      <c r="U81" t="n">
-        <v>21</v>
-      </c>
-      <c r="V81" t="n">
-        <v>12</v>
-      </c>
-      <c r="W81" t="n">
-        <v>15</v>
-      </c>
       <c r="X81" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y81" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="Z81" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>King Saud University Stadium</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
         <v>3</v>
       </c>
@@ -38567,82 +38559,82 @@
         <v>3</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.14</v>
+        <v>2.29</v>
       </c>
       <c r="AF81" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="AG81" t="n">
-        <v>12</v>
+        <v>2.65</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AI81" t="n">
-        <v>1.21</v>
+        <v>1.73</v>
       </c>
       <c r="AJ81" t="n">
-        <v>1.56</v>
+        <v>3</v>
       </c>
       <c r="AK81" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL81" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AM81" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AN81" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="AO81" t="n">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="AP81" t="n">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="AS81" t="n">
-        <v>5</v>
+        <v>2.91</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.99</v>
+        <v>1.42</v>
       </c>
       <c r="AU81" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW81" t="n">
         <v>0</v>
       </c>
       <c r="AX81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY81" t="n">
         <v>1</v>
       </c>
       <c r="AZ81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB81" t="n">
-        <v>5069</v>
+        <v>-1</v>
       </c>
       <c r="BC81" t="n">
         <v>0</v>
       </c>
       <c r="BD81" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="BE81" t="n">
         <v>0</v>
@@ -38657,10 +38649,10 @@
         <v>1</v>
       </c>
       <c r="BI81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK81" t="n">
         <v>2</v>
@@ -38669,7 +38661,7 @@
         <v>1</v>
       </c>
       <c r="BM81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN81" t="n">
         <v>3</v>
@@ -38684,49 +38676,49 @@
         <v>2</v>
       </c>
       <c r="BR81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS81" t="n">
         <v>2</v>
       </c>
       <c r="BT81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU81" t="n">
         <v>1</v>
       </c>
       <c r="BV81" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="BW81" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="BX81" t="n">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="BY81" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="BZ81" t="n">
-        <v>2.36</v>
+        <v>0.91</v>
       </c>
       <c r="CA81" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CB81" t="n">
-        <v>3.68</v>
+        <v>2.21</v>
       </c>
       <c r="CC81" t="n">
         <v>0</v>
       </c>
       <c r="CD81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE81" t="n">
         <v>0</v>
       </c>
       <c r="CF81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG81" t="n">
         <v>0</v>
@@ -38753,82 +38745,82 @@
         <v>0</v>
       </c>
       <c r="CO81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ81" t="n">
         <v>1</v>
       </c>
       <c r="CR81" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CS81" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="CT81" t="n">
         <v>1</v>
       </c>
       <c r="CU81" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV81" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX81" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY81" t="n">
         <v>8</v>
-      </c>
-      <c r="CV81" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX81" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY81" t="n">
-        <v>14</v>
       </c>
       <c r="CZ81" t="n">
         <v>75</v>
       </c>
       <c r="DA81" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="DB81" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="DC81" t="n">
         <v>88</v>
       </c>
       <c r="DD81" t="n">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="DF81" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="DG81" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="DH81" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="DI81" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="DJ81" t="n">
         <v>25</v>
       </c>
       <c r="DK81" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="DL81" t="n">
-        <v>2.59</v>
+        <v>1.2</v>
       </c>
       <c r="DM81" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="DN81" t="n">
-        <v>3.82</v>
+        <v>2.51</v>
       </c>
       <c r="DO81" t="n">
         <v>10</v>
@@ -38840,13 +38832,13 @@
         <v>1</v>
       </c>
       <c r="DR81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU81" t="b">
         <v>0</v>
@@ -38855,73 +38847,85 @@
         <v>1</v>
       </c>
       <c r="DW81" t="n">
-        <v>21.64</v>
+        <v>30.11</v>
       </c>
       <c r="DX81" t="n">
-        <v>4.03</v>
+        <v>4.86</v>
       </c>
       <c r="DY81" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="DZ81" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="EA81" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EB81" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="EA81" t="inlineStr"/>
+      <c r="EB81" t="inlineStr"/>
       <c r="EC81" t="inlineStr"/>
       <c r="ED81" t="inlineStr"/>
       <c r="EE81" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EF81" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EG81" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EH81" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EI81" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EJ81" t="inlineStr"/>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EJ81" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
       <c r="EK81" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EL81" t="inlineStr">
         <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="EM81" t="inlineStr"/>
-      <c r="EN81" t="inlineStr"/>
-      <c r="EO81" t="inlineStr"/>
-      <c r="EP81" t="inlineStr"/>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EM81" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EN81" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EO81" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EP81" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -38939,79 +38943,87 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
         <v>45984.72916666666</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H82" t="n">
         <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J82" t="n">
+        <v>4</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" t="n">
+        <v>6</v>
+      </c>
+      <c r="M82" t="n">
+        <v>3</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>10</v>
+      </c>
+      <c r="R82" t="n">
+        <v>5</v>
+      </c>
+      <c r="S82" t="n">
+        <v>11</v>
+      </c>
+      <c r="T82" t="n">
+        <v>7</v>
+      </c>
+      <c r="U82" t="n">
+        <v>21</v>
+      </c>
+      <c r="V82" t="n">
+        <v>12</v>
+      </c>
+      <c r="W82" t="n">
+        <v>15</v>
+      </c>
+      <c r="X82" t="n">
         <v>8</v>
       </c>
-      <c r="K82" t="n">
-        <v>1</v>
-      </c>
-      <c r="L82" t="n">
-        <v>9</v>
-      </c>
-      <c r="M82" t="n">
-        <v>3</v>
-      </c>
-      <c r="N82" t="n">
-        <v>3</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>2</v>
-      </c>
-      <c r="R82" t="n">
-        <v>2</v>
-      </c>
-      <c r="S82" t="n">
-        <v>6</v>
-      </c>
-      <c r="T82" t="n">
-        <v>13</v>
-      </c>
-      <c r="U82" t="n">
-        <v>8</v>
-      </c>
-      <c r="V82" t="n">
-        <v>15</v>
-      </c>
-      <c r="W82" t="n">
-        <v>11</v>
-      </c>
-      <c r="X82" t="n">
-        <v>16</v>
-      </c>
       <c r="Y82" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Z82" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA82" t="inlineStr"/>
-      <c r="AB82" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>King Saud University Stadium</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
+        </is>
+      </c>
       <c r="AC82" t="n">
         <v>3</v>
       </c>
@@ -39019,82 +39031,82 @@
         <v>3</v>
       </c>
       <c r="AE82" t="n">
-        <v>2.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF82" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="AG82" t="n">
-        <v>2.65</v>
+        <v>12</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="AI82" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR82" t="n">
         <v>1.73</v>
       </c>
-      <c r="AJ82" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK82" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL82" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM82" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AN82" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AO82" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AP82" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AQ82" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR82" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AS82" t="n">
-        <v>2.91</v>
+        <v>5</v>
       </c>
       <c r="AT82" t="n">
-        <v>1.42</v>
+        <v>1.99</v>
       </c>
       <c r="AU82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW82" t="n">
         <v>0</v>
       </c>
       <c r="AX82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY82" t="n">
         <v>1</v>
       </c>
       <c r="AZ82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB82" t="n">
-        <v>-1</v>
+        <v>5069</v>
       </c>
       <c r="BC82" t="n">
         <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="BE82" t="n">
         <v>0</v>
@@ -39109,10 +39121,10 @@
         <v>1</v>
       </c>
       <c r="BI82" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BJ82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK82" t="n">
         <v>2</v>
@@ -39121,7 +39133,7 @@
         <v>1</v>
       </c>
       <c r="BM82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BN82" t="n">
         <v>3</v>
@@ -39136,49 +39148,49 @@
         <v>2</v>
       </c>
       <c r="BR82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS82" t="n">
         <v>2</v>
       </c>
       <c r="BT82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU82" t="n">
         <v>1</v>
       </c>
       <c r="BV82" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="BW82" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BX82" t="n">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="BY82" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BZ82" t="n">
-        <v>0.91</v>
+        <v>2.36</v>
       </c>
       <c r="CA82" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CB82" t="n">
-        <v>2.21</v>
+        <v>3.68</v>
       </c>
       <c r="CC82" t="n">
         <v>0</v>
       </c>
       <c r="CD82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE82" t="n">
         <v>0</v>
       </c>
       <c r="CF82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG82" t="n">
         <v>0</v>
@@ -39205,82 +39217,82 @@
         <v>0</v>
       </c>
       <c r="CO82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ82" t="n">
         <v>1</v>
       </c>
       <c r="CR82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CS82" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CT82" t="n">
         <v>1</v>
       </c>
       <c r="CU82" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="CV82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="CW82" t="n">
         <v>1</v>
       </c>
       <c r="CX82" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="CY82" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="CZ82" t="n">
         <v>75</v>
       </c>
       <c r="DA82" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="DB82" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="DC82" t="n">
         <v>88</v>
       </c>
       <c r="DD82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DE82" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="DF82" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="DG82" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="DH82" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="DI82" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="DJ82" t="n">
         <v>25</v>
       </c>
       <c r="DK82" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="DL82" t="n">
-        <v>1.2</v>
+        <v>2.59</v>
       </c>
       <c r="DM82" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="DN82" t="n">
-        <v>2.51</v>
+        <v>3.82</v>
       </c>
       <c r="DO82" t="n">
         <v>10</v>
@@ -39292,13 +39304,13 @@
         <v>1</v>
       </c>
       <c r="DR82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU82" t="b">
         <v>0</v>
@@ -39307,85 +39319,73 @@
         <v>1</v>
       </c>
       <c r="DW82" t="n">
-        <v>30.11</v>
+        <v>21.64</v>
       </c>
       <c r="DX82" t="n">
-        <v>4.86</v>
+        <v>4.03</v>
       </c>
       <c r="DY82" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="DZ82" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="EA82" t="inlineStr"/>
-      <c r="EB82" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA82" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EB82" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
       <c r="EC82" t="inlineStr"/>
       <c r="ED82" t="inlineStr"/>
       <c r="EE82" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="EF82" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="EG82" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="EH82" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EI82" t="inlineStr">
         <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EJ82" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EJ82" t="inlineStr"/>
       <c r="EK82" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EL82" t="inlineStr">
         <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="EM82" t="inlineStr">
-        <is>
-          <t>2.71</t>
-        </is>
-      </c>
-      <c r="EN82" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EO82" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EP82" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EM82" t="inlineStr"/>
+      <c r="EN82" t="inlineStr"/>
+      <c r="EO82" t="inlineStr"/>
+      <c r="EP82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -39717,7 +39717,7 @@
         <v>1.2</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DF83" t="n">
         <v>1.25</v>
@@ -39883,143 +39883,143 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
         <v>46016.72916666666</v>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L84" t="n">
+        <v>4</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>2</v>
+      </c>
+      <c r="R84" t="n">
         <v>8</v>
       </c>
-      <c r="M84" t="n">
-        <v>1</v>
-      </c>
-      <c r="N84" t="n">
-        <v>3</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>5</v>
-      </c>
-      <c r="R84" t="n">
-        <v>2</v>
-      </c>
       <c r="S84" t="n">
+        <v>6</v>
+      </c>
+      <c r="T84" t="n">
         <v>7</v>
       </c>
-      <c r="T84" t="n">
+      <c r="U84" t="n">
         <v>8</v>
       </c>
-      <c r="U84" t="n">
-        <v>12</v>
-      </c>
       <c r="V84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W84" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X84" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y84" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="Z84" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>King Khalid Sport City Stadium</t>
+          <t>Prince Turki bin Abdul Aziz Stadium</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>, Tabouk</t>
+          <t>, Riyadh</t>
         </is>
       </c>
       <c r="AC84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.4</v>
+        <v>2.97</v>
       </c>
       <c r="AF84" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="AG84" t="n">
-        <v>10</v>
+        <v>2.22</v>
       </c>
       <c r="AH84" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI84" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="AJ84" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AK84" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AL84" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AM84" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AN84" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AO84" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR84" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AS84" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT84" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AU84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV84" t="n">
         <v>0</v>
@@ -40028,25 +40028,25 @@
         <v>0</v>
       </c>
       <c r="AX84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA84" t="n">
         <v>0</v>
       </c>
       <c r="BB84" t="n">
-        <v>5097</v>
+        <v>5065</v>
       </c>
       <c r="BC84" t="n">
         <v>0</v>
       </c>
       <c r="BD84" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="BE84" t="n">
         <v>0</v>
@@ -40061,178 +40061,178 @@
         <v>1</v>
       </c>
       <c r="BI84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN84" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS84" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV84" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW84" t="n">
+        <v>80</v>
+      </c>
+      <c r="BX84" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY84" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ84" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CA84" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CB84" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP84" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR84" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS84" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU84" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV84" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX84" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY84" t="n">
         <v>4</v>
       </c>
-      <c r="BJ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK84" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL84" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM84" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN84" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP84" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ84" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR84" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS84" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT84" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU84" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV84" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW84" t="n">
-        <v>37</v>
-      </c>
-      <c r="BX84" t="n">
-        <v>66</v>
-      </c>
-      <c r="BY84" t="n">
-        <v>64</v>
-      </c>
-      <c r="BZ84" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CA84" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB84" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="CC84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR84" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS84" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU84" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV84" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX84" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY84" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ84" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="DA84" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="DB84" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="DC84" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="DD84" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DE84" t="n">
         <v>1.4</v>
       </c>
-      <c r="DE84" t="n">
-        <v>0.17</v>
-      </c>
       <c r="DF84" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="DG84" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="DH84" t="n">
-        <v>1.56</v>
+        <v>0.89</v>
       </c>
       <c r="DI84" t="n">
-        <v>0.11</v>
+        <v>1.33</v>
       </c>
       <c r="DJ84" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="DK84" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="DL84" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="DM84" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="DN84" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="DO84" t="n">
         <v>10</v>
@@ -40244,7 +40244,7 @@
         <v>1</v>
       </c>
       <c r="DR84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS84" t="b">
         <v>0</v>
@@ -40256,94 +40256,50 @@
         <v>0</v>
       </c>
       <c r="DV84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW84" t="n">
-        <v>15.82</v>
+        <v>18.15</v>
       </c>
       <c r="DX84" t="n">
-        <v>3.69</v>
+        <v>4.4</v>
       </c>
       <c r="DY84" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="DZ84" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="EA84" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="EB84" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="EC84" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="ED84" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="EA84" t="inlineStr"/>
+      <c r="EB84" t="inlineStr"/>
+      <c r="EC84" t="inlineStr"/>
+      <c r="ED84" t="inlineStr"/>
       <c r="EE84" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EF84" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EG84" t="inlineStr">
         <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="EH84" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="EI84" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EJ84" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="EK84" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="EL84" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EM84" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="EN84" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="EH84" t="inlineStr"/>
+      <c r="EI84" t="inlineStr"/>
+      <c r="EJ84" t="inlineStr"/>
+      <c r="EK84" t="inlineStr"/>
+      <c r="EL84" t="inlineStr"/>
+      <c r="EM84" t="inlineStr"/>
+      <c r="EN84" t="inlineStr"/>
       <c r="EO84" t="inlineStr"/>
       <c r="EP84" t="inlineStr"/>
     </row>
@@ -40363,143 +40319,143 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
         <v>46016.72916666666</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L85" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M85" t="n">
         <v>1</v>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R85" t="n">
+        <v>2</v>
+      </c>
+      <c r="S85" t="n">
+        <v>7</v>
+      </c>
+      <c r="T85" t="n">
         <v>8</v>
       </c>
-      <c r="S85" t="n">
+      <c r="U85" t="n">
+        <v>12</v>
+      </c>
+      <c r="V85" t="n">
+        <v>10</v>
+      </c>
+      <c r="W85" t="n">
+        <v>12</v>
+      </c>
+      <c r="X85" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>King Khalid Sport City Stadium</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>, Tabouk</t>
+        </is>
+      </c>
+      <c r="AC85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF85" t="n">
         <v>6</v>
       </c>
-      <c r="T85" t="n">
-        <v>7</v>
-      </c>
-      <c r="U85" t="n">
-        <v>8</v>
-      </c>
-      <c r="V85" t="n">
-        <v>15</v>
-      </c>
-      <c r="W85" t="n">
-        <v>15</v>
-      </c>
-      <c r="X85" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>66</v>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>Prince Turki bin Abdul Aziz Stadium</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>, Riyadh</t>
-        </is>
-      </c>
-      <c r="AC85" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE85" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AF85" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AG85" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR85" t="n">
         <v>2.22</v>
       </c>
-      <c r="AH85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI85" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK85" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL85" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR85" t="n">
-        <v>0</v>
-      </c>
       <c r="AS85" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AU85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV85" t="n">
         <v>0</v>
@@ -40508,25 +40464,25 @@
         <v>0</v>
       </c>
       <c r="AX85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA85" t="n">
         <v>0</v>
       </c>
       <c r="BB85" t="n">
-        <v>5065</v>
+        <v>5097</v>
       </c>
       <c r="BC85" t="n">
         <v>0</v>
       </c>
       <c r="BD85" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="BE85" t="n">
         <v>0</v>
@@ -40541,7 +40497,7 @@
         <v>1</v>
       </c>
       <c r="BI85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ85" t="n">
         <v>0</v>
@@ -40550,16 +40506,16 @@
         <v>1</v>
       </c>
       <c r="BL85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BN85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP85" t="n">
         <v>1</v>
@@ -40568,49 +40524,49 @@
         <v>1</v>
       </c>
       <c r="BR85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU85" t="n">
         <v>1</v>
       </c>
       <c r="BV85" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="BW85" t="n">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="BX85" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="BY85" t="n">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="BZ85" t="n">
-        <v>0.88</v>
+        <v>1.39</v>
       </c>
       <c r="CA85" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="CB85" t="n">
-        <v>2.96</v>
+        <v>2.43</v>
       </c>
       <c r="CC85" t="n">
         <v>0</v>
       </c>
       <c r="CD85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE85" t="n">
         <v>0</v>
       </c>
       <c r="CF85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG85" t="n">
         <v>0</v>
@@ -40631,7 +40587,7 @@
         <v>0</v>
       </c>
       <c r="CM85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN85" t="n">
         <v>0</v>
@@ -40646,73 +40602,73 @@
         <v>1</v>
       </c>
       <c r="CR85" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS85" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU85" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV85" t="n">
         <v>11</v>
       </c>
-      <c r="CS85" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU85" t="n">
+      <c r="CW85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX85" t="n">
         <v>6</v>
       </c>
-      <c r="CV85" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX85" t="n">
-        <v>5</v>
-      </c>
       <c r="CY85" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="CZ85" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="DA85" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="DB85" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="DC85" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="DD85" t="n">
         <v>1.4</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.4</v>
+        <v>0.14</v>
       </c>
       <c r="DF85" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="DG85" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="DH85" t="n">
-        <v>0.89</v>
+        <v>1.56</v>
       </c>
       <c r="DI85" t="n">
-        <v>1.33</v>
+        <v>0.11</v>
       </c>
       <c r="DJ85" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="DK85" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="DL85" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="DM85" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="DN85" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="DO85" t="n">
         <v>10</v>
@@ -40724,7 +40680,7 @@
         <v>1</v>
       </c>
       <c r="DR85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS85" t="b">
         <v>0</v>
@@ -40736,50 +40692,94 @@
         <v>0</v>
       </c>
       <c r="DV85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW85" t="n">
-        <v>18.15</v>
+        <v>15.82</v>
       </c>
       <c r="DX85" t="n">
-        <v>4.4</v>
+        <v>3.69</v>
       </c>
       <c r="DY85" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="DZ85" t="inlineStr">
         <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="EA85" t="inlineStr"/>
-      <c r="EB85" t="inlineStr"/>
-      <c r="EC85" t="inlineStr"/>
-      <c r="ED85" t="inlineStr"/>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA85" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EB85" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EC85" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="ED85" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
       <c r="EE85" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="EF85" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="EG85" t="inlineStr">
         <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EH85" t="inlineStr"/>
-      <c r="EI85" t="inlineStr"/>
-      <c r="EJ85" t="inlineStr"/>
-      <c r="EK85" t="inlineStr"/>
-      <c r="EL85" t="inlineStr"/>
-      <c r="EM85" t="inlineStr"/>
-      <c r="EN85" t="inlineStr"/>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EH85" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EI85" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EJ85" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EK85" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EL85" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EM85" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EN85" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
       <c r="EO85" t="inlineStr"/>
       <c r="EP85" t="inlineStr"/>
     </row>
@@ -42227,13 +42227,13 @@
         <v>3</v>
       </c>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T89" t="n">
         <v>3</v>
       </c>
       <c r="U89" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V89" t="n">
         <v>6</v>
@@ -42400,13 +42400,13 @@
         <v>53</v>
       </c>
       <c r="BZ89" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="CA89" t="n">
         <v>0.71</v>
       </c>
       <c r="CB89" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="CC89" t="n">
         <v>0</v>
@@ -42667,10 +42667,10 @@
         <v>4</v>
       </c>
       <c r="W90" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X90" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y90" t="n">
         <v>65</v>
@@ -43117,7 +43117,7 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R91" t="n">
         <v>4</v>
@@ -43129,7 +43129,7 @@
         <v>2</v>
       </c>
       <c r="U91" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V91" t="n">
         <v>6</v>
@@ -43304,13 +43304,13 @@
         <v>72</v>
       </c>
       <c r="BZ91" t="n">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="CA91" t="n">
         <v>0.92</v>
       </c>
       <c r="CB91" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="CC91" t="n">
         <v>0</v>
@@ -43544,6 +43544,1422 @@
       <c r="EP91" t="inlineStr">
         <is>
           <t>3.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>12</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Al Fateh</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>46020.60763888889</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" t="n">
+        <v>5</v>
+      </c>
+      <c r="K92" t="n">
+        <v>5</v>
+      </c>
+      <c r="L92" t="n">
+        <v>10</v>
+      </c>
+      <c r="M92" t="n">
+        <v>2</v>
+      </c>
+      <c r="N92" t="n">
+        <v>4</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>4</v>
+      </c>
+      <c r="S92" t="n">
+        <v>9</v>
+      </c>
+      <c r="T92" t="n">
+        <v>8</v>
+      </c>
+      <c r="U92" t="n">
+        <v>9</v>
+      </c>
+      <c r="V92" t="n">
+        <v>12</v>
+      </c>
+      <c r="W92" t="n">
+        <v>7</v>
+      </c>
+      <c r="X92" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>67</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>33</v>
+      </c>
+      <c r="AA92" t="inlineStr"/>
+      <c r="AB92" t="inlineStr"/>
+      <c r="AC92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ92" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR92" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS92" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT92" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB92" t="n">
+        <v>5064</v>
+      </c>
+      <c r="BC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD92" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR92" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT92" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV92" t="n">
+        <v>57</v>
+      </c>
+      <c r="BW92" t="n">
+        <v>51</v>
+      </c>
+      <c r="BX92" t="n">
+        <v>19</v>
+      </c>
+      <c r="BY92" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ92" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CA92" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CB92" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="CC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR92" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS92" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU92" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV92" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX92" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY92" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ92" t="n">
+        <v>68</v>
+      </c>
+      <c r="DA92" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB92" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC92" t="n">
+        <v>68</v>
+      </c>
+      <c r="DD92" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DE92" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DF92" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG92" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DH92" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DI92" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DJ92" t="n">
+        <v>33</v>
+      </c>
+      <c r="DK92" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL92" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DM92" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DN92" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="DO92" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP92" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW92" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="DX92" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="DY92" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="DZ92" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA92" t="inlineStr"/>
+      <c r="EB92" t="inlineStr"/>
+      <c r="EC92" t="inlineStr"/>
+      <c r="ED92" t="inlineStr"/>
+      <c r="EE92" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="EF92" t="inlineStr">
+        <is>
+          <t>3.83</t>
+        </is>
+      </c>
+      <c r="EG92" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EH92" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EI92" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EJ92" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EK92" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EL92" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EM92" t="inlineStr"/>
+      <c r="EN92" t="inlineStr"/>
+      <c r="EO92" t="inlineStr"/>
+      <c r="EP92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>12</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Al Riyadh</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Al Hazm</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>46020.72916666666</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2</v>
+      </c>
+      <c r="I93" t="n">
+        <v>3</v>
+      </c>
+      <c r="J93" t="n">
+        <v>8</v>
+      </c>
+      <c r="K93" t="n">
+        <v>5</v>
+      </c>
+      <c r="L93" t="n">
+        <v>13</v>
+      </c>
+      <c r="M93" t="n">
+        <v>2</v>
+      </c>
+      <c r="N93" t="n">
+        <v>5</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>7</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7</v>
+      </c>
+      <c r="S93" t="n">
+        <v>12</v>
+      </c>
+      <c r="T93" t="n">
+        <v>3</v>
+      </c>
+      <c r="U93" t="n">
+        <v>19</v>
+      </c>
+      <c r="V93" t="n">
+        <v>10</v>
+      </c>
+      <c r="W93" t="n">
+        <v>8</v>
+      </c>
+      <c r="X93" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>Prince Turki bin Abdul Aziz Stadium</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>, Riyadh</t>
+        </is>
+      </c>
+      <c r="AC93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>5089</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>64</v>
+      </c>
+      <c r="BE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF93" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI93" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK93" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL93" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM93" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN93" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT93" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV93" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW93" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX93" t="n">
+        <v>105</v>
+      </c>
+      <c r="BY93" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ93" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CA93" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CB93" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="CC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM93" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR93" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS93" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU93" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV93" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX93" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY93" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ93" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA93" t="n">
+        <v>74</v>
+      </c>
+      <c r="DB93" t="n">
+        <v>37</v>
+      </c>
+      <c r="DC93" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD93" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DE93" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DF93" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DG93" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH93" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DI93" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ93" t="n">
+        <v>55</v>
+      </c>
+      <c r="DK93" t="n">
+        <v>27</v>
+      </c>
+      <c r="DL93" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DM93" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DN93" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DO93" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP93" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ93" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR93" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV93" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW93" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="DX93" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="DY93" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="DZ93" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA93" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EB93" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EC93" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="ED93" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EE93" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EF93" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EG93" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EH93" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="EI93" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EJ93" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EK93" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EL93" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EM93" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EN93" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EO93" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EP93" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>12</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Al Taawon</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Al Najma</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>46020.72916666666</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" t="n">
+        <v>10</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" t="n">
+        <v>11</v>
+      </c>
+      <c r="M94" t="n">
+        <v>3</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1</v>
+      </c>
+      <c r="S94" t="n">
+        <v>14</v>
+      </c>
+      <c r="T94" t="n">
+        <v>4</v>
+      </c>
+      <c r="U94" t="n">
+        <v>15</v>
+      </c>
+      <c r="V94" t="n">
+        <v>5</v>
+      </c>
+      <c r="W94" t="n">
+        <v>13</v>
+      </c>
+      <c r="X94" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr"/>
+      <c r="AC94" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>5074</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>72</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF94" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI94" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK94" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN94" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV94" t="n">
+        <v>63</v>
+      </c>
+      <c r="BW94" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX94" t="n">
+        <v>117</v>
+      </c>
+      <c r="BY94" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ94" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CA94" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="CB94" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR94" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS94" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU94" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV94" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX94" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY94" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ94" t="n">
+        <v>72</v>
+      </c>
+      <c r="DA94" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB94" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC94" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD94" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DE94" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DF94" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG94" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DH94" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DI94" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DJ94" t="n">
+        <v>29</v>
+      </c>
+      <c r="DK94" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL94" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DM94" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DN94" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DO94" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP94" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV94" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW94" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="DX94" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="DY94" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="DZ94" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA94" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EB94" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EC94" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="ED94" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EE94" t="inlineStr">
+        <is>
+          <t>6.63</t>
+        </is>
+      </c>
+      <c r="EF94" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="EG94" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EH94" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EI94" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EJ94" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EK94" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EL94" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EM94" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EN94" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EO94" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EP94" t="inlineStr">
+        <is>
+          <t>3.28</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP94" headerRowCount="1">
-  <autoFilter ref="A1:EP94"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP100" headerRowCount="1">
+  <autoFilter ref="A1:EP100"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP94"/>
+  <dimension ref="A1:EP100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="DE3" t="n">
         <v>2</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DE4" t="n">
         <v>0.6</v>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3673,7 +3673,7 @@
         <v>2.17</v>
       </c>
       <c r="DE6" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4142,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DE7" t="n">
         <v>1.17</v>
@@ -4175,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4609,7 +4609,7 @@
         <v>1.2</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5086,10 +5086,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DE9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6030,7 +6030,7 @@
         <v>50</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DE11" t="n">
         <v>2</v>
@@ -6063,7 +6063,7 @@
         <v>0.93</v>
       </c>
       <c r="DO11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP11" t="b">
         <v>0</v>
@@ -6486,7 +6486,7 @@
         <v>50</v>
       </c>
       <c r="DD12" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DE12" t="n">
         <v>1.71</v>
@@ -6519,7 +6519,7 @@
         <v>2.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6983,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7409,7 +7409,7 @@
         <v>1.4</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7439,7 +7439,7 @@
         <v>0.87</v>
       </c>
       <c r="DO14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7870,7 +7870,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DE15" t="n">
         <v>3</v>
@@ -7903,7 +7903,7 @@
         <v>0.91</v>
       </c>
       <c r="DO15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8337,7 +8337,7 @@
         <v>2.67</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DF16" t="n">
         <v>3</v>
@@ -8367,7 +8367,7 @@
         <v>1.8</v>
       </c>
       <c r="DO16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -9295,7 +9295,7 @@
         <v>2.11</v>
       </c>
       <c r="DO18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9751,7 +9751,7 @@
         <v>1.18</v>
       </c>
       <c r="DO19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -9867,70 +9867,70 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
         <v>45918.65277777778</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
+        <v>7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>5</v>
       </c>
-      <c r="L20" t="n">
-        <v>8</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
+        <v>10</v>
+      </c>
+      <c r="U20" t="n">
         <v>11</v>
       </c>
-      <c r="U20" t="n">
-        <v>10</v>
-      </c>
       <c r="V20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="X20" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y20" t="n">
         <v>45</v>
@@ -9941,82 +9941,82 @@
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AK20" t="n">
         <v>1.72</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.01</v>
+        <v>1.56</v>
       </c>
       <c r="AN20" t="n">
-        <v>3.22</v>
+        <v>2.2</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AU20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV20" t="n">
         <v>1</v>
       </c>
       <c r="AW20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BA20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB20" t="n">
-        <v>5125</v>
+        <v>5074</v>
       </c>
       <c r="BC20" t="n">
         <v>0</v>
@@ -10037,19 +10037,19 @@
         <v>1</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ20" t="n">
         <v>2</v>
       </c>
       <c r="BK20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BM20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN20" t="n">
         <v>6</v>
@@ -10058,55 +10058,55 @@
         <v>1</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BU20" t="n">
         <v>1</v>
       </c>
       <c r="BV20" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BW20" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="BX20" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="BY20" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="CB20" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="CC20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG20" t="n">
         <v>0</v>
@@ -10121,7 +10121,7 @@
         <v>1</v>
       </c>
       <c r="CK20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL20" t="n">
         <v>0</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="CN20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO20" t="n">
         <v>0</v>
@@ -10142,46 +10142,46 @@
         <v>1</v>
       </c>
       <c r="CR20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CS20" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="CT20" t="n">
         <v>1</v>
       </c>
       <c r="CU20" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="CV20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CW20" t="n">
         <v>1</v>
       </c>
       <c r="CX20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CY20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CZ20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DB20" t="n">
         <v>0</v>
       </c>
       <c r="DC20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.2</v>
+        <v>2.17</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="DF20" t="n">
         <v>0</v>
@@ -10190,10 +10190,10 @@
         <v>0</v>
       </c>
       <c r="DH20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DJ20" t="n">
         <v>0</v>
@@ -10202,16 +10202,16 @@
         <v>0</v>
       </c>
       <c r="DL20" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="DM20" t="n">
         <v>0</v>
       </c>
       <c r="DN20" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="DO20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10223,10 +10223,10 @@
         <v>1</v>
       </c>
       <c r="DS20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU20" t="b">
         <v>0</v>
@@ -10252,72 +10252,72 @@
       </c>
       <c r="EA20" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EB20" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EC20" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="ED20" t="inlineStr">
         <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EE20" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EF20" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EG20" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EH20" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EI20" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EJ20" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EK20" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EL20" t="inlineStr">
+        <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="EE20" t="inlineStr">
-        <is>
-          <t>2.98</t>
-        </is>
-      </c>
-      <c r="EF20" t="inlineStr">
-        <is>
-          <t>3.41</t>
-        </is>
-      </c>
-      <c r="EG20" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EH20" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="EI20" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EJ20" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EK20" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EL20" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
       <c r="EM20" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EN20" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EO20" t="inlineStr">
@@ -10347,70 +10347,70 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
         <v>45918.65277777778</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
         <v>5</v>
       </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
+        <v>8</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" t="n">
         <v>7</v>
       </c>
-      <c r="L21" t="n">
-        <v>9</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>6</v>
-      </c>
       <c r="T21" t="n">
+        <v>11</v>
+      </c>
+      <c r="U21" t="n">
         <v>10</v>
       </c>
-      <c r="U21" t="n">
-        <v>11</v>
-      </c>
       <c r="V21" t="n">
+        <v>13</v>
+      </c>
+      <c r="W21" t="n">
         <v>14</v>
       </c>
-      <c r="W21" t="n">
-        <v>12</v>
-      </c>
       <c r="X21" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="n">
         <v>45</v>
@@ -10421,82 +10421,82 @@
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AI21" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="AK21" t="n">
         <v>1.72</v>
       </c>
       <c r="AL21" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.56</v>
+        <v>2.01</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.2</v>
+        <v>3.22</v>
       </c>
       <c r="AO21" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.96</v>
+        <v>1.48</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AU21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BA21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB21" t="n">
-        <v>5074</v>
+        <v>5125</v>
       </c>
       <c r="BC21" t="n">
         <v>0</v>
@@ -10517,19 +10517,19 @@
         <v>1</v>
       </c>
       <c r="BI21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ21" t="n">
         <v>2</v>
       </c>
       <c r="BK21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BM21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BN21" t="n">
         <v>6</v>
@@ -10538,55 +10538,55 @@
         <v>1</v>
       </c>
       <c r="BP21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BU21" t="n">
         <v>1</v>
       </c>
       <c r="BV21" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BW21" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="BX21" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="BY21" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="CB21" t="n">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="CC21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG21" t="n">
         <v>0</v>
@@ -10601,7 +10601,7 @@
         <v>1</v>
       </c>
       <c r="CK21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL21" t="n">
         <v>0</v>
@@ -10610,7 +10610,7 @@
         <v>0</v>
       </c>
       <c r="CN21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO21" t="n">
         <v>0</v>
@@ -10622,46 +10622,46 @@
         <v>1</v>
       </c>
       <c r="CR21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CS21" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="CT21" t="n">
         <v>1</v>
       </c>
       <c r="CU21" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV21" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX21" t="n">
         <v>8</v>
       </c>
-      <c r="CV21" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW21" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX21" t="n">
-        <v>6</v>
-      </c>
       <c r="CY21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CZ21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DB21" t="n">
         <v>0</v>
       </c>
       <c r="DC21" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DD21" t="n">
-        <v>2.17</v>
+        <v>1</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10670,10 +10670,10 @@
         <v>0</v>
       </c>
       <c r="DH21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DI21" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="DJ21" t="n">
         <v>0</v>
@@ -10682,16 +10682,16 @@
         <v>0</v>
       </c>
       <c r="DL21" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="DM21" t="n">
         <v>0</v>
       </c>
       <c r="DN21" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="DO21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10703,10 +10703,10 @@
         <v>1</v>
       </c>
       <c r="DS21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU21" t="b">
         <v>0</v>
@@ -10732,42 +10732,42 @@
       </c>
       <c r="EA21" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="EB21" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EC21" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="ED21" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EE21" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="EF21" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EG21" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EH21" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EI21" t="inlineStr">
@@ -10777,27 +10777,27 @@
       </c>
       <c r="EJ21" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EK21" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EL21" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EM21" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EN21" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EO21" t="inlineStr">
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DE22" t="n">
         <v>0.2</v>
@@ -11171,7 +11171,7 @@
         <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11639,7 +11639,7 @@
         <v>3.01</v>
       </c>
       <c r="DO23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12111,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="DO24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP24" t="b">
         <v>0</v>
@@ -12566,10 +12566,10 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="DE25" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="DF25" t="n">
         <v>3</v>
@@ -12599,7 +12599,7 @@
         <v>1.06</v>
       </c>
       <c r="DO25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12711,12 +12711,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -12726,120 +12726,120 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L26" t="n">
+        <v>11</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="n">
         <v>8</v>
       </c>
-      <c r="M26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>11</v>
-      </c>
       <c r="U26" t="n">
+        <v>13</v>
+      </c>
+      <c r="V26" t="n">
         <v>9</v>
       </c>
-      <c r="V26" t="n">
-        <v>15</v>
-      </c>
       <c r="W26" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="X26" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Y26" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="Z26" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="n">
-        <v>3.6</v>
+        <v>4.35</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.45</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.49</v>
+        <v>2.19</v>
       </c>
       <c r="AO26" t="n">
-        <v>3.14</v>
+        <v>2.3</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AS26" t="n">
         <v>3.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV26" t="n">
         <v>0</v>
@@ -12851,16 +12851,16 @@
         <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA26" t="n">
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>-1</v>
+        <v>5070</v>
       </c>
       <c r="BC26" t="n">
         <v>0</v>
@@ -12875,70 +12875,70 @@
         <v>-1</v>
       </c>
       <c r="BG26" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH26" t="n">
         <v>1</v>
       </c>
       <c r="BI26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BK26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL26" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BM26" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BN26" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BO26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ26" t="n">
         <v>1</v>
       </c>
       <c r="BR26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS26" t="n">
         <v>1</v>
       </c>
       <c r="BT26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU26" t="n">
         <v>1</v>
       </c>
       <c r="BV26" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="BW26" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="BX26" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="BY26" t="n">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.55</v>
+        <v>1.16</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="CC26" t="n">
         <v>0</v>
@@ -12971,10 +12971,10 @@
         <v>0</v>
       </c>
       <c r="CM26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CN26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO26" t="n">
         <v>0</v>
@@ -12986,25 +12986,25 @@
         <v>1</v>
       </c>
       <c r="CR26" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS26" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU26" t="n">
         <v>19</v>
       </c>
-      <c r="CS26" t="n">
-        <v>20</v>
-      </c>
-      <c r="CT26" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU26" t="n">
-        <v>12</v>
-      </c>
       <c r="CV26" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="CW26" t="n">
         <v>1</v>
       </c>
       <c r="CX26" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="CY26" t="n">
         <v>8</v>
@@ -13022,22 +13022,22 @@
         <v>50</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.83</v>
+        <v>2.2</v>
       </c>
       <c r="DF26" t="n">
         <v>0</v>
       </c>
       <c r="DG26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="DI26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DJ26" t="n">
         <v>0</v>
@@ -13049,16 +13049,16 @@
         <v>0</v>
       </c>
       <c r="DM26" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="DN26" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="DO26" t="n">
         <v>11</v>
       </c>
       <c r="DP26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ26" t="b">
         <v>0</v>
@@ -13096,58 +13096,74 @@
       </c>
       <c r="EA26" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EB26" t="inlineStr">
         <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="EC26" t="inlineStr"/>
-      <c r="ED26" t="inlineStr"/>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EC26" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="ED26" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
       <c r="EE26" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EF26" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="EG26" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="EH26" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EI26" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EJ26" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="EK26" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EL26" t="inlineStr">
         <is>
-          <t>2.58</t>
-        </is>
-      </c>
-      <c r="EM26" t="inlineStr"/>
-      <c r="EN26" t="inlineStr"/>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EM26" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EN26" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="EO26" t="inlineStr"/>
       <c r="EP26" t="inlineStr"/>
     </row>
@@ -13167,12 +13183,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -13182,120 +13198,120 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L27" t="n">
         <v>8</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="n">
         <v>11</v>
       </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="n">
-        <v>8</v>
-      </c>
       <c r="U27" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W27" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="X27" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Y27" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="Z27" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="AF27" t="n">
-        <v>4.35</v>
+        <v>3.6</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.31</v>
+        <v>2.45</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AM27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN27" t="n">
         <v>1.49</v>
       </c>
-      <c r="AN27" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AO27" t="n">
-        <v>2.3</v>
+        <v>3.14</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AS27" t="n">
         <v>3.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AU27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
         <v>0</v>
@@ -13307,16 +13323,16 @@
         <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>5070</v>
+        <v>-1</v>
       </c>
       <c r="BC27" t="n">
         <v>0</v>
@@ -13331,70 +13347,70 @@
         <v>-1</v>
       </c>
       <c r="BG27" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH27" t="n">
         <v>1</v>
       </c>
       <c r="BI27" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BJ27" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK27" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL27" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BM27" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BN27" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BO27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ27" t="n">
         <v>1</v>
       </c>
       <c r="BR27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS27" t="n">
         <v>1</v>
       </c>
       <c r="BT27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU27" t="n">
         <v>1</v>
       </c>
       <c r="BV27" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="BW27" t="n">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="BX27" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="BY27" t="n">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.16</v>
+        <v>1.55</v>
       </c>
       <c r="CB27" t="n">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="CC27" t="n">
         <v>0</v>
@@ -13427,10 +13443,10 @@
         <v>0</v>
       </c>
       <c r="CM27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO27" t="n">
         <v>0</v>
@@ -13442,25 +13458,25 @@
         <v>1</v>
       </c>
       <c r="CR27" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="CS27" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="CT27" t="n">
         <v>1</v>
       </c>
       <c r="CU27" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CV27" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="CW27" t="n">
         <v>1</v>
       </c>
       <c r="CX27" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="CY27" t="n">
         <v>8</v>
@@ -13478,22 +13494,22 @@
         <v>50</v>
       </c>
       <c r="DD27" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DE27" t="n">
-        <v>2</v>
+        <v>0.83</v>
       </c>
       <c r="DF27" t="n">
         <v>0</v>
       </c>
       <c r="DG27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DI27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DJ27" t="n">
         <v>0</v>
@@ -13505,16 +13521,16 @@
         <v>0</v>
       </c>
       <c r="DM27" t="n">
-        <v>2.14</v>
+        <v>1.42</v>
       </c>
       <c r="DN27" t="n">
-        <v>2.14</v>
+        <v>1.42</v>
       </c>
       <c r="DO27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ27" t="b">
         <v>0</v>
@@ -13552,74 +13568,58 @@
       </c>
       <c r="EA27" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EB27" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EC27" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="ED27" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EC27" t="inlineStr"/>
+      <c r="ED27" t="inlineStr"/>
       <c r="EE27" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EF27" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="EG27" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="EH27" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EI27" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EJ27" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EK27" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EL27" t="inlineStr">
         <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="EM27" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EN27" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EM27" t="inlineStr"/>
+      <c r="EN27" t="inlineStr"/>
       <c r="EO27" t="inlineStr"/>
       <c r="EP27" t="inlineStr"/>
     </row>
@@ -13991,7 +13991,7 @@
         <v>3.72</v>
       </c>
       <c r="DO28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14910,7 +14910,7 @@
         <v>50</v>
       </c>
       <c r="DD30" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DE30" t="n">
         <v>0.6</v>
@@ -14943,7 +14943,7 @@
         <v>2.34</v>
       </c>
       <c r="DO30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15399,7 +15399,7 @@
         <v>2.97</v>
       </c>
       <c r="DO31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15855,7 +15855,7 @@
         <v>2.93</v>
       </c>
       <c r="DO32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16311,7 +16311,7 @@
         <v>2.59</v>
       </c>
       <c r="DO33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16741,7 +16741,7 @@
         <v>1.5</v>
       </c>
       <c r="DE34" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="DF34" t="n">
         <v>3</v>
@@ -16771,7 +16771,7 @@
         <v>4.3</v>
       </c>
       <c r="DO34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17251,7 +17251,7 @@
         <v>2.37</v>
       </c>
       <c r="DO35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17701,7 +17701,7 @@
         <v>0</v>
       </c>
       <c r="DE36" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF36" t="n">
         <v>0</v>
@@ -17731,7 +17731,7 @@
         <v>2.25</v>
       </c>
       <c r="DO36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18173,7 +18173,7 @@
         <v>1.2</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DF37" t="n">
         <v>0</v>
@@ -18203,7 +18203,7 @@
         <v>2.65</v>
       </c>
       <c r="DO37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18645,7 +18645,7 @@
         <v>1.2</v>
       </c>
       <c r="DE38" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -18675,7 +18675,7 @@
         <v>2.44</v>
       </c>
       <c r="DO38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19114,7 +19114,7 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DE39" t="n">
         <v>0.14</v>
@@ -19147,7 +19147,7 @@
         <v>2.02</v>
       </c>
       <c r="DO39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19602,7 +19602,7 @@
         <v>50</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="DE40" t="n">
         <v>0.6</v>
@@ -19635,7 +19635,7 @@
         <v>2.66</v>
       </c>
       <c r="DO40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20074,10 +20074,10 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DE41" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="DF41" t="n">
         <v>2</v>
@@ -20107,7 +20107,7 @@
         <v>2</v>
       </c>
       <c r="DO41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20530,7 +20530,7 @@
         <v>50</v>
       </c>
       <c r="DD42" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DE42" t="n">
         <v>1.71</v>
@@ -20563,7 +20563,7 @@
         <v>1.63</v>
       </c>
       <c r="DO42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21035,7 +21035,7 @@
         <v>4.22</v>
       </c>
       <c r="DO43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21933,7 +21933,7 @@
         <v>2.17</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="DF45" t="n">
         <v>1.5</v>
@@ -21963,7 +21963,7 @@
         <v>2.14</v>
       </c>
       <c r="DO45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22394,10 +22394,10 @@
         <v>75</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DF46" t="n">
         <v>3</v>
@@ -22427,7 +22427,7 @@
         <v>2.57</v>
       </c>
       <c r="DO46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22891,7 +22891,7 @@
         <v>1.84</v>
       </c>
       <c r="DO47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23371,7 +23371,7 @@
         <v>1.94</v>
       </c>
       <c r="DO48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23851,7 +23851,7 @@
         <v>2.9</v>
       </c>
       <c r="DO49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24331,7 +24331,7 @@
         <v>2.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24770,7 +24770,7 @@
         <v>100</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DE51" t="n">
         <v>1.17</v>
@@ -24803,7 +24803,7 @@
         <v>2.84</v>
       </c>
       <c r="DO51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25241,7 +25241,7 @@
         <v>1.5</v>
       </c>
       <c r="DE52" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="DF52" t="n">
         <v>1.5</v>
@@ -25271,7 +25271,7 @@
         <v>3.18</v>
       </c>
       <c r="DO52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25735,7 +25735,7 @@
         <v>2.21</v>
       </c>
       <c r="DO53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP53" t="b">
         <v>0</v>
@@ -26146,10 +26146,10 @@
         <v>67</v>
       </c>
       <c r="DD54" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="DF54" t="n">
         <v>1</v>
@@ -26179,7 +26179,7 @@
         <v>2.64</v>
       </c>
       <c r="DO54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26597,7 +26597,7 @@
         <v>0.25</v>
       </c>
       <c r="DE55" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="DF55" t="n">
         <v>0.5</v>
@@ -26627,7 +26627,7 @@
         <v>3.19</v>
       </c>
       <c r="DO55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27099,7 +27099,7 @@
         <v>2.65</v>
       </c>
       <c r="DO56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27546,7 +27546,7 @@
         <v>100</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="DE57" t="n">
         <v>0.2</v>
@@ -27579,7 +27579,7 @@
         <v>2.85</v>
       </c>
       <c r="DO57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28014,7 +28014,7 @@
         <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DE58" t="n">
         <v>2</v>
@@ -28047,7 +28047,7 @@
         <v>2.85</v>
       </c>
       <c r="DO58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28494,7 +28494,7 @@
         <v>100</v>
       </c>
       <c r="DD59" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DE59" t="n">
         <v>0.14</v>
@@ -28527,7 +28527,7 @@
         <v>2.02</v>
       </c>
       <c r="DO59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29007,7 +29007,7 @@
         <v>3.38</v>
       </c>
       <c r="DO60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29438,7 +29438,7 @@
         <v>50</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DE61" t="n">
         <v>1.71</v>
@@ -29471,7 +29471,7 @@
         <v>1.4</v>
       </c>
       <c r="DO61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29921,7 +29921,7 @@
         <v>2.17</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DF62" t="n">
         <v>2</v>
@@ -29951,7 +29951,7 @@
         <v>2.42</v>
       </c>
       <c r="DO62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30401,7 +30401,7 @@
         <v>1.4</v>
       </c>
       <c r="DE63" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="DF63" t="n">
         <v>2</v>
@@ -30431,7 +30431,7 @@
         <v>3.33</v>
       </c>
       <c r="DO63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30873,7 +30873,7 @@
         <v>3</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF64" t="n">
         <v>3</v>
@@ -30903,7 +30903,7 @@
         <v>3.73</v>
       </c>
       <c r="DO64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31823,7 +31823,7 @@
         <v>2.65</v>
       </c>
       <c r="DO66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32257,7 +32257,7 @@
         <v>1.17</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="DF67" t="n">
         <v>2</v>
@@ -32287,7 +32287,7 @@
         <v>2.17</v>
       </c>
       <c r="DO67" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32751,7 +32751,7 @@
         <v>1.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33657,7 +33657,7 @@
         <v>0</v>
       </c>
       <c r="DE70" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="DF70" t="n">
         <v>0</v>
@@ -33687,7 +33687,7 @@
         <v>2.5</v>
       </c>
       <c r="DO70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34118,10 +34118,10 @@
         <v>100</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="DE71" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="DF71" t="n">
         <v>1.33</v>
@@ -34151,7 +34151,7 @@
         <v>3.72</v>
       </c>
       <c r="DO71" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34590,7 +34590,7 @@
         <v>75</v>
       </c>
       <c r="DD72" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DE72" t="n">
         <v>1.4</v>
@@ -34623,7 +34623,7 @@
         <v>2.76</v>
       </c>
       <c r="DO72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35111,7 +35111,7 @@
         <v>3.05</v>
       </c>
       <c r="DO73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35550,7 +35550,7 @@
         <v>75</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DE74" t="n">
         <v>1.71</v>
@@ -35583,7 +35583,7 @@
         <v>2.12</v>
       </c>
       <c r="DO74" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36055,7 +36055,7 @@
         <v>2.45</v>
       </c>
       <c r="DO75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36502,10 +36502,10 @@
         <v>63</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DF76" t="n">
         <v>1.5</v>
@@ -36535,7 +36535,7 @@
         <v>3.13</v>
       </c>
       <c r="DO76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36991,7 +36991,7 @@
         <v>2.28</v>
       </c>
       <c r="DO77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -37422,10 +37422,10 @@
         <v>75</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DF78" t="n">
         <v>1.25</v>
@@ -37455,7 +37455,7 @@
         <v>1.69</v>
       </c>
       <c r="DO78" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37883,7 +37883,7 @@
         <v>3.63</v>
       </c>
       <c r="DO79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -38310,7 +38310,7 @@
         <v>84</v>
       </c>
       <c r="DD80" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DE80" t="n">
         <v>0.6</v>
@@ -38343,7 +38343,7 @@
         <v>2.38</v>
       </c>
       <c r="DO80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38823,7 +38823,7 @@
         <v>2.51</v>
       </c>
       <c r="DO81" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -39295,7 +39295,7 @@
         <v>3.82</v>
       </c>
       <c r="DO82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39747,7 +39747,7 @@
         <v>2.19</v>
       </c>
       <c r="DO83" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP83" t="b">
         <v>0</v>
@@ -39883,143 +39883,143 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
         <v>46016.72916666666</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L84" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M84" t="n">
         <v>1</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R84" t="n">
+        <v>2</v>
+      </c>
+      <c r="S84" t="n">
+        <v>7</v>
+      </c>
+      <c r="T84" t="n">
         <v>8</v>
       </c>
-      <c r="S84" t="n">
+      <c r="U84" t="n">
+        <v>12</v>
+      </c>
+      <c r="V84" t="n">
+        <v>10</v>
+      </c>
+      <c r="W84" t="n">
+        <v>12</v>
+      </c>
+      <c r="X84" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>King Khalid Sport City Stadium</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>, Tabouk</t>
+        </is>
+      </c>
+      <c r="AC84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF84" t="n">
         <v>6</v>
       </c>
-      <c r="T84" t="n">
-        <v>7</v>
-      </c>
-      <c r="U84" t="n">
-        <v>8</v>
-      </c>
-      <c r="V84" t="n">
-        <v>15</v>
-      </c>
-      <c r="W84" t="n">
-        <v>15</v>
-      </c>
-      <c r="X84" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>66</v>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>Prince Turki bin Abdul Aziz Stadium</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>, Riyadh</t>
-        </is>
-      </c>
-      <c r="AC84" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AF84" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AG84" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR84" t="n">
         <v>2.22</v>
       </c>
-      <c r="AH84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI84" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK84" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL84" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR84" t="n">
-        <v>0</v>
-      </c>
       <c r="AS84" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AU84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV84" t="n">
         <v>0</v>
@@ -40028,25 +40028,25 @@
         <v>0</v>
       </c>
       <c r="AX84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA84" t="n">
         <v>0</v>
       </c>
       <c r="BB84" t="n">
-        <v>5065</v>
+        <v>5097</v>
       </c>
       <c r="BC84" t="n">
         <v>0</v>
       </c>
       <c r="BD84" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="BE84" t="n">
         <v>0</v>
@@ -40061,7 +40061,7 @@
         <v>1</v>
       </c>
       <c r="BI84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ84" t="n">
         <v>0</v>
@@ -40070,16 +40070,16 @@
         <v>1</v>
       </c>
       <c r="BL84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BN84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP84" t="n">
         <v>1</v>
@@ -40088,49 +40088,49 @@
         <v>1</v>
       </c>
       <c r="BR84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU84" t="n">
         <v>1</v>
       </c>
       <c r="BV84" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="BW84" t="n">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="BX84" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="BY84" t="n">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="BZ84" t="n">
-        <v>0.88</v>
+        <v>1.39</v>
       </c>
       <c r="CA84" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="CB84" t="n">
-        <v>2.96</v>
+        <v>2.43</v>
       </c>
       <c r="CC84" t="n">
         <v>0</v>
       </c>
       <c r="CD84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE84" t="n">
         <v>0</v>
       </c>
       <c r="CF84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG84" t="n">
         <v>0</v>
@@ -40151,7 +40151,7 @@
         <v>0</v>
       </c>
       <c r="CM84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN84" t="n">
         <v>0</v>
@@ -40166,76 +40166,76 @@
         <v>1</v>
       </c>
       <c r="CR84" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS84" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU84" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV84" t="n">
         <v>11</v>
       </c>
-      <c r="CS84" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU84" t="n">
+      <c r="CW84" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX84" t="n">
         <v>6</v>
       </c>
-      <c r="CV84" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW84" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX84" t="n">
-        <v>5</v>
-      </c>
       <c r="CY84" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="CZ84" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="DA84" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="DB84" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="DC84" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="DD84" t="n">
         <v>1.17</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.4</v>
+        <v>0.14</v>
       </c>
       <c r="DF84" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="DG84" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="DH84" t="n">
-        <v>0.89</v>
+        <v>1.56</v>
       </c>
       <c r="DI84" t="n">
-        <v>1.33</v>
+        <v>0.11</v>
       </c>
       <c r="DJ84" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="DK84" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="DL84" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="DM84" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="DN84" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="DO84" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40244,7 +40244,7 @@
         <v>1</v>
       </c>
       <c r="DR84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS84" t="b">
         <v>0</v>
@@ -40256,50 +40256,94 @@
         <v>0</v>
       </c>
       <c r="DV84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW84" t="n">
-        <v>18.15</v>
+        <v>15.82</v>
       </c>
       <c r="DX84" t="n">
-        <v>4.4</v>
+        <v>3.69</v>
       </c>
       <c r="DY84" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="DZ84" t="inlineStr">
         <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="EA84" t="inlineStr"/>
-      <c r="EB84" t="inlineStr"/>
-      <c r="EC84" t="inlineStr"/>
-      <c r="ED84" t="inlineStr"/>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA84" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EB84" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EC84" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="ED84" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
       <c r="EE84" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="EF84" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="EG84" t="inlineStr">
         <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EH84" t="inlineStr"/>
-      <c r="EI84" t="inlineStr"/>
-      <c r="EJ84" t="inlineStr"/>
-      <c r="EK84" t="inlineStr"/>
-      <c r="EL84" t="inlineStr"/>
-      <c r="EM84" t="inlineStr"/>
-      <c r="EN84" t="inlineStr"/>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EH84" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EI84" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EJ84" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EK84" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EL84" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EM84" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EN84" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
       <c r="EO84" t="inlineStr"/>
       <c r="EP84" t="inlineStr"/>
     </row>
@@ -40319,143 +40363,143 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
         <v>46016.72916666666</v>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L85" t="n">
+        <v>4</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1</v>
+      </c>
+      <c r="N85" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>2</v>
+      </c>
+      <c r="R85" t="n">
         <v>8</v>
       </c>
-      <c r="M85" t="n">
-        <v>1</v>
-      </c>
-      <c r="N85" t="n">
-        <v>3</v>
-      </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>5</v>
-      </c>
-      <c r="R85" t="n">
-        <v>2</v>
-      </c>
       <c r="S85" t="n">
+        <v>6</v>
+      </c>
+      <c r="T85" t="n">
         <v>7</v>
       </c>
-      <c r="T85" t="n">
+      <c r="U85" t="n">
         <v>8</v>
       </c>
-      <c r="U85" t="n">
-        <v>12</v>
-      </c>
       <c r="V85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W85" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X85" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y85" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="Z85" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>King Khalid Sport City Stadium</t>
+          <t>Prince Turki bin Abdul Aziz Stadium</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>, Tabouk</t>
+          <t>, Riyadh</t>
         </is>
       </c>
       <c r="AC85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.4</v>
+        <v>2.97</v>
       </c>
       <c r="AF85" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="AG85" t="n">
-        <v>10</v>
+        <v>2.22</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI85" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="AJ85" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AK85" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AL85" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AM85" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AN85" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AO85" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AR85" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AS85" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT85" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AU85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV85" t="n">
         <v>0</v>
@@ -40464,25 +40508,25 @@
         <v>0</v>
       </c>
       <c r="AX85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA85" t="n">
         <v>0</v>
       </c>
       <c r="BB85" t="n">
-        <v>5097</v>
+        <v>5065</v>
       </c>
       <c r="BC85" t="n">
         <v>0</v>
       </c>
       <c r="BD85" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="BE85" t="n">
         <v>0</v>
@@ -40497,182 +40541,182 @@
         <v>1</v>
       </c>
       <c r="BI85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS85" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV85" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW85" t="n">
+        <v>80</v>
+      </c>
+      <c r="BX85" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY85" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ85" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CA85" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CB85" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP85" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR85" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS85" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU85" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV85" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX85" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY85" t="n">
         <v>4</v>
       </c>
-      <c r="BJ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL85" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM85" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN85" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR85" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT85" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV85" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW85" t="n">
-        <v>37</v>
-      </c>
-      <c r="BX85" t="n">
-        <v>66</v>
-      </c>
-      <c r="BY85" t="n">
-        <v>64</v>
-      </c>
-      <c r="BZ85" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CA85" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB85" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="CC85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR85" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS85" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU85" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV85" t="n">
+      <c r="CZ85" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA85" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB85" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC85" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD85" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DE85" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF85" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG85" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH85" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DI85" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DJ85" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK85" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL85" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DM85" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DN85" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DO85" t="n">
         <v>11</v>
       </c>
-      <c r="CW85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX85" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY85" t="n">
-        <v>9</v>
-      </c>
-      <c r="CZ85" t="n">
-        <v>65</v>
-      </c>
-      <c r="DA85" t="n">
-        <v>78</v>
-      </c>
-      <c r="DB85" t="n">
-        <v>55</v>
-      </c>
-      <c r="DC85" t="n">
-        <v>78</v>
-      </c>
-      <c r="DD85" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DE85" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DF85" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG85" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DH85" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="DI85" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DJ85" t="n">
-        <v>35</v>
-      </c>
-      <c r="DK85" t="n">
-        <v>23</v>
-      </c>
-      <c r="DL85" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="DM85" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="DN85" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="DO85" t="n">
-        <v>10</v>
-      </c>
       <c r="DP85" t="b">
         <v>1</v>
       </c>
@@ -40680,7 +40724,7 @@
         <v>1</v>
       </c>
       <c r="DR85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS85" t="b">
         <v>0</v>
@@ -40692,94 +40736,50 @@
         <v>0</v>
       </c>
       <c r="DV85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW85" t="n">
-        <v>15.82</v>
+        <v>18.15</v>
       </c>
       <c r="DX85" t="n">
-        <v>3.69</v>
+        <v>4.4</v>
       </c>
       <c r="DY85" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="DZ85" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="EA85" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="EB85" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="EC85" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="ED85" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="EA85" t="inlineStr"/>
+      <c r="EB85" t="inlineStr"/>
+      <c r="EC85" t="inlineStr"/>
+      <c r="ED85" t="inlineStr"/>
       <c r="EE85" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EF85" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EG85" t="inlineStr">
         <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="EH85" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="EI85" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EJ85" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="EK85" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="EL85" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EM85" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="EN85" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="EH85" t="inlineStr"/>
+      <c r="EI85" t="inlineStr"/>
+      <c r="EJ85" t="inlineStr"/>
+      <c r="EK85" t="inlineStr"/>
+      <c r="EL85" t="inlineStr"/>
+      <c r="EM85" t="inlineStr"/>
+      <c r="EN85" t="inlineStr"/>
       <c r="EO85" t="inlineStr"/>
       <c r="EP85" t="inlineStr"/>
     </row>
@@ -41151,7 +41151,7 @@
         <v>3.42</v>
       </c>
       <c r="DO86" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41546,7 +41546,7 @@
         <v>88</v>
       </c>
       <c r="DD87" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DE87" t="n">
         <v>3</v>
@@ -41579,7 +41579,7 @@
         <v>2.81</v>
       </c>
       <c r="DO87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -42059,7 +42059,7 @@
         <v>3.44</v>
       </c>
       <c r="DO88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42493,7 +42493,7 @@
         <v>2.2</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="DF89" t="n">
         <v>2.5</v>
@@ -42523,7 +42523,7 @@
         <v>2.71</v>
       </c>
       <c r="DO89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42959,7 +42959,7 @@
         <v>3.16</v>
       </c>
       <c r="DO90" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -43427,7 +43427,7 @@
         <v>2.54</v>
       </c>
       <c r="DO91" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44062,13 +44062,13 @@
         <v>12</v>
       </c>
       <c r="T93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U93" t="n">
         <v>19</v>
       </c>
       <c r="V93" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W93" t="n">
         <v>8</v>
@@ -44243,10 +44243,10 @@
         <v>2.01</v>
       </c>
       <c r="CA93" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="CB93" t="n">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="CC93" t="n">
         <v>0</v>
@@ -44565,10 +44565,10 @@
         <v>11</v>
       </c>
       <c r="Y94" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Z94" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA94" t="inlineStr"/>
       <c r="AB94" t="inlineStr"/>
@@ -44962,6 +44962,2718 @@
           <t>3.28</t>
         </is>
       </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>12</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Al Feiha</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>46021.64583333334</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>2</v>
+      </c>
+      <c r="J95" t="n">
+        <v>4</v>
+      </c>
+      <c r="K95" t="n">
+        <v>3</v>
+      </c>
+      <c r="L95" t="n">
+        <v>7</v>
+      </c>
+      <c r="M95" t="n">
+        <v>4</v>
+      </c>
+      <c r="N95" t="n">
+        <v>1</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>4</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="n">
+        <v>7</v>
+      </c>
+      <c r="U95" t="n">
+        <v>9</v>
+      </c>
+      <c r="V95" t="n">
+        <v>8</v>
+      </c>
+      <c r="W95" t="n">
+        <v>11</v>
+      </c>
+      <c r="X95" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>63</v>
+      </c>
+      <c r="AA95" t="inlineStr"/>
+      <c r="AB95" t="inlineStr"/>
+      <c r="AC95" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ95" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AT95" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AU95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>5062</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>80</v>
+      </c>
+      <c r="BE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK95" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN95" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ95" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT95" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV95" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW95" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX95" t="n">
+        <v>61</v>
+      </c>
+      <c r="BY95" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ95" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CA95" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="CB95" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR95" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS95" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU95" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV95" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX95" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY95" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ95" t="n">
+        <v>70</v>
+      </c>
+      <c r="DA95" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB95" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC95" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD95" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE95" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF95" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DG95" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DH95" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DI95" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DJ95" t="n">
+        <v>30</v>
+      </c>
+      <c r="DK95" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL95" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DM95" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DN95" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="DO95" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW95" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="DX95" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="DY95" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="DZ95" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA95" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EB95" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EC95" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="ED95" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EE95" t="inlineStr">
+        <is>
+          <t>5.60</t>
+        </is>
+      </c>
+      <c r="EF95" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="EG95" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EH95" t="inlineStr"/>
+      <c r="EI95" t="inlineStr"/>
+      <c r="EJ95" t="inlineStr"/>
+      <c r="EK95" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EL95" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EM95" t="inlineStr"/>
+      <c r="EN95" t="inlineStr"/>
+      <c r="EO95" t="inlineStr"/>
+      <c r="EP95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>12</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Al Akhdoud</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Dhamk</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>46021.72916666666</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" t="n">
+        <v>8</v>
+      </c>
+      <c r="K96" t="n">
+        <v>5</v>
+      </c>
+      <c r="L96" t="n">
+        <v>13</v>
+      </c>
+      <c r="M96" t="n">
+        <v>2</v>
+      </c>
+      <c r="N96" t="n">
+        <v>1</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>4</v>
+      </c>
+      <c r="R96" t="n">
+        <v>3</v>
+      </c>
+      <c r="S96" t="n">
+        <v>8</v>
+      </c>
+      <c r="T96" t="n">
+        <v>3</v>
+      </c>
+      <c r="U96" t="n">
+        <v>12</v>
+      </c>
+      <c r="V96" t="n">
+        <v>6</v>
+      </c>
+      <c r="W96" t="n">
+        <v>7</v>
+      </c>
+      <c r="X96" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr"/>
+      <c r="AC96" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>5083</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF96" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK96" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM96" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN96" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV96" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW96" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX96" t="n">
+        <v>120</v>
+      </c>
+      <c r="BY96" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ96" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CA96" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="CB96" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR96" t="n">
+        <v>37</v>
+      </c>
+      <c r="CS96" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU96" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV96" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX96" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY96" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ96" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA96" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB96" t="n">
+        <v>80</v>
+      </c>
+      <c r="DC96" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD96" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DE96" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF96" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DG96" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DH96" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI96" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DJ96" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK96" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL96" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DM96" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DN96" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DO96" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP96" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW96" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="DX96" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="DY96" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="DZ96" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="EA96" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EB96" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EC96" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="ED96" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EE96" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF96" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EG96" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EH96" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="EI96" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EJ96" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EK96" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EL96" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EM96" t="inlineStr"/>
+      <c r="EN96" t="inlineStr"/>
+      <c r="EO96" t="inlineStr"/>
+      <c r="EP96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>12</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Al Ittifaq</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>46021.72916666666</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2</v>
+      </c>
+      <c r="I97" t="n">
+        <v>4</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" t="n">
+        <v>16</v>
+      </c>
+      <c r="L97" t="n">
+        <v>17</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1</v>
+      </c>
+      <c r="N97" t="n">
+        <v>2</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>4</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7</v>
+      </c>
+      <c r="S97" t="n">
+        <v>2</v>
+      </c>
+      <c r="T97" t="n">
+        <v>19</v>
+      </c>
+      <c r="U97" t="n">
+        <v>6</v>
+      </c>
+      <c r="V97" t="n">
+        <v>26</v>
+      </c>
+      <c r="W97" t="n">
+        <v>7</v>
+      </c>
+      <c r="X97" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
+      <c r="AC97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ97" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR97" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS97" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT97" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AU97" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ97" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB97" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF97" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ97" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL97" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM97" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN97" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS97" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV97" t="n">
+        <v>12</v>
+      </c>
+      <c r="BW97" t="n">
+        <v>124</v>
+      </c>
+      <c r="BX97" t="n">
+        <v>59</v>
+      </c>
+      <c r="BY97" t="n">
+        <v>125</v>
+      </c>
+      <c r="BZ97" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CA97" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CB97" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="CC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP97" t="n">
+        <v>2</v>
+      </c>
+      <c r="CQ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR97" t="n">
+        <v>8</v>
+      </c>
+      <c r="CS97" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU97" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV97" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX97" t="n">
+        <v>20</v>
+      </c>
+      <c r="CY97" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ97" t="n">
+        <v>65</v>
+      </c>
+      <c r="DA97" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB97" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC97" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD97" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE97" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DF97" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DG97" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH97" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI97" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ97" t="n">
+        <v>35</v>
+      </c>
+      <c r="DK97" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL97" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DM97" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="DN97" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="DO97" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP97" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ97" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR97" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS97" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT97" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU97" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV97" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW97" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="DX97" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="DY97" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="DZ97" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA97" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EB97" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EC97" t="inlineStr"/>
+      <c r="ED97" t="inlineStr"/>
+      <c r="EE97" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EF97" t="inlineStr">
+        <is>
+          <t>6.36</t>
+        </is>
+      </c>
+      <c r="EG97" t="inlineStr">
+        <is>
+          <t>7.66</t>
+        </is>
+      </c>
+      <c r="EH97" t="inlineStr"/>
+      <c r="EI97" t="inlineStr"/>
+      <c r="EJ97" t="inlineStr"/>
+      <c r="EK97" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EL97" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EM97" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EN97" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EO97" t="inlineStr"/>
+      <c r="EP97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>12</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Neom SC</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>46022.64236111111</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" t="n">
+        <v>3</v>
+      </c>
+      <c r="I98" t="n">
+        <v>4</v>
+      </c>
+      <c r="J98" t="n">
+        <v>5</v>
+      </c>
+      <c r="K98" t="n">
+        <v>4</v>
+      </c>
+      <c r="L98" t="n">
+        <v>9</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>3</v>
+      </c>
+      <c r="R98" t="n">
+        <v>4</v>
+      </c>
+      <c r="S98" t="n">
+        <v>11</v>
+      </c>
+      <c r="T98" t="n">
+        <v>7</v>
+      </c>
+      <c r="U98" t="n">
+        <v>14</v>
+      </c>
+      <c r="V98" t="n">
+        <v>11</v>
+      </c>
+      <c r="W98" t="n">
+        <v>11</v>
+      </c>
+      <c r="X98" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
+      <c r="AC98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ98" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR98" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AT98" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AU98" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB98" t="n">
+        <v>5070</v>
+      </c>
+      <c r="BC98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD98" t="n">
+        <v>78</v>
+      </c>
+      <c r="BE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ98" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK98" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM98" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN98" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV98" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW98" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX98" t="n">
+        <v>93</v>
+      </c>
+      <c r="BY98" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ98" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CA98" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CB98" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="CC98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR98" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS98" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU98" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV98" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX98" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY98" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ98" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA98" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB98" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC98" t="n">
+        <v>68</v>
+      </c>
+      <c r="DD98" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DE98" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DF98" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DG98" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH98" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DI98" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DJ98" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK98" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL98" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DM98" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DN98" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="DO98" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW98" t="inlineStr"/>
+      <c r="DX98" t="inlineStr"/>
+      <c r="DY98" t="inlineStr"/>
+      <c r="DZ98" t="inlineStr"/>
+      <c r="EA98" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EB98" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EC98" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="ED98" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EE98" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EF98" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="EG98" t="inlineStr">
+        <is>
+          <t>4.34</t>
+        </is>
+      </c>
+      <c r="EH98" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EI98" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EJ98" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EK98" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EL98" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EM98" t="inlineStr"/>
+      <c r="EN98" t="inlineStr"/>
+      <c r="EO98" t="inlineStr"/>
+      <c r="EP98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>12</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>46022.72916666666</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" t="n">
+        <v>3</v>
+      </c>
+      <c r="I99" t="n">
+        <v>4</v>
+      </c>
+      <c r="J99" t="n">
+        <v>2</v>
+      </c>
+      <c r="K99" t="n">
+        <v>10</v>
+      </c>
+      <c r="L99" t="n">
+        <v>12</v>
+      </c>
+      <c r="M99" t="n">
+        <v>2</v>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" t="n">
+        <v>1</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>4</v>
+      </c>
+      <c r="R99" t="n">
+        <v>10</v>
+      </c>
+      <c r="S99" t="n">
+        <v>7</v>
+      </c>
+      <c r="T99" t="n">
+        <v>14</v>
+      </c>
+      <c r="U99" t="n">
+        <v>11</v>
+      </c>
+      <c r="V99" t="n">
+        <v>24</v>
+      </c>
+      <c r="W99" t="n">
+        <v>11</v>
+      </c>
+      <c r="X99" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>64</v>
+      </c>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AT99" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AU99" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB99" t="n">
+        <v>5066</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL99" t="n">
+        <v>8</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV99" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW99" t="n">
+        <v>68</v>
+      </c>
+      <c r="BX99" t="n">
+        <v>57</v>
+      </c>
+      <c r="BY99" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ99" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CA99" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="CB99" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="CC99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR99" t="n">
+        <v>6</v>
+      </c>
+      <c r="CS99" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU99" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV99" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX99" t="n">
+        <v>16</v>
+      </c>
+      <c r="CY99" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ99" t="n">
+        <v>78</v>
+      </c>
+      <c r="DA99" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB99" t="n">
+        <v>78</v>
+      </c>
+      <c r="DC99" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD99" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE99" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DF99" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG99" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DH99" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DI99" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DJ99" t="n">
+        <v>23</v>
+      </c>
+      <c r="DK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL99" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DM99" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DN99" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="DO99" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP99" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ99" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR99" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS99" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV99" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW99" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="DX99" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="DY99" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="DZ99" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA99" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EB99" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EC99" t="inlineStr"/>
+      <c r="ED99" t="inlineStr"/>
+      <c r="EE99" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EF99" t="inlineStr">
+        <is>
+          <t>6.79</t>
+        </is>
+      </c>
+      <c r="EG99" t="inlineStr">
+        <is>
+          <t>8.72</t>
+        </is>
+      </c>
+      <c r="EH99" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EI99" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EJ99" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="EK99" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EL99" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EM99" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EN99" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EO99" t="inlineStr"/>
+      <c r="EP99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>12</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Al Shabab</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Al Quadisiya</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>46022.72916666666</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2</v>
+      </c>
+      <c r="H100" t="n">
+        <v>3</v>
+      </c>
+      <c r="I100" t="n">
+        <v>5</v>
+      </c>
+      <c r="J100" t="n">
+        <v>6</v>
+      </c>
+      <c r="K100" t="n">
+        <v>6</v>
+      </c>
+      <c r="L100" t="n">
+        <v>12</v>
+      </c>
+      <c r="M100" t="n">
+        <v>4</v>
+      </c>
+      <c r="N100" t="n">
+        <v>1</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>6</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6</v>
+      </c>
+      <c r="S100" t="n">
+        <v>8</v>
+      </c>
+      <c r="T100" t="n">
+        <v>5</v>
+      </c>
+      <c r="U100" t="n">
+        <v>14</v>
+      </c>
+      <c r="V100" t="n">
+        <v>11</v>
+      </c>
+      <c r="W100" t="n">
+        <v>9</v>
+      </c>
+      <c r="X100" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
+      <c r="AC100" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU100" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB100" t="n">
+        <v>5068</v>
+      </c>
+      <c r="BC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD100" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF100" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK100" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV100" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW100" t="n">
+        <v>61</v>
+      </c>
+      <c r="BX100" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY100" t="n">
+        <v>116</v>
+      </c>
+      <c r="BZ100" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CC100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR100" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS100" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU100" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV100" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX100" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY100" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ100" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA100" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB100" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC100" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD100" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DE100" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DF100" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG100" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DH100" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DI100" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DJ100" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK100" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL100" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DM100" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DN100" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="DO100" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP100" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ100" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR100" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS100" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT100" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV100" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW100" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="DX100" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="DY100" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="DZ100" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA100" t="inlineStr"/>
+      <c r="EB100" t="inlineStr"/>
+      <c r="EC100" t="inlineStr"/>
+      <c r="ED100" t="inlineStr"/>
+      <c r="EE100" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EF100" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
+      </c>
+      <c r="EG100" t="inlineStr">
+        <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="EH100" t="inlineStr"/>
+      <c r="EI100" t="inlineStr"/>
+      <c r="EJ100" t="inlineStr"/>
+      <c r="EK100" t="inlineStr"/>
+      <c r="EL100" t="inlineStr"/>
+      <c r="EM100" t="inlineStr"/>
+      <c r="EN100" t="inlineStr"/>
+      <c r="EO100" t="inlineStr"/>
+      <c r="EP100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP100" headerRowCount="1">
-  <autoFilter ref="A1:EP100"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP106" headerRowCount="1">
+  <autoFilter ref="A1:EP106"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP100"/>
+  <dimension ref="A1:EP106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DE3" t="n">
         <v>2</v>
@@ -2746,10 +2746,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3673,7 +3673,7 @@
         <v>2.17</v>
       </c>
       <c r="DE6" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4145,7 +4145,7 @@
         <v>0.83</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4175,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DE8" t="n">
         <v>1</v>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -6030,7 +6030,7 @@
         <v>50</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE11" t="n">
         <v>2</v>
@@ -6063,7 +6063,7 @@
         <v>0.93</v>
       </c>
       <c r="DO11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP11" t="b">
         <v>0</v>
@@ -6950,7 +6950,7 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE13" t="n">
         <v>0.83</v>
@@ -6983,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7439,7 +7439,7 @@
         <v>0.87</v>
       </c>
       <c r="DO14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7873,7 +7873,7 @@
         <v>0.67</v>
       </c>
       <c r="DE15" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -7903,7 +7903,7 @@
         <v>0.91</v>
       </c>
       <c r="DO15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -9721,7 +9721,7 @@
         <v>3</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -9751,7 +9751,7 @@
         <v>1.18</v>
       </c>
       <c r="DO19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10211,7 +10211,7 @@
         <v>0.44</v>
       </c>
       <c r="DO20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -11141,7 +11141,7 @@
         <v>1.17</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11609,7 +11609,7 @@
         <v>2.2</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DF23" t="n">
         <v>3</v>
@@ -12078,10 +12078,10 @@
         <v>0</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -12111,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="DO24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP24" t="b">
         <v>0</v>
@@ -12566,7 +12566,7 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DE25" t="n">
         <v>2.6</v>
@@ -13022,7 +13022,7 @@
         <v>50</v>
       </c>
       <c r="DD26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DE26" t="n">
         <v>2.2</v>
@@ -13055,7 +13055,7 @@
         <v>2.14</v>
       </c>
       <c r="DO26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -14433,7 +14433,7 @@
         <v>1.4</v>
       </c>
       <c r="DE29" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -14463,7 +14463,7 @@
         <v>2.82</v>
       </c>
       <c r="DO29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14913,7 +14913,7 @@
         <v>0.83</v>
       </c>
       <c r="DE30" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="DF30" t="n">
         <v>1.5</v>
@@ -14943,7 +14943,7 @@
         <v>2.34</v>
       </c>
       <c r="DO30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15369,7 +15369,7 @@
         <v>2.67</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF31" t="n">
         <v>2</v>
@@ -16738,10 +16738,10 @@
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE34" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="DF34" t="n">
         <v>3</v>
@@ -16771,7 +16771,7 @@
         <v>4.3</v>
       </c>
       <c r="DO34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17698,7 +17698,7 @@
         <v>50</v>
       </c>
       <c r="DD36" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DE36" t="n">
         <v>1</v>
@@ -17731,7 +17731,7 @@
         <v>2.25</v>
       </c>
       <c r="DO36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18170,7 +18170,7 @@
         <v>100</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DE37" t="n">
         <v>1.67</v>
@@ -18642,7 +18642,7 @@
         <v>25</v>
       </c>
       <c r="DD38" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DE38" t="n">
         <v>2.2</v>
@@ -18675,7 +18675,7 @@
         <v>2.44</v>
       </c>
       <c r="DO38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19147,7 +19147,7 @@
         <v>2.02</v>
       </c>
       <c r="DO39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19602,10 +19602,10 @@
         <v>50</v>
       </c>
       <c r="DD40" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DF40" t="n">
         <v>2</v>
@@ -19635,7 +19635,7 @@
         <v>2.66</v>
       </c>
       <c r="DO40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20074,7 +20074,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE41" t="n">
         <v>2.6</v>
@@ -21035,7 +21035,7 @@
         <v>4.22</v>
       </c>
       <c r="DO43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -22861,7 +22861,7 @@
         <v>1.17</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="DF47" t="n">
         <v>1.5</v>
@@ -23338,10 +23338,10 @@
         <v>50</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DE48" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="DF48" t="n">
         <v>1</v>
@@ -23371,7 +23371,7 @@
         <v>1.94</v>
       </c>
       <c r="DO48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23818,7 +23818,7 @@
         <v>0</v>
       </c>
       <c r="DD49" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DE49" t="n">
         <v>2</v>
@@ -23851,7 +23851,7 @@
         <v>2.9</v>
       </c>
       <c r="DO49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24298,7 +24298,7 @@
         <v>75</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DE50" t="n">
         <v>1.4</v>
@@ -24331,7 +24331,7 @@
         <v>2.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24773,7 +24773,7 @@
         <v>1.17</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DF51" t="n">
         <v>1.5</v>
@@ -25238,7 +25238,7 @@
         <v>100</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE52" t="n">
         <v>2.6</v>
@@ -25705,7 +25705,7 @@
         <v>2.2</v>
       </c>
       <c r="DE53" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF53" t="n">
         <v>3</v>
@@ -26597,7 +26597,7 @@
         <v>0.25</v>
       </c>
       <c r="DE55" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="DF55" t="n">
         <v>0.5</v>
@@ -27227,149 +27227,141 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
         <v>45960.72916666666</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J57" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K57" t="n">
+        <v>2</v>
+      </c>
+      <c r="L57" t="n">
+        <v>6</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
         <v>4</v>
       </c>
-      <c r="L57" t="n">
-        <v>13</v>
-      </c>
-      <c r="M57" t="n">
-        <v>2</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
+        <v>4</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
         <v>6</v>
-      </c>
-      <c r="R57" t="n">
-        <v>3</v>
-      </c>
-      <c r="S57" t="n">
-        <v>13</v>
-      </c>
-      <c r="T57" t="n">
-        <v>3</v>
-      </c>
-      <c r="U57" t="n">
-        <v>19</v>
       </c>
       <c r="V57" t="n">
         <v>6</v>
       </c>
       <c r="W57" t="n">
+        <v>14</v>
+      </c>
+      <c r="X57" t="n">
         <v>13</v>
       </c>
-      <c r="X57" t="n">
-        <v>8</v>
-      </c>
       <c r="Y57" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="Z57" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>King Abdullah Sports City</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>, Jeddah</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD57" t="n">
         <v>3</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.14</v>
+        <v>3.6</v>
       </c>
       <c r="AF57" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG57" t="n">
-        <v>11.7</v>
+        <v>1.95</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AI57" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT57" t="n">
         <v>1.4</v>
       </c>
-      <c r="AJ57" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AU57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX57" t="n">
         <v>1</v>
@@ -27381,16 +27373,16 @@
         <v>2</v>
       </c>
       <c r="BA57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB57" t="n">
-        <v>-1</v>
+        <v>5097</v>
       </c>
       <c r="BC57" t="n">
         <v>0</v>
       </c>
       <c r="BD57" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="BE57" t="n">
         <v>0</v>
@@ -27405,76 +27397,76 @@
         <v>1</v>
       </c>
       <c r="BI57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BJ57" t="n">
         <v>0</v>
       </c>
       <c r="BK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL57" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM57" t="n">
         <v>4</v>
       </c>
-      <c r="BL57" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM57" t="n">
-        <v>5</v>
-      </c>
       <c r="BN57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BO57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP57" t="n">
         <v>1</v>
       </c>
       <c r="BQ57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR57" t="n">
         <v>2</v>
       </c>
       <c r="BS57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BU57" t="n">
         <v>1</v>
       </c>
       <c r="BV57" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="BW57" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="BX57" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="BY57" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="BZ57" t="n">
-        <v>2.19</v>
+        <v>1.01</v>
       </c>
       <c r="CA57" t="n">
-        <v>0.71</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CB57" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="CC57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG57" t="n">
         <v>0</v>
@@ -27489,10 +27481,10 @@
         <v>1</v>
       </c>
       <c r="CK57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM57" t="n">
         <v>0</v>
@@ -27510,31 +27502,31 @@
         <v>1</v>
       </c>
       <c r="CR57" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS57" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU57" t="n">
         <v>13</v>
       </c>
-      <c r="CS57" t="n">
+      <c r="CV57" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX57" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY57" t="n">
         <v>10</v>
       </c>
-      <c r="CT57" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU57" t="n">
-        <v>7</v>
-      </c>
-      <c r="CV57" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW57" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX57" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY57" t="n">
-        <v>14</v>
-      </c>
       <c r="CZ57" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="DA57" t="n">
         <v>84</v>
@@ -27546,34 +27538,34 @@
         <v>100</v>
       </c>
       <c r="DD57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="DF57" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG57" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI57" t="n">
         <v>1.67</v>
       </c>
-      <c r="DG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH57" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI57" t="n">
-        <v>1</v>
-      </c>
       <c r="DJ57" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="DK57" t="n">
         <v>17</v>
       </c>
       <c r="DL57" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="DM57" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="DN57" t="n">
         <v>2.85</v>
@@ -27588,13 +27580,13 @@
         <v>1</v>
       </c>
       <c r="DR57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU57" t="b">
         <v>0</v>
@@ -27603,87 +27595,99 @@
         <v>1</v>
       </c>
       <c r="DW57" t="n">
-        <v>32.58</v>
+        <v>29.89</v>
       </c>
       <c r="DX57" t="n">
-        <v>6</v>
+        <v>6.19</v>
       </c>
       <c r="DY57" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="DZ57" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA57" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EB57" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EC57" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="ED57" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EE57" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF57" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="EG57" t="inlineStr">
         <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="EH57" t="inlineStr"/>
-      <c r="EI57" t="inlineStr"/>
-      <c r="EJ57" t="inlineStr"/>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="EH57" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EI57" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EJ57" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
       <c r="EK57" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EL57" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EM57" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="EN57" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EO57" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EP57" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.18</t>
         </is>
       </c>
     </row>
@@ -27703,141 +27707,149 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>45960.72916666666</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
+        <v>9</v>
+      </c>
+      <c r="K58" t="n">
         <v>4</v>
       </c>
-      <c r="K58" t="n">
-        <v>2</v>
-      </c>
       <c r="L58" t="n">
+        <v>13</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
         <v>6</v>
       </c>
-      <c r="M58" t="n">
-        <v>3</v>
-      </c>
-      <c r="N58" t="n">
-        <v>3</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>4</v>
-      </c>
       <c r="R58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U58" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="V58" t="n">
         <v>6</v>
       </c>
       <c r="W58" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="X58" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y58" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="Z58" t="n">
-        <v>53</v>
-      </c>
-      <c r="AA58" t="inlineStr"/>
-      <c r="AB58" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>King Abdullah Sports City</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>, Jeddah</t>
+        </is>
+      </c>
       <c r="AC58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD58" t="n">
         <v>3</v>
       </c>
       <c r="AE58" t="n">
-        <v>3.6</v>
+        <v>1.14</v>
       </c>
       <c r="AF58" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.95</v>
+        <v>11.7</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AJ58" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AL58" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="AM58" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AN58" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AO58" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AR58" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AS58" t="n">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AU58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX58" t="n">
         <v>1</v>
@@ -27849,16 +27861,16 @@
         <v>2</v>
       </c>
       <c r="BA58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB58" t="n">
-        <v>5097</v>
+        <v>-1</v>
       </c>
       <c r="BC58" t="n">
         <v>0</v>
       </c>
       <c r="BD58" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="BE58" t="n">
         <v>0</v>
@@ -27873,76 +27885,76 @@
         <v>1</v>
       </c>
       <c r="BI58" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK58" t="n">
         <v>4</v>
       </c>
-      <c r="BJ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK58" t="n">
-        <v>0</v>
-      </c>
       <c r="BL58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BO58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP58" t="n">
         <v>1</v>
       </c>
       <c r="BQ58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR58" t="n">
         <v>2</v>
       </c>
       <c r="BS58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BU58" t="n">
         <v>1</v>
       </c>
       <c r="BV58" t="n">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="BW58" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="BX58" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="BY58" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="BZ58" t="n">
-        <v>1.01</v>
+        <v>2.19</v>
       </c>
       <c r="CA58" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="CB58" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="CC58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG58" t="n">
         <v>0</v>
@@ -27957,10 +27969,10 @@
         <v>1</v>
       </c>
       <c r="CK58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM58" t="n">
         <v>0</v>
@@ -27978,31 +27990,31 @@
         <v>1</v>
       </c>
       <c r="CR58" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CS58" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="CT58" t="n">
         <v>1</v>
       </c>
       <c r="CU58" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="CV58" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW58" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX58" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY58" t="n">
         <v>14</v>
       </c>
-      <c r="CW58" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX58" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY58" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ58" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="DA58" t="n">
         <v>84</v>
@@ -28014,34 +28026,34 @@
         <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="DE58" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="DF58" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="DG58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DH58" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DI58" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DJ58" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="DK58" t="n">
         <v>17</v>
       </c>
       <c r="DL58" t="n">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="DM58" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="DN58" t="n">
         <v>2.85</v>
@@ -28056,13 +28068,13 @@
         <v>1</v>
       </c>
       <c r="DR58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU58" t="b">
         <v>0</v>
@@ -28071,99 +28083,87 @@
         <v>1</v>
       </c>
       <c r="DW58" t="n">
-        <v>29.89</v>
+        <v>32.58</v>
       </c>
       <c r="DX58" t="n">
-        <v>6.19</v>
+        <v>6</v>
       </c>
       <c r="DY58" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="DZ58" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="EA58" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EB58" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EC58" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="ED58" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EE58" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="EF58" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="EG58" t="inlineStr">
         <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="EH58" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
-      <c r="EI58" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EJ58" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="EH58" t="inlineStr"/>
+      <c r="EI58" t="inlineStr"/>
+      <c r="EJ58" t="inlineStr"/>
       <c r="EK58" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EL58" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EM58" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EN58" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EO58" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="EP58" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -28527,7 +28527,7 @@
         <v>2.02</v>
       </c>
       <c r="DO59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -28977,7 +28977,7 @@
         <v>2.67</v>
       </c>
       <c r="DE60" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DF60" t="n">
         <v>2.33</v>
@@ -29438,7 +29438,7 @@
         <v>50</v>
       </c>
       <c r="DD61" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE61" t="n">
         <v>1.71</v>
@@ -30431,7 +30431,7 @@
         <v>3.33</v>
       </c>
       <c r="DO63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30903,7 +30903,7 @@
         <v>3.73</v>
       </c>
       <c r="DO64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31329,7 +31329,7 @@
         <v>0.25</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DF65" t="n">
         <v>0.33</v>
@@ -31793,7 +31793,7 @@
         <v>2.2</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="DF66" t="n">
         <v>2.33</v>
@@ -32718,10 +32718,10 @@
         <v>67</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DE68" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF68" t="n">
         <v>0.67</v>
@@ -32751,7 +32751,7 @@
         <v>1.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33190,10 +33190,10 @@
         <v>67</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DE69" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="DF69" t="n">
         <v>1</v>
@@ -33223,7 +33223,7 @@
         <v>2.68</v>
       </c>
       <c r="DO69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33654,7 +33654,7 @@
         <v>67</v>
       </c>
       <c r="DD70" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DE70" t="n">
         <v>2.6</v>
@@ -34121,7 +34121,7 @@
         <v>1.17</v>
       </c>
       <c r="DE71" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="DF71" t="n">
         <v>1.33</v>
@@ -34623,7 +34623,7 @@
         <v>2.76</v>
       </c>
       <c r="DO72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35078,7 +35078,7 @@
         <v>67</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE73" t="n">
         <v>2</v>
@@ -35111,7 +35111,7 @@
         <v>3.05</v>
       </c>
       <c r="DO73" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -36022,7 +36022,7 @@
         <v>75</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE75" t="n">
         <v>0.2</v>
@@ -36502,7 +36502,7 @@
         <v>63</v>
       </c>
       <c r="DD76" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DE76" t="n">
         <v>1.67</v>
@@ -37422,7 +37422,7 @@
         <v>75</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE78" t="n">
         <v>1</v>
@@ -37455,7 +37455,7 @@
         <v>1.69</v>
       </c>
       <c r="DO78" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38313,7 +38313,7 @@
         <v>0.67</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DF80" t="n">
         <v>0.75</v>
@@ -38343,7 +38343,7 @@
         <v>2.38</v>
       </c>
       <c r="DO80" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38479,79 +38479,87 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
         <v>45984.72916666666</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H81" t="n">
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
+        <v>4</v>
+      </c>
+      <c r="K81" t="n">
+        <v>2</v>
+      </c>
+      <c r="L81" t="n">
+        <v>6</v>
+      </c>
+      <c r="M81" t="n">
+        <v>3</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>10</v>
+      </c>
+      <c r="R81" t="n">
+        <v>5</v>
+      </c>
+      <c r="S81" t="n">
+        <v>11</v>
+      </c>
+      <c r="T81" t="n">
+        <v>7</v>
+      </c>
+      <c r="U81" t="n">
+        <v>21</v>
+      </c>
+      <c r="V81" t="n">
+        <v>12</v>
+      </c>
+      <c r="W81" t="n">
+        <v>15</v>
+      </c>
+      <c r="X81" t="n">
         <v>8</v>
       </c>
-      <c r="K81" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" t="n">
-        <v>9</v>
-      </c>
-      <c r="M81" t="n">
-        <v>3</v>
-      </c>
-      <c r="N81" t="n">
-        <v>3</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>2</v>
-      </c>
-      <c r="R81" t="n">
-        <v>2</v>
-      </c>
-      <c r="S81" t="n">
-        <v>6</v>
-      </c>
-      <c r="T81" t="n">
-        <v>13</v>
-      </c>
-      <c r="U81" t="n">
-        <v>8</v>
-      </c>
-      <c r="V81" t="n">
-        <v>15</v>
-      </c>
-      <c r="W81" t="n">
-        <v>11</v>
-      </c>
-      <c r="X81" t="n">
-        <v>16</v>
-      </c>
       <c r="Y81" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Z81" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA81" t="inlineStr"/>
-      <c r="AB81" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>King Saud University Stadium</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
+        </is>
+      </c>
       <c r="AC81" t="n">
         <v>3</v>
       </c>
@@ -38559,82 +38567,82 @@
         <v>3</v>
       </c>
       <c r="AE81" t="n">
-        <v>2.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF81" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="AG81" t="n">
-        <v>2.65</v>
+        <v>12</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="AI81" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR81" t="n">
         <v>1.73</v>
       </c>
-      <c r="AJ81" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK81" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL81" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM81" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AN81" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AO81" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AP81" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AQ81" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR81" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AS81" t="n">
-        <v>2.91</v>
+        <v>5</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.42</v>
+        <v>1.99</v>
       </c>
       <c r="AU81" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW81" t="n">
         <v>0</v>
       </c>
       <c r="AX81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY81" t="n">
         <v>1</v>
       </c>
       <c r="AZ81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB81" t="n">
-        <v>-1</v>
+        <v>5069</v>
       </c>
       <c r="BC81" t="n">
         <v>0</v>
       </c>
       <c r="BD81" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="BE81" t="n">
         <v>0</v>
@@ -38649,10 +38657,10 @@
         <v>1</v>
       </c>
       <c r="BI81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BJ81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK81" t="n">
         <v>2</v>
@@ -38661,7 +38669,7 @@
         <v>1</v>
       </c>
       <c r="BM81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BN81" t="n">
         <v>3</v>
@@ -38676,49 +38684,49 @@
         <v>2</v>
       </c>
       <c r="BR81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS81" t="n">
         <v>2</v>
       </c>
       <c r="BT81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU81" t="n">
         <v>1</v>
       </c>
       <c r="BV81" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="BW81" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="BX81" t="n">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="BY81" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="BZ81" t="n">
-        <v>0.91</v>
+        <v>2.36</v>
       </c>
       <c r="CA81" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CB81" t="n">
-        <v>2.21</v>
+        <v>3.68</v>
       </c>
       <c r="CC81" t="n">
         <v>0</v>
       </c>
       <c r="CD81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE81" t="n">
         <v>0</v>
       </c>
       <c r="CF81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG81" t="n">
         <v>0</v>
@@ -38745,85 +38753,85 @@
         <v>0</v>
       </c>
       <c r="CO81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ81" t="n">
         <v>1</v>
       </c>
       <c r="CR81" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CS81" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CT81" t="n">
         <v>1</v>
       </c>
       <c r="CU81" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="CV81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="CW81" t="n">
         <v>1</v>
       </c>
       <c r="CX81" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="CY81" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="CZ81" t="n">
         <v>75</v>
       </c>
       <c r="DA81" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="DB81" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="DC81" t="n">
         <v>88</v>
       </c>
       <c r="DD81" t="n">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="DE81" t="n">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="DF81" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="DG81" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="DH81" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="DI81" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="DJ81" t="n">
         <v>25</v>
       </c>
       <c r="DK81" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="DL81" t="n">
-        <v>1.2</v>
+        <v>2.59</v>
       </c>
       <c r="DM81" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="DN81" t="n">
-        <v>2.51</v>
+        <v>3.82</v>
       </c>
       <c r="DO81" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38832,13 +38840,13 @@
         <v>1</v>
       </c>
       <c r="DR81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU81" t="b">
         <v>0</v>
@@ -38847,85 +38855,73 @@
         <v>1</v>
       </c>
       <c r="DW81" t="n">
-        <v>30.11</v>
+        <v>21.64</v>
       </c>
       <c r="DX81" t="n">
-        <v>4.86</v>
+        <v>4.03</v>
       </c>
       <c r="DY81" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="DZ81" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="EA81" t="inlineStr"/>
-      <c r="EB81" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA81" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EB81" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
       <c r="EC81" t="inlineStr"/>
       <c r="ED81" t="inlineStr"/>
       <c r="EE81" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="EF81" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="EG81" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="EH81" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EI81" t="inlineStr">
         <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EJ81" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EJ81" t="inlineStr"/>
       <c r="EK81" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EL81" t="inlineStr">
         <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="EM81" t="inlineStr">
-        <is>
-          <t>2.71</t>
-        </is>
-      </c>
-      <c r="EN81" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EO81" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EP81" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EM81" t="inlineStr"/>
+      <c r="EN81" t="inlineStr"/>
+      <c r="EO81" t="inlineStr"/>
+      <c r="EP81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -38943,87 +38939,79 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
         <v>45984.72916666666</v>
       </c>
       <c r="G82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
         <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
+        <v>9</v>
+      </c>
+      <c r="M82" t="n">
+        <v>3</v>
+      </c>
+      <c r="N82" t="n">
+        <v>3</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>2</v>
+      </c>
+      <c r="R82" t="n">
+        <v>2</v>
+      </c>
+      <c r="S82" t="n">
         <v>6</v>
       </c>
-      <c r="M82" t="n">
-        <v>3</v>
-      </c>
-      <c r="N82" t="n">
-        <v>1</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>10</v>
-      </c>
-      <c r="R82" t="n">
-        <v>5</v>
-      </c>
-      <c r="S82" t="n">
+      <c r="T82" t="n">
+        <v>13</v>
+      </c>
+      <c r="U82" t="n">
+        <v>8</v>
+      </c>
+      <c r="V82" t="n">
+        <v>15</v>
+      </c>
+      <c r="W82" t="n">
         <v>11</v>
       </c>
-      <c r="T82" t="n">
-        <v>7</v>
-      </c>
-      <c r="U82" t="n">
-        <v>21</v>
-      </c>
-      <c r="V82" t="n">
-        <v>12</v>
-      </c>
-      <c r="W82" t="n">
-        <v>15</v>
-      </c>
       <c r="X82" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y82" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="Z82" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>King Saud University Stadium</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
         <v>3</v>
       </c>
@@ -39031,82 +39019,82 @@
         <v>3</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.14</v>
+        <v>2.29</v>
       </c>
       <c r="AF82" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="AG82" t="n">
-        <v>12</v>
+        <v>2.65</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AI82" t="n">
-        <v>1.21</v>
+        <v>1.73</v>
       </c>
       <c r="AJ82" t="n">
-        <v>1.56</v>
+        <v>3</v>
       </c>
       <c r="AK82" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL82" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AM82" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AN82" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="AO82" t="n">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="AS82" t="n">
-        <v>5</v>
+        <v>2.91</v>
       </c>
       <c r="AT82" t="n">
-        <v>1.99</v>
+        <v>1.42</v>
       </c>
       <c r="AU82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW82" t="n">
         <v>0</v>
       </c>
       <c r="AX82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY82" t="n">
         <v>1</v>
       </c>
       <c r="AZ82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB82" t="n">
-        <v>5069</v>
+        <v>-1</v>
       </c>
       <c r="BC82" t="n">
         <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="BE82" t="n">
         <v>0</v>
@@ -39121,10 +39109,10 @@
         <v>1</v>
       </c>
       <c r="BI82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK82" t="n">
         <v>2</v>
@@ -39133,7 +39121,7 @@
         <v>1</v>
       </c>
       <c r="BM82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN82" t="n">
         <v>3</v>
@@ -39148,49 +39136,49 @@
         <v>2</v>
       </c>
       <c r="BR82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS82" t="n">
         <v>2</v>
       </c>
       <c r="BT82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU82" t="n">
         <v>1</v>
       </c>
       <c r="BV82" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="BW82" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="BX82" t="n">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="BY82" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="BZ82" t="n">
-        <v>2.36</v>
+        <v>0.91</v>
       </c>
       <c r="CA82" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CB82" t="n">
-        <v>3.68</v>
+        <v>2.21</v>
       </c>
       <c r="CC82" t="n">
         <v>0</v>
       </c>
       <c r="CD82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE82" t="n">
         <v>0</v>
       </c>
       <c r="CF82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG82" t="n">
         <v>0</v>
@@ -39217,82 +39205,82 @@
         <v>0</v>
       </c>
       <c r="CO82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ82" t="n">
         <v>1</v>
       </c>
       <c r="CR82" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CS82" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="CT82" t="n">
         <v>1</v>
       </c>
       <c r="CU82" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV82" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX82" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY82" t="n">
         <v>8</v>
-      </c>
-      <c r="CV82" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX82" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY82" t="n">
-        <v>14</v>
       </c>
       <c r="CZ82" t="n">
         <v>75</v>
       </c>
       <c r="DA82" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="DB82" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="DC82" t="n">
         <v>88</v>
       </c>
       <c r="DD82" t="n">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="DF82" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="DG82" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="DH82" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="DI82" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="DJ82" t="n">
         <v>25</v>
       </c>
       <c r="DK82" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="DL82" t="n">
-        <v>2.59</v>
+        <v>1.2</v>
       </c>
       <c r="DM82" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="DN82" t="n">
-        <v>3.82</v>
+        <v>2.51</v>
       </c>
       <c r="DO82" t="n">
         <v>11</v>
@@ -39304,13 +39292,13 @@
         <v>1</v>
       </c>
       <c r="DR82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU82" t="b">
         <v>0</v>
@@ -39319,73 +39307,85 @@
         <v>1</v>
       </c>
       <c r="DW82" t="n">
-        <v>21.64</v>
+        <v>30.11</v>
       </c>
       <c r="DX82" t="n">
-        <v>4.03</v>
+        <v>4.86</v>
       </c>
       <c r="DY82" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="DZ82" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="EA82" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EB82" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="EA82" t="inlineStr"/>
+      <c r="EB82" t="inlineStr"/>
       <c r="EC82" t="inlineStr"/>
       <c r="ED82" t="inlineStr"/>
       <c r="EE82" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EF82" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EG82" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EH82" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EI82" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EJ82" t="inlineStr"/>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EJ82" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
       <c r="EK82" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EL82" t="inlineStr">
         <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="EM82" t="inlineStr"/>
-      <c r="EN82" t="inlineStr"/>
-      <c r="EO82" t="inlineStr"/>
-      <c r="EP82" t="inlineStr"/>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EM82" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EN82" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EO82" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EP82" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -39714,7 +39714,7 @@
         <v>55</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DE83" t="n">
         <v>1.71</v>
@@ -41118,7 +41118,7 @@
         <v>50</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DE86" t="n">
         <v>2</v>
@@ -41151,7 +41151,7 @@
         <v>3.42</v>
       </c>
       <c r="DO86" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41549,7 +41549,7 @@
         <v>1</v>
       </c>
       <c r="DE87" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="DF87" t="n">
         <v>1.5</v>
@@ -41579,7 +41579,7 @@
         <v>2.81</v>
       </c>
       <c r="DO87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -42029,7 +42029,7 @@
         <v>2.67</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DF88" t="n">
         <v>2.6</v>
@@ -42929,7 +42929,7 @@
         <v>3</v>
       </c>
       <c r="DE90" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF90" t="n">
         <v>3</v>
@@ -42959,7 +42959,7 @@
         <v>3.16</v>
       </c>
       <c r="DO90" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -43394,10 +43394,10 @@
         <v>78</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DF91" t="n">
         <v>1.2</v>
@@ -43427,7 +43427,7 @@
         <v>2.54</v>
       </c>
       <c r="DO91" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43907,7 +43907,7 @@
         <v>2.77</v>
       </c>
       <c r="DO92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -44011,12 +44011,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
@@ -44026,25 +44026,25 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K93" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N93" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -44053,128 +44053,120 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R93" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S93" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T93" t="n">
         <v>4</v>
       </c>
       <c r="U93" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="V93" t="n">
+        <v>5</v>
+      </c>
+      <c r="W93" t="n">
+        <v>13</v>
+      </c>
+      <c r="X93" t="n">
         <v>11</v>
       </c>
-      <c r="W93" t="n">
-        <v>8</v>
-      </c>
-      <c r="X93" t="n">
-        <v>12</v>
-      </c>
       <c r="Y93" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="Z93" t="n">
-        <v>49</v>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>Prince Turki bin Abdul Aziz Stadium</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>, Riyadh</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD93" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>2.5</v>
+        <v>1.45</v>
       </c>
       <c r="AF93" t="n">
-        <v>3.1</v>
+        <v>4.35</v>
       </c>
       <c r="AG93" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AI93" t="n">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="AJ93" t="n">
-        <v>3.42</v>
+        <v>2.63</v>
       </c>
       <c r="AK93" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AL93" t="n">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="AM93" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT93" t="n">
         <v>1.55</v>
       </c>
-      <c r="AN93" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO93" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AP93" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AQ93" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR93" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AS93" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AT93" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AU93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV93" t="n">
         <v>0</v>
       </c>
       <c r="AW93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX93" t="n">
         <v>1</v>
       </c>
       <c r="AY93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB93" t="n">
-        <v>5089</v>
+        <v>5074</v>
       </c>
       <c r="BC93" t="n">
         <v>0</v>
       </c>
       <c r="BD93" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="BE93" t="n">
         <v>0</v>
@@ -44189,64 +44181,64 @@
         <v>1</v>
       </c>
       <c r="BI93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK93" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM93" t="n">
         <v>4</v>
       </c>
-      <c r="BJ93" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK93" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL93" t="n">
-        <v>4</v>
-      </c>
-      <c r="BM93" t="n">
-        <v>5</v>
-      </c>
       <c r="BN93" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BO93" t="n">
         <v>1</v>
       </c>
       <c r="BP93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU93" t="n">
         <v>1</v>
       </c>
       <c r="BV93" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="BW93" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="BX93" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="BY93" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="BZ93" t="n">
-        <v>2.01</v>
+        <v>1.48</v>
       </c>
       <c r="CA93" t="n">
-        <v>1.53</v>
+        <v>0.61</v>
       </c>
       <c r="CB93" t="n">
-        <v>3.55</v>
+        <v>2.09</v>
       </c>
       <c r="CC93" t="n">
         <v>0</v>
@@ -44279,7 +44271,7 @@
         <v>0</v>
       </c>
       <c r="CM93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN93" t="n">
         <v>0</v>
@@ -44288,91 +44280,91 @@
         <v>0</v>
       </c>
       <c r="CP93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ93" t="n">
         <v>1</v>
       </c>
       <c r="CR93" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="CS93" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CT93" t="n">
         <v>1</v>
       </c>
       <c r="CU93" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV93" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX93" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY93" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ93" t="n">
+        <v>72</v>
+      </c>
+      <c r="DA93" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB93" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC93" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD93" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DE93" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DF93" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG93" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DH93" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DI93" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DJ93" t="n">
+        <v>29</v>
+      </c>
+      <c r="DK93" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL93" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DM93" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DN93" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DO93" t="n">
         <v>12</v>
       </c>
-      <c r="CV93" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX93" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY93" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ93" t="n">
-        <v>45</v>
-      </c>
-      <c r="DA93" t="n">
-        <v>74</v>
-      </c>
-      <c r="DB93" t="n">
-        <v>37</v>
-      </c>
-      <c r="DC93" t="n">
-        <v>65</v>
-      </c>
-      <c r="DD93" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DE93" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DF93" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DG93" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DH93" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DI93" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ93" t="n">
-        <v>55</v>
-      </c>
-      <c r="DK93" t="n">
-        <v>27</v>
-      </c>
-      <c r="DL93" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="DM93" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="DN93" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="DO93" t="n">
-        <v>11</v>
-      </c>
       <c r="DP93" t="b">
         <v>1</v>
       </c>
       <c r="DQ93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS93" t="b">
         <v>0</v>
@@ -44384,17 +44376,17 @@
         <v>0</v>
       </c>
       <c r="DV93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW93" t="n">
-        <v>18.59</v>
+        <v>17.94</v>
       </c>
       <c r="DX93" t="n">
-        <v>5.81</v>
+        <v>6.89</v>
       </c>
       <c r="DY93" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="DZ93" t="inlineStr">
@@ -44404,52 +44396,52 @@
       </c>
       <c r="EA93" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EB93" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EC93" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="ED93" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EE93" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="EF93" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="EG93" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EH93" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="EI93" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EJ93" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EK93" t="inlineStr">
@@ -44459,27 +44451,27 @@
       </c>
       <c r="EL93" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EM93" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="EN93" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EO93" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="EP93" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.28</t>
         </is>
       </c>
     </row>
@@ -44499,12 +44491,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
@@ -44514,25 +44506,25 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J94" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L94" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -44541,120 +44533,128 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R94" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S94" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T94" t="n">
         <v>4</v>
       </c>
       <c r="U94" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V94" t="n">
+        <v>11</v>
+      </c>
+      <c r="W94" t="n">
+        <v>8</v>
+      </c>
+      <c r="X94" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>Prince Turki bin Abdul Aziz Stadium</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>, Riyadh</t>
+        </is>
+      </c>
+      <c r="AC94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD94" t="n">
         <v>5</v>
       </c>
-      <c r="W94" t="n">
-        <v>13</v>
-      </c>
-      <c r="X94" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y94" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z94" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA94" t="inlineStr"/>
-      <c r="AB94" t="inlineStr"/>
-      <c r="AC94" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD94" t="n">
-        <v>0</v>
-      </c>
       <c r="AE94" t="n">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="AF94" t="n">
-        <v>4.35</v>
+        <v>3.1</v>
       </c>
       <c r="AG94" t="n">
-        <v>6.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH94" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AI94" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="AJ94" t="n">
-        <v>2.63</v>
+        <v>3.42</v>
       </c>
       <c r="AK94" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AL94" t="n">
-        <v>1.71</v>
+        <v>1.99</v>
       </c>
       <c r="AM94" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AN94" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AO94" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AR94" t="n">
-        <v>2.39</v>
+        <v>2.91</v>
       </c>
       <c r="AS94" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="AT94" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AU94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV94" t="n">
         <v>0</v>
       </c>
       <c r="AW94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX94" t="n">
         <v>1</v>
       </c>
       <c r="AY94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB94" t="n">
-        <v>5074</v>
+        <v>5089</v>
       </c>
       <c r="BC94" t="n">
         <v>0</v>
       </c>
       <c r="BD94" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="BE94" t="n">
         <v>0</v>
@@ -44669,178 +44669,178 @@
         <v>1</v>
       </c>
       <c r="BI94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BJ94" t="n">
         <v>1</v>
       </c>
       <c r="BK94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM94" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN94" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR94" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS94" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV94" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW94" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX94" t="n">
+        <v>105</v>
+      </c>
+      <c r="BY94" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ94" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CA94" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CB94" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM94" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR94" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS94" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU94" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV94" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX94" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY94" t="n">
         <v>7</v>
       </c>
-      <c r="BL94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM94" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN94" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ94" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT94" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV94" t="n">
-        <v>63</v>
-      </c>
-      <c r="BW94" t="n">
-        <v>29</v>
-      </c>
-      <c r="BX94" t="n">
-        <v>117</v>
-      </c>
-      <c r="BY94" t="n">
-        <v>88</v>
-      </c>
-      <c r="BZ94" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CA94" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="CB94" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="CC94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR94" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS94" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU94" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV94" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX94" t="n">
-        <v>2</v>
-      </c>
-      <c r="CY94" t="n">
-        <v>13</v>
-      </c>
       <c r="CZ94" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="DA94" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="DB94" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="DC94" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="DD94" t="n">
-        <v>2.17</v>
+        <v>1.17</v>
       </c>
       <c r="DE94" t="n">
-        <v>0.14</v>
+        <v>1.71</v>
       </c>
       <c r="DF94" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="DG94" t="n">
-        <v>0.17</v>
+        <v>1.5</v>
       </c>
       <c r="DH94" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="DI94" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="DJ94" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="DK94" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="DL94" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="DM94" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="DN94" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DO94" t="n">
         <v>11</v>
@@ -44849,10 +44849,10 @@
         <v>1</v>
       </c>
       <c r="DQ94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS94" t="b">
         <v>0</v>
@@ -44864,17 +44864,17 @@
         <v>0</v>
       </c>
       <c r="DV94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW94" t="n">
-        <v>17.94</v>
+        <v>18.59</v>
       </c>
       <c r="DX94" t="n">
-        <v>6.89</v>
+        <v>5.81</v>
       </c>
       <c r="DY94" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="DZ94" t="inlineStr">
@@ -44884,52 +44884,52 @@
       </c>
       <c r="EA94" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EB94" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EC94" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="ED94" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EE94" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EF94" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EG94" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EH94" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="EI94" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EJ94" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EK94" t="inlineStr">
@@ -44939,27 +44939,27 @@
       </c>
       <c r="EL94" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EM94" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="EN94" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EO94" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EP94" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
@@ -45290,7 +45290,7 @@
         <v>80</v>
       </c>
       <c r="DD95" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DE95" t="n">
         <v>1</v>
@@ -45323,7 +45323,7 @@
         <v>2.91</v>
       </c>
       <c r="DO95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45431,43 +45431,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
         <v>46021.72916666666</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J96" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="L96" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
@@ -45476,117 +45476,117 @@
         <v>4</v>
       </c>
       <c r="R96" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S96" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T96" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="U96" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="V96" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="W96" t="n">
         <v>7</v>
       </c>
       <c r="X96" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y96" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="Z96" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="AA96" t="inlineStr"/>
       <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AU96" t="n">
         <v>4</v>
       </c>
-      <c r="AD96" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE96" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AF96" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AG96" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH96" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI96" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AJ96" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AK96" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AL96" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM96" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AN96" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AO96" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AP96" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AQ96" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR96" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AS96" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT96" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AU96" t="n">
-        <v>1</v>
-      </c>
       <c r="AV96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA96" t="n">
         <v>1</v>
       </c>
       <c r="BB96" t="n">
-        <v>5083</v>
+        <v>-1</v>
       </c>
       <c r="BC96" t="n">
         <v>0</v>
       </c>
       <c r="BD96" t="n">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="BE96" t="n">
         <v>0</v>
@@ -45601,64 +45601,64 @@
         <v>1</v>
       </c>
       <c r="BI96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ96" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="BK96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL96" t="n">
         <v>5</v>
       </c>
-      <c r="BL96" t="n">
-        <v>2</v>
-      </c>
       <c r="BM96" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN96" t="n">
         <v>6</v>
       </c>
-      <c r="BN96" t="n">
-        <v>7</v>
-      </c>
       <c r="BO96" t="n">
         <v>1</v>
       </c>
       <c r="BP96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR96" t="n">
         <v>0</v>
       </c>
       <c r="BS96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BT96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BU96" t="n">
         <v>1</v>
       </c>
       <c r="BV96" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="BW96" t="n">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="BX96" t="n">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="BY96" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="BZ96" t="n">
-        <v>1.35</v>
+        <v>0.75</v>
       </c>
       <c r="CA96" t="n">
-        <v>0.82</v>
+        <v>3.01</v>
       </c>
       <c r="CB96" t="n">
-        <v>2.18</v>
+        <v>3.76</v>
       </c>
       <c r="CC96" t="n">
         <v>0</v>
@@ -45688,7 +45688,7 @@
         <v>0</v>
       </c>
       <c r="CL96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM96" t="n">
         <v>0</v>
@@ -45700,22 +45700,22 @@
         <v>0</v>
       </c>
       <c r="CP96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CQ96" t="n">
         <v>1</v>
       </c>
       <c r="CR96" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="CS96" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CT96" t="n">
         <v>1</v>
       </c>
       <c r="CU96" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="CV96" t="n">
         <v>7</v>
@@ -45724,70 +45724,70 @@
         <v>1</v>
       </c>
       <c r="CX96" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="CY96" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ96" t="n">
+        <v>65</v>
+      </c>
+      <c r="DA96" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB96" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC96" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD96" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DE96" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DF96" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DG96" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH96" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI96" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ96" t="n">
+        <v>35</v>
+      </c>
+      <c r="DK96" t="n">
         <v>10</v>
       </c>
-      <c r="CZ96" t="n">
-        <v>60</v>
-      </c>
-      <c r="DA96" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB96" t="n">
-        <v>80</v>
-      </c>
-      <c r="DC96" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD96" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DE96" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF96" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DG96" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="DH96" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DI96" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="DJ96" t="n">
-        <v>40</v>
-      </c>
-      <c r="DK96" t="n">
-        <v>0</v>
-      </c>
       <c r="DL96" t="n">
-        <v>1.24</v>
+        <v>0.86</v>
       </c>
       <c r="DM96" t="n">
-        <v>0.91</v>
+        <v>2.26</v>
       </c>
       <c r="DN96" t="n">
-        <v>2.15</v>
+        <v>3.12</v>
       </c>
       <c r="DO96" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
       </c>
       <c r="DQ96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT96" t="b">
         <v>0</v>
@@ -45796,86 +45796,74 @@
         <v>0</v>
       </c>
       <c r="DV96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW96" t="n">
-        <v>23.3</v>
+        <v>19.88</v>
       </c>
       <c r="DX96" t="n">
-        <v>6.98</v>
+        <v>9.33</v>
       </c>
       <c r="DY96" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="DZ96" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA96" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EB96" t="inlineStr">
         <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="EC96" t="inlineStr">
-        <is>
-          <t>2.27</t>
-        </is>
-      </c>
-      <c r="ED96" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EC96" t="inlineStr"/>
+      <c r="ED96" t="inlineStr"/>
       <c r="EE96" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EF96" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="EG96" t="inlineStr">
         <is>
-          <t>3.13</t>
-        </is>
-      </c>
-      <c r="EH96" t="inlineStr">
-        <is>
-          <t>4.88</t>
-        </is>
-      </c>
-      <c r="EI96" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="EJ96" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
+          <t>7.66</t>
+        </is>
+      </c>
+      <c r="EH96" t="inlineStr"/>
+      <c r="EI96" t="inlineStr"/>
+      <c r="EJ96" t="inlineStr"/>
       <c r="EK96" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EL96" t="inlineStr">
         <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EM96" t="inlineStr"/>
-      <c r="EN96" t="inlineStr"/>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EM96" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EN96" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
       <c r="EO96" t="inlineStr"/>
       <c r="EP96" t="inlineStr"/>
     </row>
@@ -45895,43 +45883,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
         <v>46021.72916666666</v>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K97" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="L97" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
@@ -45940,117 +45928,117 @@
         <v>4</v>
       </c>
       <c r="R97" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S97" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T97" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="U97" t="n">
+        <v>12</v>
+      </c>
+      <c r="V97" t="n">
         <v>6</v>
-      </c>
-      <c r="V97" t="n">
-        <v>26</v>
       </c>
       <c r="W97" t="n">
         <v>7</v>
       </c>
       <c r="X97" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y97" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="Z97" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="AA97" t="inlineStr"/>
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE97" t="n">
-        <v>8</v>
+        <v>2.62</v>
       </c>
       <c r="AF97" t="n">
-        <v>6.4</v>
+        <v>2.9</v>
       </c>
       <c r="AG97" t="n">
-        <v>1.14</v>
+        <v>2.7</v>
       </c>
       <c r="AH97" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="AI97" t="n">
-        <v>1.3</v>
+        <v>2.33</v>
       </c>
       <c r="AJ97" t="n">
-        <v>1.85</v>
+        <v>4.35</v>
       </c>
       <c r="AK97" t="n">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AL97" t="n">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="AM97" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AN97" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AO97" t="n">
-        <v>2.65</v>
+        <v>2.24</v>
       </c>
       <c r="AP97" t="n">
-        <v>2.08</v>
+        <v>1.72</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.94</v>
+        <v>3.05</v>
       </c>
       <c r="AS97" t="n">
-        <v>4.2</v>
+        <v>2.33</v>
       </c>
       <c r="AT97" t="n">
-        <v>1.76</v>
+        <v>1.26</v>
       </c>
       <c r="AU97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA97" t="n">
         <v>1</v>
       </c>
       <c r="BB97" t="n">
-        <v>-1</v>
+        <v>5083</v>
       </c>
       <c r="BC97" t="n">
         <v>0</v>
       </c>
       <c r="BD97" t="n">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="BE97" t="n">
         <v>0</v>
@@ -46065,64 +46053,64 @@
         <v>1</v>
       </c>
       <c r="BI97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ97" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="BK97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BL97" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BM97" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BN97" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BO97" t="n">
         <v>1</v>
       </c>
       <c r="BP97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR97" t="n">
         <v>0</v>
       </c>
       <c r="BS97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BU97" t="n">
         <v>1</v>
       </c>
       <c r="BV97" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="BW97" t="n">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="BX97" t="n">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="BY97" t="n">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="BZ97" t="n">
-        <v>0.75</v>
+        <v>1.35</v>
       </c>
       <c r="CA97" t="n">
-        <v>3.01</v>
+        <v>0.82</v>
       </c>
       <c r="CB97" t="n">
-        <v>3.76</v>
+        <v>2.18</v>
       </c>
       <c r="CC97" t="n">
         <v>0</v>
@@ -46152,7 +46140,7 @@
         <v>0</v>
       </c>
       <c r="CL97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM97" t="n">
         <v>0</v>
@@ -46164,22 +46152,22 @@
         <v>0</v>
       </c>
       <c r="CP97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CQ97" t="n">
         <v>1</v>
       </c>
       <c r="CR97" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="CS97" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CT97" t="n">
         <v>1</v>
       </c>
       <c r="CU97" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="CV97" t="n">
         <v>7</v>
@@ -46188,55 +46176,55 @@
         <v>1</v>
       </c>
       <c r="CX97" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="CY97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="CZ97" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="DA97" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="DB97" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="DC97" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="DE97" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="DF97" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="DG97" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="DH97" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="DI97" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="DJ97" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="DK97" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="DL97" t="n">
-        <v>0.86</v>
+        <v>1.24</v>
       </c>
       <c r="DM97" t="n">
-        <v>2.26</v>
+        <v>0.91</v>
       </c>
       <c r="DN97" t="n">
-        <v>3.12</v>
+        <v>2.15</v>
       </c>
       <c r="DO97" t="n">
         <v>11</v>
@@ -46245,13 +46233,13 @@
         <v>1</v>
       </c>
       <c r="DQ97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT97" t="b">
         <v>0</v>
@@ -46260,74 +46248,86 @@
         <v>0</v>
       </c>
       <c r="DV97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW97" t="n">
-        <v>19.88</v>
+        <v>23.3</v>
       </c>
       <c r="DX97" t="n">
-        <v>9.33</v>
+        <v>6.98</v>
       </c>
       <c r="DY97" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="DZ97" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="EA97" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EB97" t="inlineStr">
         <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EC97" t="inlineStr"/>
-      <c r="ED97" t="inlineStr"/>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EC97" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="ED97" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
       <c r="EE97" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EF97" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="EG97" t="inlineStr">
         <is>
-          <t>7.66</t>
-        </is>
-      </c>
-      <c r="EH97" t="inlineStr"/>
-      <c r="EI97" t="inlineStr"/>
-      <c r="EJ97" t="inlineStr"/>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EH97" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="EI97" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EJ97" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
       <c r="EK97" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EL97" t="inlineStr">
         <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EM97" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EN97" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EM97" t="inlineStr"/>
+      <c r="EN97" t="inlineStr"/>
       <c r="EO97" t="inlineStr"/>
       <c r="EP97" t="inlineStr"/>
     </row>
@@ -47675,6 +47675,2750 @@
       <c r="EO100" t="inlineStr"/>
       <c r="EP100" t="inlineStr"/>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>13</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Al Najma</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>46024.5625</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2</v>
+      </c>
+      <c r="I101" t="n">
+        <v>4</v>
+      </c>
+      <c r="J101" t="n">
+        <v>5</v>
+      </c>
+      <c r="K101" t="n">
+        <v>5</v>
+      </c>
+      <c r="L101" t="n">
+        <v>10</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>3</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>6</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6</v>
+      </c>
+      <c r="S101" t="n">
+        <v>7</v>
+      </c>
+      <c r="T101" t="n">
+        <v>10</v>
+      </c>
+      <c r="U101" t="n">
+        <v>13</v>
+      </c>
+      <c r="V101" t="n">
+        <v>16</v>
+      </c>
+      <c r="W101" t="n">
+        <v>9</v>
+      </c>
+      <c r="X101" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>Al-Najma Club Stadium</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>, Unaizah</t>
+        </is>
+      </c>
+      <c r="AC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK101" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL101" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM101" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN101" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR101" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT101" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV101" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW101" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX101" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY101" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ101" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CA101" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CB101" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="CC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR101" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS101" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU101" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV101" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX101" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY101" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ101" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA101" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB101" t="n">
+        <v>46</v>
+      </c>
+      <c r="DC101" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD101" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DE101" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG101" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DH101" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DI101" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DJ101" t="n">
+        <v>34</v>
+      </c>
+      <c r="DK101" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL101" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="DM101" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DN101" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="DO101" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW101" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="DX101" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="DY101" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="DZ101" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA101" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EB101" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EC101" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="ED101" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EE101" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EF101" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="EG101" t="inlineStr">
+        <is>
+          <t>5.04</t>
+        </is>
+      </c>
+      <c r="EH101" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="EI101" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EJ101" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EK101" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EL101" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EM101" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="EN101" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EO101" t="inlineStr"/>
+      <c r="EP101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>13</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Al Ittifaq</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Al Akhdoud</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>46024.60763888889</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>2</v>
+      </c>
+      <c r="J102" t="n">
+        <v>8</v>
+      </c>
+      <c r="K102" t="n">
+        <v>3</v>
+      </c>
+      <c r="L102" t="n">
+        <v>11</v>
+      </c>
+      <c r="M102" t="n">
+        <v>2</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>9</v>
+      </c>
+      <c r="R102" t="n">
+        <v>2</v>
+      </c>
+      <c r="S102" t="n">
+        <v>6</v>
+      </c>
+      <c r="T102" t="n">
+        <v>5</v>
+      </c>
+      <c r="U102" t="n">
+        <v>15</v>
+      </c>
+      <c r="V102" t="n">
+        <v>7</v>
+      </c>
+      <c r="W102" t="n">
+        <v>11</v>
+      </c>
+      <c r="X102" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA102" t="inlineStr"/>
+      <c r="AB102" t="inlineStr"/>
+      <c r="AC102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB102" t="n">
+        <v>5065</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD102" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI102" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK102" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL102" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM102" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN102" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV102" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW102" t="n">
+        <v>16</v>
+      </c>
+      <c r="BX102" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY102" t="n">
+        <v>57</v>
+      </c>
+      <c r="BZ102" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CA102" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CB102" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="CC102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR102" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS102" t="n">
+        <v>6</v>
+      </c>
+      <c r="CT102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU102" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV102" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX102" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY102" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ102" t="n">
+        <v>62</v>
+      </c>
+      <c r="DA102" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB102" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC102" t="n">
+        <v>72</v>
+      </c>
+      <c r="DD102" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DE102" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DF102" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG102" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DH102" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DI102" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DJ102" t="n">
+        <v>39</v>
+      </c>
+      <c r="DK102" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL102" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="DM102" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DN102" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DO102" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP102" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ102" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW102" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="DX102" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="DY102" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="DZ102" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA102" t="inlineStr"/>
+      <c r="EB102" t="inlineStr"/>
+      <c r="EC102" t="inlineStr"/>
+      <c r="ED102" t="inlineStr"/>
+      <c r="EE102" t="inlineStr">
+        <is>
+          <t>5.19</t>
+        </is>
+      </c>
+      <c r="EF102" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="EG102" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EH102" t="inlineStr"/>
+      <c r="EI102" t="inlineStr"/>
+      <c r="EJ102" t="inlineStr"/>
+      <c r="EK102" t="inlineStr"/>
+      <c r="EL102" t="inlineStr"/>
+      <c r="EM102" t="inlineStr"/>
+      <c r="EN102" t="inlineStr"/>
+      <c r="EO102" t="inlineStr"/>
+      <c r="EP102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>13</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>46024.72916666666</v>
+      </c>
+      <c r="G103" t="n">
+        <v>3</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2</v>
+      </c>
+      <c r="I103" t="n">
+        <v>5</v>
+      </c>
+      <c r="J103" t="n">
+        <v>3</v>
+      </c>
+      <c r="K103" t="n">
+        <v>4</v>
+      </c>
+      <c r="L103" t="n">
+        <v>7</v>
+      </c>
+      <c r="M103" t="n">
+        <v>4</v>
+      </c>
+      <c r="N103" t="n">
+        <v>3</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1</v>
+      </c>
+      <c r="P103" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>7</v>
+      </c>
+      <c r="R103" t="n">
+        <v>4</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="n">
+        <v>16</v>
+      </c>
+      <c r="U103" t="n">
+        <v>17</v>
+      </c>
+      <c r="V103" t="n">
+        <v>20</v>
+      </c>
+      <c r="W103" t="n">
+        <v>20</v>
+      </c>
+      <c r="X103" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>King Abdullah Sports City</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>, Jeddah</t>
+        </is>
+      </c>
+      <c r="AC103" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>5062</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD103" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ103" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK103" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM103" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN103" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ103" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR103" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT103" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV103" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW103" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX103" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY103" t="n">
+        <v>124</v>
+      </c>
+      <c r="BZ103" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CA103" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CB103" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="CC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR103" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS103" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU103" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV103" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX103" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY103" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ103" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA103" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB103" t="n">
+        <v>19</v>
+      </c>
+      <c r="DC103" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD103" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DE103" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DF103" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG103" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DH103" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI103" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DJ103" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK103" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL103" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DM103" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="DN103" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="DO103" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW103" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="DX103" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="DY103" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="DZ103" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA103" t="inlineStr"/>
+      <c r="EB103" t="inlineStr"/>
+      <c r="EC103" t="inlineStr"/>
+      <c r="ED103" t="inlineStr"/>
+      <c r="EE103" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EF103" t="inlineStr">
+        <is>
+          <t>4.51</t>
+        </is>
+      </c>
+      <c r="EG103" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="EH103" t="inlineStr"/>
+      <c r="EI103" t="inlineStr"/>
+      <c r="EJ103" t="inlineStr"/>
+      <c r="EK103" t="inlineStr"/>
+      <c r="EL103" t="inlineStr"/>
+      <c r="EM103" t="inlineStr"/>
+      <c r="EN103" t="inlineStr"/>
+      <c r="EO103" t="inlineStr"/>
+      <c r="EP103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>13</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Al Fateh</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Al Shabab</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>46025.54861111111</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>2</v>
+      </c>
+      <c r="J104" t="n">
+        <v>6</v>
+      </c>
+      <c r="K104" t="n">
+        <v>9</v>
+      </c>
+      <c r="L104" t="n">
+        <v>15</v>
+      </c>
+      <c r="M104" t="n">
+        <v>4</v>
+      </c>
+      <c r="N104" t="n">
+        <v>3</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>5</v>
+      </c>
+      <c r="R104" t="n">
+        <v>1</v>
+      </c>
+      <c r="S104" t="n">
+        <v>8</v>
+      </c>
+      <c r="T104" t="n">
+        <v>10</v>
+      </c>
+      <c r="U104" t="n">
+        <v>13</v>
+      </c>
+      <c r="V104" t="n">
+        <v>11</v>
+      </c>
+      <c r="W104" t="n">
+        <v>19</v>
+      </c>
+      <c r="X104" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>Prince Abdullah bin Jalawi Sports City Stadium</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>, Al-Hasa</t>
+        </is>
+      </c>
+      <c r="AC104" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB104" t="n">
+        <v>5064</v>
+      </c>
+      <c r="BC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD104" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI104" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ104" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM104" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN104" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ104" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR104" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS104" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT104" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV104" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW104" t="n">
+        <v>52</v>
+      </c>
+      <c r="BX104" t="n">
+        <v>76</v>
+      </c>
+      <c r="BY104" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ104" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CA104" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CB104" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN104" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR104" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS104" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU104" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV104" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX104" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY104" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ104" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA104" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB104" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC104" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD104" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE104" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF104" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG104" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DH104" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI104" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DJ104" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK104" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL104" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DM104" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN104" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DO104" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW104" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="DX104" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="DY104" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="DZ104" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="EA104" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EB104" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EC104" t="inlineStr"/>
+      <c r="ED104" t="inlineStr"/>
+      <c r="EE104" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EF104" t="inlineStr">
+        <is>
+          <t>3.58</t>
+        </is>
+      </c>
+      <c r="EG104" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EH104" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EI104" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EJ104" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EK104" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EL104" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="EM104" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EN104" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EO104" t="inlineStr"/>
+      <c r="EP104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>13</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Al Feiha</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>46025.62152777778</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>5</v>
+      </c>
+      <c r="I105" t="n">
+        <v>5</v>
+      </c>
+      <c r="J105" t="n">
+        <v>4</v>
+      </c>
+      <c r="K105" t="n">
+        <v>6</v>
+      </c>
+      <c r="L105" t="n">
+        <v>10</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1</v>
+      </c>
+      <c r="N105" t="n">
+        <v>2</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>5</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6</v>
+      </c>
+      <c r="S105" t="n">
+        <v>8</v>
+      </c>
+      <c r="T105" t="n">
+        <v>9</v>
+      </c>
+      <c r="U105" t="n">
+        <v>13</v>
+      </c>
+      <c r="V105" t="n">
+        <v>15</v>
+      </c>
+      <c r="W105" t="n">
+        <v>10</v>
+      </c>
+      <c r="X105" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr"/>
+      <c r="AC105" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU105" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA105" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB105" t="n">
+        <v>5125</v>
+      </c>
+      <c r="BC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD105" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ105" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM105" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN105" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT105" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV105" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW105" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX105" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY105" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ105" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CA105" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CB105" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR105" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS105" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU105" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV105" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX105" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY105" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ105" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA105" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB105" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC105" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD105" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE105" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF105" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG105" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DH105" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DI105" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DJ105" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK105" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL105" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DM105" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="DN105" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="DO105" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU105" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV105" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW105" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="DX105" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="DY105" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="DZ105" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA105" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EB105" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EC105" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="ED105" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EE105" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="EF105" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="EG105" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EH105" t="inlineStr">
+        <is>
+          <t>4.31</t>
+        </is>
+      </c>
+      <c r="EI105" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EJ105" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EK105" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EL105" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EM105" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="EN105" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EO105" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EP105" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>13</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Al Taawon</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>46025.72916666666</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" t="n">
+        <v>7</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" t="n">
+        <v>8</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>6</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>13</v>
+      </c>
+      <c r="T106" t="n">
+        <v>7</v>
+      </c>
+      <c r="U106" t="n">
+        <v>19</v>
+      </c>
+      <c r="V106" t="n">
+        <v>7</v>
+      </c>
+      <c r="W106" t="n">
+        <v>17</v>
+      </c>
+      <c r="X106" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA106" t="inlineStr"/>
+      <c r="AB106" t="inlineStr"/>
+      <c r="AC106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR106" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AU106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB106" t="n">
+        <v>5070</v>
+      </c>
+      <c r="BC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD106" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI106" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK106" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM106" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN106" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV106" t="n">
+        <v>78</v>
+      </c>
+      <c r="BW106" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX106" t="n">
+        <v>123</v>
+      </c>
+      <c r="BY106" t="n">
+        <v>68</v>
+      </c>
+      <c r="BZ106" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CA106" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CB106" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="CC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR106" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS106" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU106" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV106" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX106" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY106" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ106" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA106" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB106" t="n">
+        <v>55</v>
+      </c>
+      <c r="DC106" t="n">
+        <v>82</v>
+      </c>
+      <c r="DD106" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DE106" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DF106" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG106" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH106" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DI106" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="DJ106" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK106" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL106" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="DM106" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DN106" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="DO106" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP106" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV106" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW106" t="n">
+        <v>26.83</v>
+      </c>
+      <c r="DX106" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="DY106" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="DZ106" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="EA106" t="inlineStr"/>
+      <c r="EB106" t="inlineStr"/>
+      <c r="EC106" t="inlineStr"/>
+      <c r="ED106" t="inlineStr"/>
+      <c r="EE106" t="inlineStr">
+        <is>
+          <t>6.23</t>
+        </is>
+      </c>
+      <c r="EF106" t="inlineStr">
+        <is>
+          <t>5.12</t>
+        </is>
+      </c>
+      <c r="EG106" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EH106" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EI106" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EJ106" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EK106" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EL106" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EM106" t="inlineStr"/>
+      <c r="EN106" t="inlineStr"/>
+      <c r="EO106" t="inlineStr"/>
+      <c r="EP106" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP106" headerRowCount="1">
-  <autoFilter ref="A1:EP106"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP109" headerRowCount="1">
+  <autoFilter ref="A1:EP109"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP106"/>
+  <dimension ref="A1:EP109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DE2" t="n">
         <v>1.71</v>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2285,7 +2285,7 @@
         <v>2.14</v>
       </c>
       <c r="DE3" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>2.67</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -5558,7 +5558,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DE10" t="n">
         <v>0.14</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6519,7 +6519,7 @@
         <v>2.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -8367,7 +8367,7 @@
         <v>1.8</v>
       </c>
       <c r="DO16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8831,7 +8831,7 @@
         <v>0.99</v>
       </c>
       <c r="DO17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9262,10 +9262,10 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DE18" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF18" t="n">
         <v>1</v>
@@ -9295,7 +9295,7 @@
         <v>2.11</v>
       </c>
       <c r="DO18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -10691,7 +10691,7 @@
         <v>0</v>
       </c>
       <c r="DO21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11171,7 +11171,7 @@
         <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11606,7 +11606,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DE23" t="n">
         <v>1.14</v>
@@ -11639,7 +11639,7 @@
         <v>3.01</v>
       </c>
       <c r="DO23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12569,7 +12569,7 @@
         <v>2.14</v>
       </c>
       <c r="DE25" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DF25" t="n">
         <v>3</v>
@@ -12599,7 +12599,7 @@
         <v>1.06</v>
       </c>
       <c r="DO25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13494,7 +13494,7 @@
         <v>50</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DE27" t="n">
         <v>0.83</v>
@@ -13527,7 +13527,7 @@
         <v>1.42</v>
       </c>
       <c r="DO27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP27" t="b">
         <v>0</v>
@@ -13961,7 +13961,7 @@
         <v>3</v>
       </c>
       <c r="DE28" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -13991,7 +13991,7 @@
         <v>3.72</v>
       </c>
       <c r="DO28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -15399,7 +15399,7 @@
         <v>2.97</v>
       </c>
       <c r="DO31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15672,7 +15672,7 @@
         <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>-1</v>
+        <v>1612</v>
       </c>
       <c r="BG32" t="n">
         <v>2</v>
@@ -15822,7 +15822,7 @@
         <v>0</v>
       </c>
       <c r="DD32" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DE32" t="n">
         <v>2</v>
@@ -15855,7 +15855,7 @@
         <v>2.93</v>
       </c>
       <c r="DO32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16038,8 +16038,16 @@
       <c r="Z33" t="n">
         <v>46</v>
       </c>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Dhamak Club Stadium</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>, Khamis Mushait</t>
+        </is>
+      </c>
       <c r="AC33" t="n">
         <v>3</v>
       </c>
@@ -16128,7 +16136,7 @@
         <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>-1</v>
+        <v>2581</v>
       </c>
       <c r="BG33" t="n">
         <v>2</v>
@@ -16278,7 +16286,7 @@
         <v>75</v>
       </c>
       <c r="DD33" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DE33" t="n">
         <v>1.4</v>
@@ -16311,7 +16319,7 @@
         <v>2.59</v>
       </c>
       <c r="DO33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16588,7 +16596,7 @@
         <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>-1</v>
+        <v>53282</v>
       </c>
       <c r="BG34" t="n">
         <v>2</v>
@@ -17068,7 +17076,7 @@
         <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>-1</v>
+        <v>1038</v>
       </c>
       <c r="BG35" t="n">
         <v>2</v>
@@ -17221,7 +17229,7 @@
         <v>1.17</v>
       </c>
       <c r="DE35" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF35" t="n">
         <v>3</v>
@@ -17251,7 +17259,7 @@
         <v>2.37</v>
       </c>
       <c r="DO35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17548,7 +17556,7 @@
         <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>-1</v>
+        <v>844</v>
       </c>
       <c r="BG36" t="n">
         <v>2</v>
@@ -18020,7 +18028,7 @@
         <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>-1</v>
+        <v>10519</v>
       </c>
       <c r="BG37" t="n">
         <v>2</v>
@@ -18203,7 +18211,7 @@
         <v>2.65</v>
       </c>
       <c r="DO37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -19452,7 +19460,7 @@
         <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>-1</v>
+        <v>14590</v>
       </c>
       <c r="BG40" t="n">
         <v>2</v>
@@ -19924,7 +19932,7 @@
         <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>-1</v>
+        <v>10187</v>
       </c>
       <c r="BG41" t="n">
         <v>2</v>
@@ -20077,7 +20085,7 @@
         <v>1.71</v>
       </c>
       <c r="DE41" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DF41" t="n">
         <v>2</v>
@@ -20107,7 +20115,7 @@
         <v>2</v>
       </c>
       <c r="DO41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20380,7 +20388,7 @@
         <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>-1</v>
+        <v>1788</v>
       </c>
       <c r="BG42" t="n">
         <v>-1</v>
@@ -20563,7 +20571,7 @@
         <v>1.63</v>
       </c>
       <c r="DO42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20852,7 +20860,7 @@
         <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>-1</v>
+        <v>18763</v>
       </c>
       <c r="BG43" t="n">
         <v>2</v>
@@ -21316,7 +21324,7 @@
         <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>-1</v>
+        <v>1884</v>
       </c>
       <c r="BG44" t="n">
         <v>2</v>
@@ -21469,7 +21477,7 @@
         <v>1.4</v>
       </c>
       <c r="DE44" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF44" t="n">
         <v>1.5</v>
@@ -21499,7 +21507,7 @@
         <v>2.13</v>
       </c>
       <c r="DO44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21658,7 +21666,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
         <v>8</v>
@@ -21696,7 +21704,7 @@
         <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE45" t="n">
         <v>1.5</v>
@@ -21780,7 +21788,7 @@
         <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>-1</v>
+        <v>4037</v>
       </c>
       <c r="BG45" t="n">
         <v>2</v>
@@ -21816,13 +21824,13 @@
         <v>0</v>
       </c>
       <c r="BR45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS45" t="n">
         <v>1</v>
       </c>
       <c r="BT45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU45" t="n">
         <v>1</v>
@@ -21963,7 +21971,7 @@
         <v>2.14</v>
       </c>
       <c r="DO45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22244,7 +22252,7 @@
         <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>-1</v>
+        <v>6576</v>
       </c>
       <c r="BG46" t="n">
         <v>2</v>
@@ -22427,7 +22435,7 @@
         <v>2.57</v>
       </c>
       <c r="DO46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22891,7 +22899,7 @@
         <v>1.84</v>
       </c>
       <c r="DO47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23057,7 +23065,7 @@
         <v>7</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
         <v>2</v>
@@ -23101,7 +23109,7 @@
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD48" t="n">
         <v>2</v>
@@ -23221,7 +23229,7 @@
         <v>1</v>
       </c>
       <c r="BQ48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR48" t="n">
         <v>1</v>
@@ -23230,7 +23238,7 @@
         <v>2</v>
       </c>
       <c r="BT48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU48" t="n">
         <v>1</v>
@@ -23537,7 +23545,7 @@
         <v>7</v>
       </c>
       <c r="M49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
         <v>3</v>
@@ -23567,10 +23575,10 @@
         <v>14</v>
       </c>
       <c r="W49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y49" t="n">
         <v>41</v>
@@ -23581,7 +23589,7 @@
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD49" t="n">
         <v>3</v>
@@ -23668,7 +23676,7 @@
         <v>0</v>
       </c>
       <c r="BF49" t="n">
-        <v>-1</v>
+        <v>2473</v>
       </c>
       <c r="BG49" t="n">
         <v>2</v>
@@ -23701,7 +23709,7 @@
         <v>2</v>
       </c>
       <c r="BQ49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR49" t="n">
         <v>1</v>
@@ -23710,7 +23718,7 @@
         <v>3</v>
       </c>
       <c r="BT49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU49" t="n">
         <v>1</v>
@@ -24148,7 +24156,7 @@
         <v>0</v>
       </c>
       <c r="BF50" t="n">
-        <v>-1</v>
+        <v>9345</v>
       </c>
       <c r="BG50" t="n">
         <v>2</v>
@@ -24620,7 +24628,7 @@
         <v>0</v>
       </c>
       <c r="BF51" t="n">
-        <v>-1</v>
+        <v>2169</v>
       </c>
       <c r="BG51" t="n">
         <v>-1</v>
@@ -24803,7 +24811,7 @@
         <v>2.84</v>
       </c>
       <c r="DO51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25088,7 +25096,7 @@
         <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>-1</v>
+        <v>46542</v>
       </c>
       <c r="BG52" t="n">
         <v>2</v>
@@ -25241,7 +25249,7 @@
         <v>1.71</v>
       </c>
       <c r="DE52" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DF52" t="n">
         <v>1.5</v>
@@ -25271,7 +25279,7 @@
         <v>3.18</v>
       </c>
       <c r="DO52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25552,7 +25560,7 @@
         <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>-1</v>
+        <v>6482</v>
       </c>
       <c r="BG53" t="n">
         <v>2</v>
@@ -25702,7 +25710,7 @@
         <v>100</v>
       </c>
       <c r="DD53" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DE53" t="n">
         <v>0.17</v>
@@ -25735,7 +25743,7 @@
         <v>2.21</v>
       </c>
       <c r="DO53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP53" t="b">
         <v>0</v>
@@ -25906,8 +25914,16 @@
       <c r="Z54" t="n">
         <v>38</v>
       </c>
-      <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Prince Turki bin Abdul Aziz Stadium</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>, Riyadh</t>
+        </is>
+      </c>
       <c r="AC54" t="n">
         <v>0</v>
       </c>
@@ -25996,7 +26012,7 @@
         <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>-1</v>
+        <v>2521</v>
       </c>
       <c r="BG54" t="n">
         <v>-1</v>
@@ -26179,7 +26195,7 @@
         <v>2.64</v>
       </c>
       <c r="DO54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26444,7 +26460,7 @@
         <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>-1</v>
+        <v>10520</v>
       </c>
       <c r="BG55" t="n">
         <v>2</v>
@@ -26594,7 +26610,7 @@
         <v>50</v>
       </c>
       <c r="DD55" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DE55" t="n">
         <v>2.17</v>
@@ -26627,7 +26643,7 @@
         <v>3.19</v>
       </c>
       <c r="DO55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26826,8 +26842,16 @@
       <c r="Z56" t="n">
         <v>50</v>
       </c>
-      <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Dhamak Club Stadium</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>, Khamis Mushait</t>
+        </is>
+      </c>
       <c r="AC56" t="n">
         <v>2</v>
       </c>
@@ -26916,7 +26940,7 @@
         <v>0</v>
       </c>
       <c r="BF56" t="n">
-        <v>-1</v>
+        <v>271</v>
       </c>
       <c r="BG56" t="n">
         <v>2</v>
@@ -27066,7 +27090,7 @@
         <v>67</v>
       </c>
       <c r="DD56" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DE56" t="n">
         <v>0.83</v>
@@ -27099,7 +27123,7 @@
         <v>2.65</v>
       </c>
       <c r="DO56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27227,246 +27251,246 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
         <v>45960.72916666666</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
+        <v>9</v>
+      </c>
+      <c r="K57" t="n">
         <v>4</v>
       </c>
-      <c r="K57" t="n">
-        <v>2</v>
-      </c>
       <c r="L57" t="n">
+        <v>13</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
         <v>6</v>
       </c>
-      <c r="M57" t="n">
-        <v>3</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>4</v>
-      </c>
       <c r="R57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U57" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="V57" t="n">
         <v>6</v>
       </c>
       <c r="W57" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="X57" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y57" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="Z57" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD57" t="n">
         <v>3</v>
       </c>
       <c r="AE57" t="n">
-        <v>3.6</v>
+        <v>1.14</v>
       </c>
       <c r="AF57" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.95</v>
+        <v>11.7</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AI57" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AJ57" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AL57" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="AM57" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AN57" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AO57" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AR57" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AS57" t="n">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="AT57" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AU57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>8549</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI57" t="n">
         <v>5</v>
       </c>
-      <c r="AV57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>5097</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>84</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG57" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH57" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI57" t="n">
+      <c r="BJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK57" t="n">
         <v>4</v>
       </c>
-      <c r="BJ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK57" t="n">
-        <v>0</v>
-      </c>
       <c r="BL57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BO57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP57" t="n">
         <v>1</v>
       </c>
       <c r="BQ57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR57" t="n">
         <v>2</v>
       </c>
       <c r="BS57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BU57" t="n">
         <v>1</v>
       </c>
       <c r="BV57" t="n">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="BW57" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="BX57" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="BY57" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="BZ57" t="n">
-        <v>1.01</v>
+        <v>2.19</v>
       </c>
       <c r="CA57" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="CB57" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="CC57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG57" t="n">
         <v>0</v>
@@ -27481,10 +27505,10 @@
         <v>1</v>
       </c>
       <c r="CK57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM57" t="n">
         <v>0</v>
@@ -27502,31 +27526,31 @@
         <v>1</v>
       </c>
       <c r="CR57" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CS57" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="CT57" t="n">
         <v>1</v>
       </c>
       <c r="CU57" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="CV57" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX57" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY57" t="n">
         <v>14</v>
       </c>
-      <c r="CW57" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX57" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY57" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ57" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="DA57" t="n">
         <v>84</v>
@@ -27538,40 +27562,40 @@
         <v>100</v>
       </c>
       <c r="DD57" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="DE57" t="n">
-        <v>2</v>
+        <v>0.17</v>
       </c>
       <c r="DF57" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="DG57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DH57" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DI57" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DJ57" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="DK57" t="n">
         <v>17</v>
       </c>
       <c r="DL57" t="n">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="DM57" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="DN57" t="n">
         <v>2.85</v>
       </c>
       <c r="DO57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27580,13 +27604,13 @@
         <v>1</v>
       </c>
       <c r="DR57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU57" t="b">
         <v>0</v>
@@ -27595,99 +27619,87 @@
         <v>1</v>
       </c>
       <c r="DW57" t="n">
-        <v>29.89</v>
+        <v>32.58</v>
       </c>
       <c r="DX57" t="n">
-        <v>6.19</v>
+        <v>6</v>
       </c>
       <c r="DY57" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="DZ57" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="EA57" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EB57" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EC57" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="ED57" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EE57" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="EF57" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="EG57" t="inlineStr">
         <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="EH57" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
-      <c r="EI57" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EJ57" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="EH57" t="inlineStr"/>
+      <c r="EI57" t="inlineStr"/>
+      <c r="EJ57" t="inlineStr"/>
       <c r="EK57" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EL57" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EM57" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EN57" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EO57" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="EP57" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -27707,254 +27719,246 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>45960.72916666666</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K58" t="n">
+        <v>2</v>
+      </c>
+      <c r="L58" t="n">
+        <v>6</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
         <v>4</v>
       </c>
-      <c r="L58" t="n">
-        <v>13</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2</v>
-      </c>
-      <c r="N58" t="n">
-        <v>3</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
+        <v>4</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
         <v>6</v>
-      </c>
-      <c r="R58" t="n">
-        <v>3</v>
-      </c>
-      <c r="S58" t="n">
-        <v>13</v>
-      </c>
-      <c r="T58" t="n">
-        <v>3</v>
-      </c>
-      <c r="U58" t="n">
-        <v>19</v>
       </c>
       <c r="V58" t="n">
         <v>6</v>
       </c>
       <c r="W58" t="n">
+        <v>14</v>
+      </c>
+      <c r="X58" t="n">
         <v>13</v>
       </c>
-      <c r="X58" t="n">
-        <v>8</v>
-      </c>
       <c r="Y58" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="Z58" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>King Abdullah Sports City</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>, Jeddah</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>5097</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>84</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>981</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI58" t="n">
         <v>4</v>
       </c>
-      <c r="AD58" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN58" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AO58" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ58" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB58" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD58" t="n">
-        <v>67</v>
-      </c>
-      <c r="BE58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF58" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG58" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH58" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI58" t="n">
-        <v>5</v>
-      </c>
       <c r="BJ58" t="n">
         <v>0</v>
       </c>
       <c r="BK58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL58" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM58" t="n">
         <v>4</v>
       </c>
-      <c r="BL58" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM58" t="n">
-        <v>5</v>
-      </c>
       <c r="BN58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BO58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP58" t="n">
         <v>1</v>
       </c>
       <c r="BQ58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR58" t="n">
         <v>2</v>
       </c>
       <c r="BS58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BU58" t="n">
         <v>1</v>
       </c>
       <c r="BV58" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="BW58" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="BX58" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="BY58" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="BZ58" t="n">
-        <v>2.19</v>
+        <v>1.01</v>
       </c>
       <c r="CA58" t="n">
-        <v>0.71</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CB58" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="CC58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG58" t="n">
         <v>0</v>
@@ -27969,10 +27973,10 @@
         <v>1</v>
       </c>
       <c r="CK58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM58" t="n">
         <v>0</v>
@@ -27990,31 +27994,31 @@
         <v>1</v>
       </c>
       <c r="CR58" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS58" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT58" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU58" t="n">
         <v>13</v>
       </c>
-      <c r="CS58" t="n">
+      <c r="CV58" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW58" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX58" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY58" t="n">
         <v>10</v>
       </c>
-      <c r="CT58" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU58" t="n">
-        <v>7</v>
-      </c>
-      <c r="CV58" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW58" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX58" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY58" t="n">
-        <v>14</v>
-      </c>
       <c r="CZ58" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="DA58" t="n">
         <v>84</v>
@@ -28026,40 +28030,40 @@
         <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.2</v>
+        <v>2.17</v>
       </c>
       <c r="DF58" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG58" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI58" t="n">
         <v>1.67</v>
       </c>
-      <c r="DG58" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH58" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI58" t="n">
-        <v>1</v>
-      </c>
       <c r="DJ58" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="DK58" t="n">
         <v>17</v>
       </c>
       <c r="DL58" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="DM58" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="DN58" t="n">
         <v>2.85</v>
       </c>
       <c r="DO58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28068,13 +28072,13 @@
         <v>1</v>
       </c>
       <c r="DR58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU58" t="b">
         <v>0</v>
@@ -28083,87 +28087,99 @@
         <v>1</v>
       </c>
       <c r="DW58" t="n">
-        <v>32.58</v>
+        <v>29.89</v>
       </c>
       <c r="DX58" t="n">
-        <v>6</v>
+        <v>6.19</v>
       </c>
       <c r="DY58" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="DZ58" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA58" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EB58" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EC58" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="ED58" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EE58" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF58" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="EG58" t="inlineStr">
         <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="EH58" t="inlineStr"/>
-      <c r="EI58" t="inlineStr"/>
-      <c r="EJ58" t="inlineStr"/>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="EH58" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EI58" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EJ58" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
       <c r="EK58" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EL58" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EM58" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="EN58" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EO58" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EP58" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.18</t>
         </is>
       </c>
     </row>
@@ -28344,7 +28360,7 @@
         <v>0</v>
       </c>
       <c r="BF59" t="n">
-        <v>-1</v>
+        <v>1242</v>
       </c>
       <c r="BG59" t="n">
         <v>2</v>
@@ -28824,7 +28840,7 @@
         <v>0</v>
       </c>
       <c r="BF60" t="n">
-        <v>-1</v>
+        <v>22293</v>
       </c>
       <c r="BG60" t="n">
         <v>2</v>
@@ -29007,7 +29023,7 @@
         <v>3.38</v>
       </c>
       <c r="DO60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29288,7 +29304,7 @@
         <v>0</v>
       </c>
       <c r="BF61" t="n">
-        <v>-1</v>
+        <v>2959</v>
       </c>
       <c r="BG61" t="n">
         <v>2</v>
@@ -29471,7 +29487,7 @@
         <v>1.4</v>
       </c>
       <c r="DO61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29768,7 +29784,7 @@
         <v>0</v>
       </c>
       <c r="BF62" t="n">
-        <v>-1</v>
+        <v>6119</v>
       </c>
       <c r="BG62" t="n">
         <v>2</v>
@@ -29951,7 +29967,7 @@
         <v>2.42</v>
       </c>
       <c r="DO62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30248,7 +30264,7 @@
         <v>0</v>
       </c>
       <c r="BF63" t="n">
-        <v>-1</v>
+        <v>13504</v>
       </c>
       <c r="BG63" t="n">
         <v>-1</v>
@@ -30720,7 +30736,7 @@
         <v>0</v>
       </c>
       <c r="BF64" t="n">
-        <v>-1</v>
+        <v>16242</v>
       </c>
       <c r="BG64" t="n">
         <v>2</v>
@@ -31176,7 +31192,7 @@
         <v>0</v>
       </c>
       <c r="BF65" t="n">
-        <v>-1</v>
+        <v>1064</v>
       </c>
       <c r="BG65" t="n">
         <v>2</v>
@@ -31326,7 +31342,7 @@
         <v>67</v>
       </c>
       <c r="DD65" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DE65" t="n">
         <v>1.14</v>
@@ -31359,7 +31375,7 @@
         <v>2.02</v>
       </c>
       <c r="DO65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31640,7 +31656,7 @@
         <v>0</v>
       </c>
       <c r="BF66" t="n">
-        <v>-1</v>
+        <v>6765</v>
       </c>
       <c r="BG66" t="n">
         <v>2</v>
@@ -31790,7 +31806,7 @@
         <v>59</v>
       </c>
       <c r="DD66" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DE66" t="n">
         <v>1</v>
@@ -31823,7 +31839,7 @@
         <v>2.65</v>
       </c>
       <c r="DO66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32104,7 +32120,7 @@
         <v>0</v>
       </c>
       <c r="BF67" t="n">
-        <v>-1</v>
+        <v>550</v>
       </c>
       <c r="BG67" t="n">
         <v>2</v>
@@ -32287,7 +32303,7 @@
         <v>2.17</v>
       </c>
       <c r="DO67" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32440,7 +32456,7 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -32484,7 +32500,7 @@
         <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE68" t="n">
         <v>1.57</v>
@@ -32568,13 +32584,13 @@
         <v>0</v>
       </c>
       <c r="BF68" t="n">
-        <v>-1</v>
+        <v>852</v>
       </c>
       <c r="BG68" t="n">
         <v>2</v>
       </c>
       <c r="BH68" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI68" t="n">
         <v>3</v>
@@ -32604,13 +32620,13 @@
         <v>0</v>
       </c>
       <c r="BR68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS68" t="n">
         <v>0</v>
       </c>
       <c r="BT68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU68" t="n">
         <v>1</v>
@@ -32673,10 +32689,10 @@
         <v>1</v>
       </c>
       <c r="CO68" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CP68" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CQ68" t="n">
         <v>1</v>
@@ -33040,7 +33056,7 @@
         <v>0</v>
       </c>
       <c r="BF69" t="n">
-        <v>-1</v>
+        <v>6357</v>
       </c>
       <c r="BG69" t="n">
         <v>2</v>
@@ -33504,7 +33520,7 @@
         <v>0</v>
       </c>
       <c r="BF70" t="n">
-        <v>-1</v>
+        <v>12641</v>
       </c>
       <c r="BG70" t="n">
         <v>2</v>
@@ -33657,7 +33673,7 @@
         <v>0.2</v>
       </c>
       <c r="DE70" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DF70" t="n">
         <v>0</v>
@@ -33687,7 +33703,7 @@
         <v>2.5</v>
       </c>
       <c r="DO70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33968,7 +33984,7 @@
         <v>0</v>
       </c>
       <c r="BF71" t="n">
-        <v>-1</v>
+        <v>7652</v>
       </c>
       <c r="BG71" t="n">
         <v>2</v>
@@ -34151,7 +34167,7 @@
         <v>3.72</v>
       </c>
       <c r="DO71" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34440,7 +34456,7 @@
         <v>0</v>
       </c>
       <c r="BF72" t="n">
-        <v>-1</v>
+        <v>1895</v>
       </c>
       <c r="BG72" t="n">
         <v>2</v>
@@ -34928,7 +34944,7 @@
         <v>0</v>
       </c>
       <c r="BF73" t="n">
-        <v>-1</v>
+        <v>46027</v>
       </c>
       <c r="BG73" t="n">
         <v>2</v>
@@ -35400,7 +35416,7 @@
         <v>0</v>
       </c>
       <c r="BF74" t="n">
-        <v>-1</v>
+        <v>3583</v>
       </c>
       <c r="BG74" t="n">
         <v>2</v>
@@ -35583,7 +35599,7 @@
         <v>2.12</v>
       </c>
       <c r="DO74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35736,7 +35752,7 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75" t="n">
         <v>1</v>
@@ -35774,21 +35790,13 @@
       <c r="Z75" t="n">
         <v>35</v>
       </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>King Abdullah Sports City</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>, Jeddah</t>
-        </is>
-      </c>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
         <v>2</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE75" t="n">
         <v>1.29</v>
@@ -35872,7 +35880,7 @@
         <v>0</v>
       </c>
       <c r="BF75" t="n">
-        <v>-1</v>
+        <v>13447</v>
       </c>
       <c r="BG75" t="n">
         <v>2</v>
@@ -35908,13 +35916,13 @@
         <v>1</v>
       </c>
       <c r="BR75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS75" t="n">
         <v>0</v>
       </c>
       <c r="BT75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU75" t="n">
         <v>1</v>
@@ -36025,7 +36033,7 @@
         <v>1.71</v>
       </c>
       <c r="DE75" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF75" t="n">
         <v>0.75</v>
@@ -36055,7 +36063,7 @@
         <v>2.45</v>
       </c>
       <c r="DO75" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36352,7 +36360,7 @@
         <v>0</v>
       </c>
       <c r="BF76" t="n">
-        <v>-1</v>
+        <v>17404</v>
       </c>
       <c r="BG76" t="n">
         <v>2</v>
@@ -36535,7 +36543,7 @@
         <v>3.13</v>
       </c>
       <c r="DO76" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36808,7 +36816,7 @@
         <v>0</v>
       </c>
       <c r="BF77" t="n">
-        <v>-1</v>
+        <v>624</v>
       </c>
       <c r="BG77" t="n">
         <v>2</v>
@@ -36958,7 +36966,7 @@
         <v>75</v>
       </c>
       <c r="DD77" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DE77" t="n">
         <v>0.14</v>
@@ -36991,7 +36999,7 @@
         <v>2.28</v>
       </c>
       <c r="DO77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -37272,7 +37280,7 @@
         <v>0</v>
       </c>
       <c r="BF78" t="n">
-        <v>-1</v>
+        <v>2992</v>
       </c>
       <c r="BG78" t="n">
         <v>2</v>
@@ -37700,7 +37708,7 @@
         <v>0</v>
       </c>
       <c r="BF79" t="n">
-        <v>-1</v>
+        <v>19200</v>
       </c>
       <c r="BG79" t="n">
         <v>-1</v>
@@ -37883,7 +37891,7 @@
         <v>3.63</v>
       </c>
       <c r="DO79" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -38029,7 +38037,7 @@
         <v>8</v>
       </c>
       <c r="M80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N80" t="n">
         <v>2</v>
@@ -38073,7 +38081,7 @@
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD80" t="n">
         <v>2</v>
@@ -38160,7 +38168,7 @@
         <v>0</v>
       </c>
       <c r="BF80" t="n">
-        <v>-1</v>
+        <v>2851</v>
       </c>
       <c r="BG80" t="n">
         <v>2</v>
@@ -38193,7 +38201,7 @@
         <v>1</v>
       </c>
       <c r="BQ80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR80" t="n">
         <v>1</v>
@@ -38202,7 +38210,7 @@
         <v>1</v>
       </c>
       <c r="BT80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU80" t="n">
         <v>1</v>
@@ -38648,7 +38656,7 @@
         <v>0</v>
       </c>
       <c r="BF81" t="n">
-        <v>-1</v>
+        <v>26003</v>
       </c>
       <c r="BG81" t="n">
         <v>2</v>
@@ -39100,7 +39108,7 @@
         <v>0</v>
       </c>
       <c r="BF82" t="n">
-        <v>-1</v>
+        <v>5050</v>
       </c>
       <c r="BG82" t="n">
         <v>2</v>
@@ -39253,7 +39261,7 @@
         <v>2.17</v>
       </c>
       <c r="DE82" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF82" t="n">
         <v>2.25</v>
@@ -39283,7 +39291,7 @@
         <v>2.51</v>
       </c>
       <c r="DO82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39564,7 +39572,7 @@
         <v>0</v>
       </c>
       <c r="BF83" t="n">
-        <v>-1</v>
+        <v>647</v>
       </c>
       <c r="BG83" t="n">
         <v>2</v>
@@ -39747,7 +39755,7 @@
         <v>2.19</v>
       </c>
       <c r="DO83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP83" t="b">
         <v>0</v>
@@ -40052,7 +40060,7 @@
         <v>0</v>
       </c>
       <c r="BF84" t="n">
-        <v>-1</v>
+        <v>965</v>
       </c>
       <c r="BG84" t="n">
         <v>2</v>
@@ -40235,7 +40243,7 @@
         <v>2.45</v>
       </c>
       <c r="DO84" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40532,7 +40540,7 @@
         <v>0</v>
       </c>
       <c r="BF85" t="n">
-        <v>-1</v>
+        <v>891</v>
       </c>
       <c r="BG85" t="n">
         <v>2</v>
@@ -40715,7 +40723,7 @@
         <v>2.29</v>
       </c>
       <c r="DO85" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40968,7 +40976,7 @@
         <v>0</v>
       </c>
       <c r="BF86" t="n">
-        <v>-1</v>
+        <v>10982</v>
       </c>
       <c r="BG86" t="n">
         <v>2</v>
@@ -41396,7 +41404,7 @@
         <v>0</v>
       </c>
       <c r="BF87" t="n">
-        <v>-1</v>
+        <v>1895</v>
       </c>
       <c r="BG87" t="n">
         <v>2</v>
@@ -41876,7 +41884,7 @@
         <v>0</v>
       </c>
       <c r="BF88" t="n">
-        <v>-1</v>
+        <v>13300</v>
       </c>
       <c r="BG88" t="n">
         <v>2</v>
@@ -42059,7 +42067,7 @@
         <v>3.44</v>
       </c>
       <c r="DO88" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42340,7 +42348,7 @@
         <v>0</v>
       </c>
       <c r="BF89" t="n">
-        <v>-1</v>
+        <v>6106</v>
       </c>
       <c r="BG89" t="n">
         <v>2</v>
@@ -42490,7 +42498,7 @@
         <v>88</v>
       </c>
       <c r="DD89" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DE89" t="n">
         <v>1</v>
@@ -42523,7 +42531,7 @@
         <v>2.71</v>
       </c>
       <c r="DO89" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42776,7 +42784,7 @@
         <v>0</v>
       </c>
       <c r="BF90" t="n">
-        <v>-1</v>
+        <v>19472</v>
       </c>
       <c r="BG90" t="n">
         <v>2</v>
@@ -43244,7 +43252,7 @@
         <v>0</v>
       </c>
       <c r="BF91" t="n">
-        <v>-1</v>
+        <v>15871</v>
       </c>
       <c r="BG91" t="n">
         <v>2</v>
@@ -43724,7 +43732,7 @@
         <v>0</v>
       </c>
       <c r="BF92" t="n">
-        <v>-1</v>
+        <v>3294</v>
       </c>
       <c r="BG92" t="n">
         <v>-1</v>
@@ -44011,12 +44019,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
@@ -44026,25 +44034,25 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L93" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -44053,120 +44061,128 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R93" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S93" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T93" t="n">
         <v>4</v>
       </c>
       <c r="U93" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V93" t="n">
+        <v>11</v>
+      </c>
+      <c r="W93" t="n">
+        <v>8</v>
+      </c>
+      <c r="X93" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>Prince Turki bin Abdul Aziz Stadium</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>, Riyadh</t>
+        </is>
+      </c>
+      <c r="AC93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD93" t="n">
         <v>5</v>
       </c>
-      <c r="W93" t="n">
-        <v>13</v>
-      </c>
-      <c r="X93" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA93" t="inlineStr"/>
-      <c r="AB93" t="inlineStr"/>
-      <c r="AC93" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD93" t="n">
-        <v>0</v>
-      </c>
       <c r="AE93" t="n">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="AF93" t="n">
-        <v>4.35</v>
+        <v>3.1</v>
       </c>
       <c r="AG93" t="n">
-        <v>6.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AI93" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="AJ93" t="n">
-        <v>2.63</v>
+        <v>3.42</v>
       </c>
       <c r="AK93" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AL93" t="n">
-        <v>1.71</v>
+        <v>1.99</v>
       </c>
       <c r="AM93" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AN93" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AO93" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AR93" t="n">
-        <v>2.39</v>
+        <v>2.91</v>
       </c>
       <c r="AS93" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="AT93" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AU93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV93" t="n">
         <v>0</v>
       </c>
       <c r="AW93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX93" t="n">
         <v>1</v>
       </c>
       <c r="AY93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB93" t="n">
-        <v>5074</v>
+        <v>5089</v>
       </c>
       <c r="BC93" t="n">
         <v>0</v>
       </c>
       <c r="BD93" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="BE93" t="n">
         <v>0</v>
@@ -44181,178 +44197,178 @@
         <v>1</v>
       </c>
       <c r="BI93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BJ93" t="n">
         <v>1</v>
       </c>
       <c r="BK93" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL93" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM93" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN93" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT93" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV93" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW93" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX93" t="n">
+        <v>105</v>
+      </c>
+      <c r="BY93" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ93" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CA93" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CB93" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM93" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR93" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS93" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU93" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV93" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX93" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY93" t="n">
         <v>7</v>
       </c>
-      <c r="BL93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM93" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN93" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO93" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ93" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS93" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT93" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU93" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV93" t="n">
-        <v>63</v>
-      </c>
-      <c r="BW93" t="n">
-        <v>29</v>
-      </c>
-      <c r="BX93" t="n">
-        <v>117</v>
-      </c>
-      <c r="BY93" t="n">
-        <v>88</v>
-      </c>
-      <c r="BZ93" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CA93" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="CB93" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="CC93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR93" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS93" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU93" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV93" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX93" t="n">
-        <v>2</v>
-      </c>
-      <c r="CY93" t="n">
-        <v>13</v>
-      </c>
       <c r="CZ93" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="DA93" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="DB93" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="DC93" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="DD93" t="n">
-        <v>2.17</v>
+        <v>1.17</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.14</v>
+        <v>1.71</v>
       </c>
       <c r="DF93" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="DG93" t="n">
-        <v>0.17</v>
+        <v>1.5</v>
       </c>
       <c r="DH93" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="DI93" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="DJ93" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="DK93" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="DL93" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="DM93" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="DN93" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DO93" t="n">
         <v>12</v>
@@ -44361,10 +44377,10 @@
         <v>1</v>
       </c>
       <c r="DQ93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS93" t="b">
         <v>0</v>
@@ -44376,17 +44392,17 @@
         <v>0</v>
       </c>
       <c r="DV93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW93" t="n">
-        <v>17.94</v>
+        <v>18.59</v>
       </c>
       <c r="DX93" t="n">
-        <v>6.89</v>
+        <v>5.81</v>
       </c>
       <c r="DY93" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="DZ93" t="inlineStr">
@@ -44396,52 +44412,52 @@
       </c>
       <c r="EA93" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EB93" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EC93" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="ED93" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EE93" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EF93" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EG93" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EH93" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="EI93" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EJ93" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EK93" t="inlineStr">
@@ -44451,27 +44467,27 @@
       </c>
       <c r="EL93" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EM93" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="EN93" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EO93" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EP93" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
@@ -44491,12 +44507,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
@@ -44506,25 +44522,25 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K94" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N94" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -44533,326 +44549,318 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S94" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T94" t="n">
         <v>4</v>
       </c>
       <c r="U94" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="V94" t="n">
+        <v>5</v>
+      </c>
+      <c r="W94" t="n">
+        <v>13</v>
+      </c>
+      <c r="X94" t="n">
         <v>11</v>
       </c>
-      <c r="W94" t="n">
-        <v>8</v>
-      </c>
-      <c r="X94" t="n">
+      <c r="Y94" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr"/>
+      <c r="AC94" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>5074</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>72</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF94" t="n">
+        <v>4294</v>
+      </c>
+      <c r="BG94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI94" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK94" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN94" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV94" t="n">
+        <v>63</v>
+      </c>
+      <c r="BW94" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX94" t="n">
+        <v>117</v>
+      </c>
+      <c r="BY94" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ94" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CA94" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="CB94" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR94" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS94" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU94" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV94" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX94" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY94" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ94" t="n">
+        <v>72</v>
+      </c>
+      <c r="DA94" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB94" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC94" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD94" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DE94" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DF94" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG94" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DH94" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DI94" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DJ94" t="n">
+        <v>29</v>
+      </c>
+      <c r="DK94" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL94" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DM94" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DN94" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DO94" t="n">
         <v>12</v>
       </c>
-      <c r="Y94" t="n">
-        <v>51</v>
-      </c>
-      <c r="Z94" t="n">
-        <v>49</v>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>Prince Turki bin Abdul Aziz Stadium</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>, Riyadh</t>
-        </is>
-      </c>
-      <c r="AC94" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD94" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE94" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF94" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG94" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH94" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI94" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AJ94" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AK94" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL94" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AM94" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AN94" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO94" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AP94" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AQ94" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR94" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AS94" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AT94" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU94" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW94" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX94" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY94" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ94" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB94" t="n">
-        <v>5089</v>
-      </c>
-      <c r="BC94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD94" t="n">
-        <v>64</v>
-      </c>
-      <c r="BE94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF94" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG94" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI94" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK94" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL94" t="n">
-        <v>4</v>
-      </c>
-      <c r="BM94" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN94" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP94" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR94" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS94" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT94" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV94" t="n">
-        <v>45</v>
-      </c>
-      <c r="BW94" t="n">
-        <v>48</v>
-      </c>
-      <c r="BX94" t="n">
-        <v>105</v>
-      </c>
-      <c r="BY94" t="n">
-        <v>80</v>
-      </c>
-      <c r="BZ94" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CA94" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CB94" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="CC94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM94" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR94" t="n">
-        <v>28</v>
-      </c>
-      <c r="CS94" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU94" t="n">
-        <v>12</v>
-      </c>
-      <c r="CV94" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX94" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY94" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ94" t="n">
-        <v>45</v>
-      </c>
-      <c r="DA94" t="n">
-        <v>74</v>
-      </c>
-      <c r="DB94" t="n">
-        <v>37</v>
-      </c>
-      <c r="DC94" t="n">
-        <v>65</v>
-      </c>
-      <c r="DD94" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DE94" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DF94" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DG94" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DH94" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DI94" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ94" t="n">
-        <v>55</v>
-      </c>
-      <c r="DK94" t="n">
-        <v>27</v>
-      </c>
-      <c r="DL94" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="DM94" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="DN94" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="DO94" t="n">
-        <v>11</v>
-      </c>
       <c r="DP94" t="b">
         <v>1</v>
       </c>
       <c r="DQ94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS94" t="b">
         <v>0</v>
@@ -44864,17 +44872,17 @@
         <v>0</v>
       </c>
       <c r="DV94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW94" t="n">
-        <v>18.59</v>
+        <v>17.94</v>
       </c>
       <c r="DX94" t="n">
-        <v>5.81</v>
+        <v>6.89</v>
       </c>
       <c r="DY94" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="DZ94" t="inlineStr">
@@ -44884,52 +44892,52 @@
       </c>
       <c r="EA94" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EB94" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EC94" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="ED94" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EE94" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="EF94" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="EG94" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EH94" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="EI94" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EJ94" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EK94" t="inlineStr">
@@ -44939,27 +44947,27 @@
       </c>
       <c r="EL94" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EM94" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="EN94" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EO94" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="EP94" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.28</t>
         </is>
       </c>
     </row>
@@ -45140,7 +45148,7 @@
         <v>0</v>
       </c>
       <c r="BF95" t="n">
-        <v>-1</v>
+        <v>4259</v>
       </c>
       <c r="BG95" t="n">
         <v>2</v>
@@ -45592,7 +45600,7 @@
         <v>0</v>
       </c>
       <c r="BF96" t="n">
-        <v>-1</v>
+        <v>9512</v>
       </c>
       <c r="BG96" t="n">
         <v>2</v>
@@ -45919,7 +45927,7 @@
         <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
@@ -45957,7 +45965,7 @@
       <c r="AA97" t="inlineStr"/>
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD97" t="n">
         <v>1</v>
@@ -46044,7 +46052,7 @@
         <v>0</v>
       </c>
       <c r="BF97" t="n">
-        <v>-1</v>
+        <v>1214</v>
       </c>
       <c r="BG97" t="n">
         <v>2</v>
@@ -46077,7 +46085,7 @@
         <v>1</v>
       </c>
       <c r="BQ97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR97" t="n">
         <v>0</v>
@@ -46086,7 +46094,7 @@
         <v>2</v>
       </c>
       <c r="BT97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU97" t="n">
         <v>1</v>
@@ -46227,7 +46235,7 @@
         <v>2.15</v>
       </c>
       <c r="DO97" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46508,7 +46516,7 @@
         <v>0</v>
       </c>
       <c r="BF98" t="n">
-        <v>-1</v>
+        <v>7052</v>
       </c>
       <c r="BG98" t="n">
         <v>2</v>
@@ -46691,7 +46699,7 @@
         <v>3.06</v>
       </c>
       <c r="DO98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46799,76 +46807,76 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
         <v>46022.72916666666</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" t="n">
         <v>3</v>
       </c>
       <c r="I99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J99" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K99" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L99" t="n">
         <v>12</v>
       </c>
       <c r="M99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N99" t="n">
         <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R99" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S99" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T99" t="n">
+        <v>5</v>
+      </c>
+      <c r="U99" t="n">
         <v>14</v>
       </c>
-      <c r="U99" t="n">
+      <c r="V99" t="n">
         <v>11</v>
       </c>
-      <c r="V99" t="n">
-        <v>24</v>
-      </c>
       <c r="W99" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y99" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z99" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr"/>
@@ -46879,88 +46887,88 @@
         <v>1</v>
       </c>
       <c r="AE99" t="n">
-        <v>10</v>
+        <v>5.59</v>
       </c>
       <c r="AF99" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="AG99" t="n">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI99" t="n">
-        <v>1.31</v>
+        <v>1.72</v>
       </c>
       <c r="AJ99" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AK99" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AL99" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AM99" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN99" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO99" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AS99" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AT99" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AU99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ99" t="n">
         <v>2</v>
       </c>
       <c r="BA99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB99" t="n">
-        <v>5066</v>
+        <v>5068</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BE99" t="n">
         <v>0</v>
       </c>
       <c r="BF99" t="n">
-        <v>-1</v>
+        <v>2556</v>
       </c>
       <c r="BG99" t="n">
         <v>2</v>
@@ -46969,181 +46977,181 @@
         <v>1</v>
       </c>
       <c r="BI99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BL99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV99" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW99" t="n">
+        <v>61</v>
+      </c>
+      <c r="BX99" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY99" t="n">
+        <v>116</v>
+      </c>
+      <c r="BZ99" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CA99" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CB99" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CC99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR99" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS99" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU99" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV99" t="n">
         <v>8</v>
       </c>
-      <c r="BM99" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN99" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO99" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ99" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR99" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS99" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT99" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU99" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV99" t="n">
-        <v>18</v>
-      </c>
-      <c r="BW99" t="n">
-        <v>68</v>
-      </c>
-      <c r="BX99" t="n">
-        <v>57</v>
-      </c>
-      <c r="BY99" t="n">
-        <v>110</v>
-      </c>
-      <c r="BZ99" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="CA99" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="CB99" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="CC99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR99" t="n">
-        <v>6</v>
-      </c>
-      <c r="CS99" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU99" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV99" t="n">
-        <v>11</v>
-      </c>
       <c r="CW99" t="n">
         <v>1</v>
       </c>
       <c r="CX99" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="CY99" t="n">
         <v>9</v>
       </c>
       <c r="CZ99" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="DA99" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="DB99" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="DC99" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="DD99" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="DE99" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="DF99" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DG99" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="DH99" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="DI99" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="DJ99" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="DK99" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="DL99" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="DM99" t="n">
-        <v>1.88</v>
+        <v>1.41</v>
       </c>
       <c r="DN99" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="DO99" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47158,7 +47166,7 @@
         <v>1</v>
       </c>
       <c r="DT99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU99" t="b">
         <v>0</v>
@@ -47167,14 +47175,14 @@
         <v>1</v>
       </c>
       <c r="DW99" t="n">
-        <v>15.88</v>
+        <v>13.4</v>
       </c>
       <c r="DX99" t="n">
-        <v>5.15</v>
+        <v>4.76</v>
       </c>
       <c r="DY99" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="DZ99" t="inlineStr">
@@ -47182,68 +47190,32 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA99" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EB99" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
+      <c r="EA99" t="inlineStr"/>
+      <c r="EB99" t="inlineStr"/>
       <c r="EC99" t="inlineStr"/>
       <c r="ED99" t="inlineStr"/>
       <c r="EE99" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EF99" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="EG99" t="inlineStr">
         <is>
-          <t>8.72</t>
-        </is>
-      </c>
-      <c r="EH99" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EI99" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EJ99" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="EK99" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EL99" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EM99" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EN99" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="EH99" t="inlineStr"/>
+      <c r="EI99" t="inlineStr"/>
+      <c r="EJ99" t="inlineStr"/>
+      <c r="EK99" t="inlineStr"/>
+      <c r="EL99" t="inlineStr"/>
+      <c r="EM99" t="inlineStr"/>
+      <c r="EN99" t="inlineStr"/>
       <c r="EO99" t="inlineStr"/>
       <c r="EP99" t="inlineStr"/>
     </row>
@@ -47263,76 +47235,76 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
         <v>46022.72916666666</v>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
         <v>3</v>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K100" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L100" t="n">
         <v>12</v>
       </c>
       <c r="M100" t="n">
+        <v>2</v>
+      </c>
+      <c r="N100" t="n">
+        <v>1</v>
+      </c>
+      <c r="O100" t="n">
+        <v>1</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
         <v>4</v>
       </c>
-      <c r="N100" t="n">
-        <v>1</v>
-      </c>
-      <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>6</v>
-      </c>
       <c r="R100" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T100" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="U100" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V100" t="n">
+        <v>24</v>
+      </c>
+      <c r="W100" t="n">
         <v>11</v>
       </c>
-      <c r="W100" t="n">
-        <v>9</v>
-      </c>
       <c r="X100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y100" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z100" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr"/>
@@ -47343,88 +47315,88 @@
         <v>1</v>
       </c>
       <c r="AE100" t="n">
-        <v>5.59</v>
+        <v>10</v>
       </c>
       <c r="AF100" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AU100" t="n">
         <v>4</v>
       </c>
-      <c r="AG100" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI100" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AJ100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK100" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL100" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU100" t="n">
-        <v>5</v>
-      </c>
       <c r="AV100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ100" t="n">
         <v>2</v>
       </c>
       <c r="BA100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB100" t="n">
-        <v>5068</v>
+        <v>5066</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
       </c>
       <c r="BF100" t="n">
-        <v>-1</v>
+        <v>9253</v>
       </c>
       <c r="BG100" t="n">
         <v>2</v>
@@ -47433,181 +47405,181 @@
         <v>1</v>
       </c>
       <c r="BI100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL100" t="n">
+        <v>8</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV100" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW100" t="n">
+        <v>68</v>
+      </c>
+      <c r="BX100" t="n">
+        <v>57</v>
+      </c>
+      <c r="BY100" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ100" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="CC100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR100" t="n">
         <v>6</v>
       </c>
-      <c r="BL100" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM100" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN100" t="n">
+      <c r="CS100" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU100" t="n">
         <v>9</v>
       </c>
-      <c r="BO100" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ100" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR100" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS100" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT100" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU100" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV100" t="n">
-        <v>59</v>
-      </c>
-      <c r="BW100" t="n">
-        <v>61</v>
-      </c>
-      <c r="BX100" t="n">
-        <v>99</v>
-      </c>
-      <c r="BY100" t="n">
-        <v>116</v>
-      </c>
-      <c r="BZ100" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="CA100" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CB100" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="CC100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR100" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS100" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU100" t="n">
-        <v>14</v>
-      </c>
       <c r="CV100" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CW100" t="n">
         <v>1</v>
       </c>
       <c r="CX100" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="CY100" t="n">
         <v>9</v>
       </c>
       <c r="CZ100" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="DA100" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="DB100" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="DC100" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="DD100" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="DE100" t="n">
-        <v>1.67</v>
+        <v>2.67</v>
       </c>
       <c r="DF100" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DG100" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="DH100" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="DI100" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="DJ100" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="DK100" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="DL100" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="DM100" t="n">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="DN100" t="n">
-        <v>3.04</v>
+        <v>3.24</v>
       </c>
       <c r="DO100" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47622,7 +47594,7 @@
         <v>1</v>
       </c>
       <c r="DT100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU100" t="b">
         <v>0</v>
@@ -47631,14 +47603,14 @@
         <v>1</v>
       </c>
       <c r="DW100" t="n">
-        <v>13.4</v>
+        <v>15.88</v>
       </c>
       <c r="DX100" t="n">
-        <v>4.76</v>
+        <v>5.15</v>
       </c>
       <c r="DY100" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="DZ100" t="inlineStr">
@@ -47646,32 +47618,68 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA100" t="inlineStr"/>
-      <c r="EB100" t="inlineStr"/>
+      <c r="EA100" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EB100" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
       <c r="EC100" t="inlineStr"/>
       <c r="ED100" t="inlineStr"/>
       <c r="EE100" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EF100" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="EG100" t="inlineStr">
         <is>
-          <t>5.07</t>
-        </is>
-      </c>
-      <c r="EH100" t="inlineStr"/>
-      <c r="EI100" t="inlineStr"/>
-      <c r="EJ100" t="inlineStr"/>
-      <c r="EK100" t="inlineStr"/>
-      <c r="EL100" t="inlineStr"/>
-      <c r="EM100" t="inlineStr"/>
-      <c r="EN100" t="inlineStr"/>
+          <t>8.72</t>
+        </is>
+      </c>
+      <c r="EH100" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EI100" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EJ100" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="EK100" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EL100" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EM100" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EN100" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
       <c r="EO100" t="inlineStr"/>
       <c r="EP100" t="inlineStr"/>
     </row>
@@ -50029,13 +50037,13 @@
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
       <c r="S106" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T106" t="n">
         <v>7</v>
@@ -50208,13 +50216,13 @@
         <v>68</v>
       </c>
       <c r="BZ106" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="CA106" t="n">
         <v>0.6</v>
       </c>
       <c r="CB106" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="CC106" t="n">
         <v>0</v>
@@ -50418,6 +50426,1370 @@
       <c r="EN106" t="inlineStr"/>
       <c r="EO106" t="inlineStr"/>
       <c r="EP106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>13</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Al Hazm</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Neom SC</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>46026.62847222222</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" t="n">
+        <v>3</v>
+      </c>
+      <c r="J107" t="n">
+        <v>2</v>
+      </c>
+      <c r="K107" t="n">
+        <v>3</v>
+      </c>
+      <c r="L107" t="n">
+        <v>5</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>1</v>
+      </c>
+      <c r="R107" t="n">
+        <v>5</v>
+      </c>
+      <c r="S107" t="n">
+        <v>11</v>
+      </c>
+      <c r="T107" t="n">
+        <v>5</v>
+      </c>
+      <c r="U107" t="n">
+        <v>12</v>
+      </c>
+      <c r="V107" t="n">
+        <v>10</v>
+      </c>
+      <c r="W107" t="n">
+        <v>14</v>
+      </c>
+      <c r="X107" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr"/>
+      <c r="AC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ107" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB107" t="n">
+        <v>5097</v>
+      </c>
+      <c r="BC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD107" t="n">
+        <v>53</v>
+      </c>
+      <c r="BE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ107" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM107" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV107" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW107" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX107" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY107" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ107" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CA107" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CB107" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CC107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR107" t="n">
+        <v>32</v>
+      </c>
+      <c r="CS107" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU107" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV107" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX107" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY107" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ107" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA107" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB107" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC107" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD107" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DE107" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DF107" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DG107" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH107" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DI107" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DJ107" t="n">
+        <v>58</v>
+      </c>
+      <c r="DK107" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL107" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DM107" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DN107" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DO107" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW107" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="DX107" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="DY107" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="DZ107" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA107" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EB107" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EC107" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="ED107" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EE107" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EF107" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="EG107" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="EH107" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EI107" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EJ107" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EK107" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EL107" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EM107" t="inlineStr"/>
+      <c r="EN107" t="inlineStr"/>
+      <c r="EO107" t="inlineStr"/>
+      <c r="EP107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>13</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Al Quadisiya</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Al Riyadh</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>46026.72916666666</v>
+      </c>
+      <c r="G108" t="n">
+        <v>4</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>4</v>
+      </c>
+      <c r="J108" t="n">
+        <v>9</v>
+      </c>
+      <c r="K108" t="n">
+        <v>4</v>
+      </c>
+      <c r="L108" t="n">
+        <v>13</v>
+      </c>
+      <c r="M108" t="n">
+        <v>3</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>7</v>
+      </c>
+      <c r="R108" t="n">
+        <v>3</v>
+      </c>
+      <c r="S108" t="n">
+        <v>8</v>
+      </c>
+      <c r="T108" t="n">
+        <v>9</v>
+      </c>
+      <c r="U108" t="n">
+        <v>15</v>
+      </c>
+      <c r="V108" t="n">
+        <v>12</v>
+      </c>
+      <c r="W108" t="n">
+        <v>12</v>
+      </c>
+      <c r="X108" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr"/>
+      <c r="AC108" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU108" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB108" t="n">
+        <v>5068</v>
+      </c>
+      <c r="BC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD108" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF108" t="n">
+        <v>6160</v>
+      </c>
+      <c r="BG108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI108" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK108" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM108" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN108" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV108" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW108" t="n">
+        <v>52</v>
+      </c>
+      <c r="BX108" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY108" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ108" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CA108" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CB108" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CC108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR108" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS108" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU108" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV108" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX108" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY108" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ108" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA108" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB108" t="n">
+        <v>60</v>
+      </c>
+      <c r="DC108" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD108" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DE108" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DF108" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DG108" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DH108" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DI108" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DJ108" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK108" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL108" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="DM108" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DN108" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="DO108" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP108" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ108" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR108" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS108" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW108" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="DX108" t="n">
+        <v>12.01</v>
+      </c>
+      <c r="DY108" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="DZ108" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA108" t="inlineStr"/>
+      <c r="EB108" t="inlineStr"/>
+      <c r="EC108" t="inlineStr"/>
+      <c r="ED108" t="inlineStr"/>
+      <c r="EE108" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="EF108" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="EG108" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EH108" t="inlineStr"/>
+      <c r="EI108" t="inlineStr"/>
+      <c r="EJ108" t="inlineStr"/>
+      <c r="EK108" t="inlineStr"/>
+      <c r="EL108" t="inlineStr"/>
+      <c r="EM108" t="inlineStr"/>
+      <c r="EN108" t="inlineStr"/>
+      <c r="EO108" t="inlineStr"/>
+      <c r="EP108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>13</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Dhamk</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>46026.72916666666</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2</v>
+      </c>
+      <c r="I109" t="n">
+        <v>2</v>
+      </c>
+      <c r="J109" t="n">
+        <v>2</v>
+      </c>
+      <c r="K109" t="n">
+        <v>9</v>
+      </c>
+      <c r="L109" t="n">
+        <v>11</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1</v>
+      </c>
+      <c r="N109" t="n">
+        <v>3</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>5</v>
+      </c>
+      <c r="S109" t="n">
+        <v>8</v>
+      </c>
+      <c r="T109" t="n">
+        <v>11</v>
+      </c>
+      <c r="U109" t="n">
+        <v>8</v>
+      </c>
+      <c r="V109" t="n">
+        <v>16</v>
+      </c>
+      <c r="W109" t="n">
+        <v>8</v>
+      </c>
+      <c r="X109" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>Dhamak Club Stadium</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>, Khamis Mushait</t>
+        </is>
+      </c>
+      <c r="AC109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB109" t="n">
+        <v>5066</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ109" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL109" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV109" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW109" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX109" t="n">
+        <v>71</v>
+      </c>
+      <c r="BY109" t="n">
+        <v>119</v>
+      </c>
+      <c r="BZ109" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CA109" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CB109" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR109" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS109" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU109" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV109" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX109" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY109" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ109" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA109" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB109" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC109" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD109" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE109" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DF109" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DG109" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DH109" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DI109" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="DJ109" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK109" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL109" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DM109" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DN109" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="DO109" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW109" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="DX109" t="n">
+        <v>4</v>
+      </c>
+      <c r="DY109" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="DZ109" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="EA109" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EB109" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EC109" t="inlineStr"/>
+      <c r="ED109" t="inlineStr"/>
+      <c r="EE109" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EF109" t="inlineStr">
+        <is>
+          <t>7.73</t>
+        </is>
+      </c>
+      <c r="EG109" t="inlineStr">
+        <is>
+          <t>11.34</t>
+        </is>
+      </c>
+      <c r="EH109" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EI109" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EJ109" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EK109" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EL109" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EM109" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EN109" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EO109" t="inlineStr"/>
+      <c r="EP109" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP109" headerRowCount="1">
-  <autoFilter ref="A1:EP109"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP118" headerRowCount="1">
+  <autoFilter ref="A1:EP118"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP109"/>
+  <dimension ref="A1:EP118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1797,7 +1797,7 @@
         <v>0.5</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE5" t="n">
         <v>0.17</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3670,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DE6" t="n">
         <v>2.17</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4175,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5086,10 +5086,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE9" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6033,7 +6033,7 @@
         <v>1.71</v>
       </c>
       <c r="DE11" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -6063,7 +6063,7 @@
         <v>0.93</v>
       </c>
       <c r="DO11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP11" t="b">
         <v>0</v>
@@ -6489,7 +6489,7 @@
         <v>0.83</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6519,7 +6519,7 @@
         <v>2.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6953,7 +6953,7 @@
         <v>1.71</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7406,7 +7406,7 @@
         <v>50</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DE14" t="n">
         <v>1</v>
@@ -7439,7 +7439,7 @@
         <v>0.87</v>
       </c>
       <c r="DO14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7870,7 +7870,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE15" t="n">
         <v>2.5</v>
@@ -7903,7 +7903,7 @@
         <v>0.91</v>
       </c>
       <c r="DO15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8334,10 +8334,10 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF16" t="n">
         <v>3</v>
@@ -8367,7 +8367,7 @@
         <v>1.8</v>
       </c>
       <c r="DO16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8798,7 +8798,7 @@
         <v>50</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DE17" t="n">
         <v>0.14</v>
@@ -8831,7 +8831,7 @@
         <v>0.99</v>
       </c>
       <c r="DO17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9295,7 +9295,7 @@
         <v>2.11</v>
       </c>
       <c r="DO18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9718,7 +9718,7 @@
         <v>50</v>
       </c>
       <c r="DD19" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="DE19" t="n">
         <v>1</v>
@@ -9751,7 +9751,7 @@
         <v>1.18</v>
       </c>
       <c r="DO19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10178,10 +10178,10 @@
         <v>50</v>
       </c>
       <c r="DD20" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DF20" t="n">
         <v>0</v>
@@ -10211,7 +10211,7 @@
         <v>0.44</v>
       </c>
       <c r="DO20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10658,10 +10658,10 @@
         <v>0</v>
       </c>
       <c r="DD21" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DE21" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10691,7 +10691,7 @@
         <v>0</v>
       </c>
       <c r="DO21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DE22" t="n">
         <v>0.17</v>
@@ -11171,7 +11171,7 @@
         <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11639,7 +11639,7 @@
         <v>3.01</v>
       </c>
       <c r="DO23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12081,7 +12081,7 @@
         <v>1</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -12111,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="DO24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP24" t="b">
         <v>0</v>
@@ -12599,7 +12599,7 @@
         <v>1.06</v>
       </c>
       <c r="DO25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13022,10 +13022,10 @@
         <v>50</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DE26" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DF26" t="n">
         <v>0</v>
@@ -13055,7 +13055,7 @@
         <v>2.14</v>
       </c>
       <c r="DO26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13497,7 +13497,7 @@
         <v>0.2</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="DF27" t="n">
         <v>0</v>
@@ -13527,7 +13527,7 @@
         <v>1.42</v>
       </c>
       <c r="DO27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP27" t="b">
         <v>0</v>
@@ -13958,7 +13958,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="DE28" t="n">
         <v>0.17</v>
@@ -13991,7 +13991,7 @@
         <v>3.72</v>
       </c>
       <c r="DO28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14430,7 +14430,7 @@
         <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DE29" t="n">
         <v>2.5</v>
@@ -14463,7 +14463,7 @@
         <v>2.82</v>
       </c>
       <c r="DO29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14943,7 +14943,7 @@
         <v>2.34</v>
       </c>
       <c r="DO30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15366,7 +15366,7 @@
         <v>100</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE31" t="n">
         <v>0.17</v>
@@ -15399,7 +15399,7 @@
         <v>2.97</v>
       </c>
       <c r="DO31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15825,7 +15825,7 @@
         <v>0.2</v>
       </c>
       <c r="DE32" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF32" t="n">
         <v>1</v>
@@ -15855,7 +15855,7 @@
         <v>2.93</v>
       </c>
       <c r="DO32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16289,7 +16289,7 @@
         <v>0.5</v>
       </c>
       <c r="DE33" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DF33" t="n">
         <v>0.5</v>
@@ -16319,7 +16319,7 @@
         <v>2.59</v>
       </c>
       <c r="DO33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16779,7 +16779,7 @@
         <v>4.3</v>
       </c>
       <c r="DO34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17226,7 +17226,7 @@
         <v>100</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DE35" t="n">
         <v>2.17</v>
@@ -17259,7 +17259,7 @@
         <v>2.37</v>
       </c>
       <c r="DO35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17706,7 +17706,7 @@
         <v>50</v>
       </c>
       <c r="DD36" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DE36" t="n">
         <v>1</v>
@@ -17739,7 +17739,7 @@
         <v>2.25</v>
       </c>
       <c r="DO36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18181,7 +18181,7 @@
         <v>1.5</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF37" t="n">
         <v>0</v>
@@ -18211,7 +18211,7 @@
         <v>2.65</v>
       </c>
       <c r="DO37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18653,7 +18653,7 @@
         <v>1</v>
       </c>
       <c r="DE38" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -18683,7 +18683,7 @@
         <v>2.44</v>
       </c>
       <c r="DO38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19122,7 +19122,7 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DE39" t="n">
         <v>0.14</v>
@@ -19155,7 +19155,7 @@
         <v>2.02</v>
       </c>
       <c r="DO39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19613,7 +19613,7 @@
         <v>2.14</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF40" t="n">
         <v>2</v>
@@ -19643,7 +19643,7 @@
         <v>2.66</v>
       </c>
       <c r="DO40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20115,7 +20115,7 @@
         <v>2</v>
       </c>
       <c r="DO41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20538,10 +20538,10 @@
         <v>50</v>
       </c>
       <c r="DD42" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DF42" t="n">
         <v>0</v>
@@ -20571,7 +20571,7 @@
         <v>1.63</v>
       </c>
       <c r="DO42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21010,10 +21010,10 @@
         <v>50</v>
       </c>
       <c r="DD43" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="DE43" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="DF43" t="n">
         <v>3</v>
@@ -21043,7 +21043,7 @@
         <v>4.22</v>
       </c>
       <c r="DO43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21474,7 +21474,7 @@
         <v>75</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DE44" t="n">
         <v>0.17</v>
@@ -21507,7 +21507,7 @@
         <v>2.13</v>
       </c>
       <c r="DO44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21938,10 +21938,10 @@
         <v>100</v>
       </c>
       <c r="DD45" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DE45" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF45" t="n">
         <v>1.5</v>
@@ -21971,7 +21971,7 @@
         <v>2.14</v>
       </c>
       <c r="DO45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22402,10 +22402,10 @@
         <v>75</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF46" t="n">
         <v>3</v>
@@ -22435,7 +22435,7 @@
         <v>2.57</v>
       </c>
       <c r="DO46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22866,7 +22866,7 @@
         <v>67</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DE47" t="n">
         <v>1</v>
@@ -22899,7 +22899,7 @@
         <v>1.84</v>
       </c>
       <c r="DO47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23379,7 +23379,7 @@
         <v>1.94</v>
       </c>
       <c r="DO48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23826,10 +23826,10 @@
         <v>0</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DE49" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF49" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>2.9</v>
       </c>
       <c r="DO49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24309,7 +24309,7 @@
         <v>1.5</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DF50" t="n">
         <v>0</v>
@@ -24339,7 +24339,7 @@
         <v>2.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24778,7 +24778,7 @@
         <v>100</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DE51" t="n">
         <v>1.14</v>
@@ -24811,7 +24811,7 @@
         <v>2.84</v>
       </c>
       <c r="DO51" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25279,7 +25279,7 @@
         <v>3.18</v>
       </c>
       <c r="DO52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25743,7 +25743,7 @@
         <v>2.21</v>
       </c>
       <c r="DO53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP53" t="b">
         <v>0</v>
@@ -26165,7 +26165,7 @@
         <v>0.83</v>
       </c>
       <c r="DE54" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF54" t="n">
         <v>1</v>
@@ -26195,7 +26195,7 @@
         <v>2.64</v>
       </c>
       <c r="DO54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26643,7 +26643,7 @@
         <v>3.19</v>
       </c>
       <c r="DO55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27093,7 +27093,7 @@
         <v>0.5</v>
       </c>
       <c r="DE56" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="DF56" t="n">
         <v>0.33</v>
@@ -27123,7 +27123,7 @@
         <v>2.65</v>
       </c>
       <c r="DO56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27251,246 +27251,246 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
         <v>45960.72916666666</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J57" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K57" t="n">
+        <v>2</v>
+      </c>
+      <c r="L57" t="n">
+        <v>6</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
         <v>4</v>
       </c>
-      <c r="L57" t="n">
-        <v>13</v>
-      </c>
-      <c r="M57" t="n">
-        <v>2</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
+        <v>4</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
         <v>6</v>
-      </c>
-      <c r="R57" t="n">
-        <v>3</v>
-      </c>
-      <c r="S57" t="n">
-        <v>13</v>
-      </c>
-      <c r="T57" t="n">
-        <v>3</v>
-      </c>
-      <c r="U57" t="n">
-        <v>19</v>
       </c>
       <c r="V57" t="n">
         <v>6</v>
       </c>
       <c r="W57" t="n">
+        <v>14</v>
+      </c>
+      <c r="X57" t="n">
         <v>13</v>
       </c>
-      <c r="X57" t="n">
-        <v>8</v>
-      </c>
       <c r="Y57" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="Z57" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>5097</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>84</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>981</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI57" t="n">
         <v>4</v>
       </c>
-      <c r="AD57" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>67</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>8549</v>
-      </c>
-      <c r="BG57" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH57" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI57" t="n">
-        <v>5</v>
-      </c>
       <c r="BJ57" t="n">
         <v>0</v>
       </c>
       <c r="BK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL57" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM57" t="n">
         <v>4</v>
       </c>
-      <c r="BL57" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM57" t="n">
-        <v>5</v>
-      </c>
       <c r="BN57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BO57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP57" t="n">
         <v>1</v>
       </c>
       <c r="BQ57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR57" t="n">
         <v>2</v>
       </c>
       <c r="BS57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BU57" t="n">
         <v>1</v>
       </c>
       <c r="BV57" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="BW57" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="BX57" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="BY57" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="BZ57" t="n">
-        <v>2.19</v>
+        <v>1.01</v>
       </c>
       <c r="CA57" t="n">
-        <v>0.71</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CB57" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="CC57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG57" t="n">
         <v>0</v>
@@ -27505,10 +27505,10 @@
         <v>1</v>
       </c>
       <c r="CK57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM57" t="n">
         <v>0</v>
@@ -27526,31 +27526,31 @@
         <v>1</v>
       </c>
       <c r="CR57" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS57" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU57" t="n">
         <v>13</v>
       </c>
-      <c r="CS57" t="n">
+      <c r="CV57" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX57" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY57" t="n">
         <v>10</v>
       </c>
-      <c r="CT57" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU57" t="n">
-        <v>7</v>
-      </c>
-      <c r="CV57" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW57" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX57" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY57" t="n">
-        <v>14</v>
-      </c>
       <c r="CZ57" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="DA57" t="n">
         <v>84</v>
@@ -27562,40 +27562,40 @@
         <v>100</v>
       </c>
       <c r="DD57" t="n">
-        <v>2.14</v>
+        <v>0.86</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.17</v>
+        <v>2.17</v>
       </c>
       <c r="DF57" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG57" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI57" t="n">
         <v>1.67</v>
       </c>
-      <c r="DG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH57" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI57" t="n">
-        <v>1</v>
-      </c>
       <c r="DJ57" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="DK57" t="n">
         <v>17</v>
       </c>
       <c r="DL57" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="DM57" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="DN57" t="n">
         <v>2.85</v>
       </c>
       <c r="DO57" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27604,13 +27604,13 @@
         <v>1</v>
       </c>
       <c r="DR57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU57" t="b">
         <v>0</v>
@@ -27619,87 +27619,99 @@
         <v>1</v>
       </c>
       <c r="DW57" t="n">
-        <v>32.58</v>
+        <v>29.89</v>
       </c>
       <c r="DX57" t="n">
-        <v>6</v>
+        <v>6.19</v>
       </c>
       <c r="DY57" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="DZ57" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA57" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EB57" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EC57" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="ED57" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EE57" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF57" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="EG57" t="inlineStr">
         <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="EH57" t="inlineStr"/>
-      <c r="EI57" t="inlineStr"/>
-      <c r="EJ57" t="inlineStr"/>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="EH57" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EI57" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EJ57" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
       <c r="EK57" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EL57" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EM57" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="EN57" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EO57" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EP57" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.18</t>
         </is>
       </c>
     </row>
@@ -27719,246 +27731,246 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>45960.72916666666</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
+        <v>9</v>
+      </c>
+      <c r="K58" t="n">
         <v>4</v>
       </c>
-      <c r="K58" t="n">
-        <v>2</v>
-      </c>
       <c r="L58" t="n">
+        <v>13</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
         <v>6</v>
       </c>
-      <c r="M58" t="n">
-        <v>3</v>
-      </c>
-      <c r="N58" t="n">
-        <v>3</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>4</v>
-      </c>
       <c r="R58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U58" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="V58" t="n">
         <v>6</v>
       </c>
       <c r="W58" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="X58" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y58" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="Z58" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="AA58" t="inlineStr"/>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD58" t="n">
         <v>3</v>
       </c>
       <c r="AE58" t="n">
-        <v>3.6</v>
+        <v>1.14</v>
       </c>
       <c r="AF58" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.95</v>
+        <v>11.7</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AJ58" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AL58" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="AM58" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AN58" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AO58" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AR58" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AS58" t="n">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AU58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>8549</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI58" t="n">
         <v>5</v>
       </c>
-      <c r="AV58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ58" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA58" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB58" t="n">
-        <v>5097</v>
-      </c>
-      <c r="BC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD58" t="n">
-        <v>84</v>
-      </c>
-      <c r="BE58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF58" t="n">
-        <v>981</v>
-      </c>
-      <c r="BG58" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH58" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI58" t="n">
+      <c r="BJ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK58" t="n">
         <v>4</v>
       </c>
-      <c r="BJ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK58" t="n">
-        <v>0</v>
-      </c>
       <c r="BL58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BO58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP58" t="n">
         <v>1</v>
       </c>
       <c r="BQ58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR58" t="n">
         <v>2</v>
       </c>
       <c r="BS58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BU58" t="n">
         <v>1</v>
       </c>
       <c r="BV58" t="n">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="BW58" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="BX58" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="BY58" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="BZ58" t="n">
-        <v>1.01</v>
+        <v>2.19</v>
       </c>
       <c r="CA58" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="CB58" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="CC58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG58" t="n">
         <v>0</v>
@@ -27973,10 +27985,10 @@
         <v>1</v>
       </c>
       <c r="CK58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM58" t="n">
         <v>0</v>
@@ -27994,31 +28006,31 @@
         <v>1</v>
       </c>
       <c r="CR58" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CS58" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="CT58" t="n">
         <v>1</v>
       </c>
       <c r="CU58" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="CV58" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW58" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX58" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY58" t="n">
         <v>14</v>
       </c>
-      <c r="CW58" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX58" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY58" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ58" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="DA58" t="n">
         <v>84</v>
@@ -28030,40 +28042,40 @@
         <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="DE58" t="n">
-        <v>2.17</v>
+        <v>0.17</v>
       </c>
       <c r="DF58" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="DG58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DH58" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DI58" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DJ58" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="DK58" t="n">
         <v>17</v>
       </c>
       <c r="DL58" t="n">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="DM58" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="DN58" t="n">
         <v>2.85</v>
       </c>
       <c r="DO58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28072,13 +28084,13 @@
         <v>1</v>
       </c>
       <c r="DR58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU58" t="b">
         <v>0</v>
@@ -28087,99 +28099,87 @@
         <v>1</v>
       </c>
       <c r="DW58" t="n">
-        <v>29.89</v>
+        <v>32.58</v>
       </c>
       <c r="DX58" t="n">
-        <v>6.19</v>
+        <v>6</v>
       </c>
       <c r="DY58" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="DZ58" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="EA58" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EB58" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EC58" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="ED58" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EE58" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="EF58" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="EG58" t="inlineStr">
         <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="EH58" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
-      <c r="EI58" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EJ58" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="EH58" t="inlineStr"/>
+      <c r="EI58" t="inlineStr"/>
+      <c r="EJ58" t="inlineStr"/>
       <c r="EK58" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EL58" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EM58" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EN58" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EO58" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="EP58" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -28510,7 +28510,7 @@
         <v>100</v>
       </c>
       <c r="DD59" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE59" t="n">
         <v>0.14</v>
@@ -28543,7 +28543,7 @@
         <v>2.02</v>
       </c>
       <c r="DO59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -28990,10 +28990,10 @@
         <v>75</v>
       </c>
       <c r="DD60" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE60" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF60" t="n">
         <v>2.33</v>
@@ -29023,7 +29023,7 @@
         <v>3.38</v>
       </c>
       <c r="DO60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29457,7 +29457,7 @@
         <v>1.71</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DF61" t="n">
         <v>1.33</v>
@@ -29487,7 +29487,7 @@
         <v>1.4</v>
       </c>
       <c r="DO61" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29934,10 +29934,10 @@
         <v>84</v>
       </c>
       <c r="DD62" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF62" t="n">
         <v>2</v>
@@ -29967,7 +29967,7 @@
         <v>2.42</v>
       </c>
       <c r="DO62" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30414,10 +30414,10 @@
         <v>67</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DE63" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DF63" t="n">
         <v>2</v>
@@ -30447,7 +30447,7 @@
         <v>3.33</v>
       </c>
       <c r="DO63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30886,7 +30886,7 @@
         <v>67</v>
       </c>
       <c r="DD64" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="DE64" t="n">
         <v>1</v>
@@ -30919,7 +30919,7 @@
         <v>3.73</v>
       </c>
       <c r="DO64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31375,7 +31375,7 @@
         <v>2.02</v>
       </c>
       <c r="DO65" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31495,246 +31495,254 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>45967.72916666666</v>
       </c>
       <c r="G66" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K66" t="n">
         <v>5</v>
       </c>
       <c r="L66" t="n">
+        <v>8</v>
+      </c>
+      <c r="M66" t="n">
+        <v>3</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1</v>
+      </c>
+      <c r="R66" t="n">
+        <v>2</v>
+      </c>
+      <c r="S66" t="n">
+        <v>6</v>
+      </c>
+      <c r="T66" t="n">
         <v>12</v>
       </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
-        <v>2</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>6</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
+      <c r="U66" t="n">
+        <v>7</v>
+      </c>
+      <c r="V66" t="n">
+        <v>14</v>
+      </c>
+      <c r="W66" t="n">
+        <v>12</v>
+      </c>
+      <c r="X66" t="n">
         <v>13</v>
       </c>
-      <c r="T66" t="n">
-        <v>6</v>
-      </c>
-      <c r="U66" t="n">
-        <v>19</v>
-      </c>
-      <c r="V66" t="n">
-        <v>6</v>
-      </c>
-      <c r="W66" t="n">
-        <v>16</v>
-      </c>
-      <c r="X66" t="n">
-        <v>6</v>
-      </c>
       <c r="Y66" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="Z66" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Prince Turki bin Abdul Aziz Stadium</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>, Riyadh</t>
+        </is>
+      </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.46</v>
+        <v>2.14</v>
       </c>
       <c r="AF66" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="AG66" t="n">
-        <v>6.1</v>
+        <v>3.5</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AI66" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AP66" t="n">
         <v>1.75</v>
       </c>
-      <c r="AJ66" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AQ66" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AR66" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AS66" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AU66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>84</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF66" t="n">
+        <v>550</v>
+      </c>
+      <c r="BG66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ66" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL66" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM66" t="n">
         <v>4</v>
-      </c>
-      <c r="AV66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX66" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ66" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB66" t="n">
-        <v>5068</v>
-      </c>
-      <c r="BC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD66" t="n">
-        <v>59</v>
-      </c>
-      <c r="BE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF66" t="n">
-        <v>6765</v>
-      </c>
-      <c r="BG66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI66" t="n">
-        <v>6</v>
-      </c>
-      <c r="BJ66" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL66" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM66" t="n">
-        <v>8</v>
       </c>
       <c r="BN66" t="n">
         <v>4</v>
       </c>
       <c r="BO66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP66" t="n">
         <v>0</v>
       </c>
       <c r="BQ66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU66" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BV66" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="BW66" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BX66" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="BY66" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="BZ66" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="CA66" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="CB66" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="CC66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG66" t="n">
         <v>0</v>
@@ -31755,13 +31763,13 @@
         <v>0</v>
       </c>
       <c r="CM66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP66" t="n">
         <v>0</v>
@@ -31773,73 +31781,73 @@
         <v>17</v>
       </c>
       <c r="CS66" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="CT66" t="n">
         <v>1</v>
       </c>
       <c r="CU66" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="CV66" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CW66" t="n">
         <v>1</v>
       </c>
       <c r="CX66" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CY66" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CZ66" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="DA66" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="DB66" t="n">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="DC66" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="DD66" t="n">
-        <v>2.33</v>
+        <v>1.14</v>
       </c>
       <c r="DE66" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF66" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="DG66" t="n">
-        <v>0.75</v>
+        <v>0.33</v>
       </c>
       <c r="DH66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DI66" t="n">
-        <v>1.29</v>
+        <v>0.43</v>
       </c>
       <c r="DJ66" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="DK66" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="DL66" t="n">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="DM66" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="DN66" t="n">
-        <v>2.65</v>
+        <v>2.17</v>
       </c>
       <c r="DO66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31848,10 +31856,10 @@
         <v>1</v>
       </c>
       <c r="DR66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT66" t="b">
         <v>0</v>
@@ -31860,17 +31868,17 @@
         <v>0</v>
       </c>
       <c r="DV66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW66" t="n">
-        <v>27.94</v>
+        <v>25.56</v>
       </c>
       <c r="DX66" t="n">
-        <v>4.87</v>
+        <v>2.71</v>
       </c>
       <c r="DY66" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="DZ66" t="inlineStr">
@@ -31878,60 +31886,68 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA66" t="inlineStr"/>
-      <c r="EB66" t="inlineStr"/>
-      <c r="EC66" t="inlineStr"/>
-      <c r="ED66" t="inlineStr"/>
+      <c r="EA66" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EB66" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EC66" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="ED66" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
       <c r="EE66" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="EF66" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EG66" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EH66" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="EI66" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EJ66" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EK66" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EL66" t="inlineStr">
         <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EM66" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="EN66" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EM66" t="inlineStr"/>
+      <c r="EN66" t="inlineStr"/>
       <c r="EO66" t="inlineStr"/>
       <c r="EP66" t="inlineStr"/>
     </row>
@@ -31951,254 +31967,246 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
         <v>45967.72916666666</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K67" t="n">
         <v>5</v>
       </c>
       <c r="L67" t="n">
+        <v>12</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>6</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>13</v>
+      </c>
+      <c r="T67" t="n">
+        <v>6</v>
+      </c>
+      <c r="U67" t="n">
+        <v>19</v>
+      </c>
+      <c r="V67" t="n">
+        <v>6</v>
+      </c>
+      <c r="W67" t="n">
+        <v>16</v>
+      </c>
+      <c r="X67" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>5068</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>6765</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI67" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL67" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM67" t="n">
         <v>8</v>
-      </c>
-      <c r="M67" t="n">
-        <v>3</v>
-      </c>
-      <c r="N67" t="n">
-        <v>3</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>1</v>
-      </c>
-      <c r="R67" t="n">
-        <v>2</v>
-      </c>
-      <c r="S67" t="n">
-        <v>6</v>
-      </c>
-      <c r="T67" t="n">
-        <v>12</v>
-      </c>
-      <c r="U67" t="n">
-        <v>7</v>
-      </c>
-      <c r="V67" t="n">
-        <v>14</v>
-      </c>
-      <c r="W67" t="n">
-        <v>12</v>
-      </c>
-      <c r="X67" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>66</v>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>Prince Turki bin Abdul Aziz Stadium</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>, Riyadh</t>
-        </is>
-      </c>
-      <c r="AC67" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AJ67" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL67" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM67" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AO67" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AP67" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AQ67" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR67" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AS67" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT67" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AU67" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD67" t="n">
-        <v>84</v>
-      </c>
-      <c r="BE67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF67" t="n">
-        <v>550</v>
-      </c>
-      <c r="BG67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ67" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL67" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM67" t="n">
-        <v>4</v>
       </c>
       <c r="BN67" t="n">
         <v>4</v>
       </c>
       <c r="BO67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP67" t="n">
         <v>0</v>
       </c>
       <c r="BQ67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU67" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BV67" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="BW67" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BX67" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="BY67" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="BZ67" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="CA67" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="CB67" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="CC67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG67" t="n">
         <v>0</v>
@@ -32219,13 +32227,13 @@
         <v>0</v>
       </c>
       <c r="CM67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP67" t="n">
         <v>0</v>
@@ -32237,74 +32245,74 @@
         <v>17</v>
       </c>
       <c r="CS67" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="CT67" t="n">
         <v>1</v>
       </c>
       <c r="CU67" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV67" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX67" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY67" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ67" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA67" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB67" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC67" t="n">
+        <v>59</v>
+      </c>
+      <c r="DD67" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF67" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DG67" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH67" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI67" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DJ67" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK67" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL67" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DM67" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="DN67" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="DO67" t="n">
         <v>13</v>
       </c>
-      <c r="CV67" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX67" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY67" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ67" t="n">
-        <v>67</v>
-      </c>
-      <c r="DA67" t="n">
-        <v>84</v>
-      </c>
-      <c r="DB67" t="n">
-        <v>84</v>
-      </c>
-      <c r="DC67" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD67" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DE67" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF67" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG67" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DH67" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI67" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="DJ67" t="n">
-        <v>33</v>
-      </c>
-      <c r="DK67" t="n">
-        <v>17</v>
-      </c>
-      <c r="DL67" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="DM67" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="DN67" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="DO67" t="n">
-        <v>12</v>
-      </c>
       <c r="DP67" t="b">
         <v>1</v>
       </c>
@@ -32312,10 +32320,10 @@
         <v>1</v>
       </c>
       <c r="DR67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT67" t="b">
         <v>0</v>
@@ -32324,17 +32332,17 @@
         <v>0</v>
       </c>
       <c r="DV67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW67" t="n">
-        <v>25.56</v>
+        <v>27.94</v>
       </c>
       <c r="DX67" t="n">
-        <v>2.71</v>
+        <v>4.87</v>
       </c>
       <c r="DY67" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="DZ67" t="inlineStr">
@@ -32342,68 +32350,60 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA67" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EB67" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EC67" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="ED67" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
+      <c r="EA67" t="inlineStr"/>
+      <c r="EB67" t="inlineStr"/>
+      <c r="EC67" t="inlineStr"/>
+      <c r="ED67" t="inlineStr"/>
       <c r="EE67" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="EF67" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="EG67" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EH67" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EI67" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EJ67" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EK67" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EL67" t="inlineStr">
         <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="EM67" t="inlineStr"/>
-      <c r="EN67" t="inlineStr"/>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM67" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EN67" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
       <c r="EO67" t="inlineStr"/>
       <c r="EP67" t="inlineStr"/>
     </row>
@@ -32767,7 +32767,7 @@
         <v>1.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33239,7 +33239,7 @@
         <v>2.68</v>
       </c>
       <c r="DO69" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33670,7 +33670,7 @@
         <v>67</v>
       </c>
       <c r="DD70" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DE70" t="n">
         <v>2.67</v>
@@ -33703,7 +33703,7 @@
         <v>2.5</v>
       </c>
       <c r="DO70" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34134,7 +34134,7 @@
         <v>100</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DE71" t="n">
         <v>2.17</v>
@@ -34167,7 +34167,7 @@
         <v>3.72</v>
       </c>
       <c r="DO71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34609,7 +34609,7 @@
         <v>0.83</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DF72" t="n">
         <v>1</v>
@@ -34639,7 +34639,7 @@
         <v>2.76</v>
       </c>
       <c r="DO72" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35097,7 +35097,7 @@
         <v>1.71</v>
       </c>
       <c r="DE73" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -35127,7 +35127,7 @@
         <v>3.05</v>
       </c>
       <c r="DO73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35566,10 +35566,10 @@
         <v>75</v>
       </c>
       <c r="DD74" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DF74" t="n">
         <v>2</v>
@@ -35599,7 +35599,7 @@
         <v>2.12</v>
       </c>
       <c r="DO74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36063,7 +36063,7 @@
         <v>2.45</v>
       </c>
       <c r="DO75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36513,7 +36513,7 @@
         <v>2.14</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF76" t="n">
         <v>1.5</v>
@@ -36543,7 +36543,7 @@
         <v>3.13</v>
       </c>
       <c r="DO76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36999,7 +36999,7 @@
         <v>2.28</v>
       </c>
       <c r="DO77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -37463,7 +37463,7 @@
         <v>1.69</v>
       </c>
       <c r="DO78" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37858,10 +37858,10 @@
         <v>75</v>
       </c>
       <c r="DD79" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="DF79" t="n">
         <v>2.5</v>
@@ -37891,7 +37891,7 @@
         <v>3.63</v>
       </c>
       <c r="DO79" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -38318,10 +38318,10 @@
         <v>84</v>
       </c>
       <c r="DD80" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF80" t="n">
         <v>0.75</v>
@@ -38351,7 +38351,7 @@
         <v>2.38</v>
       </c>
       <c r="DO80" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38806,7 +38806,7 @@
         <v>88</v>
       </c>
       <c r="DD81" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="DE81" t="n">
         <v>1.14</v>
@@ -38839,7 +38839,7 @@
         <v>3.82</v>
       </c>
       <c r="DO81" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -39258,7 +39258,7 @@
         <v>88</v>
       </c>
       <c r="DD82" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DE82" t="n">
         <v>2.17</v>
@@ -39291,7 +39291,7 @@
         <v>2.51</v>
       </c>
       <c r="DO82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39725,7 +39725,7 @@
         <v>1</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DF83" t="n">
         <v>1.25</v>
@@ -39755,7 +39755,7 @@
         <v>2.19</v>
       </c>
       <c r="DO83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP83" t="b">
         <v>0</v>
@@ -40210,7 +40210,7 @@
         <v>78</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DE84" t="n">
         <v>0.14</v>
@@ -40243,7 +40243,7 @@
         <v>2.45</v>
       </c>
       <c r="DO84" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40690,10 +40690,10 @@
         <v>100</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DE85" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DF85" t="n">
         <v>1.75</v>
@@ -40723,7 +40723,7 @@
         <v>2.29</v>
       </c>
       <c r="DO85" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41129,7 +41129,7 @@
         <v>1.5</v>
       </c>
       <c r="DE86" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DF86" t="n">
         <v>0.75</v>
@@ -41159,7 +41159,7 @@
         <v>3.42</v>
       </c>
       <c r="DO86" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41554,7 +41554,7 @@
         <v>88</v>
       </c>
       <c r="DD87" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DE87" t="n">
         <v>2.5</v>
@@ -41587,7 +41587,7 @@
         <v>2.81</v>
       </c>
       <c r="DO87" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -42034,7 +42034,7 @@
         <v>100</v>
       </c>
       <c r="DD88" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE88" t="n">
         <v>1.14</v>
@@ -42067,7 +42067,7 @@
         <v>3.44</v>
       </c>
       <c r="DO88" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42501,7 +42501,7 @@
         <v>2.33</v>
       </c>
       <c r="DE89" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF89" t="n">
         <v>2.5</v>
@@ -42531,7 +42531,7 @@
         <v>2.71</v>
       </c>
       <c r="DO89" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42934,7 +42934,7 @@
         <v>65</v>
       </c>
       <c r="DD90" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="DE90" t="n">
         <v>0.17</v>
@@ -42967,7 +42967,7 @@
         <v>3.16</v>
       </c>
       <c r="DO90" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -43405,7 +43405,7 @@
         <v>1.71</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF91" t="n">
         <v>1.2</v>
@@ -43435,7 +43435,7 @@
         <v>2.54</v>
       </c>
       <c r="DO91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43882,10 +43882,10 @@
         <v>68</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DE92" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="DF92" t="n">
         <v>1.75</v>
@@ -43915,7 +43915,7 @@
         <v>2.77</v>
       </c>
       <c r="DO92" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -44338,10 +44338,10 @@
         <v>65</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DE93" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DF93" t="n">
         <v>1.4</v>
@@ -44371,7 +44371,7 @@
         <v>2.18</v>
       </c>
       <c r="DO93" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44818,7 +44818,7 @@
         <v>64</v>
       </c>
       <c r="DD94" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DE94" t="n">
         <v>0.14</v>
@@ -44851,7 +44851,7 @@
         <v>2.24</v>
       </c>
       <c r="DO94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -45331,7 +45331,7 @@
         <v>2.91</v>
       </c>
       <c r="DO95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45783,7 +45783,7 @@
         <v>3.12</v>
       </c>
       <c r="DO96" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -46202,10 +46202,10 @@
         <v>100</v>
       </c>
       <c r="DD97" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE97" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DF97" t="n">
         <v>0.8</v>
@@ -46235,7 +46235,7 @@
         <v>2.15</v>
       </c>
       <c r="DO97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46666,10 +46666,10 @@
         <v>68</v>
       </c>
       <c r="DD98" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DE98" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DF98" t="n">
         <v>1.4</v>
@@ -46699,7 +46699,7 @@
         <v>3.06</v>
       </c>
       <c r="DO98" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -47121,7 +47121,7 @@
         <v>0.83</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF99" t="n">
         <v>1</v>
@@ -47151,7 +47151,7 @@
         <v>3.04</v>
       </c>
       <c r="DO99" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47546,7 +47546,7 @@
         <v>100</v>
       </c>
       <c r="DD100" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DE100" t="n">
         <v>2.67</v>
@@ -47579,7 +47579,7 @@
         <v>3.24</v>
       </c>
       <c r="DO100" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47868,7 +47868,7 @@
         <v>0</v>
       </c>
       <c r="BF101" t="n">
-        <v>-1</v>
+        <v>370</v>
       </c>
       <c r="BG101" t="n">
         <v>2</v>
@@ -48018,7 +48018,7 @@
         <v>75</v>
       </c>
       <c r="DD101" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DE101" t="n">
         <v>1.14</v>
@@ -48051,7 +48051,7 @@
         <v>2.03</v>
       </c>
       <c r="DO101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -48340,7 +48340,7 @@
         <v>0</v>
       </c>
       <c r="BF102" t="n">
-        <v>-1</v>
+        <v>1696</v>
       </c>
       <c r="BG102" t="n">
         <v>2</v>
@@ -48523,7 +48523,7 @@
         <v>1.44</v>
       </c>
       <c r="DO102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48776,7 +48776,7 @@
         <v>0</v>
       </c>
       <c r="BF103" t="n">
-        <v>-1</v>
+        <v>41315</v>
       </c>
       <c r="BG103" t="n">
         <v>2</v>
@@ -48959,7 +48959,7 @@
         <v>3.97</v>
       </c>
       <c r="DO103" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -49212,7 +49212,7 @@
         <v>0</v>
       </c>
       <c r="BF104" t="n">
-        <v>-1</v>
+        <v>6017</v>
       </c>
       <c r="BG104" t="n">
         <v>2</v>
@@ -49365,7 +49365,7 @@
         <v>1.5</v>
       </c>
       <c r="DE104" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF104" t="n">
         <v>1.2</v>
@@ -49395,7 +49395,7 @@
         <v>2.58</v>
       </c>
       <c r="DO104" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49676,7 +49676,7 @@
         <v>0</v>
       </c>
       <c r="BF105" t="n">
-        <v>-1</v>
+        <v>494</v>
       </c>
       <c r="BG105" t="n">
         <v>2</v>
@@ -49859,7 +49859,7 @@
         <v>2.03</v>
       </c>
       <c r="DO105" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -50156,7 +50156,7 @@
         <v>0</v>
       </c>
       <c r="BF106" t="n">
-        <v>-1</v>
+        <v>11141</v>
       </c>
       <c r="BG106" t="n">
         <v>2</v>
@@ -50339,7 +50339,7 @@
         <v>3.01</v>
       </c>
       <c r="DO106" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -50604,7 +50604,7 @@
         <v>0</v>
       </c>
       <c r="BF107" t="n">
-        <v>-1</v>
+        <v>1044</v>
       </c>
       <c r="BG107" t="n">
         <v>2</v>
@@ -50787,7 +50787,7 @@
         <v>2.44</v>
       </c>
       <c r="DO107" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50828,68 +50828,84 @@
       </c>
       <c r="EA107" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EB107" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EC107" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="ED107" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EE107" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EF107" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EG107" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EH107" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="EI107" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EJ107" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EK107" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EL107" t="inlineStr">
         <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EM107" t="inlineStr"/>
-      <c r="EN107" t="inlineStr"/>
-      <c r="EO107" t="inlineStr"/>
-      <c r="EP107" t="inlineStr"/>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EM107" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EN107" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EO107" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EP107" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -50907,40 +50923,40 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
         <v>46026.72916666666</v>
       </c>
       <c r="G108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I108" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J108" t="n">
+        <v>2</v>
+      </c>
+      <c r="K108" t="n">
         <v>9</v>
       </c>
-      <c r="K108" t="n">
-        <v>4</v>
-      </c>
       <c r="L108" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -50949,114 +50965,122 @@
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S108" t="n">
         <v>8</v>
       </c>
       <c r="T108" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U108" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="V108" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="W108" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="X108" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="Y108" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="Z108" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA108" t="inlineStr"/>
-      <c r="AB108" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>Dhamak Club Stadium</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>, Khamis Mushait</t>
+        </is>
+      </c>
       <c r="AC108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.3</v>
+        <v>12.2</v>
       </c>
       <c r="AF108" t="n">
-        <v>5.2</v>
+        <v>6.15</v>
       </c>
       <c r="AG108" t="n">
-        <v>9.140000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="AH108" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI108" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AJ108" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AK108" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AL108" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AM108" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN108" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AO108" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AP108" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR108" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS108" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AU108" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB108" t="n">
-        <v>5068</v>
+        <v>5066</v>
       </c>
       <c r="BC108" t="n">
         <v>0</v>
@@ -51068,7 +51092,7 @@
         <v>0</v>
       </c>
       <c r="BF108" t="n">
-        <v>6160</v>
+        <v>14873</v>
       </c>
       <c r="BG108" t="n">
         <v>2</v>
@@ -51077,133 +51101,133 @@
         <v>1</v>
       </c>
       <c r="BI108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ108" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL108" t="n">
         <v>6</v>
       </c>
-      <c r="BJ108" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK108" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL108" t="n">
-        <v>2</v>
-      </c>
       <c r="BM108" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN108" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV108" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW108" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX108" t="n">
+        <v>71</v>
+      </c>
+      <c r="BY108" t="n">
+        <v>119</v>
+      </c>
+      <c r="BZ108" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CA108" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CB108" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR108" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS108" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU108" t="n">
         <v>8</v>
       </c>
-      <c r="BN108" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ108" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT108" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV108" t="n">
-        <v>49</v>
-      </c>
-      <c r="BW108" t="n">
-        <v>52</v>
-      </c>
-      <c r="BX108" t="n">
-        <v>90</v>
-      </c>
-      <c r="BY108" t="n">
-        <v>79</v>
-      </c>
-      <c r="BZ108" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CA108" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CB108" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="CC108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR108" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS108" t="n">
-        <v>18</v>
-      </c>
-      <c r="CT108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU108" t="n">
-        <v>19</v>
-      </c>
       <c r="CV108" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CW108" t="n">
         <v>1</v>
       </c>
       <c r="CX108" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CY108" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CZ108" t="n">
         <v>60</v>
@@ -51212,28 +51236,28 @@
         <v>90</v>
       </c>
       <c r="DB108" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="DC108" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="DD108" t="n">
-        <v>2.33</v>
+        <v>0.5</v>
       </c>
       <c r="DE108" t="n">
-        <v>0.17</v>
+        <v>2.67</v>
       </c>
       <c r="DF108" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="DG108" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="DH108" t="n">
-        <v>1.91</v>
+        <v>0.82</v>
       </c>
       <c r="DI108" t="n">
-        <v>0.73</v>
+        <v>2.64</v>
       </c>
       <c r="DJ108" t="n">
         <v>40</v>
@@ -51242,16 +51266,16 @@
         <v>10</v>
       </c>
       <c r="DL108" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="DM108" t="n">
-        <v>1.05</v>
+        <v>2.04</v>
       </c>
       <c r="DN108" t="n">
-        <v>2.86</v>
+        <v>3.29</v>
       </c>
       <c r="DO108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -51260,10 +51284,10 @@
         <v>1</v>
       </c>
       <c r="DR108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT108" t="b">
         <v>0</v>
@@ -51275,47 +51299,83 @@
         <v>0</v>
       </c>
       <c r="DW108" t="n">
-        <v>19.18</v>
+        <v>20.33</v>
       </c>
       <c r="DX108" t="n">
-        <v>12.01</v>
+        <v>4</v>
       </c>
       <c r="DY108" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="DZ108" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="EA108" t="inlineStr"/>
-      <c r="EB108" t="inlineStr"/>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="EA108" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EB108" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
       <c r="EC108" t="inlineStr"/>
       <c r="ED108" t="inlineStr"/>
       <c r="EE108" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EF108" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="EG108" t="inlineStr">
         <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EH108" t="inlineStr"/>
-      <c r="EI108" t="inlineStr"/>
-      <c r="EJ108" t="inlineStr"/>
-      <c r="EK108" t="inlineStr"/>
-      <c r="EL108" t="inlineStr"/>
-      <c r="EM108" t="inlineStr"/>
-      <c r="EN108" t="inlineStr"/>
+          <t>9.85</t>
+        </is>
+      </c>
+      <c r="EH108" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EI108" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EJ108" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EK108" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EL108" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EM108" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EN108" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
       <c r="EO108" t="inlineStr"/>
       <c r="EP108" t="inlineStr"/>
     </row>
@@ -51335,40 +51395,40 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
         <v>46026.72916666666</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J109" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K109" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L109" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -51377,122 +51437,114 @@
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R109" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S109" t="n">
         <v>8</v>
       </c>
       <c r="T109" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="U109" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="V109" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="W109" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="X109" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="Y109" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="Z109" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>Dhamak Club Stadium</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>, Khamis Mushait</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr"/>
       <c r="AC109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>12.2</v>
+        <v>1.3</v>
       </c>
       <c r="AF109" t="n">
-        <v>6.15</v>
+        <v>5.2</v>
       </c>
       <c r="AG109" t="n">
-        <v>1.11</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AH109" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI109" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ109" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AK109" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AL109" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AM109" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN109" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AO109" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR109" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS109" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AT109" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AU109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB109" t="n">
-        <v>5066</v>
+        <v>5068</v>
       </c>
       <c r="BC109" t="n">
         <v>0</v>
@@ -51504,7 +51556,7 @@
         <v>0</v>
       </c>
       <c r="BF109" t="n">
-        <v>-1</v>
+        <v>6160</v>
       </c>
       <c r="BG109" t="n">
         <v>2</v>
@@ -51513,133 +51565,133 @@
         <v>1</v>
       </c>
       <c r="BI109" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BJ109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV109" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW109" t="n">
+        <v>52</v>
+      </c>
+      <c r="BX109" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY109" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ109" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CA109" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CB109" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CC109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR109" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS109" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU109" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV109" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX109" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY109" t="n">
         <v>6</v>
-      </c>
-      <c r="BM109" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN109" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP109" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS109" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT109" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV109" t="n">
-        <v>22</v>
-      </c>
-      <c r="BW109" t="n">
-        <v>56</v>
-      </c>
-      <c r="BX109" t="n">
-        <v>71</v>
-      </c>
-      <c r="BY109" t="n">
-        <v>119</v>
-      </c>
-      <c r="BZ109" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="CA109" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CB109" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="CC109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR109" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS109" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU109" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV109" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX109" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY109" t="n">
-        <v>9</v>
       </c>
       <c r="CZ109" t="n">
         <v>60</v>
@@ -51648,28 +51700,28 @@
         <v>90</v>
       </c>
       <c r="DB109" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="DC109" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="DD109" t="n">
-        <v>0.5</v>
+        <v>2.33</v>
       </c>
       <c r="DE109" t="n">
-        <v>2.67</v>
+        <v>0.17</v>
       </c>
       <c r="DF109" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="DG109" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="DH109" t="n">
-        <v>0.82</v>
+        <v>1.91</v>
       </c>
       <c r="DI109" t="n">
-        <v>2.64</v>
+        <v>0.73</v>
       </c>
       <c r="DJ109" t="n">
         <v>40</v>
@@ -51678,16 +51730,16 @@
         <v>10</v>
       </c>
       <c r="DL109" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="DM109" t="n">
-        <v>2.04</v>
+        <v>1.05</v>
       </c>
       <c r="DN109" t="n">
-        <v>3.29</v>
+        <v>2.86</v>
       </c>
       <c r="DO109" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51696,10 +51748,10 @@
         <v>1</v>
       </c>
       <c r="DR109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT109" t="b">
         <v>0</v>
@@ -51711,85 +51763,4181 @@
         <v>0</v>
       </c>
       <c r="DW109" t="n">
-        <v>20.33</v>
+        <v>19.18</v>
       </c>
       <c r="DX109" t="n">
-        <v>4</v>
+        <v>12.01</v>
       </c>
       <c r="DY109" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="DZ109" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="EA109" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EB109" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA109" t="inlineStr"/>
+      <c r="EB109" t="inlineStr"/>
       <c r="EC109" t="inlineStr"/>
       <c r="ED109" t="inlineStr"/>
       <c r="EE109" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="EF109" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="EG109" t="inlineStr">
         <is>
-          <t>11.34</t>
-        </is>
-      </c>
-      <c r="EH109" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="EI109" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EJ109" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="EK109" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="EL109" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="EM109" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="EN109" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EH109" t="inlineStr"/>
+      <c r="EI109" t="inlineStr"/>
+      <c r="EJ109" t="inlineStr"/>
+      <c r="EK109" t="inlineStr"/>
+      <c r="EL109" t="inlineStr"/>
+      <c r="EM109" t="inlineStr"/>
+      <c r="EN109" t="inlineStr"/>
       <c r="EO109" t="inlineStr"/>
       <c r="EP109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>14</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Al Hazm</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>46030.62152777778</v>
+      </c>
+      <c r="G110" t="n">
+        <v>3</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>3</v>
+      </c>
+      <c r="J110" t="n">
+        <v>7</v>
+      </c>
+      <c r="K110" t="n">
+        <v>2</v>
+      </c>
+      <c r="L110" t="n">
+        <v>9</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>7</v>
+      </c>
+      <c r="R110" t="n">
+        <v>1</v>
+      </c>
+      <c r="S110" t="n">
+        <v>7</v>
+      </c>
+      <c r="T110" t="n">
+        <v>5</v>
+      </c>
+      <c r="U110" t="n">
+        <v>14</v>
+      </c>
+      <c r="V110" t="n">
+        <v>6</v>
+      </c>
+      <c r="W110" t="n">
+        <v>10</v>
+      </c>
+      <c r="X110" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr"/>
+      <c r="AC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>5066</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>14920</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK110" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM110" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN110" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV110" t="n">
+        <v>70</v>
+      </c>
+      <c r="BW110" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX110" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY110" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ110" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CA110" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CB110" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="CC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR110" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS110" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU110" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV110" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX110" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY110" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ110" t="n">
+        <v>62</v>
+      </c>
+      <c r="DA110" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB110" t="n">
+        <v>48</v>
+      </c>
+      <c r="DC110" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD110" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DE110" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF110" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DG110" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DH110" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DI110" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DJ110" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK110" t="n">
+        <v>23</v>
+      </c>
+      <c r="DL110" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DM110" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DN110" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="DO110" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP110" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ110" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR110" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW110" t="n">
+        <v>18</v>
+      </c>
+      <c r="DX110" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="DY110" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="DZ110" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="EA110" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EB110" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EC110" t="inlineStr"/>
+      <c r="ED110" t="inlineStr"/>
+      <c r="EE110" t="inlineStr">
+        <is>
+          <t>11.79</t>
+        </is>
+      </c>
+      <c r="EF110" t="inlineStr">
+        <is>
+          <t>9.03</t>
+        </is>
+      </c>
+      <c r="EG110" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EH110" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EI110" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EJ110" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="EK110" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EL110" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EM110" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EN110" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EO110" t="inlineStr"/>
+      <c r="EP110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>14</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Al Najma</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Al Ittifaq</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>46030.72916666666</v>
+      </c>
+      <c r="G111" t="n">
+        <v>3</v>
+      </c>
+      <c r="H111" t="n">
+        <v>4</v>
+      </c>
+      <c r="I111" t="n">
+        <v>7</v>
+      </c>
+      <c r="J111" t="n">
+        <v>2</v>
+      </c>
+      <c r="K111" t="n">
+        <v>4</v>
+      </c>
+      <c r="L111" t="n">
+        <v>6</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>2</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>5</v>
+      </c>
+      <c r="R111" t="n">
+        <v>8</v>
+      </c>
+      <c r="S111" t="n">
+        <v>11</v>
+      </c>
+      <c r="T111" t="n">
+        <v>8</v>
+      </c>
+      <c r="U111" t="n">
+        <v>16</v>
+      </c>
+      <c r="V111" t="n">
+        <v>16</v>
+      </c>
+      <c r="W111" t="n">
+        <v>5</v>
+      </c>
+      <c r="X111" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>Al-Najma Club Stadium</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>, Unaizah</t>
+        </is>
+      </c>
+      <c r="AC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU111" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ111" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA111" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB111" t="n">
+        <v>5065</v>
+      </c>
+      <c r="BC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD111" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN111" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV111" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW111" t="n">
+        <v>52</v>
+      </c>
+      <c r="BX111" t="n">
+        <v>86</v>
+      </c>
+      <c r="BY111" t="n">
+        <v>113</v>
+      </c>
+      <c r="BZ111" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CA111" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CB111" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="CC111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR111" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS111" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU111" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV111" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX111" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY111" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ111" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA111" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB111" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC111" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD111" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DE111" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DF111" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DG111" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DH111" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DI111" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DJ111" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK111" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL111" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="DM111" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DN111" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DO111" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP111" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ111" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR111" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS111" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT111" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU111" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV111" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW111" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="DX111" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="DY111" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="DZ111" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA111" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EB111" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EC111" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="ED111" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EE111" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EF111" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="EG111" t="inlineStr">
+        <is>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="EH111" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="EI111" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EJ111" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EK111" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EL111" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EM111" t="inlineStr"/>
+      <c r="EN111" t="inlineStr"/>
+      <c r="EO111" t="inlineStr"/>
+      <c r="EP111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>14</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Al Quadisiya</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>46030.72916666666</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="n">
+        <v>2</v>
+      </c>
+      <c r="I112" t="n">
+        <v>3</v>
+      </c>
+      <c r="J112" t="n">
+        <v>4</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" t="n">
+        <v>5</v>
+      </c>
+      <c r="M112" t="n">
+        <v>2</v>
+      </c>
+      <c r="N112" t="n">
+        <v>6</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>3</v>
+      </c>
+      <c r="R112" t="n">
+        <v>5</v>
+      </c>
+      <c r="S112" t="n">
+        <v>13</v>
+      </c>
+      <c r="T112" t="n">
+        <v>2</v>
+      </c>
+      <c r="U112" t="n">
+        <v>16</v>
+      </c>
+      <c r="V112" t="n">
+        <v>7</v>
+      </c>
+      <c r="W112" t="n">
+        <v>9</v>
+      </c>
+      <c r="X112" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>King Saud University Stadium</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
+        </is>
+      </c>
+      <c r="AC112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB112" t="n">
+        <v>5068</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>25827</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR112" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT112" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV112" t="n">
+        <v>57</v>
+      </c>
+      <c r="BW112" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX112" t="n">
+        <v>121</v>
+      </c>
+      <c r="BY112" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ112" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CA112" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB112" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CC112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR112" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS112" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU112" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV112" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX112" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY112" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ112" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA112" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB112" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC112" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD112" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DE112" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DF112" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG112" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DH112" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DI112" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ112" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK112" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL112" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="DM112" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DN112" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="DO112" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP112" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ112" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR112" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS112" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT112" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU112" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV112" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW112" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="DX112" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="DY112" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="DZ112" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="EA112" t="inlineStr"/>
+      <c r="EB112" t="inlineStr"/>
+      <c r="EC112" t="inlineStr"/>
+      <c r="ED112" t="inlineStr"/>
+      <c r="EE112" t="inlineStr">
+        <is>
+          <t>4.44</t>
+        </is>
+      </c>
+      <c r="EF112" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+      <c r="EG112" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EH112" t="inlineStr"/>
+      <c r="EI112" t="inlineStr"/>
+      <c r="EJ112" t="inlineStr"/>
+      <c r="EK112" t="inlineStr"/>
+      <c r="EL112" t="inlineStr"/>
+      <c r="EM112" t="inlineStr"/>
+      <c r="EN112" t="inlineStr"/>
+      <c r="EO112" t="inlineStr"/>
+      <c r="EP112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>14</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Dhamk</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>46031.54861111111</v>
+      </c>
+      <c r="G113" t="n">
+        <v>4</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>4</v>
+      </c>
+      <c r="J113" t="n">
+        <v>9</v>
+      </c>
+      <c r="K113" t="n">
+        <v>2</v>
+      </c>
+      <c r="L113" t="n">
+        <v>11</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1</v>
+      </c>
+      <c r="N113" t="n">
+        <v>1</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>9</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>9</v>
+      </c>
+      <c r="T113" t="n">
+        <v>3</v>
+      </c>
+      <c r="U113" t="n">
+        <v>18</v>
+      </c>
+      <c r="V113" t="n">
+        <v>3</v>
+      </c>
+      <c r="W113" t="n">
+        <v>11</v>
+      </c>
+      <c r="X113" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>67</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>33</v>
+      </c>
+      <c r="AA113" t="inlineStr"/>
+      <c r="AB113" t="inlineStr"/>
+      <c r="AC113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU113" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB113" t="n">
+        <v>5077</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI113" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK113" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM113" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN113" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR113" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS113" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV113" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW113" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX113" t="n">
+        <v>134</v>
+      </c>
+      <c r="BY113" t="n">
+        <v>65</v>
+      </c>
+      <c r="BZ113" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CA113" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CB113" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR113" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS113" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU113" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV113" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX113" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY113" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ113" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA113" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB113" t="n">
+        <v>54</v>
+      </c>
+      <c r="DC113" t="n">
+        <v>90</v>
+      </c>
+      <c r="DD113" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE113" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DF113" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DG113" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH113" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DI113" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DJ113" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK113" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL113" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DM113" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DN113" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DO113" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP113" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ113" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR113" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS113" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV113" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW113" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="DX113" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="DY113" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="DZ113" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA113" t="inlineStr"/>
+      <c r="EB113" t="inlineStr"/>
+      <c r="EC113" t="inlineStr"/>
+      <c r="ED113" t="inlineStr"/>
+      <c r="EE113" t="inlineStr">
+        <is>
+          <t>5.21</t>
+        </is>
+      </c>
+      <c r="EF113" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="EG113" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EH113" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="EI113" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EJ113" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EK113" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EL113" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EM113" t="inlineStr"/>
+      <c r="EN113" t="inlineStr"/>
+      <c r="EO113" t="inlineStr"/>
+      <c r="EP113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>14</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Al Taawon</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Al Shabab</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>46031.62847222222</v>
+      </c>
+      <c r="G114" t="n">
+        <v>2</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>2</v>
+      </c>
+      <c r="J114" t="n">
+        <v>7</v>
+      </c>
+      <c r="K114" t="n">
+        <v>3</v>
+      </c>
+      <c r="L114" t="n">
+        <v>10</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1</v>
+      </c>
+      <c r="N114" t="n">
+        <v>5</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>4</v>
+      </c>
+      <c r="R114" t="n">
+        <v>4</v>
+      </c>
+      <c r="S114" t="n">
+        <v>15</v>
+      </c>
+      <c r="T114" t="n">
+        <v>6</v>
+      </c>
+      <c r="U114" t="n">
+        <v>19</v>
+      </c>
+      <c r="V114" t="n">
+        <v>10</v>
+      </c>
+      <c r="W114" t="n">
+        <v>11</v>
+      </c>
+      <c r="X114" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA114" t="inlineStr"/>
+      <c r="AB114" t="inlineStr"/>
+      <c r="AC114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>5074</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF114" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK114" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL114" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN114" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP114" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR114" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS114" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT114" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV114" t="n">
+        <v>68</v>
+      </c>
+      <c r="BW114" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX114" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY114" t="n">
+        <v>47</v>
+      </c>
+      <c r="BZ114" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CA114" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CB114" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CC114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR114" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS114" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU114" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV114" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX114" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY114" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ114" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA114" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB114" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC114" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD114" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DE114" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DF114" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DG114" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH114" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DI114" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DJ114" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK114" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL114" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DM114" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="DN114" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DO114" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP114" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ114" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV114" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW114" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="DX114" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="DY114" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="DZ114" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="EA114" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EB114" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EC114" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="ED114" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EE114" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EF114" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EG114" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EH114" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="EI114" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EJ114" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EK114" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EL114" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EM114" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EN114" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EO114" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EP114" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>14</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>46031.72916666666</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>4</v>
+      </c>
+      <c r="I115" t="n">
+        <v>4</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" t="n">
+        <v>12</v>
+      </c>
+      <c r="L115" t="n">
+        <v>13</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>2</v>
+      </c>
+      <c r="R115" t="n">
+        <v>11</v>
+      </c>
+      <c r="S115" t="n">
+        <v>3</v>
+      </c>
+      <c r="T115" t="n">
+        <v>13</v>
+      </c>
+      <c r="U115" t="n">
+        <v>5</v>
+      </c>
+      <c r="V115" t="n">
+        <v>24</v>
+      </c>
+      <c r="W115" t="n">
+        <v>5</v>
+      </c>
+      <c r="X115" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>72</v>
+      </c>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr"/>
+      <c r="AC115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>5070</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>82</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ115" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL115" t="n">
+        <v>8</v>
+      </c>
+      <c r="BM115" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN115" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV115" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW115" t="n">
+        <v>79</v>
+      </c>
+      <c r="BX115" t="n">
+        <v>69</v>
+      </c>
+      <c r="BY115" t="n">
+        <v>108</v>
+      </c>
+      <c r="BZ115" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="CA115" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CB115" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="CC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR115" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS115" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU115" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV115" t="n">
+        <v>4</v>
+      </c>
+      <c r="CW115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX115" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY115" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ115" t="n">
+        <v>72</v>
+      </c>
+      <c r="DA115" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB115" t="n">
+        <v>72</v>
+      </c>
+      <c r="DC115" t="n">
+        <v>90</v>
+      </c>
+      <c r="DD115" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DE115" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DF115" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG115" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DH115" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI115" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DJ115" t="n">
+        <v>29</v>
+      </c>
+      <c r="DK115" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL115" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DM115" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DN115" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="DO115" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP115" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ115" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR115" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS115" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV115" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW115" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="DX115" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="DY115" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="DZ115" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="EA115" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EB115" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EC115" t="inlineStr"/>
+      <c r="ED115" t="inlineStr"/>
+      <c r="EE115" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EF115" t="inlineStr">
+        <is>
+          <t>5.12</t>
+        </is>
+      </c>
+      <c r="EG115" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="EH115" t="inlineStr"/>
+      <c r="EI115" t="inlineStr"/>
+      <c r="EJ115" t="inlineStr"/>
+      <c r="EK115" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EL115" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EM115" t="inlineStr"/>
+      <c r="EN115" t="inlineStr"/>
+      <c r="EO115" t="inlineStr"/>
+      <c r="EP115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>14</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Neom SC</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Al Fateh</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>46032.58333333334</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" t="n">
+        <v>10</v>
+      </c>
+      <c r="K116" t="n">
+        <v>3</v>
+      </c>
+      <c r="L116" t="n">
+        <v>13</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" t="n">
+        <v>4</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>4</v>
+      </c>
+      <c r="R116" t="n">
+        <v>2</v>
+      </c>
+      <c r="S116" t="n">
+        <v>9</v>
+      </c>
+      <c r="T116" t="n">
+        <v>6</v>
+      </c>
+      <c r="U116" t="n">
+        <v>13</v>
+      </c>
+      <c r="V116" t="n">
+        <v>8</v>
+      </c>
+      <c r="W116" t="n">
+        <v>13</v>
+      </c>
+      <c r="X116" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr"/>
+      <c r="AC116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>5064</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI116" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK116" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM116" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN116" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR116" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT116" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV116" t="n">
+        <v>47</v>
+      </c>
+      <c r="BW116" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX116" t="n">
+        <v>112</v>
+      </c>
+      <c r="BY116" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ116" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CA116" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CB116" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR116" t="n">
+        <v>36</v>
+      </c>
+      <c r="CS116" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU116" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV116" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX116" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY116" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ116" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA116" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB116" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC116" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD116" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE116" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DF116" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DG116" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DH116" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DI116" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DJ116" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK116" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL116" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DM116" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DN116" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="DO116" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP116" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW116" t="inlineStr"/>
+      <c r="DX116" t="inlineStr"/>
+      <c r="DY116" t="inlineStr"/>
+      <c r="DZ116" t="inlineStr"/>
+      <c r="EA116" t="inlineStr"/>
+      <c r="EB116" t="inlineStr"/>
+      <c r="EC116" t="inlineStr"/>
+      <c r="ED116" t="inlineStr"/>
+      <c r="EE116" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="EF116" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="EG116" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EH116" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EI116" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EJ116" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EK116" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EL116" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EM116" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EN116" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EO116" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EP116" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>14</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Al Riyadh</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Al Feiha</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>46032.625</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" t="n">
+        <v>2</v>
+      </c>
+      <c r="J117" t="n">
+        <v>13</v>
+      </c>
+      <c r="K117" t="n">
+        <v>3</v>
+      </c>
+      <c r="L117" t="n">
+        <v>16</v>
+      </c>
+      <c r="M117" t="n">
+        <v>4</v>
+      </c>
+      <c r="N117" t="n">
+        <v>3</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>4</v>
+      </c>
+      <c r="R117" t="n">
+        <v>4</v>
+      </c>
+      <c r="S117" t="n">
+        <v>13</v>
+      </c>
+      <c r="T117" t="n">
+        <v>4</v>
+      </c>
+      <c r="U117" t="n">
+        <v>17</v>
+      </c>
+      <c r="V117" t="n">
+        <v>8</v>
+      </c>
+      <c r="W117" t="n">
+        <v>16</v>
+      </c>
+      <c r="X117" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>King Saud University Stadium</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
+        </is>
+      </c>
+      <c r="AC117" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>58</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>19</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>119</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>38</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU117" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV117" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX117" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY117" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ117" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA117" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB117" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC117" t="n">
+        <v>83</v>
+      </c>
+      <c r="DD117" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DE117" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF117" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DG117" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH117" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DI117" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ117" t="n">
+        <v>34</v>
+      </c>
+      <c r="DK117" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL117" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DM117" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DN117" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DO117" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW117" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="DX117" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="DY117" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="DZ117" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA117" t="inlineStr"/>
+      <c r="EB117" t="inlineStr"/>
+      <c r="EC117" t="inlineStr"/>
+      <c r="ED117" t="inlineStr"/>
+      <c r="EE117" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EF117" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="EG117" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EH117" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="EI117" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EJ117" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EK117" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EL117" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EM117" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="EN117" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EO117" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EP117" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>14</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Al Akhdoud</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>46032.72916666666</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" t="n">
+        <v>3</v>
+      </c>
+      <c r="K118" t="n">
+        <v>6</v>
+      </c>
+      <c r="L118" t="n">
+        <v>9</v>
+      </c>
+      <c r="M118" t="n">
+        <v>4</v>
+      </c>
+      <c r="N118" t="n">
+        <v>3</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>5</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="n">
+        <v>7</v>
+      </c>
+      <c r="U118" t="n">
+        <v>5</v>
+      </c>
+      <c r="V118" t="n">
+        <v>12</v>
+      </c>
+      <c r="W118" t="n">
+        <v>10</v>
+      </c>
+      <c r="X118" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA118" t="inlineStr"/>
+      <c r="AB118" t="inlineStr"/>
+      <c r="AC118" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>5062</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>52</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>76</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU118" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV118" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX118" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY118" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ118" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA118" t="n">
+        <v>62</v>
+      </c>
+      <c r="DB118" t="n">
+        <v>44</v>
+      </c>
+      <c r="DC118" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD118" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DE118" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DF118" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DG118" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH118" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="DI118" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DJ118" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK118" t="n">
+        <v>39</v>
+      </c>
+      <c r="DL118" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DM118" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DN118" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="DO118" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP118" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW118" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="DX118" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="DY118" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="DZ118" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA118" t="inlineStr"/>
+      <c r="EB118" t="inlineStr"/>
+      <c r="EC118" t="inlineStr"/>
+      <c r="ED118" t="inlineStr"/>
+      <c r="EE118" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EF118" t="inlineStr">
+        <is>
+          <t>5.17</t>
+        </is>
+      </c>
+      <c r="EG118" t="inlineStr">
+        <is>
+          <t>8.25</t>
+        </is>
+      </c>
+      <c r="EH118" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EI118" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EJ118" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EK118" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EL118" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EM118" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EN118" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EO118" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EP118" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP127" headerRowCount="1">
-  <autoFilter ref="A1:EP127"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP130" headerRowCount="1">
+  <autoFilter ref="A1:EP130"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP127"/>
+  <dimension ref="A1:EP130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -6950,10 +6950,10 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7406,7 +7406,7 @@
         <v>50</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE14" t="n">
         <v>0.88</v>
@@ -10661,7 +10661,7 @@
         <v>2.29</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -11141,7 +11141,7 @@
         <v>1</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -12711,12 +12711,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -12726,120 +12726,120 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L26" t="n">
+        <v>11</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="n">
         <v>8</v>
       </c>
-      <c r="M26" t="n">
-        <v>2</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>11</v>
-      </c>
       <c r="U26" t="n">
+        <v>13</v>
+      </c>
+      <c r="V26" t="n">
         <v>9</v>
       </c>
-      <c r="V26" t="n">
-        <v>15</v>
-      </c>
       <c r="W26" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="X26" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Y26" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="Z26" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="n">
-        <v>3.6</v>
+        <v>4.35</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.45</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.49</v>
+        <v>2.19</v>
       </c>
       <c r="AO26" t="n">
-        <v>3.14</v>
+        <v>2.3</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AS26" t="n">
         <v>3.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV26" t="n">
         <v>0</v>
@@ -12851,16 +12851,16 @@
         <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA26" t="n">
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>-1</v>
+        <v>5070</v>
       </c>
       <c r="BC26" t="n">
         <v>0</v>
@@ -12875,70 +12875,70 @@
         <v>-1</v>
       </c>
       <c r="BG26" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH26" t="n">
         <v>1</v>
       </c>
       <c r="BI26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BK26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL26" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BM26" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BN26" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BO26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ26" t="n">
         <v>1</v>
       </c>
       <c r="BR26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS26" t="n">
         <v>1</v>
       </c>
       <c r="BT26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU26" t="n">
         <v>1</v>
       </c>
       <c r="BV26" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="BW26" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="BX26" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="BY26" t="n">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.55</v>
+        <v>1.16</v>
       </c>
       <c r="CB26" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="CC26" t="n">
         <v>0</v>
@@ -12971,10 +12971,10 @@
         <v>0</v>
       </c>
       <c r="CM26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CN26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO26" t="n">
         <v>0</v>
@@ -12986,25 +12986,25 @@
         <v>1</v>
       </c>
       <c r="CR26" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS26" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU26" t="n">
         <v>19</v>
       </c>
-      <c r="CS26" t="n">
-        <v>20</v>
-      </c>
-      <c r="CT26" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU26" t="n">
-        <v>12</v>
-      </c>
       <c r="CV26" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="CW26" t="n">
         <v>1</v>
       </c>
       <c r="CX26" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="CY26" t="n">
         <v>8</v>
@@ -13022,22 +13022,22 @@
         <v>50</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.67</v>
+        <v>0.29</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.14</v>
+        <v>2.14</v>
       </c>
       <c r="DF26" t="n">
         <v>0</v>
       </c>
       <c r="DG26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="DI26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DJ26" t="n">
         <v>0</v>
@@ -13049,16 +13049,16 @@
         <v>0</v>
       </c>
       <c r="DM26" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="DN26" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="DO26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ26" t="b">
         <v>0</v>
@@ -13096,58 +13096,74 @@
       </c>
       <c r="EA26" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EB26" t="inlineStr">
         <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="EC26" t="inlineStr"/>
-      <c r="ED26" t="inlineStr"/>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EC26" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="ED26" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
       <c r="EE26" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EF26" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="EG26" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="EH26" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EI26" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EJ26" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="EK26" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EL26" t="inlineStr">
         <is>
-          <t>2.58</t>
-        </is>
-      </c>
-      <c r="EM26" t="inlineStr"/>
-      <c r="EN26" t="inlineStr"/>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EM26" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EN26" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="EO26" t="inlineStr"/>
       <c r="EP26" t="inlineStr"/>
     </row>
@@ -13167,12 +13183,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -13182,120 +13198,120 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L27" t="n">
         <v>8</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="n">
         <v>11</v>
       </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="n">
-        <v>8</v>
-      </c>
       <c r="U27" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W27" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="X27" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Y27" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="Z27" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="AF27" t="n">
-        <v>4.35</v>
+        <v>3.6</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.31</v>
+        <v>2.45</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AM27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN27" t="n">
         <v>1.49</v>
       </c>
-      <c r="AN27" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AO27" t="n">
-        <v>2.3</v>
+        <v>3.14</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AS27" t="n">
         <v>3.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AU27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
         <v>0</v>
@@ -13307,16 +13323,16 @@
         <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>5070</v>
+        <v>-1</v>
       </c>
       <c r="BC27" t="n">
         <v>0</v>
@@ -13331,70 +13347,70 @@
         <v>-1</v>
       </c>
       <c r="BG27" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH27" t="n">
         <v>1</v>
       </c>
       <c r="BI27" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BJ27" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK27" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL27" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BM27" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BN27" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BO27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ27" t="n">
         <v>1</v>
       </c>
       <c r="BR27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS27" t="n">
         <v>1</v>
       </c>
       <c r="BT27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU27" t="n">
         <v>1</v>
       </c>
       <c r="BV27" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="BW27" t="n">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="BX27" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="BY27" t="n">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.16</v>
+        <v>1.55</v>
       </c>
       <c r="CB27" t="n">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="CC27" t="n">
         <v>0</v>
@@ -13427,10 +13443,10 @@
         <v>0</v>
       </c>
       <c r="CM27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO27" t="n">
         <v>0</v>
@@ -13442,25 +13458,25 @@
         <v>1</v>
       </c>
       <c r="CR27" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="CS27" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="CT27" t="n">
         <v>1</v>
       </c>
       <c r="CU27" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="CV27" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="CW27" t="n">
         <v>1</v>
       </c>
       <c r="CX27" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="CY27" t="n">
         <v>8</v>
@@ -13478,22 +13494,22 @@
         <v>50</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.17</v>
+        <v>0.67</v>
       </c>
       <c r="DE27" t="n">
-        <v>2.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF27" t="n">
         <v>0</v>
       </c>
       <c r="DG27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DI27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DJ27" t="n">
         <v>0</v>
@@ -13505,16 +13521,16 @@
         <v>0</v>
       </c>
       <c r="DM27" t="n">
-        <v>2.14</v>
+        <v>1.42</v>
       </c>
       <c r="DN27" t="n">
-        <v>2.14</v>
+        <v>1.42</v>
       </c>
       <c r="DO27" t="n">
         <v>14</v>
       </c>
       <c r="DP27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ27" t="b">
         <v>0</v>
@@ -13552,74 +13568,58 @@
       </c>
       <c r="EA27" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EB27" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EC27" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="ED27" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EC27" t="inlineStr"/>
+      <c r="ED27" t="inlineStr"/>
       <c r="EE27" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EF27" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="EG27" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="EH27" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EI27" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EJ27" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EK27" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EL27" t="inlineStr">
         <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="EM27" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EN27" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EM27" t="inlineStr"/>
+      <c r="EN27" t="inlineStr"/>
       <c r="EO27" t="inlineStr"/>
       <c r="EP27" t="inlineStr"/>
     </row>
@@ -14430,7 +14430,7 @@
         <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE29" t="n">
         <v>2.14</v>
@@ -15369,7 +15369,7 @@
         <v>2.75</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF31" t="n">
         <v>2</v>
@@ -16289,7 +16289,7 @@
         <v>0.57</v>
       </c>
       <c r="DE33" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF33" t="n">
         <v>0.5</v>
@@ -16746,7 +16746,7 @@
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE34" t="n">
         <v>1.86</v>
@@ -17706,7 +17706,7 @@
         <v>50</v>
       </c>
       <c r="DD36" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="DE36" t="n">
         <v>0.88</v>
@@ -21013,7 +21013,7 @@
         <v>2.57</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF43" t="n">
         <v>3</v>
@@ -21474,7 +21474,7 @@
         <v>75</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE44" t="n">
         <v>0.14</v>
@@ -23826,7 +23826,7 @@
         <v>0</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="DE49" t="n">
         <v>2.17</v>
@@ -24309,7 +24309,7 @@
         <v>1.71</v>
       </c>
       <c r="DE50" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF50" t="n">
         <v>0</v>
@@ -24339,7 +24339,7 @@
         <v>2.43</v>
       </c>
       <c r="DO50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25246,7 +25246,7 @@
         <v>100</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE52" t="n">
         <v>2.67</v>
@@ -25713,7 +25713,7 @@
         <v>2.43</v>
       </c>
       <c r="DE53" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF53" t="n">
         <v>3</v>
@@ -27093,7 +27093,7 @@
         <v>0.57</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF56" t="n">
         <v>0.33</v>
@@ -28543,7 +28543,7 @@
         <v>2.02</v>
       </c>
       <c r="DO59" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -30414,7 +30414,7 @@
         <v>67</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE63" t="n">
         <v>2.14</v>
@@ -30447,7 +30447,7 @@
         <v>3.33</v>
       </c>
       <c r="DO63" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -32737,7 +32737,7 @@
         <v>1</v>
       </c>
       <c r="DE68" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF68" t="n">
         <v>0.67</v>
@@ -33670,7 +33670,7 @@
         <v>67</v>
       </c>
       <c r="DD70" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="DE70" t="n">
         <v>2.67</v>
@@ -34609,7 +34609,7 @@
         <v>1.14</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF72" t="n">
         <v>1</v>
@@ -35094,7 +35094,7 @@
         <v>67</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE73" t="n">
         <v>2.17</v>
@@ -36030,7 +36030,7 @@
         <v>75</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE75" t="n">
         <v>0.14</v>
@@ -37861,7 +37861,7 @@
         <v>2.75</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF79" t="n">
         <v>2.5</v>
@@ -38487,348 +38487,356 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
         <v>45984.72916666666</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H81" t="n">
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
+        <v>4</v>
+      </c>
+      <c r="K81" t="n">
+        <v>2</v>
+      </c>
+      <c r="L81" t="n">
+        <v>6</v>
+      </c>
+      <c r="M81" t="n">
+        <v>3</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>10</v>
+      </c>
+      <c r="R81" t="n">
+        <v>5</v>
+      </c>
+      <c r="S81" t="n">
+        <v>11</v>
+      </c>
+      <c r="T81" t="n">
+        <v>7</v>
+      </c>
+      <c r="U81" t="n">
+        <v>21</v>
+      </c>
+      <c r="V81" t="n">
+        <v>12</v>
+      </c>
+      <c r="W81" t="n">
+        <v>15</v>
+      </c>
+      <c r="X81" t="n">
         <v>8</v>
       </c>
-      <c r="K81" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" t="n">
-        <v>9</v>
-      </c>
-      <c r="M81" t="n">
-        <v>3</v>
-      </c>
-      <c r="N81" t="n">
-        <v>3</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>2</v>
-      </c>
-      <c r="R81" t="n">
-        <v>2</v>
-      </c>
-      <c r="S81" t="n">
+      <c r="Y81" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>King Saud University Stadium</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
+        </is>
+      </c>
+      <c r="AC81" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>5069</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>88</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>26003</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV81" t="n">
+        <v>47</v>
+      </c>
+      <c r="BW81" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX81" t="n">
+        <v>113</v>
+      </c>
+      <c r="BY81" t="n">
+        <v>54</v>
+      </c>
+      <c r="BZ81" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CA81" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CB81" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="CC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR81" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS81" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU81" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV81" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX81" t="n">
         <v>6</v>
       </c>
-      <c r="T81" t="n">
-        <v>13</v>
-      </c>
-      <c r="U81" t="n">
-        <v>8</v>
-      </c>
-      <c r="V81" t="n">
-        <v>15</v>
-      </c>
-      <c r="W81" t="n">
-        <v>11</v>
-      </c>
-      <c r="X81" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>49</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA81" t="inlineStr"/>
-      <c r="AB81" t="inlineStr"/>
-      <c r="AC81" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE81" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF81" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG81" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AH81" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI81" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ81" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK81" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL81" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM81" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AN81" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AO81" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AP81" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AQ81" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR81" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AS81" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AT81" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AU81" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ81" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB81" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD81" t="n">
-        <v>63</v>
-      </c>
-      <c r="BE81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF81" t="n">
-        <v>5050</v>
-      </c>
-      <c r="BG81" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH81" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI81" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK81" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL81" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM81" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN81" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO81" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP81" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ81" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR81" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS81" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT81" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU81" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV81" t="n">
-        <v>37</v>
-      </c>
-      <c r="BW81" t="n">
-        <v>31</v>
-      </c>
-      <c r="BX81" t="n">
-        <v>45</v>
-      </c>
-      <c r="BY81" t="n">
-        <v>55</v>
-      </c>
-      <c r="BZ81" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="CA81" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="CB81" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="CC81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR81" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS81" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU81" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV81" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX81" t="n">
-        <v>10</v>
-      </c>
       <c r="CY81" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="CZ81" t="n">
         <v>75</v>
       </c>
       <c r="DA81" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="DB81" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="DC81" t="n">
         <v>88</v>
       </c>
       <c r="DD81" t="n">
-        <v>2.29</v>
+        <v>2.57</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.86</v>
+        <v>1.38</v>
       </c>
       <c r="DF81" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="DG81" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="DH81" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="DI81" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="DJ81" t="n">
         <v>25</v>
       </c>
       <c r="DK81" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="DL81" t="n">
-        <v>1.2</v>
+        <v>2.59</v>
       </c>
       <c r="DM81" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="DN81" t="n">
-        <v>2.51</v>
+        <v>3.82</v>
       </c>
       <c r="DO81" t="n">
         <v>14</v>
@@ -38840,13 +38848,13 @@
         <v>1</v>
       </c>
       <c r="DR81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU81" t="b">
         <v>0</v>
@@ -38855,85 +38863,73 @@
         <v>1</v>
       </c>
       <c r="DW81" t="n">
-        <v>30.11</v>
+        <v>21.64</v>
       </c>
       <c r="DX81" t="n">
-        <v>4.86</v>
+        <v>4.03</v>
       </c>
       <c r="DY81" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="DZ81" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="EA81" t="inlineStr"/>
-      <c r="EB81" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA81" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EB81" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
       <c r="EC81" t="inlineStr"/>
       <c r="ED81" t="inlineStr"/>
       <c r="EE81" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="EF81" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="EG81" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="EH81" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EI81" t="inlineStr">
         <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EJ81" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EJ81" t="inlineStr"/>
       <c r="EK81" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EL81" t="inlineStr">
         <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="EM81" t="inlineStr">
-        <is>
-          <t>2.71</t>
-        </is>
-      </c>
-      <c r="EN81" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EO81" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EP81" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EM81" t="inlineStr"/>
+      <c r="EN81" t="inlineStr"/>
+      <c r="EO81" t="inlineStr"/>
+      <c r="EP81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -38951,356 +38947,348 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
         <v>45984.72916666666</v>
       </c>
       <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>2</v>
+      </c>
+      <c r="J82" t="n">
+        <v>8</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" t="n">
+        <v>9</v>
+      </c>
+      <c r="M82" t="n">
+        <v>3</v>
+      </c>
+      <c r="N82" t="n">
+        <v>3</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>2</v>
+      </c>
+      <c r="R82" t="n">
+        <v>2</v>
+      </c>
+      <c r="S82" t="n">
+        <v>6</v>
+      </c>
+      <c r="T82" t="n">
+        <v>13</v>
+      </c>
+      <c r="U82" t="n">
+        <v>8</v>
+      </c>
+      <c r="V82" t="n">
+        <v>15</v>
+      </c>
+      <c r="W82" t="n">
+        <v>11</v>
+      </c>
+      <c r="X82" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>5050</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI82" t="n">
         <v>4</v>
       </c>
-      <c r="H82" t="n">
-        <v>1</v>
-      </c>
-      <c r="I82" t="n">
-        <v>5</v>
-      </c>
-      <c r="J82" t="n">
+      <c r="BJ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM82" t="n">
         <v>4</v>
       </c>
-      <c r="K82" t="n">
-        <v>2</v>
-      </c>
-      <c r="L82" t="n">
-        <v>6</v>
-      </c>
-      <c r="M82" t="n">
-        <v>3</v>
-      </c>
-      <c r="N82" t="n">
-        <v>1</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q82" t="n">
+      <c r="BN82" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT82" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV82" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW82" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX82" t="n">
+        <v>45</v>
+      </c>
+      <c r="BY82" t="n">
+        <v>55</v>
+      </c>
+      <c r="BZ82" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CA82" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CB82" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR82" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS82" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU82" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV82" t="n">
         <v>10</v>
       </c>
-      <c r="R82" t="n">
-        <v>5</v>
-      </c>
-      <c r="S82" t="n">
-        <v>11</v>
-      </c>
-      <c r="T82" t="n">
-        <v>7</v>
-      </c>
-      <c r="U82" t="n">
-        <v>21</v>
-      </c>
-      <c r="V82" t="n">
-        <v>12</v>
-      </c>
-      <c r="W82" t="n">
-        <v>15</v>
-      </c>
-      <c r="X82" t="n">
+      <c r="CW82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX82" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY82" t="n">
         <v>8</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>King Saud University Stadium</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
-        </is>
-      </c>
-      <c r="AC82" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AG82" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH82" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AI82" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AJ82" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AK82" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL82" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM82" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AN82" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO82" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AP82" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AQ82" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AR82" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS82" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT82" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AU82" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV82" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX82" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ82" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA82" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB82" t="n">
-        <v>5069</v>
-      </c>
-      <c r="BC82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD82" t="n">
-        <v>88</v>
-      </c>
-      <c r="BE82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF82" t="n">
-        <v>26003</v>
-      </c>
-      <c r="BG82" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH82" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI82" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ82" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK82" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL82" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM82" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN82" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO82" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP82" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ82" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR82" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS82" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT82" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU82" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV82" t="n">
-        <v>47</v>
-      </c>
-      <c r="BW82" t="n">
-        <v>29</v>
-      </c>
-      <c r="BX82" t="n">
-        <v>113</v>
-      </c>
-      <c r="BY82" t="n">
-        <v>54</v>
-      </c>
-      <c r="BZ82" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="CA82" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CB82" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="CC82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR82" t="n">
-        <v>14</v>
-      </c>
-      <c r="CS82" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU82" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV82" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX82" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY82" t="n">
-        <v>14</v>
       </c>
       <c r="CZ82" t="n">
         <v>75</v>
       </c>
       <c r="DA82" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="DB82" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="DC82" t="n">
         <v>88</v>
       </c>
       <c r="DD82" t="n">
-        <v>2.57</v>
+        <v>2.29</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="DF82" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="DG82" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="DH82" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="DI82" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="DJ82" t="n">
         <v>25</v>
       </c>
       <c r="DK82" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="DL82" t="n">
-        <v>2.59</v>
+        <v>1.2</v>
       </c>
       <c r="DM82" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="DN82" t="n">
-        <v>3.82</v>
+        <v>2.51</v>
       </c>
       <c r="DO82" t="n">
         <v>14</v>
@@ -39312,13 +39300,13 @@
         <v>1</v>
       </c>
       <c r="DR82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU82" t="b">
         <v>0</v>
@@ -39327,73 +39315,85 @@
         <v>1</v>
       </c>
       <c r="DW82" t="n">
-        <v>21.64</v>
+        <v>30.11</v>
       </c>
       <c r="DX82" t="n">
-        <v>4.03</v>
+        <v>4.86</v>
       </c>
       <c r="DY82" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="DZ82" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="EA82" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EB82" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="EA82" t="inlineStr"/>
+      <c r="EB82" t="inlineStr"/>
       <c r="EC82" t="inlineStr"/>
       <c r="ED82" t="inlineStr"/>
       <c r="EE82" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EF82" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EG82" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EH82" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EI82" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EJ82" t="inlineStr"/>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EJ82" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
       <c r="EK82" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EL82" t="inlineStr">
         <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="EM82" t="inlineStr"/>
-      <c r="EN82" t="inlineStr"/>
-      <c r="EO82" t="inlineStr"/>
-      <c r="EP82" t="inlineStr"/>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EM82" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EN82" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EO82" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EP82" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -40213,7 +40213,7 @@
         <v>1.14</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF84" t="n">
         <v>1.75</v>
@@ -42937,7 +42937,7 @@
         <v>2.57</v>
       </c>
       <c r="DE90" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF90" t="n">
         <v>3</v>
@@ -43402,7 +43402,7 @@
         <v>78</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE91" t="n">
         <v>0.43</v>
@@ -43882,10 +43882,10 @@
         <v>68</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE92" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF92" t="n">
         <v>1.75</v>
@@ -43915,7 +43915,7 @@
         <v>2.77</v>
       </c>
       <c r="DO92" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -46807,76 +46807,76 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
         <v>46022.72916666666</v>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
         <v>3</v>
       </c>
       <c r="I99" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J99" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K99" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L99" t="n">
         <v>12</v>
       </c>
       <c r="M99" t="n">
+        <v>2</v>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" t="n">
+        <v>1</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
         <v>4</v>
       </c>
-      <c r="N99" t="n">
-        <v>1</v>
-      </c>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>6</v>
-      </c>
       <c r="R99" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S99" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T99" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="U99" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V99" t="n">
+        <v>24</v>
+      </c>
+      <c r="W99" t="n">
         <v>11</v>
       </c>
-      <c r="W99" t="n">
-        <v>9</v>
-      </c>
       <c r="X99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y99" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z99" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr"/>
@@ -46887,88 +46887,88 @@
         <v>1</v>
       </c>
       <c r="AE99" t="n">
-        <v>5.59</v>
+        <v>10</v>
       </c>
       <c r="AF99" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AT99" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AU99" t="n">
         <v>4</v>
       </c>
-      <c r="AG99" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI99" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AJ99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK99" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL99" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU99" t="n">
-        <v>5</v>
-      </c>
       <c r="AV99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ99" t="n">
         <v>2</v>
       </c>
       <c r="BA99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB99" t="n">
-        <v>5068</v>
+        <v>5066</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BE99" t="n">
         <v>0</v>
       </c>
       <c r="BF99" t="n">
-        <v>2556</v>
+        <v>9253</v>
       </c>
       <c r="BG99" t="n">
         <v>2</v>
@@ -46977,178 +46977,178 @@
         <v>1</v>
       </c>
       <c r="BI99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL99" t="n">
+        <v>8</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV99" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW99" t="n">
+        <v>68</v>
+      </c>
+      <c r="BX99" t="n">
+        <v>57</v>
+      </c>
+      <c r="BY99" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ99" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CA99" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="CB99" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="CC99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR99" t="n">
         <v>6</v>
       </c>
-      <c r="BL99" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM99" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN99" t="n">
+      <c r="CS99" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU99" t="n">
         <v>9</v>
       </c>
-      <c r="BO99" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ99" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR99" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS99" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT99" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU99" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV99" t="n">
-        <v>59</v>
-      </c>
-      <c r="BW99" t="n">
-        <v>61</v>
-      </c>
-      <c r="BX99" t="n">
-        <v>99</v>
-      </c>
-      <c r="BY99" t="n">
-        <v>116</v>
-      </c>
-      <c r="BZ99" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="CA99" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CB99" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="CC99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR99" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS99" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU99" t="n">
-        <v>14</v>
-      </c>
       <c r="CV99" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CW99" t="n">
         <v>1</v>
       </c>
       <c r="CX99" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="CY99" t="n">
         <v>9</v>
       </c>
       <c r="CZ99" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="DA99" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="DB99" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="DC99" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.14</v>
+        <v>0.86</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.86</v>
+        <v>2.67</v>
       </c>
       <c r="DF99" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DG99" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="DH99" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="DI99" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="DJ99" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="DK99" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="DL99" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="DM99" t="n">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="DN99" t="n">
-        <v>3.04</v>
+        <v>3.24</v>
       </c>
       <c r="DO99" t="n">
         <v>14</v>
@@ -47166,7 +47166,7 @@
         <v>1</v>
       </c>
       <c r="DT99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU99" t="b">
         <v>0</v>
@@ -47175,14 +47175,14 @@
         <v>1</v>
       </c>
       <c r="DW99" t="n">
-        <v>13.4</v>
+        <v>15.88</v>
       </c>
       <c r="DX99" t="n">
-        <v>4.76</v>
+        <v>5.15</v>
       </c>
       <c r="DY99" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="DZ99" t="inlineStr">
@@ -47190,32 +47190,68 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA99" t="inlineStr"/>
-      <c r="EB99" t="inlineStr"/>
+      <c r="EA99" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EB99" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
       <c r="EC99" t="inlineStr"/>
       <c r="ED99" t="inlineStr"/>
       <c r="EE99" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EF99" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="EG99" t="inlineStr">
         <is>
-          <t>5.07</t>
-        </is>
-      </c>
-      <c r="EH99" t="inlineStr"/>
-      <c r="EI99" t="inlineStr"/>
-      <c r="EJ99" t="inlineStr"/>
-      <c r="EK99" t="inlineStr"/>
-      <c r="EL99" t="inlineStr"/>
-      <c r="EM99" t="inlineStr"/>
-      <c r="EN99" t="inlineStr"/>
+          <t>8.72</t>
+        </is>
+      </c>
+      <c r="EH99" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EI99" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EJ99" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="EK99" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EL99" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EM99" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EN99" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
       <c r="EO99" t="inlineStr"/>
       <c r="EP99" t="inlineStr"/>
     </row>
@@ -47235,76 +47271,76 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
         <v>46022.72916666666</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" t="n">
         <v>3</v>
       </c>
       <c r="I100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J100" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K100" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L100" t="n">
         <v>12</v>
       </c>
       <c r="M100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N100" t="n">
         <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R100" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T100" t="n">
+        <v>5</v>
+      </c>
+      <c r="U100" t="n">
         <v>14</v>
       </c>
-      <c r="U100" t="n">
+      <c r="V100" t="n">
         <v>11</v>
       </c>
-      <c r="V100" t="n">
-        <v>24</v>
-      </c>
       <c r="W100" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y100" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z100" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr"/>
@@ -47315,88 +47351,88 @@
         <v>1</v>
       </c>
       <c r="AE100" t="n">
-        <v>10</v>
+        <v>5.59</v>
       </c>
       <c r="AF100" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="AG100" t="n">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI100" t="n">
-        <v>1.31</v>
+        <v>1.72</v>
       </c>
       <c r="AJ100" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AK100" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AL100" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AM100" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN100" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO100" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AS100" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AU100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ100" t="n">
         <v>2</v>
       </c>
       <c r="BA100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB100" t="n">
-        <v>5066</v>
+        <v>5068</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
       </c>
       <c r="BF100" t="n">
-        <v>9253</v>
+        <v>2556</v>
       </c>
       <c r="BG100" t="n">
         <v>2</v>
@@ -47405,178 +47441,178 @@
         <v>1</v>
       </c>
       <c r="BI100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK100" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BL100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV100" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW100" t="n">
+        <v>61</v>
+      </c>
+      <c r="BX100" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY100" t="n">
+        <v>116</v>
+      </c>
+      <c r="BZ100" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CC100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR100" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS100" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU100" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV100" t="n">
         <v>8</v>
       </c>
-      <c r="BM100" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN100" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO100" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ100" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR100" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS100" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT100" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU100" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV100" t="n">
-        <v>18</v>
-      </c>
-      <c r="BW100" t="n">
-        <v>68</v>
-      </c>
-      <c r="BX100" t="n">
-        <v>57</v>
-      </c>
-      <c r="BY100" t="n">
-        <v>110</v>
-      </c>
-      <c r="BZ100" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="CA100" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="CB100" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="CC100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR100" t="n">
-        <v>6</v>
-      </c>
-      <c r="CS100" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU100" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV100" t="n">
-        <v>11</v>
-      </c>
       <c r="CW100" t="n">
         <v>1</v>
       </c>
       <c r="CX100" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="CY100" t="n">
         <v>9</v>
       </c>
       <c r="CZ100" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="DA100" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="DB100" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="DC100" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="DD100" t="n">
-        <v>0.86</v>
+        <v>1.14</v>
       </c>
       <c r="DE100" t="n">
-        <v>2.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF100" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DG100" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="DH100" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="DI100" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="DJ100" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="DK100" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="DL100" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="DM100" t="n">
-        <v>1.88</v>
+        <v>1.41</v>
       </c>
       <c r="DN100" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="DO100" t="n">
         <v>14</v>
@@ -47594,7 +47630,7 @@
         <v>1</v>
       </c>
       <c r="DT100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU100" t="b">
         <v>0</v>
@@ -47603,14 +47639,14 @@
         <v>1</v>
       </c>
       <c r="DW100" t="n">
-        <v>15.88</v>
+        <v>13.4</v>
       </c>
       <c r="DX100" t="n">
-        <v>5.15</v>
+        <v>4.76</v>
       </c>
       <c r="DY100" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="DZ100" t="inlineStr">
@@ -47618,68 +47654,32 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA100" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EB100" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
+      <c r="EA100" t="inlineStr"/>
+      <c r="EB100" t="inlineStr"/>
       <c r="EC100" t="inlineStr"/>
       <c r="ED100" t="inlineStr"/>
       <c r="EE100" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EF100" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="EG100" t="inlineStr">
         <is>
-          <t>8.72</t>
-        </is>
-      </c>
-      <c r="EH100" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EI100" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EJ100" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="EK100" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EL100" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EM100" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EN100" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="EH100" t="inlineStr"/>
+      <c r="EI100" t="inlineStr"/>
+      <c r="EJ100" t="inlineStr"/>
+      <c r="EK100" t="inlineStr"/>
+      <c r="EL100" t="inlineStr"/>
+      <c r="EM100" t="inlineStr"/>
+      <c r="EN100" t="inlineStr"/>
       <c r="EO100" t="inlineStr"/>
       <c r="EP100" t="inlineStr"/>
     </row>
@@ -48018,7 +48018,7 @@
         <v>75</v>
       </c>
       <c r="DD101" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="DE101" t="n">
         <v>1.38</v>
@@ -48051,7 +48051,7 @@
         <v>2.03</v>
       </c>
       <c r="DO101" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -48493,7 +48493,7 @@
         <v>1.5</v>
       </c>
       <c r="DE102" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF102" t="n">
         <v>1.5</v>
@@ -48523,7 +48523,7 @@
         <v>1.44</v>
       </c>
       <c r="DO102" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -50306,7 +50306,7 @@
         <v>82</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE106" t="n">
         <v>2.14</v>
@@ -50923,40 +50923,40 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
         <v>46026.72916666666</v>
       </c>
       <c r="G108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I108" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J108" t="n">
+        <v>2</v>
+      </c>
+      <c r="K108" t="n">
         <v>9</v>
       </c>
-      <c r="K108" t="n">
-        <v>4</v>
-      </c>
       <c r="L108" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -50965,114 +50965,122 @@
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S108" t="n">
         <v>8</v>
       </c>
       <c r="T108" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U108" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="V108" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="W108" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="X108" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="Y108" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="Z108" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA108" t="inlineStr"/>
-      <c r="AB108" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>Dhamak Club Stadium</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>, Khamis Mushait</t>
+        </is>
+      </c>
       <c r="AC108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.3</v>
+        <v>12.2</v>
       </c>
       <c r="AF108" t="n">
-        <v>5.2</v>
+        <v>6.15</v>
       </c>
       <c r="AG108" t="n">
-        <v>9.140000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="AH108" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI108" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AJ108" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AK108" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AL108" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AM108" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN108" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AO108" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AP108" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR108" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS108" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AU108" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB108" t="n">
-        <v>5068</v>
+        <v>5066</v>
       </c>
       <c r="BC108" t="n">
         <v>0</v>
@@ -51084,7 +51092,7 @@
         <v>0</v>
       </c>
       <c r="BF108" t="n">
-        <v>6160</v>
+        <v>14873</v>
       </c>
       <c r="BG108" t="n">
         <v>2</v>
@@ -51093,133 +51101,133 @@
         <v>1</v>
       </c>
       <c r="BI108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ108" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL108" t="n">
         <v>6</v>
       </c>
-      <c r="BJ108" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK108" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL108" t="n">
-        <v>2</v>
-      </c>
       <c r="BM108" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN108" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV108" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW108" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX108" t="n">
+        <v>71</v>
+      </c>
+      <c r="BY108" t="n">
+        <v>119</v>
+      </c>
+      <c r="BZ108" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CA108" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CB108" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR108" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS108" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU108" t="n">
         <v>8</v>
       </c>
-      <c r="BN108" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ108" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT108" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV108" t="n">
-        <v>49</v>
-      </c>
-      <c r="BW108" t="n">
-        <v>52</v>
-      </c>
-      <c r="BX108" t="n">
-        <v>90</v>
-      </c>
-      <c r="BY108" t="n">
-        <v>79</v>
-      </c>
-      <c r="BZ108" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CA108" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CB108" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="CC108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR108" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS108" t="n">
-        <v>18</v>
-      </c>
-      <c r="CT108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU108" t="n">
-        <v>19</v>
-      </c>
       <c r="CV108" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CW108" t="n">
         <v>1</v>
       </c>
       <c r="CX108" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CY108" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CZ108" t="n">
         <v>60</v>
@@ -51228,28 +51236,28 @@
         <v>90</v>
       </c>
       <c r="DB108" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="DC108" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="DD108" t="n">
-        <v>2.43</v>
+        <v>0.57</v>
       </c>
       <c r="DE108" t="n">
-        <v>0.14</v>
+        <v>2.67</v>
       </c>
       <c r="DF108" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="DG108" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="DH108" t="n">
-        <v>1.91</v>
+        <v>0.82</v>
       </c>
       <c r="DI108" t="n">
-        <v>0.73</v>
+        <v>2.64</v>
       </c>
       <c r="DJ108" t="n">
         <v>40</v>
@@ -51258,13 +51266,13 @@
         <v>10</v>
       </c>
       <c r="DL108" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="DM108" t="n">
-        <v>1.05</v>
+        <v>2.04</v>
       </c>
       <c r="DN108" t="n">
-        <v>2.86</v>
+        <v>3.29</v>
       </c>
       <c r="DO108" t="n">
         <v>14</v>
@@ -51276,10 +51284,10 @@
         <v>1</v>
       </c>
       <c r="DR108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT108" t="b">
         <v>0</v>
@@ -51291,47 +51299,83 @@
         <v>0</v>
       </c>
       <c r="DW108" t="n">
-        <v>19.18</v>
+        <v>20.33</v>
       </c>
       <c r="DX108" t="n">
-        <v>12.01</v>
+        <v>4</v>
       </c>
       <c r="DY108" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="DZ108" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="EA108" t="inlineStr"/>
-      <c r="EB108" t="inlineStr"/>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="EA108" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EB108" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
       <c r="EC108" t="inlineStr"/>
       <c r="ED108" t="inlineStr"/>
       <c r="EE108" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EF108" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="EG108" t="inlineStr">
         <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="EH108" t="inlineStr"/>
-      <c r="EI108" t="inlineStr"/>
-      <c r="EJ108" t="inlineStr"/>
-      <c r="EK108" t="inlineStr"/>
-      <c r="EL108" t="inlineStr"/>
-      <c r="EM108" t="inlineStr"/>
-      <c r="EN108" t="inlineStr"/>
+          <t>9.85</t>
+        </is>
+      </c>
+      <c r="EH108" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EI108" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EJ108" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EK108" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EL108" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EM108" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EN108" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
       <c r="EO108" t="inlineStr"/>
       <c r="EP108" t="inlineStr"/>
     </row>
@@ -51351,40 +51395,40 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
         <v>46026.72916666666</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J109" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K109" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L109" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -51393,122 +51437,114 @@
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R109" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S109" t="n">
         <v>8</v>
       </c>
       <c r="T109" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="U109" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="V109" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="W109" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="X109" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="Y109" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="Z109" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>Dhamak Club Stadium</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>, Khamis Mushait</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr"/>
       <c r="AC109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>12.2</v>
+        <v>1.3</v>
       </c>
       <c r="AF109" t="n">
-        <v>6.15</v>
+        <v>5.2</v>
       </c>
       <c r="AG109" t="n">
-        <v>1.11</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AH109" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI109" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ109" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AK109" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AL109" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AM109" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN109" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AO109" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR109" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS109" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AT109" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AU109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB109" t="n">
-        <v>5066</v>
+        <v>5068</v>
       </c>
       <c r="BC109" t="n">
         <v>0</v>
@@ -51520,7 +51556,7 @@
         <v>0</v>
       </c>
       <c r="BF109" t="n">
-        <v>14873</v>
+        <v>6160</v>
       </c>
       <c r="BG109" t="n">
         <v>2</v>
@@ -51529,133 +51565,133 @@
         <v>1</v>
       </c>
       <c r="BI109" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BJ109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV109" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW109" t="n">
+        <v>52</v>
+      </c>
+      <c r="BX109" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY109" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ109" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CA109" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CB109" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CC109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR109" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS109" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU109" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV109" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX109" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY109" t="n">
         <v>6</v>
-      </c>
-      <c r="BM109" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN109" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP109" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS109" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT109" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV109" t="n">
-        <v>22</v>
-      </c>
-      <c r="BW109" t="n">
-        <v>56</v>
-      </c>
-      <c r="BX109" t="n">
-        <v>71</v>
-      </c>
-      <c r="BY109" t="n">
-        <v>119</v>
-      </c>
-      <c r="BZ109" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="CA109" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CB109" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="CC109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR109" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS109" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU109" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV109" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX109" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY109" t="n">
-        <v>9</v>
       </c>
       <c r="CZ109" t="n">
         <v>60</v>
@@ -51664,28 +51700,28 @@
         <v>90</v>
       </c>
       <c r="DB109" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="DC109" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="DD109" t="n">
-        <v>0.57</v>
+        <v>2.43</v>
       </c>
       <c r="DE109" t="n">
-        <v>2.67</v>
+        <v>0.14</v>
       </c>
       <c r="DF109" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="DG109" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="DH109" t="n">
-        <v>0.82</v>
+        <v>1.91</v>
       </c>
       <c r="DI109" t="n">
-        <v>2.64</v>
+        <v>0.73</v>
       </c>
       <c r="DJ109" t="n">
         <v>40</v>
@@ -51694,13 +51730,13 @@
         <v>10</v>
       </c>
       <c r="DL109" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="DM109" t="n">
-        <v>2.04</v>
+        <v>1.05</v>
       </c>
       <c r="DN109" t="n">
-        <v>3.29</v>
+        <v>2.86</v>
       </c>
       <c r="DO109" t="n">
         <v>14</v>
@@ -51712,10 +51748,10 @@
         <v>1</v>
       </c>
       <c r="DR109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT109" t="b">
         <v>0</v>
@@ -51727,83 +51763,47 @@
         <v>0</v>
       </c>
       <c r="DW109" t="n">
-        <v>20.33</v>
+        <v>19.18</v>
       </c>
       <c r="DX109" t="n">
-        <v>4</v>
+        <v>12.01</v>
       </c>
       <c r="DY109" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="DZ109" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="EA109" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="EB109" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA109" t="inlineStr"/>
+      <c r="EB109" t="inlineStr"/>
       <c r="EC109" t="inlineStr"/>
       <c r="ED109" t="inlineStr"/>
       <c r="EE109" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="EF109" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="EG109" t="inlineStr">
         <is>
-          <t>9.85</t>
-        </is>
-      </c>
-      <c r="EH109" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="EI109" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EJ109" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="EK109" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="EL109" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EM109" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="EN109" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EH109" t="inlineStr"/>
+      <c r="EI109" t="inlineStr"/>
+      <c r="EJ109" t="inlineStr"/>
+      <c r="EK109" t="inlineStr"/>
+      <c r="EL109" t="inlineStr"/>
+      <c r="EM109" t="inlineStr"/>
+      <c r="EN109" t="inlineStr"/>
       <c r="EO109" t="inlineStr"/>
       <c r="EP109" t="inlineStr"/>
     </row>
@@ -53042,10 +53042,10 @@
         <v>60</v>
       </c>
       <c r="DD112" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DF112" t="n">
         <v>0.2</v>
@@ -53075,7 +53075,7 @@
         <v>2.33</v>
       </c>
       <c r="DO112" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -53506,7 +53506,7 @@
         <v>90</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="DE113" t="n">
         <v>0.86</v>
@@ -54881,7 +54881,7 @@
         <v>1</v>
       </c>
       <c r="DE116" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF116" t="n">
         <v>1.17</v>
@@ -57267,7 +57267,7 @@
         <v>2.33</v>
       </c>
       <c r="DO121" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -57851,164 +57851,164 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F123" s="2" t="n">
         <v>46035.72916666666</v>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H123" t="n">
         <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J123" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K123" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L123" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
+        <v>5</v>
+      </c>
+      <c r="R123" t="n">
+        <v>9</v>
+      </c>
+      <c r="S123" t="n">
+        <v>6</v>
+      </c>
+      <c r="T123" t="n">
+        <v>9</v>
+      </c>
+      <c r="U123" t="n">
+        <v>11</v>
+      </c>
+      <c r="V123" t="n">
+        <v>18</v>
+      </c>
+      <c r="W123" t="n">
+        <v>16</v>
+      </c>
+      <c r="X123" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>Prince Abdullah bin Jalawi Sports City Stadium</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>, Al-Hasa</t>
+        </is>
+      </c>
+      <c r="AC123" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AU123" t="n">
         <v>4</v>
       </c>
-      <c r="R123" t="n">
-        <v>3</v>
-      </c>
-      <c r="S123" t="n">
-        <v>4</v>
-      </c>
-      <c r="T123" t="n">
-        <v>14</v>
-      </c>
-      <c r="U123" t="n">
-        <v>8</v>
-      </c>
-      <c r="V123" t="n">
-        <v>17</v>
-      </c>
-      <c r="W123" t="n">
-        <v>6</v>
-      </c>
-      <c r="X123" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y123" t="n">
-        <v>33</v>
-      </c>
-      <c r="Z123" t="n">
-        <v>67</v>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>Dhamak Club Stadium</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>, Khamis Mushait</t>
-        </is>
-      </c>
-      <c r="AC123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD123" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE123" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="AF123" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG123" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH123" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI123" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AJ123" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AK123" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL123" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM123" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AN123" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AO123" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AP123" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AQ123" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AR123" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AS123" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AT123" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AU123" t="n">
-        <v>2</v>
-      </c>
       <c r="AV123" t="n">
         <v>1</v>
       </c>
       <c r="AW123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB123" t="n">
-        <v>-1</v>
+        <v>5064</v>
       </c>
       <c r="BC123" t="n">
         <v>0</v>
@@ -58020,187 +58020,187 @@
         <v>0</v>
       </c>
       <c r="BF123" t="n">
-        <v>9065</v>
+        <v>9104</v>
       </c>
       <c r="BG123" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH123" t="n">
         <v>1</v>
       </c>
       <c r="BI123" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BJ123" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BK123" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL123" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="BM123" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BN123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>62</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>124</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR123" t="n">
         <v>9</v>
       </c>
-      <c r="BO123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR123" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS123" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT123" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU123" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV123" t="n">
-        <v>15</v>
-      </c>
-      <c r="BW123" t="n">
-        <v>86</v>
-      </c>
-      <c r="BX123" t="n">
-        <v>75</v>
-      </c>
-      <c r="BY123" t="n">
-        <v>132</v>
-      </c>
-      <c r="BZ123" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="CA123" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CB123" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="CC123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI123" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ123" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP123" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ123" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR123" t="n">
-        <v>17</v>
-      </c>
       <c r="CS123" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="CT123" t="n">
         <v>1</v>
       </c>
       <c r="CU123" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="CV123" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="CW123" t="n">
         <v>1</v>
       </c>
       <c r="CX123" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="CY123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CZ123" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="DA123" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB123" t="n">
+        <v>67</v>
+      </c>
+      <c r="DC123" t="n">
         <v>83</v>
       </c>
-      <c r="DB123" t="n">
-        <v>42</v>
-      </c>
-      <c r="DC123" t="n">
-        <v>67</v>
-      </c>
       <c r="DD123" t="n">
-        <v>0.57</v>
+        <v>1.71</v>
       </c>
       <c r="DE123" t="n">
-        <v>2.14</v>
+        <v>0.14</v>
       </c>
       <c r="DF123" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="DG123" t="n">
-        <v>2.33</v>
+        <v>0.17</v>
       </c>
       <c r="DH123" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DI123" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="DI123" t="n">
-        <v>2</v>
-      </c>
       <c r="DJ123" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="DK123" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="DL123" t="n">
-        <v>1.15</v>
+        <v>1.55</v>
       </c>
       <c r="DM123" t="n">
-        <v>1.84</v>
+        <v>1.1</v>
       </c>
       <c r="DN123" t="n">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="DO123" t="n">
         <v>14</v>
@@ -58212,10 +58212,10 @@
         <v>1</v>
       </c>
       <c r="DR123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT123" t="b">
         <v>0</v>
@@ -58227,93 +58227,93 @@
         <v>1</v>
       </c>
       <c r="DW123" t="n">
-        <v>20.33</v>
+        <v>20.19</v>
       </c>
       <c r="DX123" t="n">
-        <v>5.5</v>
+        <v>5.05</v>
       </c>
       <c r="DY123" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="DZ123" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="EA123" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EB123" t="inlineStr">
         <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="EC123" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="ED123" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EC123" t="inlineStr"/>
+      <c r="ED123" t="inlineStr"/>
       <c r="EE123" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="EF123" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EG123" t="inlineStr">
         <is>
-          <t>12.95</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EH123" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="EI123" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EJ123" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EK123" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EL123" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EM123" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EN123" t="inlineStr">
+        <is>
           <t>1.47</t>
         </is>
       </c>
-      <c r="EJ123" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="EK123" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="EL123" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EM123" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="EN123" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EO123" t="inlineStr"/>
-      <c r="EP123" t="inlineStr"/>
+      <c r="EO123" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EP123" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -58331,164 +58331,164 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F124" s="2" t="n">
         <v>46035.72916666666</v>
       </c>
       <c r="G124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H124" t="n">
         <v>1</v>
       </c>
       <c r="I124" t="n">
+        <v>2</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1</v>
+      </c>
+      <c r="K124" t="n">
+        <v>12</v>
+      </c>
+      <c r="L124" t="n">
+        <v>13</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>3</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q124" t="n">
         <v>4</v>
       </c>
-      <c r="J124" t="n">
-        <v>7</v>
-      </c>
-      <c r="K124" t="n">
-        <v>9</v>
-      </c>
-      <c r="L124" t="n">
-        <v>16</v>
-      </c>
-      <c r="M124" t="n">
-        <v>3</v>
-      </c>
-      <c r="N124" t="n">
-        <v>2</v>
-      </c>
-      <c r="O124" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>5</v>
-      </c>
       <c r="R124" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="S124" t="n">
+        <v>4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>14</v>
+      </c>
+      <c r="U124" t="n">
+        <v>8</v>
+      </c>
+      <c r="V124" t="n">
+        <v>17</v>
+      </c>
+      <c r="W124" t="n">
         <v>6</v>
       </c>
-      <c r="T124" t="n">
-        <v>9</v>
-      </c>
-      <c r="U124" t="n">
-        <v>11</v>
-      </c>
-      <c r="V124" t="n">
-        <v>18</v>
-      </c>
-      <c r="W124" t="n">
-        <v>16</v>
-      </c>
       <c r="X124" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Y124" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="Z124" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>Prince Abdullah bin Jalawi Sports City Stadium</t>
+          <t>Dhamak Club Stadium</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>, Al-Hasa</t>
+          <t>, Khamis Mushait</t>
         </is>
       </c>
       <c r="AC124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.76</v>
+        <v>9.75</v>
       </c>
       <c r="AF124" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="AG124" t="n">
-        <v>3.85</v>
+        <v>1.26</v>
       </c>
       <c r="AH124" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AI124" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AT124" t="n">
         <v>1.64</v>
       </c>
-      <c r="AJ124" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AK124" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL124" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM124" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN124" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO124" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AP124" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AQ124" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR124" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AS124" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AT124" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AU124" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV124" t="n">
         <v>1</v>
       </c>
       <c r="AW124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB124" t="n">
-        <v>5064</v>
+        <v>-1</v>
       </c>
       <c r="BC124" t="n">
         <v>0</v>
@@ -58500,73 +58500,73 @@
         <v>0</v>
       </c>
       <c r="BF124" t="n">
-        <v>9104</v>
+        <v>9065</v>
       </c>
       <c r="BG124" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH124" t="n">
         <v>1</v>
       </c>
       <c r="BI124" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BJ124" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BK124" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL124" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BM124" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BN124" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BO124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR124" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BS124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU124" t="n">
         <v>1</v>
       </c>
       <c r="BV124" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="BW124" t="n">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="BX124" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="BY124" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="BZ124" t="n">
-        <v>1.27</v>
+        <v>0.9</v>
       </c>
       <c r="CA124" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="CB124" t="n">
-        <v>3.34</v>
+        <v>2.81</v>
       </c>
       <c r="CC124" t="n">
         <v>0</v>
@@ -58599,10 +58599,10 @@
         <v>0</v>
       </c>
       <c r="CM124" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN124" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO124" t="n">
         <v>0</v>
@@ -58614,73 +58614,73 @@
         <v>1</v>
       </c>
       <c r="CR124" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="CS124" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU124" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV124" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX124" t="n">
         <v>19</v>
       </c>
-      <c r="CT124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU124" t="n">
-        <v>21</v>
-      </c>
-      <c r="CV124" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX124" t="n">
-        <v>11</v>
-      </c>
       <c r="CY124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CZ124" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA124" t="n">
+        <v>83</v>
+      </c>
+      <c r="DB124" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC124" t="n">
         <v>67</v>
       </c>
-      <c r="DA124" t="n">
-        <v>92</v>
-      </c>
-      <c r="DB124" t="n">
-        <v>67</v>
-      </c>
-      <c r="DC124" t="n">
-        <v>83</v>
-      </c>
       <c r="DD124" t="n">
-        <v>1.71</v>
+        <v>0.57</v>
       </c>
       <c r="DE124" t="n">
-        <v>0.14</v>
+        <v>2.14</v>
       </c>
       <c r="DF124" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="DG124" t="n">
-        <v>0.17</v>
+        <v>2.33</v>
       </c>
       <c r="DH124" t="n">
-        <v>1.31</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DI124" t="n">
-        <v>0.6899999999999999</v>
+        <v>2</v>
       </c>
       <c r="DJ124" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="DK124" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="DL124" t="n">
-        <v>1.55</v>
+        <v>1.15</v>
       </c>
       <c r="DM124" t="n">
-        <v>1.1</v>
+        <v>1.84</v>
       </c>
       <c r="DN124" t="n">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="DO124" t="n">
         <v>14</v>
@@ -58692,10 +58692,10 @@
         <v>1</v>
       </c>
       <c r="DR124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT124" t="b">
         <v>0</v>
@@ -58707,93 +58707,93 @@
         <v>1</v>
       </c>
       <c r="DW124" t="n">
-        <v>20.19</v>
+        <v>20.33</v>
       </c>
       <c r="DX124" t="n">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="DY124" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="DZ124" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA124" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EB124" t="inlineStr">
         <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="EC124" t="inlineStr"/>
-      <c r="ED124" t="inlineStr"/>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EC124" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="ED124" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
       <c r="EE124" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EF124" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="EG124" t="inlineStr">
         <is>
+          <t>12.95</t>
+        </is>
+      </c>
+      <c r="EH124" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EI124" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EJ124" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EK124" t="inlineStr">
+        <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="EH124" t="inlineStr">
-        <is>
-          <t>2.87</t>
-        </is>
-      </c>
-      <c r="EI124" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EJ124" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="EK124" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
       <c r="EL124" t="inlineStr">
         <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EM124" t="inlineStr">
+        <is>
           <t>2.17</t>
         </is>
       </c>
-      <c r="EM124" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
       <c r="EN124" t="inlineStr">
         <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EO124" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EP124" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
-      </c>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EO124" t="inlineStr"/>
+      <c r="EP124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -59269,7 +59269,7 @@
         <v>6</v>
       </c>
       <c r="M126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N126" t="n">
         <v>2</v>
@@ -59321,7 +59321,7 @@
         </is>
       </c>
       <c r="AC126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD126" t="n">
         <v>2</v>
@@ -59441,7 +59441,7 @@
         <v>1</v>
       </c>
       <c r="BQ126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR126" t="n">
         <v>1</v>
@@ -59450,7 +59450,7 @@
         <v>1</v>
       </c>
       <c r="BT126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU126" t="n">
         <v>1</v>
@@ -60147,6 +60147,1422 @@
       <c r="EO127" t="inlineStr"/>
       <c r="EP127" t="inlineStr"/>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>16</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Al Najma</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Al Fateh</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>46038.56944444445</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" t="n">
+        <v>2</v>
+      </c>
+      <c r="J128" t="n">
+        <v>9</v>
+      </c>
+      <c r="K128" t="n">
+        <v>9</v>
+      </c>
+      <c r="L128" t="n">
+        <v>18</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>4</v>
+      </c>
+      <c r="R128" t="n">
+        <v>5</v>
+      </c>
+      <c r="S128" t="n">
+        <v>12</v>
+      </c>
+      <c r="T128" t="n">
+        <v>9</v>
+      </c>
+      <c r="U128" t="n">
+        <v>16</v>
+      </c>
+      <c r="V128" t="n">
+        <v>14</v>
+      </c>
+      <c r="W128" t="n">
+        <v>10</v>
+      </c>
+      <c r="X128" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>Al-Najma Club Stadium</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>, Unaizah</t>
+        </is>
+      </c>
+      <c r="AC128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>73</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>117</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU128" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV128" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX128" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY128" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ128" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA128" t="n">
+        <v>62</v>
+      </c>
+      <c r="DB128" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC128" t="n">
+        <v>61</v>
+      </c>
+      <c r="DD128" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DE128" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DF128" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DG128" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DH128" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DI128" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DJ128" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK128" t="n">
+        <v>38</v>
+      </c>
+      <c r="DL128" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DM128" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DN128" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="DO128" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW128" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="DX128" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="DY128" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="DZ128" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA128" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EB128" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EC128" t="inlineStr"/>
+      <c r="ED128" t="inlineStr"/>
+      <c r="EE128" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EF128" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="EG128" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="EH128" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EI128" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EJ128" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="EK128" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EL128" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EM128" t="inlineStr"/>
+      <c r="EN128" t="inlineStr"/>
+      <c r="EO128" t="inlineStr"/>
+      <c r="EP128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>16</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Al Akhdoud</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>46038.61458333334</v>
+      </c>
+      <c r="G129" t="n">
+        <v>4</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" t="n">
+        <v>5</v>
+      </c>
+      <c r="J129" t="n">
+        <v>4</v>
+      </c>
+      <c r="K129" t="n">
+        <v>2</v>
+      </c>
+      <c r="L129" t="n">
+        <v>6</v>
+      </c>
+      <c r="M129" t="n">
+        <v>1</v>
+      </c>
+      <c r="N129" t="n">
+        <v>2</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>9</v>
+      </c>
+      <c r="R129" t="n">
+        <v>4</v>
+      </c>
+      <c r="S129" t="n">
+        <v>6</v>
+      </c>
+      <c r="T129" t="n">
+        <v>3</v>
+      </c>
+      <c r="U129" t="n">
+        <v>15</v>
+      </c>
+      <c r="V129" t="n">
+        <v>7</v>
+      </c>
+      <c r="W129" t="n">
+        <v>16</v>
+      </c>
+      <c r="X129" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA129" t="inlineStr"/>
+      <c r="AB129" t="inlineStr"/>
+      <c r="AC129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>5077</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>129</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>56</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU129" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV129" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX129" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY129" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ129" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA129" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB129" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC129" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD129" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DE129" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DF129" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG129" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DH129" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI129" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DJ129" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK129" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL129" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DM129" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="DN129" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DO129" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW129" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="DX129" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="DY129" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="DZ129" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA129" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EB129" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EC129" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="ED129" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EE129" t="inlineStr">
+        <is>
+          <t>5.76</t>
+        </is>
+      </c>
+      <c r="EF129" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="EG129" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EH129" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="EI129" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EJ129" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EK129" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EL129" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EM129" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="EN129" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EO129" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EP129" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>16</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Al Ittifaq</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>46038.72916666666</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" t="n">
+        <v>1</v>
+      </c>
+      <c r="J130" t="n">
+        <v>10</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1</v>
+      </c>
+      <c r="L130" t="n">
+        <v>11</v>
+      </c>
+      <c r="M130" t="n">
+        <v>2</v>
+      </c>
+      <c r="N130" t="n">
+        <v>5</v>
+      </c>
+      <c r="O130" t="n">
+        <v>1</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>5</v>
+      </c>
+      <c r="R130" t="n">
+        <v>4</v>
+      </c>
+      <c r="S130" t="n">
+        <v>11</v>
+      </c>
+      <c r="T130" t="n">
+        <v>2</v>
+      </c>
+      <c r="U130" t="n">
+        <v>16</v>
+      </c>
+      <c r="V130" t="n">
+        <v>6</v>
+      </c>
+      <c r="W130" t="n">
+        <v>12</v>
+      </c>
+      <c r="X130" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>King Abdullah Sports City</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>, Jeddah</t>
+        </is>
+      </c>
+      <c r="AC130" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>5065</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>28363</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>134</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>55</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU130" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV130" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX130" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY130" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ130" t="n">
+        <v>48</v>
+      </c>
+      <c r="DA130" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB130" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC130" t="n">
+        <v>77</v>
+      </c>
+      <c r="DD130" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE130" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DF130" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DG130" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DH130" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DI130" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DJ130" t="n">
+        <v>52</v>
+      </c>
+      <c r="DK130" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL130" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DM130" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DN130" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="DO130" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP130" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV130" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW130" t="n">
+        <v>28.27</v>
+      </c>
+      <c r="DX130" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="DY130" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="DZ130" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA130" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EB130" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EC130" t="inlineStr"/>
+      <c r="ED130" t="inlineStr"/>
+      <c r="EE130" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="EF130" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="EG130" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EH130" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EI130" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EJ130" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="EK130" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EL130" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EM130" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EN130" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EO130" t="inlineStr"/>
+      <c r="EP130" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP130" headerRowCount="1">
-  <autoFilter ref="A1:EP130"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP136" headerRowCount="1">
+  <autoFilter ref="A1:EP136"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP130"/>
+  <dimension ref="A1:EP136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4175,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6033,7 +6033,7 @@
         <v>1.5</v>
       </c>
       <c r="DE11" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF11" t="n">
         <v>3</v>
@@ -6063,7 +6063,7 @@
         <v>0.93</v>
       </c>
       <c r="DO11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP11" t="b">
         <v>0</v>
@@ -6519,7 +6519,7 @@
         <v>2.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7439,7 +7439,7 @@
         <v>0.87</v>
       </c>
       <c r="DO14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7873,7 +7873,7 @@
         <v>0.88</v>
       </c>
       <c r="DE15" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -7903,7 +7903,7 @@
         <v>0.91</v>
       </c>
       <c r="DO15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8337,7 +8337,7 @@
         <v>2.75</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF16" t="n">
         <v>3</v>
@@ -8367,7 +8367,7 @@
         <v>1.8</v>
       </c>
       <c r="DO16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8798,7 +8798,7 @@
         <v>50</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE17" t="n">
         <v>0.13</v>
@@ -8831,7 +8831,7 @@
         <v>0.99</v>
       </c>
       <c r="DO17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9295,7 +9295,7 @@
         <v>2.11</v>
       </c>
       <c r="DO18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9718,7 +9718,7 @@
         <v>50</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE19" t="n">
         <v>0.86</v>
@@ -9751,7 +9751,7 @@
         <v>1.18</v>
       </c>
       <c r="DO19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10178,10 +10178,10 @@
         <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF20" t="n">
         <v>0</v>
@@ -10211,7 +10211,7 @@
         <v>0</v>
       </c>
       <c r="DO20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10691,7 +10691,7 @@
         <v>0.44</v>
       </c>
       <c r="DO21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="DD22" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DE22" t="n">
         <v>0.14</v>
@@ -11171,7 +11171,7 @@
         <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11639,7 +11639,7 @@
         <v>3.01</v>
       </c>
       <c r="DO23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12081,7 +12081,7 @@
         <v>1</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -12111,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="DO24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP24" t="b">
         <v>0</v>
@@ -12569,7 +12569,7 @@
         <v>2.25</v>
       </c>
       <c r="DE25" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DF25" t="n">
         <v>3</v>
@@ -12599,7 +12599,7 @@
         <v>1.06</v>
       </c>
       <c r="DO25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13494,7 +13494,7 @@
         <v>50</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE27" t="n">
         <v>1.13</v>
@@ -13527,7 +13527,7 @@
         <v>1.42</v>
       </c>
       <c r="DO27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP27" t="b">
         <v>0</v>
@@ -13958,7 +13958,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE28" t="n">
         <v>0.14</v>
@@ -13991,7 +13991,7 @@
         <v>3.72</v>
       </c>
       <c r="DO28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14433,7 +14433,7 @@
         <v>1.86</v>
       </c>
       <c r="DE29" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -14463,7 +14463,7 @@
         <v>2.82</v>
       </c>
       <c r="DO29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14943,7 +14943,7 @@
         <v>2.34</v>
       </c>
       <c r="DO30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15399,7 +15399,7 @@
         <v>2.97</v>
       </c>
       <c r="DO31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15822,10 +15822,10 @@
         <v>0</v>
       </c>
       <c r="DD32" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE32" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF32" t="n">
         <v>1</v>
@@ -15855,7 +15855,7 @@
         <v>2.93</v>
       </c>
       <c r="DO32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16319,7 +16319,7 @@
         <v>2.59</v>
       </c>
       <c r="DO33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16779,7 +16779,7 @@
         <v>4.3</v>
       </c>
       <c r="DO34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17226,7 +17226,7 @@
         <v>100</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE35" t="n">
         <v>1.86</v>
@@ -17259,7 +17259,7 @@
         <v>2.37</v>
       </c>
       <c r="DO35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17739,7 +17739,7 @@
         <v>2.25</v>
       </c>
       <c r="DO36" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18181,7 +18181,7 @@
         <v>1.71</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF37" t="n">
         <v>0</v>
@@ -18211,7 +18211,7 @@
         <v>2.65</v>
       </c>
       <c r="DO37" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18683,7 +18683,7 @@
         <v>2.44</v>
       </c>
       <c r="DO38" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19122,7 +19122,7 @@
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DE39" t="n">
         <v>0.13</v>
@@ -19155,7 +19155,7 @@
         <v>2.02</v>
       </c>
       <c r="DO39" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19613,7 +19613,7 @@
         <v>2.25</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF40" t="n">
         <v>2</v>
@@ -19643,7 +19643,7 @@
         <v>2.66</v>
       </c>
       <c r="DO40" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20085,7 +20085,7 @@
         <v>1.5</v>
       </c>
       <c r="DE41" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DF41" t="n">
         <v>2</v>
@@ -20115,7 +20115,7 @@
         <v>2</v>
       </c>
       <c r="DO41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20571,7 +20571,7 @@
         <v>1.63</v>
       </c>
       <c r="DO42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21010,7 +21010,7 @@
         <v>50</v>
       </c>
       <c r="DD43" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE43" t="n">
         <v>1.13</v>
@@ -21043,7 +21043,7 @@
         <v>4.22</v>
       </c>
       <c r="DO43" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21507,7 +21507,7 @@
         <v>2.13</v>
       </c>
       <c r="DO44" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21941,7 +21941,7 @@
         <v>2.29</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF45" t="n">
         <v>1.5</v>
@@ -21971,7 +21971,7 @@
         <v>2.14</v>
       </c>
       <c r="DO45" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22402,10 +22402,10 @@
         <v>75</v>
       </c>
       <c r="DD46" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF46" t="n">
         <v>3</v>
@@ -22435,7 +22435,7 @@
         <v>2.57</v>
       </c>
       <c r="DO46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22866,7 +22866,7 @@
         <v>67</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE47" t="n">
         <v>0.86</v>
@@ -22899,7 +22899,7 @@
         <v>1.84</v>
       </c>
       <c r="DO47" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23349,7 +23349,7 @@
         <v>1</v>
       </c>
       <c r="DE48" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF48" t="n">
         <v>1</v>
@@ -23379,7 +23379,7 @@
         <v>1.94</v>
       </c>
       <c r="DO48" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23829,7 +23829,7 @@
         <v>0.29</v>
       </c>
       <c r="DE49" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF49" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>2.9</v>
       </c>
       <c r="DO49" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24778,7 +24778,7 @@
         <v>100</v>
       </c>
       <c r="DD51" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DE51" t="n">
         <v>1.38</v>
@@ -24811,7 +24811,7 @@
         <v>2.84</v>
       </c>
       <c r="DO51" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25249,7 +25249,7 @@
         <v>1.5</v>
       </c>
       <c r="DE52" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DF52" t="n">
         <v>1.5</v>
@@ -25279,7 +25279,7 @@
         <v>3.18</v>
       </c>
       <c r="DO52" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25743,7 +25743,7 @@
         <v>2.21</v>
       </c>
       <c r="DO53" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP53" t="b">
         <v>0</v>
@@ -26165,7 +26165,7 @@
         <v>1.14</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF54" t="n">
         <v>1</v>
@@ -26195,7 +26195,7 @@
         <v>2.64</v>
       </c>
       <c r="DO54" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26610,7 +26610,7 @@
         <v>50</v>
       </c>
       <c r="DD55" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE55" t="n">
         <v>1.86</v>
@@ -26643,7 +26643,7 @@
         <v>3.19</v>
       </c>
       <c r="DO55" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27123,7 +27123,7 @@
         <v>2.65</v>
       </c>
       <c r="DO56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27595,7 +27595,7 @@
         <v>2.85</v>
       </c>
       <c r="DO57" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28030,7 +28030,7 @@
         <v>100</v>
       </c>
       <c r="DD58" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DE58" t="n">
         <v>1.86</v>
@@ -28063,7 +28063,7 @@
         <v>2.85</v>
       </c>
       <c r="DO58" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28993,7 +28993,7 @@
         <v>2.75</v>
       </c>
       <c r="DE60" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF60" t="n">
         <v>2.33</v>
@@ -29023,7 +29023,7 @@
         <v>3.38</v>
       </c>
       <c r="DO60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29487,7 +29487,7 @@
         <v>1.4</v>
       </c>
       <c r="DO61" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29937,7 +29937,7 @@
         <v>2.29</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF62" t="n">
         <v>2</v>
@@ -29967,7 +29967,7 @@
         <v>2.42</v>
       </c>
       <c r="DO62" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30886,7 +30886,7 @@
         <v>67</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE64" t="n">
         <v>0.88</v>
@@ -30919,7 +30919,7 @@
         <v>3.73</v>
       </c>
       <c r="DO64" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31342,7 +31342,7 @@
         <v>67</v>
       </c>
       <c r="DD65" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE65" t="n">
         <v>1.38</v>
@@ -31375,7 +31375,7 @@
         <v>2.02</v>
       </c>
       <c r="DO65" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31814,10 +31814,10 @@
         <v>100</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE66" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF66" t="n">
         <v>2</v>
@@ -31847,7 +31847,7 @@
         <v>2.17</v>
       </c>
       <c r="DO66" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32311,7 +32311,7 @@
         <v>2.65</v>
       </c>
       <c r="DO67" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32767,7 +32767,7 @@
         <v>1.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33209,7 +33209,7 @@
         <v>1.71</v>
       </c>
       <c r="DE69" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF69" t="n">
         <v>1</v>
@@ -33239,7 +33239,7 @@
         <v>2.68</v>
       </c>
       <c r="DO69" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33673,7 +33673,7 @@
         <v>0.29</v>
       </c>
       <c r="DE70" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DF70" t="n">
         <v>0</v>
@@ -33703,7 +33703,7 @@
         <v>2.5</v>
       </c>
       <c r="DO70" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34134,7 +34134,7 @@
         <v>100</v>
       </c>
       <c r="DD71" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DE71" t="n">
         <v>1.86</v>
@@ -34167,7 +34167,7 @@
         <v>3.72</v>
       </c>
       <c r="DO71" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -34639,7 +34639,7 @@
         <v>2.76</v>
       </c>
       <c r="DO72" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35097,7 +35097,7 @@
         <v>1.5</v>
       </c>
       <c r="DE73" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF73" t="n">
         <v>1</v>
@@ -35127,7 +35127,7 @@
         <v>3.05</v>
       </c>
       <c r="DO73" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35566,7 +35566,7 @@
         <v>75</v>
       </c>
       <c r="DD74" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DE74" t="n">
         <v>1.5</v>
@@ -35599,7 +35599,7 @@
         <v>2.12</v>
       </c>
       <c r="DO74" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36063,7 +36063,7 @@
         <v>2.45</v>
       </c>
       <c r="DO75" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36513,7 +36513,7 @@
         <v>2.25</v>
       </c>
       <c r="DE76" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF76" t="n">
         <v>1.5</v>
@@ -36543,7 +36543,7 @@
         <v>3.13</v>
       </c>
       <c r="DO76" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36999,7 +36999,7 @@
         <v>2.28</v>
       </c>
       <c r="DO77" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -37463,7 +37463,7 @@
         <v>1.69</v>
       </c>
       <c r="DO78" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37891,7 +37891,7 @@
         <v>3.63</v>
       </c>
       <c r="DO79" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -38321,7 +38321,7 @@
         <v>0.88</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF80" t="n">
         <v>0.75</v>
@@ -38351,7 +38351,7 @@
         <v>2.38</v>
       </c>
       <c r="DO80" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38806,7 +38806,7 @@
         <v>88</v>
       </c>
       <c r="DD81" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE81" t="n">
         <v>1.38</v>
@@ -38839,7 +38839,7 @@
         <v>3.82</v>
       </c>
       <c r="DO81" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -39291,7 +39291,7 @@
         <v>2.51</v>
       </c>
       <c r="DO82" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39755,7 +39755,7 @@
         <v>2.19</v>
       </c>
       <c r="DO83" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP83" t="b">
         <v>0</v>
@@ -40210,7 +40210,7 @@
         <v>100</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE84" t="n">
         <v>1.86</v>
@@ -40243,7 +40243,7 @@
         <v>2.29</v>
       </c>
       <c r="DO84" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40646,7 +40646,7 @@
         <v>78</v>
       </c>
       <c r="DD85" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DE85" t="n">
         <v>0.13</v>
@@ -40679,7 +40679,7 @@
         <v>2.45</v>
       </c>
       <c r="DO85" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41129,7 +41129,7 @@
         <v>1.71</v>
       </c>
       <c r="DE86" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF86" t="n">
         <v>0.75</v>
@@ -41159,7 +41159,7 @@
         <v>3.42</v>
       </c>
       <c r="DO86" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41554,10 +41554,10 @@
         <v>88</v>
       </c>
       <c r="DD87" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DE87" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF87" t="n">
         <v>1.5</v>
@@ -41587,7 +41587,7 @@
         <v>2.81</v>
       </c>
       <c r="DO87" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -42067,7 +42067,7 @@
         <v>3.44</v>
       </c>
       <c r="DO88" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42501,7 +42501,7 @@
         <v>2.43</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF89" t="n">
         <v>2.5</v>
@@ -42531,7 +42531,7 @@
         <v>2.71</v>
       </c>
       <c r="DO89" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42934,7 +42934,7 @@
         <v>65</v>
       </c>
       <c r="DD90" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="DE90" t="n">
         <v>0.14</v>
@@ -42967,7 +42967,7 @@
         <v>3.16</v>
       </c>
       <c r="DO90" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -43405,7 +43405,7 @@
         <v>1.5</v>
       </c>
       <c r="DE91" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF91" t="n">
         <v>1.2</v>
@@ -43435,7 +43435,7 @@
         <v>2.54</v>
       </c>
       <c r="DO91" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44363,7 +44363,7 @@
         <v>2.24</v>
       </c>
       <c r="DO93" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -44818,7 +44818,7 @@
         <v>65</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE94" t="n">
         <v>1.5</v>
@@ -44851,7 +44851,7 @@
         <v>2.18</v>
       </c>
       <c r="DO94" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -45331,7 +45331,7 @@
         <v>2.91</v>
       </c>
       <c r="DO95" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45439,43 +45439,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
         <v>46021.72916666666</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J96" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="L96" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
@@ -45484,246 +45484,246 @@
         <v>4</v>
       </c>
       <c r="R96" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S96" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T96" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="U96" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="V96" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="W96" t="n">
         <v>7</v>
       </c>
       <c r="X96" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y96" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="Z96" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="AA96" t="inlineStr"/>
       <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF96" t="n">
+        <v>9512</v>
+      </c>
+      <c r="BG96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ96" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL96" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM96" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN96" t="n">
         <v>6</v>
       </c>
-      <c r="AD96" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE96" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AF96" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AG96" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH96" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI96" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AJ96" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AK96" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AL96" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM96" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AN96" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AO96" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AP96" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AQ96" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR96" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AS96" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT96" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AU96" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW96" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB96" t="n">
-        <v>5083</v>
-      </c>
-      <c r="BC96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD96" t="n">
-        <v>100</v>
-      </c>
-      <c r="BE96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF96" t="n">
-        <v>1214</v>
-      </c>
-      <c r="BG96" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI96" t="n">
+      <c r="BO96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS96" t="n">
         <v>3</v>
       </c>
-      <c r="BJ96" t="n">
-        <v>3</v>
-      </c>
-      <c r="BK96" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL96" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM96" t="n">
+      <c r="BT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV96" t="n">
+        <v>12</v>
+      </c>
+      <c r="BW96" t="n">
+        <v>124</v>
+      </c>
+      <c r="BX96" t="n">
+        <v>59</v>
+      </c>
+      <c r="BY96" t="n">
+        <v>125</v>
+      </c>
+      <c r="BZ96" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CA96" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CB96" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="CC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP96" t="n">
+        <v>2</v>
+      </c>
+      <c r="CQ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR96" t="n">
+        <v>8</v>
+      </c>
+      <c r="CS96" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU96" t="n">
         <v>6</v>
-      </c>
-      <c r="BN96" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ96" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR96" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS96" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT96" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV96" t="n">
-        <v>42</v>
-      </c>
-      <c r="BW96" t="n">
-        <v>31</v>
-      </c>
-      <c r="BX96" t="n">
-        <v>120</v>
-      </c>
-      <c r="BY96" t="n">
-        <v>85</v>
-      </c>
-      <c r="BZ96" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CA96" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="CB96" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="CC96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP96" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR96" t="n">
-        <v>37</v>
-      </c>
-      <c r="CS96" t="n">
-        <v>18</v>
-      </c>
-      <c r="CT96" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU96" t="n">
-        <v>10</v>
       </c>
       <c r="CV96" t="n">
         <v>7</v>
@@ -45732,70 +45732,70 @@
         <v>1</v>
       </c>
       <c r="CX96" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="CY96" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ96" t="n">
+        <v>65</v>
+      </c>
+      <c r="DA96" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB96" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC96" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD96" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE96" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DF96" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DG96" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH96" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI96" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ96" t="n">
+        <v>35</v>
+      </c>
+      <c r="DK96" t="n">
         <v>10</v>
       </c>
-      <c r="CZ96" t="n">
-        <v>60</v>
-      </c>
-      <c r="DA96" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB96" t="n">
-        <v>80</v>
-      </c>
-      <c r="DC96" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD96" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="DE96" t="n">
+      <c r="DL96" t="n">
         <v>0.86</v>
       </c>
-      <c r="DF96" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DG96" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="DH96" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DI96" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="DJ96" t="n">
-        <v>40</v>
-      </c>
-      <c r="DK96" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL96" t="n">
-        <v>1.24</v>
-      </c>
       <c r="DM96" t="n">
-        <v>0.91</v>
+        <v>2.26</v>
       </c>
       <c r="DN96" t="n">
-        <v>2.15</v>
+        <v>3.12</v>
       </c>
       <c r="DO96" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
       </c>
       <c r="DQ96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT96" t="b">
         <v>0</v>
@@ -45804,86 +45804,74 @@
         <v>0</v>
       </c>
       <c r="DV96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW96" t="n">
-        <v>23.3</v>
+        <v>19.88</v>
       </c>
       <c r="DX96" t="n">
-        <v>6.98</v>
+        <v>9.33</v>
       </c>
       <c r="DY96" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="DZ96" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA96" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EB96" t="inlineStr">
         <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="EC96" t="inlineStr">
-        <is>
-          <t>2.27</t>
-        </is>
-      </c>
-      <c r="ED96" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EC96" t="inlineStr"/>
+      <c r="ED96" t="inlineStr"/>
       <c r="EE96" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EF96" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="EG96" t="inlineStr">
         <is>
-          <t>3.13</t>
-        </is>
-      </c>
-      <c r="EH96" t="inlineStr">
-        <is>
-          <t>4.88</t>
-        </is>
-      </c>
-      <c r="EI96" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="EJ96" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
+          <t>7.66</t>
+        </is>
+      </c>
+      <c r="EH96" t="inlineStr"/>
+      <c r="EI96" t="inlineStr"/>
+      <c r="EJ96" t="inlineStr"/>
       <c r="EK96" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EL96" t="inlineStr">
         <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EM96" t="inlineStr"/>
-      <c r="EN96" t="inlineStr"/>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EM96" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EN96" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
       <c r="EO96" t="inlineStr"/>
       <c r="EP96" t="inlineStr"/>
     </row>
@@ -45903,43 +45891,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
         <v>46021.72916666666</v>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K97" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="L97" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
@@ -45948,189 +45936,189 @@
         <v>4</v>
       </c>
       <c r="R97" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S97" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T97" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="U97" t="n">
+        <v>12</v>
+      </c>
+      <c r="V97" t="n">
         <v>6</v>
-      </c>
-      <c r="V97" t="n">
-        <v>26</v>
       </c>
       <c r="W97" t="n">
         <v>7</v>
       </c>
       <c r="X97" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y97" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="Z97" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="AA97" t="inlineStr"/>
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AD97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE97" t="n">
-        <v>8</v>
+        <v>2.62</v>
       </c>
       <c r="AF97" t="n">
-        <v>6.4</v>
+        <v>2.9</v>
       </c>
       <c r="AG97" t="n">
-        <v>1.14</v>
+        <v>2.7</v>
       </c>
       <c r="AH97" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="AI97" t="n">
-        <v>1.3</v>
+        <v>2.33</v>
       </c>
       <c r="AJ97" t="n">
-        <v>1.85</v>
+        <v>4.35</v>
       </c>
       <c r="AK97" t="n">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AL97" t="n">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="AM97" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AN97" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AO97" t="n">
-        <v>2.65</v>
+        <v>2.24</v>
       </c>
       <c r="AP97" t="n">
-        <v>2.08</v>
+        <v>1.72</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.94</v>
+        <v>3.05</v>
       </c>
       <c r="AS97" t="n">
-        <v>4.2</v>
+        <v>2.33</v>
       </c>
       <c r="AT97" t="n">
-        <v>1.76</v>
+        <v>1.26</v>
       </c>
       <c r="AU97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB97" t="n">
+        <v>5083</v>
+      </c>
+      <c r="BC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF97" t="n">
+        <v>1214</v>
+      </c>
+      <c r="BG97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI97" t="n">
         <v>3</v>
       </c>
-      <c r="BA97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB97" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD97" t="n">
-        <v>43</v>
-      </c>
-      <c r="BE97" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF97" t="n">
-        <v>9512</v>
-      </c>
-      <c r="BG97" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI97" t="n">
-        <v>0</v>
-      </c>
       <c r="BJ97" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="BK97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BL97" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BM97" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BN97" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BO97" t="n">
         <v>1</v>
       </c>
       <c r="BP97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BR97" t="n">
         <v>0</v>
       </c>
       <c r="BS97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT97" t="n">
         <v>3</v>
       </c>
-      <c r="BT97" t="n">
-        <v>0</v>
-      </c>
       <c r="BU97" t="n">
         <v>1</v>
       </c>
       <c r="BV97" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="BW97" t="n">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="BX97" t="n">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="BY97" t="n">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="BZ97" t="n">
-        <v>0.75</v>
+        <v>1.35</v>
       </c>
       <c r="CA97" t="n">
-        <v>3.01</v>
+        <v>0.82</v>
       </c>
       <c r="CB97" t="n">
-        <v>3.76</v>
+        <v>2.18</v>
       </c>
       <c r="CC97" t="n">
         <v>0</v>
@@ -46160,7 +46148,7 @@
         <v>0</v>
       </c>
       <c r="CL97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM97" t="n">
         <v>0</v>
@@ -46172,22 +46160,22 @@
         <v>0</v>
       </c>
       <c r="CP97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CQ97" t="n">
         <v>1</v>
       </c>
       <c r="CR97" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="CS97" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CT97" t="n">
         <v>1</v>
       </c>
       <c r="CU97" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="CV97" t="n">
         <v>7</v>
@@ -46196,70 +46184,70 @@
         <v>1</v>
       </c>
       <c r="CX97" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="CY97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="CZ97" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="DA97" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="DB97" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="DC97" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.5</v>
+        <v>0.88</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF97" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="DG97" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="DH97" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="DI97" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="DJ97" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="DK97" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="DL97" t="n">
-        <v>0.86</v>
+        <v>1.24</v>
       </c>
       <c r="DM97" t="n">
-        <v>2.26</v>
+        <v>0.91</v>
       </c>
       <c r="DN97" t="n">
-        <v>3.12</v>
+        <v>2.15</v>
       </c>
       <c r="DO97" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
       </c>
       <c r="DQ97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT97" t="b">
         <v>0</v>
@@ -46268,74 +46256,86 @@
         <v>0</v>
       </c>
       <c r="DV97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW97" t="n">
-        <v>19.88</v>
+        <v>23.3</v>
       </c>
       <c r="DX97" t="n">
-        <v>9.33</v>
+        <v>6.98</v>
       </c>
       <c r="DY97" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="DZ97" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="EA97" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EB97" t="inlineStr">
         <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EC97" t="inlineStr"/>
-      <c r="ED97" t="inlineStr"/>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EC97" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="ED97" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
       <c r="EE97" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EF97" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="EG97" t="inlineStr">
         <is>
-          <t>7.66</t>
-        </is>
-      </c>
-      <c r="EH97" t="inlineStr"/>
-      <c r="EI97" t="inlineStr"/>
-      <c r="EJ97" t="inlineStr"/>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EH97" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="EI97" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EJ97" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
       <c r="EK97" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EL97" t="inlineStr">
         <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EM97" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EN97" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EM97" t="inlineStr"/>
+      <c r="EN97" t="inlineStr"/>
       <c r="EO97" t="inlineStr"/>
       <c r="EP97" t="inlineStr"/>
     </row>
@@ -46666,7 +46666,7 @@
         <v>68</v>
       </c>
       <c r="DD98" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DE98" t="n">
         <v>2.14</v>
@@ -46699,7 +46699,7 @@
         <v>3.06</v>
       </c>
       <c r="DO98" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46807,76 +46807,76 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
         <v>46022.72916666666</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" t="n">
         <v>3</v>
       </c>
       <c r="I99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J99" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K99" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L99" t="n">
         <v>12</v>
       </c>
       <c r="M99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N99" t="n">
         <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R99" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S99" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T99" t="n">
+        <v>5</v>
+      </c>
+      <c r="U99" t="n">
         <v>14</v>
       </c>
-      <c r="U99" t="n">
+      <c r="V99" t="n">
         <v>11</v>
       </c>
-      <c r="V99" t="n">
-        <v>24</v>
-      </c>
       <c r="W99" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y99" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z99" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr"/>
@@ -46887,88 +46887,88 @@
         <v>1</v>
       </c>
       <c r="AE99" t="n">
-        <v>10</v>
+        <v>5.59</v>
       </c>
       <c r="AF99" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="AG99" t="n">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI99" t="n">
-        <v>1.31</v>
+        <v>1.72</v>
       </c>
       <c r="AJ99" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AK99" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AL99" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AM99" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN99" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO99" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AS99" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AT99" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AU99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ99" t="n">
         <v>2</v>
       </c>
       <c r="BA99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB99" t="n">
-        <v>5066</v>
+        <v>5068</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BE99" t="n">
         <v>0</v>
       </c>
       <c r="BF99" t="n">
-        <v>9253</v>
+        <v>2556</v>
       </c>
       <c r="BG99" t="n">
         <v>2</v>
@@ -46977,25 +46977,25 @@
         <v>1</v>
       </c>
       <c r="BI99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BL99" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BM99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BN99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BO99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP99" t="n">
         <v>0</v>
@@ -47007,7 +47007,7 @@
         <v>1</v>
       </c>
       <c r="BS99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT99" t="n">
         <v>3</v>
@@ -47016,37 +47016,37 @@
         <v>1</v>
       </c>
       <c r="BV99" t="n">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="BW99" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="BX99" t="n">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="BY99" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="BZ99" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="CA99" t="n">
-        <v>2.7</v>
+        <v>1.56</v>
       </c>
       <c r="CB99" t="n">
-        <v>3.8</v>
+        <v>3.29</v>
       </c>
       <c r="CC99" t="n">
         <v>1</v>
       </c>
       <c r="CD99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE99" t="n">
         <v>1</v>
       </c>
       <c r="CF99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG99" t="n">
         <v>0</v>
@@ -47070,7 +47070,7 @@
         <v>0</v>
       </c>
       <c r="CN99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO99" t="n">
         <v>0</v>
@@ -47082,76 +47082,76 @@
         <v>1</v>
       </c>
       <c r="CR99" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="CS99" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CT99" t="n">
         <v>1</v>
       </c>
       <c r="CU99" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="CV99" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="CW99" t="n">
         <v>1</v>
       </c>
       <c r="CX99" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="CY99" t="n">
         <v>9</v>
       </c>
       <c r="CZ99" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="DA99" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="DB99" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="DC99" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="DD99" t="n">
-        <v>0.86</v>
+        <v>1.14</v>
       </c>
       <c r="DE99" t="n">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="DF99" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DG99" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="DH99" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="DI99" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="DJ99" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="DK99" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="DL99" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="DM99" t="n">
-        <v>1.88</v>
+        <v>1.41</v>
       </c>
       <c r="DN99" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="DO99" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -47166,7 +47166,7 @@
         <v>1</v>
       </c>
       <c r="DT99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU99" t="b">
         <v>0</v>
@@ -47175,14 +47175,14 @@
         <v>1</v>
       </c>
       <c r="DW99" t="n">
-        <v>15.88</v>
+        <v>13.4</v>
       </c>
       <c r="DX99" t="n">
-        <v>5.15</v>
+        <v>4.76</v>
       </c>
       <c r="DY99" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="DZ99" t="inlineStr">
@@ -47190,68 +47190,32 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA99" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EB99" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
+      <c r="EA99" t="inlineStr"/>
+      <c r="EB99" t="inlineStr"/>
       <c r="EC99" t="inlineStr"/>
       <c r="ED99" t="inlineStr"/>
       <c r="EE99" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EF99" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="EG99" t="inlineStr">
         <is>
-          <t>8.72</t>
-        </is>
-      </c>
-      <c r="EH99" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EI99" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EJ99" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="EK99" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EL99" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EM99" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EN99" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="EH99" t="inlineStr"/>
+      <c r="EI99" t="inlineStr"/>
+      <c r="EJ99" t="inlineStr"/>
+      <c r="EK99" t="inlineStr"/>
+      <c r="EL99" t="inlineStr"/>
+      <c r="EM99" t="inlineStr"/>
+      <c r="EN99" t="inlineStr"/>
       <c r="EO99" t="inlineStr"/>
       <c r="EP99" t="inlineStr"/>
     </row>
@@ -47271,76 +47235,76 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
         <v>46022.72916666666</v>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
         <v>3</v>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K100" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L100" t="n">
         <v>12</v>
       </c>
       <c r="M100" t="n">
+        <v>2</v>
+      </c>
+      <c r="N100" t="n">
+        <v>1</v>
+      </c>
+      <c r="O100" t="n">
+        <v>1</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
         <v>4</v>
       </c>
-      <c r="N100" t="n">
-        <v>1</v>
-      </c>
-      <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>6</v>
-      </c>
       <c r="R100" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T100" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="U100" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V100" t="n">
+        <v>24</v>
+      </c>
+      <c r="W100" t="n">
         <v>11</v>
       </c>
-      <c r="W100" t="n">
-        <v>9</v>
-      </c>
       <c r="X100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y100" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z100" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr"/>
@@ -47351,88 +47315,88 @@
         <v>1</v>
       </c>
       <c r="AE100" t="n">
-        <v>5.59</v>
+        <v>10</v>
       </c>
       <c r="AF100" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AU100" t="n">
         <v>4</v>
       </c>
-      <c r="AG100" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI100" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AJ100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK100" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL100" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU100" t="n">
-        <v>5</v>
-      </c>
       <c r="AV100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ100" t="n">
         <v>2</v>
       </c>
       <c r="BA100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB100" t="n">
-        <v>5068</v>
+        <v>5066</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
       </c>
       <c r="BF100" t="n">
-        <v>2556</v>
+        <v>9253</v>
       </c>
       <c r="BG100" t="n">
         <v>2</v>
@@ -47441,25 +47405,25 @@
         <v>1</v>
       </c>
       <c r="BI100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK100" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL100" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BM100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BO100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP100" t="n">
         <v>0</v>
@@ -47471,7 +47435,7 @@
         <v>1</v>
       </c>
       <c r="BS100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT100" t="n">
         <v>3</v>
@@ -47480,37 +47444,37 @@
         <v>1</v>
       </c>
       <c r="BV100" t="n">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="BW100" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="BX100" t="n">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="BY100" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="BZ100" t="n">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="CA100" t="n">
-        <v>1.56</v>
+        <v>2.7</v>
       </c>
       <c r="CB100" t="n">
-        <v>3.29</v>
+        <v>3.8</v>
       </c>
       <c r="CC100" t="n">
         <v>1</v>
       </c>
       <c r="CD100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE100" t="n">
         <v>1</v>
       </c>
       <c r="CF100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG100" t="n">
         <v>0</v>
@@ -47534,7 +47498,7 @@
         <v>0</v>
       </c>
       <c r="CN100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO100" t="n">
         <v>0</v>
@@ -47546,76 +47510,76 @@
         <v>1</v>
       </c>
       <c r="CR100" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="CS100" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CT100" t="n">
         <v>1</v>
       </c>
       <c r="CU100" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="CV100" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CW100" t="n">
         <v>1</v>
       </c>
       <c r="CX100" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="CY100" t="n">
         <v>9</v>
       </c>
       <c r="CZ100" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="DA100" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="DB100" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="DC100" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="DD100" t="n">
-        <v>1.14</v>
+        <v>0.75</v>
       </c>
       <c r="DE100" t="n">
-        <v>1.86</v>
+        <v>2.71</v>
       </c>
       <c r="DF100" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DG100" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="DH100" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="DI100" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="DJ100" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="DK100" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="DL100" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="DM100" t="n">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="DN100" t="n">
-        <v>3.04</v>
+        <v>3.24</v>
       </c>
       <c r="DO100" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47630,7 +47594,7 @@
         <v>1</v>
       </c>
       <c r="DT100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU100" t="b">
         <v>0</v>
@@ -47639,14 +47603,14 @@
         <v>1</v>
       </c>
       <c r="DW100" t="n">
-        <v>13.4</v>
+        <v>15.88</v>
       </c>
       <c r="DX100" t="n">
-        <v>4.76</v>
+        <v>5.15</v>
       </c>
       <c r="DY100" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="DZ100" t="inlineStr">
@@ -47654,32 +47618,68 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA100" t="inlineStr"/>
-      <c r="EB100" t="inlineStr"/>
+      <c r="EA100" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EB100" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
       <c r="EC100" t="inlineStr"/>
       <c r="ED100" t="inlineStr"/>
       <c r="EE100" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EF100" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="EG100" t="inlineStr">
         <is>
-          <t>5.07</t>
-        </is>
-      </c>
-      <c r="EH100" t="inlineStr"/>
-      <c r="EI100" t="inlineStr"/>
-      <c r="EJ100" t="inlineStr"/>
-      <c r="EK100" t="inlineStr"/>
-      <c r="EL100" t="inlineStr"/>
-      <c r="EM100" t="inlineStr"/>
-      <c r="EN100" t="inlineStr"/>
+          <t>8.72</t>
+        </is>
+      </c>
+      <c r="EH100" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EI100" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EJ100" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="EK100" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EL100" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EM100" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EN100" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
       <c r="EO100" t="inlineStr"/>
       <c r="EP100" t="inlineStr"/>
     </row>
@@ -48959,7 +48959,7 @@
         <v>3.97</v>
       </c>
       <c r="DO103" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -49365,7 +49365,7 @@
         <v>1.71</v>
       </c>
       <c r="DE104" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF104" t="n">
         <v>1.2</v>
@@ -49395,7 +49395,7 @@
         <v>2.58</v>
       </c>
       <c r="DO104" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -49859,7 +49859,7 @@
         <v>2.03</v>
       </c>
       <c r="DO105" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -50309,7 +50309,7 @@
         <v>1.5</v>
       </c>
       <c r="DE106" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF106" t="n">
         <v>1.5</v>
@@ -50339,7 +50339,7 @@
         <v>3.01</v>
       </c>
       <c r="DO106" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -50754,7 +50754,7 @@
         <v>65</v>
       </c>
       <c r="DD107" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE107" t="n">
         <v>1.86</v>
@@ -50787,7 +50787,7 @@
         <v>2.44</v>
       </c>
       <c r="DO107" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -51245,7 +51245,7 @@
         <v>0.57</v>
       </c>
       <c r="DE108" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DF108" t="n">
         <v>0.6</v>
@@ -51275,7 +51275,7 @@
         <v>3.29</v>
       </c>
       <c r="DO108" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -51739,7 +51739,7 @@
         <v>2.86</v>
       </c>
       <c r="DO109" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -52167,7 +52167,7 @@
         <v>3.4</v>
       </c>
       <c r="DO110" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -52287,359 +52287,359 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F111" s="2" t="n">
         <v>46030.72916666666</v>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H111" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I111" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J111" t="n">
+        <v>2</v>
+      </c>
+      <c r="K111" t="n">
         <v>4</v>
       </c>
-      <c r="K111" t="n">
-        <v>1</v>
-      </c>
       <c r="L111" t="n">
+        <v>6</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>2</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
         <v>5</v>
       </c>
-      <c r="M111" t="n">
-        <v>2</v>
-      </c>
-      <c r="N111" t="n">
-        <v>6</v>
-      </c>
-      <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>3</v>
-      </c>
       <c r="R111" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S111" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T111" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U111" t="n">
         <v>16</v>
       </c>
       <c r="V111" t="n">
+        <v>16</v>
+      </c>
+      <c r="W111" t="n">
+        <v>5</v>
+      </c>
+      <c r="X111" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>Al-Najma Club Stadium</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>, Unaizah</t>
+        </is>
+      </c>
+      <c r="AC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU111" t="n">
         <v>7</v>
       </c>
-      <c r="W111" t="n">
-        <v>9</v>
-      </c>
-      <c r="X111" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y111" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z111" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>King Saud University Stadium</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
-        </is>
-      </c>
-      <c r="AC111" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD111" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE111" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF111" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AG111" t="n">
+      <c r="AV111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ111" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA111" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB111" t="n">
+        <v>5065</v>
+      </c>
+      <c r="BC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD111" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF111" t="n">
+        <v>231</v>
+      </c>
+      <c r="BG111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN111" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV111" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW111" t="n">
+        <v>52</v>
+      </c>
+      <c r="BX111" t="n">
+        <v>86</v>
+      </c>
+      <c r="BY111" t="n">
+        <v>113</v>
+      </c>
+      <c r="BZ111" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CA111" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CB111" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="CC111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR111" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS111" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU111" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV111" t="n">
         <v>5</v>
       </c>
-      <c r="AH111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI111" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK111" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AL111" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AM111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU111" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX111" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY111" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ111" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB111" t="n">
-        <v>5068</v>
-      </c>
-      <c r="BC111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD111" t="n">
-        <v>67</v>
-      </c>
-      <c r="BE111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF111" t="n">
-        <v>25827</v>
-      </c>
-      <c r="BG111" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH111" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ111" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK111" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM111" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN111" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP111" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ111" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR111" t="n">
+      <c r="CW111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX111" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY111" t="n">
         <v>5</v>
       </c>
-      <c r="BS111" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT111" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU111" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV111" t="n">
-        <v>57</v>
-      </c>
-      <c r="BW111" t="n">
-        <v>33</v>
-      </c>
-      <c r="BX111" t="n">
-        <v>121</v>
-      </c>
-      <c r="BY111" t="n">
-        <v>83</v>
-      </c>
-      <c r="BZ111" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CA111" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB111" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="CC111" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE111" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI111" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ111" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ111" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR111" t="n">
-        <v>24</v>
-      </c>
-      <c r="CS111" t="n">
-        <v>10</v>
-      </c>
-      <c r="CT111" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU111" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV111" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW111" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX111" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY111" t="n">
-        <v>12</v>
-      </c>
       <c r="CZ111" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="DA111" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="DB111" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="DC111" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="DD111" t="n">
-        <v>2.57</v>
+        <v>0.29</v>
       </c>
       <c r="DE111" t="n">
         <v>1.86</v>
       </c>
       <c r="DF111" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="DG111" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="DH111" t="n">
-        <v>2.58</v>
+        <v>0.17</v>
       </c>
       <c r="DI111" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="DJ111" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="DK111" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="DL111" t="n">
-        <v>2.41</v>
+        <v>0.96</v>
       </c>
       <c r="DM111" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="DN111" t="n">
-        <v>3.84</v>
+        <v>2.33</v>
       </c>
       <c r="DO111" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52651,57 +52651,93 @@
         <v>1</v>
       </c>
       <c r="DS111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV111" t="b">
         <v>1</v>
       </c>
       <c r="DW111" t="n">
-        <v>18.31</v>
+        <v>18.24</v>
       </c>
       <c r="DX111" t="n">
-        <v>3.56</v>
+        <v>3.79</v>
       </c>
       <c r="DY111" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="DZ111" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="EA111" t="inlineStr"/>
-      <c r="EB111" t="inlineStr"/>
-      <c r="EC111" t="inlineStr"/>
-      <c r="ED111" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA111" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="EB111" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EC111" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="ED111" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
       <c r="EE111" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EF111" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="EG111" t="inlineStr">
         <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EH111" t="inlineStr"/>
-      <c r="EI111" t="inlineStr"/>
-      <c r="EJ111" t="inlineStr"/>
-      <c r="EK111" t="inlineStr"/>
-      <c r="EL111" t="inlineStr"/>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="EH111" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="EI111" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EJ111" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EK111" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EL111" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
       <c r="EM111" t="inlineStr"/>
       <c r="EN111" t="inlineStr"/>
       <c r="EO111" t="inlineStr"/>
@@ -52723,41 +52759,41 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
         <v>46030.72916666666</v>
       </c>
       <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="n">
+        <v>2</v>
+      </c>
+      <c r="I112" t="n">
         <v>3</v>
       </c>
-      <c r="H112" t="n">
+      <c r="J112" t="n">
         <v>4</v>
       </c>
-      <c r="I112" t="n">
-        <v>7</v>
-      </c>
-      <c r="J112" t="n">
-        <v>2</v>
-      </c>
       <c r="K112" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L112" t="n">
+        <v>5</v>
+      </c>
+      <c r="M112" t="n">
+        <v>2</v>
+      </c>
+      <c r="N112" t="n">
         <v>6</v>
       </c>
-      <c r="M112" t="n">
-        <v>0</v>
-      </c>
-      <c r="N112" t="n">
-        <v>2</v>
-      </c>
       <c r="O112" t="n">
         <v>0</v>
       </c>
@@ -52765,314 +52801,314 @@
         <v>0</v>
       </c>
       <c r="Q112" t="n">
+        <v>3</v>
+      </c>
+      <c r="R112" t="n">
         <v>5</v>
       </c>
-      <c r="R112" t="n">
-        <v>8</v>
-      </c>
       <c r="S112" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T112" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U112" t="n">
         <v>16</v>
       </c>
       <c r="V112" t="n">
+        <v>7</v>
+      </c>
+      <c r="W112" t="n">
+        <v>9</v>
+      </c>
+      <c r="X112" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>King Saud University Stadium</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
+        </is>
+      </c>
+      <c r="AC112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB112" t="n">
+        <v>5068</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF112" t="n">
+        <v>25827</v>
+      </c>
+      <c r="BG112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ112" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR112" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT112" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV112" t="n">
+        <v>57</v>
+      </c>
+      <c r="BW112" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX112" t="n">
+        <v>121</v>
+      </c>
+      <c r="BY112" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ112" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CA112" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB112" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CC112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR112" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS112" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU112" t="n">
         <v>16</v>
       </c>
-      <c r="W112" t="n">
-        <v>5</v>
-      </c>
-      <c r="X112" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y112" t="n">
-        <v>52</v>
-      </c>
-      <c r="Z112" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>Al-Najma Club Stadium</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>, Unaizah</t>
-        </is>
-      </c>
-      <c r="AC112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD112" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE112" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AF112" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AG112" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH112" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI112" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AJ112" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AK112" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL112" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM112" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AN112" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AO112" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AP112" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AQ112" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR112" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AS112" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AT112" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AU112" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW112" t="n">
+      <c r="CV112" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX112" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY112" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ112" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA112" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB112" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC112" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD112" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DE112" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF112" t="n">
         <v>3</v>
       </c>
-      <c r="AX112" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ112" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA112" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB112" t="n">
-        <v>5065</v>
-      </c>
-      <c r="BC112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD112" t="n">
-        <v>70</v>
-      </c>
-      <c r="BE112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF112" t="n">
-        <v>231</v>
-      </c>
-      <c r="BG112" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH112" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ112" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK112" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL112" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM112" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN112" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP112" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR112" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS112" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT112" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU112" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV112" t="n">
-        <v>35</v>
-      </c>
-      <c r="BW112" t="n">
-        <v>52</v>
-      </c>
-      <c r="BX112" t="n">
-        <v>86</v>
-      </c>
-      <c r="BY112" t="n">
-        <v>113</v>
-      </c>
-      <c r="BZ112" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CA112" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CB112" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="CC112" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE112" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI112" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ112" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ112" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR112" t="n">
-        <v>11</v>
-      </c>
-      <c r="CS112" t="n">
-        <v>13</v>
-      </c>
-      <c r="CT112" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU112" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV112" t="n">
-        <v>5</v>
-      </c>
-      <c r="CW112" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX112" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY112" t="n">
-        <v>5</v>
-      </c>
-      <c r="CZ112" t="n">
-        <v>60</v>
-      </c>
-      <c r="DA112" t="n">
-        <v>80</v>
-      </c>
-      <c r="DB112" t="n">
-        <v>20</v>
-      </c>
-      <c r="DC112" t="n">
-        <v>60</v>
-      </c>
-      <c r="DD112" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="DE112" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DF112" t="n">
-        <v>0.2</v>
-      </c>
       <c r="DG112" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DH112" t="n">
-        <v>0.17</v>
+        <v>2.58</v>
       </c>
       <c r="DI112" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="DJ112" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="DK112" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="DL112" t="n">
-        <v>0.96</v>
+        <v>2.41</v>
       </c>
       <c r="DM112" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="DN112" t="n">
-        <v>2.33</v>
+        <v>3.84</v>
       </c>
       <c r="DO112" t="n">
         <v>15</v>
@@ -53087,93 +53123,57 @@
         <v>1</v>
       </c>
       <c r="DS112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV112" t="b">
         <v>1</v>
       </c>
       <c r="DW112" t="n">
-        <v>18.24</v>
+        <v>18.31</v>
       </c>
       <c r="DX112" t="n">
-        <v>3.79</v>
+        <v>3.56</v>
       </c>
       <c r="DY112" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="DZ112" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="EA112" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="EB112" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EC112" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="ED112" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="EA112" t="inlineStr"/>
+      <c r="EB112" t="inlineStr"/>
+      <c r="EC112" t="inlineStr"/>
+      <c r="ED112" t="inlineStr"/>
       <c r="EE112" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="EF112" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="EG112" t="inlineStr">
         <is>
-          <t>4.39</t>
-        </is>
-      </c>
-      <c r="EH112" t="inlineStr">
-        <is>
-          <t>3.64</t>
-        </is>
-      </c>
-      <c r="EI112" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="EJ112" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EK112" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="EL112" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EH112" t="inlineStr"/>
+      <c r="EI112" t="inlineStr"/>
+      <c r="EJ112" t="inlineStr"/>
+      <c r="EK112" t="inlineStr"/>
+      <c r="EL112" t="inlineStr"/>
       <c r="EM112" t="inlineStr"/>
       <c r="EN112" t="inlineStr"/>
       <c r="EO112" t="inlineStr"/>
@@ -53509,7 +53509,7 @@
         <v>1.86</v>
       </c>
       <c r="DE113" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DF113" t="n">
         <v>1.4</v>
@@ -53539,7 +53539,7 @@
         <v>2.25</v>
       </c>
       <c r="DO113" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53957,7 +53957,7 @@
         <v>2.29</v>
       </c>
       <c r="DE114" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DF114" t="n">
         <v>2.17</v>
@@ -53987,7 +53987,7 @@
         <v>2.21</v>
       </c>
       <c r="DO114" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -54434,7 +54434,7 @@
         <v>90</v>
       </c>
       <c r="DD115" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DE115" t="n">
         <v>2.14</v>
@@ -54467,7 +54467,7 @@
         <v>2.96</v>
       </c>
       <c r="DO115" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -54878,7 +54878,7 @@
         <v>67</v>
       </c>
       <c r="DD116" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DE116" t="n">
         <v>1.13</v>
@@ -54911,7 +54911,7 @@
         <v>2.69</v>
       </c>
       <c r="DO116" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -55338,7 +55338,7 @@
         <v>83</v>
       </c>
       <c r="DD117" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DE117" t="n">
         <v>0.88</v>
@@ -55371,7 +55371,7 @@
         <v>2.46</v>
       </c>
       <c r="DO117" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -55821,7 +55821,7 @@
         <v>0.88</v>
       </c>
       <c r="DE118" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DF118" t="n">
         <v>0.67</v>
@@ -55851,7 +55851,7 @@
         <v>3.01</v>
       </c>
       <c r="DO118" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -56298,7 +56298,7 @@
         <v>49</v>
       </c>
       <c r="DD119" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DE119" t="n">
         <v>0.13</v>
@@ -56331,7 +56331,7 @@
         <v>2.19</v>
       </c>
       <c r="DO119" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -56811,7 +56811,7 @@
         <v>4.5</v>
       </c>
       <c r="DO120" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -57731,7 +57731,7 @@
         <v>2.24</v>
       </c>
       <c r="DO122" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -57851,164 +57851,164 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F123" s="2" t="n">
         <v>46035.72916666666</v>
       </c>
       <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" t="n">
+        <v>2</v>
+      </c>
+      <c r="J123" t="n">
+        <v>1</v>
+      </c>
+      <c r="K123" t="n">
+        <v>12</v>
+      </c>
+      <c r="L123" t="n">
+        <v>13</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
         <v>3</v>
       </c>
-      <c r="H123" t="n">
-        <v>1</v>
-      </c>
-      <c r="I123" t="n">
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q123" t="n">
         <v>4</v>
       </c>
-      <c r="J123" t="n">
-        <v>7</v>
-      </c>
-      <c r="K123" t="n">
-        <v>9</v>
-      </c>
-      <c r="L123" t="n">
-        <v>16</v>
-      </c>
-      <c r="M123" t="n">
+      <c r="R123" t="n">
         <v>3</v>
       </c>
-      <c r="N123" t="n">
-        <v>2</v>
-      </c>
-      <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>5</v>
-      </c>
-      <c r="R123" t="n">
-        <v>9</v>
-      </c>
       <c r="S123" t="n">
+        <v>4</v>
+      </c>
+      <c r="T123" t="n">
+        <v>14</v>
+      </c>
+      <c r="U123" t="n">
+        <v>8</v>
+      </c>
+      <c r="V123" t="n">
+        <v>17</v>
+      </c>
+      <c r="W123" t="n">
         <v>6</v>
       </c>
-      <c r="T123" t="n">
-        <v>9</v>
-      </c>
-      <c r="U123" t="n">
-        <v>11</v>
-      </c>
-      <c r="V123" t="n">
-        <v>18</v>
-      </c>
-      <c r="W123" t="n">
-        <v>16</v>
-      </c>
       <c r="X123" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Y123" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="Z123" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>Prince Abdullah bin Jalawi Sports City Stadium</t>
+          <t>Dhamak Club Stadium</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>, Al-Hasa</t>
+          <t>, Khamis Mushait</t>
         </is>
       </c>
       <c r="AC123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE123" t="n">
-        <v>1.76</v>
+        <v>9.75</v>
       </c>
       <c r="AF123" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="AG123" t="n">
-        <v>3.85</v>
+        <v>1.26</v>
       </c>
       <c r="AH123" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AI123" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AT123" t="n">
         <v>1.64</v>
       </c>
-      <c r="AJ123" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AK123" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL123" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM123" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN123" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO123" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AP123" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AQ123" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR123" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AS123" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AT123" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AU123" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV123" t="n">
         <v>1</v>
       </c>
       <c r="AW123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB123" t="n">
-        <v>5064</v>
+        <v>-1</v>
       </c>
       <c r="BC123" t="n">
         <v>0</v>
@@ -58020,73 +58020,73 @@
         <v>0</v>
       </c>
       <c r="BF123" t="n">
-        <v>9104</v>
+        <v>9065</v>
       </c>
       <c r="BG123" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH123" t="n">
         <v>1</v>
       </c>
       <c r="BI123" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BJ123" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BK123" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL123" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BM123" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BN123" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BO123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR123" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BS123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU123" t="n">
         <v>1</v>
       </c>
       <c r="BV123" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="BW123" t="n">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="BX123" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="BY123" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="BZ123" t="n">
-        <v>1.27</v>
+        <v>0.9</v>
       </c>
       <c r="CA123" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="CB123" t="n">
-        <v>3.34</v>
+        <v>2.81</v>
       </c>
       <c r="CC123" t="n">
         <v>0</v>
@@ -58119,10 +58119,10 @@
         <v>0</v>
       </c>
       <c r="CM123" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN123" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO123" t="n">
         <v>0</v>
@@ -58134,76 +58134,76 @@
         <v>1</v>
       </c>
       <c r="CR123" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="CS123" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU123" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV123" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX123" t="n">
         <v>19</v>
       </c>
-      <c r="CT123" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU123" t="n">
-        <v>21</v>
-      </c>
-      <c r="CV123" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW123" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX123" t="n">
-        <v>11</v>
-      </c>
       <c r="CY123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CZ123" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA123" t="n">
+        <v>83</v>
+      </c>
+      <c r="DB123" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC123" t="n">
         <v>67</v>
       </c>
-      <c r="DA123" t="n">
-        <v>92</v>
-      </c>
-      <c r="DB123" t="n">
-        <v>67</v>
-      </c>
-      <c r="DC123" t="n">
-        <v>83</v>
-      </c>
       <c r="DD123" t="n">
-        <v>1.71</v>
+        <v>0.57</v>
       </c>
       <c r="DE123" t="n">
-        <v>0.14</v>
+        <v>2.14</v>
       </c>
       <c r="DF123" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="DG123" t="n">
-        <v>0.17</v>
+        <v>2.33</v>
       </c>
       <c r="DH123" t="n">
-        <v>1.31</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DI123" t="n">
-        <v>0.6899999999999999</v>
+        <v>2</v>
       </c>
       <c r="DJ123" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="DK123" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="DL123" t="n">
-        <v>1.55</v>
+        <v>1.15</v>
       </c>
       <c r="DM123" t="n">
-        <v>1.1</v>
+        <v>1.84</v>
       </c>
       <c r="DN123" t="n">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="DO123" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -58212,10 +58212,10 @@
         <v>1</v>
       </c>
       <c r="DR123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT123" t="b">
         <v>0</v>
@@ -58227,93 +58227,93 @@
         <v>1</v>
       </c>
       <c r="DW123" t="n">
-        <v>20.19</v>
+        <v>20.33</v>
       </c>
       <c r="DX123" t="n">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="DY123" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="DZ123" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EA123" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EB123" t="inlineStr">
         <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="EC123" t="inlineStr"/>
-      <c r="ED123" t="inlineStr"/>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EC123" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="ED123" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
       <c r="EE123" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EF123" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>7.30</t>
         </is>
       </c>
       <c r="EG123" t="inlineStr">
         <is>
+          <t>12.95</t>
+        </is>
+      </c>
+      <c r="EH123" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EI123" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EJ123" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EK123" t="inlineStr">
+        <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="EH123" t="inlineStr">
-        <is>
-          <t>2.87</t>
-        </is>
-      </c>
-      <c r="EI123" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EJ123" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="EK123" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
       <c r="EL123" t="inlineStr">
         <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EM123" t="inlineStr">
+        <is>
           <t>2.17</t>
         </is>
       </c>
-      <c r="EM123" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
       <c r="EN123" t="inlineStr">
         <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EO123" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EP123" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
-      </c>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EO123" t="inlineStr"/>
+      <c r="EP123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -58331,164 +58331,164 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F124" s="2" t="n">
         <v>46035.72916666666</v>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H124" t="n">
         <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K124" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L124" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N124" t="n">
+        <v>2</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>5</v>
+      </c>
+      <c r="R124" t="n">
+        <v>9</v>
+      </c>
+      <c r="S124" t="n">
+        <v>6</v>
+      </c>
+      <c r="T124" t="n">
+        <v>9</v>
+      </c>
+      <c r="U124" t="n">
+        <v>11</v>
+      </c>
+      <c r="V124" t="n">
+        <v>18</v>
+      </c>
+      <c r="W124" t="n">
+        <v>16</v>
+      </c>
+      <c r="X124" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>Prince Abdullah bin Jalawi Sports City Stadium</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>, Al-Hasa</t>
+        </is>
+      </c>
+      <c r="AC124" t="n">
         <v>3</v>
       </c>
-      <c r="O124" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q124" t="n">
+      <c r="AD124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AU124" t="n">
         <v>4</v>
       </c>
-      <c r="R124" t="n">
+      <c r="AV124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ124" t="n">
         <v>3</v>
       </c>
-      <c r="S124" t="n">
-        <v>4</v>
-      </c>
-      <c r="T124" t="n">
-        <v>14</v>
-      </c>
-      <c r="U124" t="n">
-        <v>8</v>
-      </c>
-      <c r="V124" t="n">
-        <v>17</v>
-      </c>
-      <c r="W124" t="n">
-        <v>6</v>
-      </c>
-      <c r="X124" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y124" t="n">
-        <v>33</v>
-      </c>
-      <c r="Z124" t="n">
-        <v>67</v>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>Dhamak Club Stadium</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>, Khamis Mushait</t>
-        </is>
-      </c>
-      <c r="AC124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD124" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE124" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="AF124" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG124" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH124" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI124" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AJ124" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AK124" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL124" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM124" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AN124" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AO124" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AP124" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AQ124" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AR124" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AS124" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AT124" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AU124" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ124" t="n">
-        <v>0</v>
-      </c>
       <c r="BA124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB124" t="n">
-        <v>-1</v>
+        <v>5064</v>
       </c>
       <c r="BC124" t="n">
         <v>0</v>
@@ -58500,191 +58500,191 @@
         <v>0</v>
       </c>
       <c r="BF124" t="n">
-        <v>9065</v>
+        <v>9104</v>
       </c>
       <c r="BG124" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH124" t="n">
         <v>1</v>
       </c>
       <c r="BI124" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BJ124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT124" t="n">
         <v>3</v>
       </c>
-      <c r="BK124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL124" t="n">
-        <v>8</v>
-      </c>
-      <c r="BM124" t="n">
+      <c r="BU124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>62</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>124</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>9</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU124" t="n">
+        <v>21</v>
+      </c>
+      <c r="CV124" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX124" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY124" t="n">
         <v>3</v>
       </c>
-      <c r="BN124" t="n">
+      <c r="CZ124" t="n">
+        <v>67</v>
+      </c>
+      <c r="DA124" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB124" t="n">
+        <v>67</v>
+      </c>
+      <c r="DC124" t="n">
+        <v>83</v>
+      </c>
+      <c r="DD124" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DE124" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DF124" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG124" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DH124" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DI124" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="DJ124" t="n">
+        <v>33</v>
+      </c>
+      <c r="DK124" t="n">
         <v>9</v>
       </c>
-      <c r="BO124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR124" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT124" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV124" t="n">
+      <c r="DL124" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DM124" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DN124" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="DO124" t="n">
         <v>15</v>
       </c>
-      <c r="BW124" t="n">
-        <v>86</v>
-      </c>
-      <c r="BX124" t="n">
-        <v>75</v>
-      </c>
-      <c r="BY124" t="n">
-        <v>132</v>
-      </c>
-      <c r="BZ124" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="CA124" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CB124" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="CC124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP124" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR124" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS124" t="n">
-        <v>30</v>
-      </c>
-      <c r="CT124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU124" t="n">
-        <v>12</v>
-      </c>
-      <c r="CV124" t="n">
-        <v>6</v>
-      </c>
-      <c r="CW124" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX124" t="n">
-        <v>19</v>
-      </c>
-      <c r="CY124" t="n">
-        <v>4</v>
-      </c>
-      <c r="CZ124" t="n">
-        <v>50</v>
-      </c>
-      <c r="DA124" t="n">
-        <v>83</v>
-      </c>
-      <c r="DB124" t="n">
-        <v>42</v>
-      </c>
-      <c r="DC124" t="n">
-        <v>67</v>
-      </c>
-      <c r="DD124" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="DE124" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DF124" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DG124" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="DH124" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="DI124" t="n">
-        <v>2</v>
-      </c>
-      <c r="DJ124" t="n">
-        <v>50</v>
-      </c>
-      <c r="DK124" t="n">
-        <v>17</v>
-      </c>
-      <c r="DL124" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="DM124" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="DN124" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="DO124" t="n">
-        <v>14</v>
-      </c>
       <c r="DP124" t="b">
         <v>1</v>
       </c>
@@ -58692,10 +58692,10 @@
         <v>1</v>
       </c>
       <c r="DR124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT124" t="b">
         <v>0</v>
@@ -58707,93 +58707,93 @@
         <v>1</v>
       </c>
       <c r="DW124" t="n">
-        <v>20.33</v>
+        <v>20.19</v>
       </c>
       <c r="DX124" t="n">
-        <v>5.5</v>
+        <v>5.05</v>
       </c>
       <c r="DY124" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="DZ124" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="EA124" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EB124" t="inlineStr">
         <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="EC124" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="ED124" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EC124" t="inlineStr"/>
+      <c r="ED124" t="inlineStr"/>
       <c r="EE124" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="EF124" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EG124" t="inlineStr">
         <is>
-          <t>12.95</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EH124" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="EI124" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EJ124" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EK124" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EL124" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EM124" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EN124" t="inlineStr">
+        <is>
           <t>1.47</t>
         </is>
       </c>
-      <c r="EJ124" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="EK124" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="EL124" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EM124" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="EN124" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EO124" t="inlineStr"/>
-      <c r="EP124" t="inlineStr"/>
+      <c r="EO124" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EP124" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -59155,7 +59155,7 @@
         <v>2.93</v>
       </c>
       <c r="DO125" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -59591,7 +59591,7 @@
         <v>2.95</v>
       </c>
       <c r="DO126" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -60049,7 +60049,7 @@
         <v>2.25</v>
       </c>
       <c r="DE127" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF127" t="n">
         <v>2.14</v>
@@ -60079,7 +60079,7 @@
         <v>2.81</v>
       </c>
       <c r="DO127" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -61155,13 +61155,13 @@
         <v>4</v>
       </c>
       <c r="S130" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T130" t="n">
         <v>2</v>
       </c>
       <c r="U130" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V130" t="n">
         <v>6</v>
@@ -61336,13 +61336,13 @@
         <v>55</v>
       </c>
       <c r="BZ130" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="CA130" t="n">
         <v>0.82</v>
       </c>
       <c r="CB130" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="CC130" t="n">
         <v>0</v>
@@ -61562,6 +61562,2798 @@
       </c>
       <c r="EO130" t="inlineStr"/>
       <c r="EP130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>16</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Al Feiha</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Dhamk</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>46039.56597222222</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" t="n">
+        <v>2</v>
+      </c>
+      <c r="J131" t="n">
+        <v>5</v>
+      </c>
+      <c r="K131" t="n">
+        <v>7</v>
+      </c>
+      <c r="L131" t="n">
+        <v>12</v>
+      </c>
+      <c r="M131" t="n">
+        <v>2</v>
+      </c>
+      <c r="N131" t="n">
+        <v>2</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>2</v>
+      </c>
+      <c r="R131" t="n">
+        <v>2</v>
+      </c>
+      <c r="S131" t="n">
+        <v>7</v>
+      </c>
+      <c r="T131" t="n">
+        <v>4</v>
+      </c>
+      <c r="U131" t="n">
+        <v>9</v>
+      </c>
+      <c r="V131" t="n">
+        <v>6</v>
+      </c>
+      <c r="W131" t="n">
+        <v>11</v>
+      </c>
+      <c r="X131" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA131" t="inlineStr"/>
+      <c r="AB131" t="inlineStr"/>
+      <c r="AC131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>52</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>114</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU131" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV131" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX131" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY131" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ131" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA131" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB131" t="n">
+        <v>52</v>
+      </c>
+      <c r="DC131" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD131" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE131" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DF131" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG131" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DH131" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DI131" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DJ131" t="n">
+        <v>62</v>
+      </c>
+      <c r="DK131" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL131" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DM131" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DN131" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DO131" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU131" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV131" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW131" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="DX131" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="DY131" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="DZ131" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="EA131" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EB131" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EC131" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="ED131" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EE131" t="inlineStr">
+        <is>
+          <t>5.03</t>
+        </is>
+      </c>
+      <c r="EF131" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="EG131" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EH131" t="inlineStr">
+        <is>
+          <t>4.79</t>
+        </is>
+      </c>
+      <c r="EI131" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EJ131" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EK131" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EL131" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EM131" t="inlineStr"/>
+      <c r="EN131" t="inlineStr"/>
+      <c r="EO131" t="inlineStr"/>
+      <c r="EP131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>16</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>46039.63194444445</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>3</v>
+      </c>
+      <c r="K132" t="n">
+        <v>8</v>
+      </c>
+      <c r="L132" t="n">
+        <v>11</v>
+      </c>
+      <c r="M132" t="n">
+        <v>2</v>
+      </c>
+      <c r="N132" t="n">
+        <v>3</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>2</v>
+      </c>
+      <c r="R132" t="n">
+        <v>5</v>
+      </c>
+      <c r="S132" t="n">
+        <v>12</v>
+      </c>
+      <c r="T132" t="n">
+        <v>9</v>
+      </c>
+      <c r="U132" t="n">
+        <v>14</v>
+      </c>
+      <c r="V132" t="n">
+        <v>14</v>
+      </c>
+      <c r="W132" t="n">
+        <v>9</v>
+      </c>
+      <c r="X132" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA132" t="inlineStr"/>
+      <c r="AB132" t="inlineStr"/>
+      <c r="AC132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>5062</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>64</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>102</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU132" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV132" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW132" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX132" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY132" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ132" t="n">
+        <v>52</v>
+      </c>
+      <c r="DA132" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB132" t="n">
+        <v>52</v>
+      </c>
+      <c r="DC132" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD132" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DE132" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DF132" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DG132" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DH132" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DI132" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DJ132" t="n">
+        <v>49</v>
+      </c>
+      <c r="DK132" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL132" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DM132" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DN132" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="DO132" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP132" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV132" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW132" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="DX132" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="DY132" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="DZ132" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="EA132" t="inlineStr"/>
+      <c r="EB132" t="inlineStr"/>
+      <c r="EC132" t="inlineStr"/>
+      <c r="ED132" t="inlineStr"/>
+      <c r="EE132" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EF132" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="EG132" t="inlineStr">
+        <is>
+          <t>5.68</t>
+        </is>
+      </c>
+      <c r="EH132" t="inlineStr"/>
+      <c r="EI132" t="inlineStr"/>
+      <c r="EJ132" t="inlineStr"/>
+      <c r="EK132" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EL132" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EM132" t="inlineStr"/>
+      <c r="EN132" t="inlineStr"/>
+      <c r="EO132" t="inlineStr"/>
+      <c r="EP132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>16</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Al Shabab</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>46039.72916666666</v>
+      </c>
+      <c r="G133" t="n">
+        <v>3</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2</v>
+      </c>
+      <c r="I133" t="n">
+        <v>5</v>
+      </c>
+      <c r="J133" t="n">
+        <v>7</v>
+      </c>
+      <c r="K133" t="n">
+        <v>5</v>
+      </c>
+      <c r="L133" t="n">
+        <v>12</v>
+      </c>
+      <c r="M133" t="n">
+        <v>2</v>
+      </c>
+      <c r="N133" t="n">
+        <v>2</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>5</v>
+      </c>
+      <c r="R133" t="n">
+        <v>3</v>
+      </c>
+      <c r="S133" t="n">
+        <v>9</v>
+      </c>
+      <c r="T133" t="n">
+        <v>4</v>
+      </c>
+      <c r="U133" t="n">
+        <v>14</v>
+      </c>
+      <c r="V133" t="n">
+        <v>7</v>
+      </c>
+      <c r="W133" t="n">
+        <v>12</v>
+      </c>
+      <c r="X133" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>King Saud University Stadium</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
+        </is>
+      </c>
+      <c r="AC133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>5069</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>105</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>68</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU133" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV133" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX133" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY133" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ133" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA133" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB133" t="n">
+        <v>43</v>
+      </c>
+      <c r="DC133" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD133" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DE133" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DF133" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DG133" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DH133" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DI133" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DJ133" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK133" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL133" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DM133" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DN133" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="DO133" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU133" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV133" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW133" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="DX133" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="DY133" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="DZ133" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="EA133" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EB133" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EC133" t="inlineStr"/>
+      <c r="ED133" t="inlineStr"/>
+      <c r="EE133" t="inlineStr">
+        <is>
+          <t>6.34</t>
+        </is>
+      </c>
+      <c r="EF133" t="inlineStr">
+        <is>
+          <t>5.32</t>
+        </is>
+      </c>
+      <c r="EG133" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EH133" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EI133" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EJ133" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EK133" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EL133" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EM133" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EN133" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EO133" t="inlineStr"/>
+      <c r="EP133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>16</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Al Hazm</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Al Quadisiya</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>46040.63541666666</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="n">
+        <v>5</v>
+      </c>
+      <c r="I134" t="n">
+        <v>6</v>
+      </c>
+      <c r="J134" t="n">
+        <v>2</v>
+      </c>
+      <c r="K134" t="n">
+        <v>3</v>
+      </c>
+      <c r="L134" t="n">
+        <v>5</v>
+      </c>
+      <c r="M134" t="n">
+        <v>2</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>3</v>
+      </c>
+      <c r="R134" t="n">
+        <v>5</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="n">
+        <v>9</v>
+      </c>
+      <c r="U134" t="n">
+        <v>13</v>
+      </c>
+      <c r="V134" t="n">
+        <v>14</v>
+      </c>
+      <c r="W134" t="n">
+        <v>12</v>
+      </c>
+      <c r="X134" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA134" t="inlineStr"/>
+      <c r="AB134" t="inlineStr"/>
+      <c r="AC134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>5068</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>61</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>68</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>96</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>123</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU134" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV134" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX134" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY134" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ134" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA134" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB134" t="n">
+        <v>31</v>
+      </c>
+      <c r="DC134" t="n">
+        <v>54</v>
+      </c>
+      <c r="DD134" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DE134" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF134" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DG134" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DH134" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DI134" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DJ134" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK134" t="n">
+        <v>16</v>
+      </c>
+      <c r="DL134" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM134" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DN134" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="DO134" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW134" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="DX134" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="DY134" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="DZ134" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA134" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EB134" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EC134" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="ED134" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EE134" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EF134" t="inlineStr">
+        <is>
+          <t>4.94</t>
+        </is>
+      </c>
+      <c r="EG134" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="EH134" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EI134" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EJ134" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="EK134" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EL134" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EM134" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EN134" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EO134" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EP134" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>16</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Neom SC</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>46040.72916666666</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="n">
+        <v>2</v>
+      </c>
+      <c r="I135" t="n">
+        <v>3</v>
+      </c>
+      <c r="J135" t="n">
+        <v>5</v>
+      </c>
+      <c r="K135" t="n">
+        <v>7</v>
+      </c>
+      <c r="L135" t="n">
+        <v>12</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1</v>
+      </c>
+      <c r="N135" t="n">
+        <v>2</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>5</v>
+      </c>
+      <c r="R135" t="n">
+        <v>8</v>
+      </c>
+      <c r="S135" t="n">
+        <v>7</v>
+      </c>
+      <c r="T135" t="n">
+        <v>8</v>
+      </c>
+      <c r="U135" t="n">
+        <v>12</v>
+      </c>
+      <c r="V135" t="n">
+        <v>16</v>
+      </c>
+      <c r="W135" t="n">
+        <v>9</v>
+      </c>
+      <c r="X135" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA135" t="inlineStr"/>
+      <c r="AB135" t="inlineStr"/>
+      <c r="AC135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>5066</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>61</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>31</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>56</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>64</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU135" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV135" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW135" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX135" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY135" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ135" t="n">
+        <v>62</v>
+      </c>
+      <c r="DA135" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB135" t="n">
+        <v>55</v>
+      </c>
+      <c r="DC135" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD135" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DE135" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DF135" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG135" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DH135" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DI135" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DJ135" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK135" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL135" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DM135" t="n">
+        <v>2</v>
+      </c>
+      <c r="DN135" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="DO135" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU135" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV135" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW135" t="inlineStr"/>
+      <c r="DX135" t="inlineStr"/>
+      <c r="DY135" t="inlineStr"/>
+      <c r="DZ135" t="inlineStr"/>
+      <c r="EA135" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EB135" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EC135" t="inlineStr"/>
+      <c r="ED135" t="inlineStr"/>
+      <c r="EE135" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EF135" t="inlineStr">
+        <is>
+          <t>5.37</t>
+        </is>
+      </c>
+      <c r="EG135" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="EH135" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EI135" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EJ135" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EK135" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EL135" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EM135" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EN135" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EO135" t="inlineStr"/>
+      <c r="EP135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>16</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Al Riyadh</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Al Taawon</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>46040.72916666666</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="n">
+        <v>3</v>
+      </c>
+      <c r="I136" t="n">
+        <v>4</v>
+      </c>
+      <c r="J136" t="n">
+        <v>8</v>
+      </c>
+      <c r="K136" t="n">
+        <v>2</v>
+      </c>
+      <c r="L136" t="n">
+        <v>10</v>
+      </c>
+      <c r="M136" t="n">
+        <v>2</v>
+      </c>
+      <c r="N136" t="n">
+        <v>4</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>4</v>
+      </c>
+      <c r="R136" t="n">
+        <v>9</v>
+      </c>
+      <c r="S136" t="n">
+        <v>18</v>
+      </c>
+      <c r="T136" t="n">
+        <v>3</v>
+      </c>
+      <c r="U136" t="n">
+        <v>22</v>
+      </c>
+      <c r="V136" t="n">
+        <v>12</v>
+      </c>
+      <c r="W136" t="n">
+        <v>16</v>
+      </c>
+      <c r="X136" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>Prince Turki bin Abdul Aziz Stadium</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>, Riyadh</t>
+        </is>
+      </c>
+      <c r="AC136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>5074</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>64</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>81</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>120</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU136" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV136" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX136" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY136" t="n">
+        <v>17</v>
+      </c>
+      <c r="CZ136" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA136" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB136" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC136" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD136" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE136" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DF136" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DG136" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DH136" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DI136" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DJ136" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK136" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL136" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DM136" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DN136" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="DO136" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU136" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV136" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW136" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="DX136" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="DY136" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="DZ136" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA136" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EB136" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EC136" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="ED136" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EE136" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EF136" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="EG136" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="EH136" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EI136" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ136" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EK136" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EL136" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EM136" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EN136" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EO136" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EP136" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP151" headerRowCount="1">
-  <autoFilter ref="A1:EP151"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP154" headerRowCount="1">
+  <autoFilter ref="A1:EP154"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP151"/>
+  <dimension ref="A1:EP154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -6519,7 +6519,7 @@
         <v>2.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6950,7 +6950,7 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE13" t="n">
         <v>1</v>
@@ -6983,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7873,7 +7873,7 @@
         <v>0.89</v>
       </c>
       <c r="DE15" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -7903,7 +7903,7 @@
         <v>0.91</v>
       </c>
       <c r="DO15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -9295,7 +9295,7 @@
         <v>2.11</v>
       </c>
       <c r="DO18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9718,7 +9718,7 @@
         <v>50</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE19" t="n">
         <v>1.13</v>
@@ -9751,7 +9751,7 @@
         <v>1.18</v>
       </c>
       <c r="DO19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10181,7 +10181,7 @@
         <v>0.67</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF20" t="n">
         <v>0</v>
@@ -10211,7 +10211,7 @@
         <v>0</v>
       </c>
       <c r="DO20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10691,7 +10691,7 @@
         <v>0.44</v>
       </c>
       <c r="DO21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11141,7 +11141,7 @@
         <v>0.78</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -11171,7 +11171,7 @@
         <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -13055,7 +13055,7 @@
         <v>2.14</v>
       </c>
       <c r="DO26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13494,7 +13494,7 @@
         <v>50</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="DE27" t="n">
         <v>1</v>
@@ -13527,7 +13527,7 @@
         <v>1.42</v>
       </c>
       <c r="DO27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP27" t="b">
         <v>0</v>
@@ -13958,7 +13958,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE28" t="n">
         <v>0.25</v>
@@ -13991,7 +13991,7 @@
         <v>3.72</v>
       </c>
       <c r="DO28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14433,7 +14433,7 @@
         <v>1.75</v>
       </c>
       <c r="DE29" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF29" t="n">
         <v>3</v>
@@ -14463,7 +14463,7 @@
         <v>2.82</v>
       </c>
       <c r="DO29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15369,7 +15369,7 @@
         <v>2.78</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF31" t="n">
         <v>2</v>
@@ -15399,7 +15399,7 @@
         <v>2.97</v>
       </c>
       <c r="DO31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15822,7 +15822,7 @@
         <v>0</v>
       </c>
       <c r="DD32" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="DE32" t="n">
         <v>2.38</v>
@@ -15855,7 +15855,7 @@
         <v>2.93</v>
       </c>
       <c r="DO32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16319,7 +16319,7 @@
         <v>2.59</v>
       </c>
       <c r="DO33" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16746,7 +16746,7 @@
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE34" t="n">
         <v>2</v>
@@ -16779,7 +16779,7 @@
         <v>4.3</v>
       </c>
       <c r="DO34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -18683,7 +18683,7 @@
         <v>2.44</v>
       </c>
       <c r="DO38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -20571,7 +20571,7 @@
         <v>1.63</v>
       </c>
       <c r="DO42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21010,7 +21010,7 @@
         <v>50</v>
       </c>
       <c r="DD43" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE43" t="n">
         <v>1</v>
@@ -21043,7 +21043,7 @@
         <v>4.22</v>
       </c>
       <c r="DO43" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21941,7 +21941,7 @@
         <v>2.13</v>
       </c>
       <c r="DE45" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF45" t="n">
         <v>1.5</v>
@@ -21971,7 +21971,7 @@
         <v>2.14</v>
       </c>
       <c r="DO45" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -23349,7 +23349,7 @@
         <v>1.25</v>
       </c>
       <c r="DE48" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF48" t="n">
         <v>1</v>
@@ -23379,7 +23379,7 @@
         <v>1.94</v>
       </c>
       <c r="DO48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -25246,7 +25246,7 @@
         <v>100</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE52" t="n">
         <v>2.5</v>
@@ -25279,7 +25279,7 @@
         <v>3.18</v>
       </c>
       <c r="DO52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25713,7 +25713,7 @@
         <v>2.5</v>
       </c>
       <c r="DE53" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF53" t="n">
         <v>3</v>
@@ -25743,7 +25743,7 @@
         <v>2.21</v>
       </c>
       <c r="DO53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP53" t="b">
         <v>0</v>
@@ -26165,7 +26165,7 @@
         <v>1.13</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF54" t="n">
         <v>1</v>
@@ -26195,7 +26195,7 @@
         <v>2.64</v>
       </c>
       <c r="DO54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26610,7 +26610,7 @@
         <v>50</v>
       </c>
       <c r="DD55" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="DE55" t="n">
         <v>2</v>
@@ -26643,7 +26643,7 @@
         <v>3.19</v>
       </c>
       <c r="DO55" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27123,7 +27123,7 @@
         <v>2.65</v>
       </c>
       <c r="DO56" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28543,7 +28543,7 @@
         <v>2.02</v>
       </c>
       <c r="DO59" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29487,7 +29487,7 @@
         <v>1.4</v>
       </c>
       <c r="DO61" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29967,7 +29967,7 @@
         <v>2.42</v>
       </c>
       <c r="DO62" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30447,7 +30447,7 @@
         <v>3.33</v>
       </c>
       <c r="DO63" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30886,7 +30886,7 @@
         <v>67</v>
       </c>
       <c r="DD64" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE64" t="n">
         <v>0.78</v>
@@ -30919,7 +30919,7 @@
         <v>3.73</v>
       </c>
       <c r="DO64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31342,7 +31342,7 @@
         <v>67</v>
       </c>
       <c r="DD65" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="DE65" t="n">
         <v>1.22</v>
@@ -31375,7 +31375,7 @@
         <v>2.02</v>
       </c>
       <c r="DO65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32273,7 +32273,7 @@
         <v>1</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF67" t="n">
         <v>2</v>
@@ -32303,7 +32303,7 @@
         <v>2.17</v>
       </c>
       <c r="DO67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32737,7 +32737,7 @@
         <v>1.25</v>
       </c>
       <c r="DE68" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF68" t="n">
         <v>0.67</v>
@@ -32767,7 +32767,7 @@
         <v>1.32</v>
       </c>
       <c r="DO68" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33209,7 +33209,7 @@
         <v>1.5</v>
       </c>
       <c r="DE69" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF69" t="n">
         <v>1</v>
@@ -33239,7 +33239,7 @@
         <v>2.68</v>
       </c>
       <c r="DO69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34167,7 +34167,7 @@
         <v>3.72</v>
       </c>
       <c r="DO71" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35094,7 +35094,7 @@
         <v>67</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE73" t="n">
         <v>2.38</v>
@@ -35127,7 +35127,7 @@
         <v>3.05</v>
       </c>
       <c r="DO73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35599,7 +35599,7 @@
         <v>2.12</v>
       </c>
       <c r="DO74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36030,7 +36030,7 @@
         <v>75</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE75" t="n">
         <v>0.25</v>
@@ -36063,7 +36063,7 @@
         <v>2.45</v>
       </c>
       <c r="DO75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36999,7 +36999,7 @@
         <v>2.28</v>
       </c>
       <c r="DO77" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -38351,7 +38351,7 @@
         <v>2.38</v>
       </c>
       <c r="DO80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -38831,7 +38831,7 @@
         <v>2.51</v>
       </c>
       <c r="DO81" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -39270,7 +39270,7 @@
         <v>88</v>
       </c>
       <c r="DD82" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE82" t="n">
         <v>1.22</v>
@@ -39303,7 +39303,7 @@
         <v>3.82</v>
       </c>
       <c r="DO82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39755,7 +39755,7 @@
         <v>2.19</v>
       </c>
       <c r="DO83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP83" t="b">
         <v>0</v>
@@ -41557,7 +41557,7 @@
         <v>0.67</v>
       </c>
       <c r="DE87" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF87" t="n">
         <v>1.5</v>
@@ -41587,7 +41587,7 @@
         <v>2.81</v>
       </c>
       <c r="DO87" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -42501,7 +42501,7 @@
         <v>2.5</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF89" t="n">
         <v>2.5</v>
@@ -42531,7 +42531,7 @@
         <v>2.71</v>
       </c>
       <c r="DO89" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42934,10 +42934,10 @@
         <v>65</v>
       </c>
       <c r="DD90" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE90" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF90" t="n">
         <v>3</v>
@@ -42967,7 +42967,7 @@
         <v>3.16</v>
       </c>
       <c r="DO90" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -43402,7 +43402,7 @@
         <v>78</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE91" t="n">
         <v>0.44</v>
@@ -43435,7 +43435,7 @@
         <v>2.54</v>
       </c>
       <c r="DO91" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44019,12 +44019,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
@@ -44034,25 +44034,25 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L93" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -44061,126 +44061,134 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R93" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S93" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T93" t="n">
         <v>4</v>
       </c>
       <c r="U93" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V93" t="n">
+        <v>11</v>
+      </c>
+      <c r="W93" t="n">
+        <v>8</v>
+      </c>
+      <c r="X93" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>Prince Turki bin Abdul Aziz Stadium</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>, Riyadh</t>
+        </is>
+      </c>
+      <c r="AC93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD93" t="n">
         <v>5</v>
       </c>
-      <c r="W93" t="n">
-        <v>13</v>
-      </c>
-      <c r="X93" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA93" t="inlineStr"/>
-      <c r="AB93" t="inlineStr"/>
-      <c r="AC93" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD93" t="n">
-        <v>0</v>
-      </c>
       <c r="AE93" t="n">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="AF93" t="n">
-        <v>4.35</v>
+        <v>3.1</v>
       </c>
       <c r="AG93" t="n">
-        <v>6.2</v>
+        <v>2.6</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AI93" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="AJ93" t="n">
-        <v>2.63</v>
+        <v>3.42</v>
       </c>
       <c r="AK93" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AL93" t="n">
-        <v>1.71</v>
+        <v>1.99</v>
       </c>
       <c r="AM93" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AN93" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AO93" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AR93" t="n">
-        <v>2.39</v>
+        <v>2.91</v>
       </c>
       <c r="AS93" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="AT93" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AU93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV93" t="n">
         <v>0</v>
       </c>
       <c r="AW93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX93" t="n">
         <v>1</v>
       </c>
       <c r="AY93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB93" t="n">
-        <v>5074</v>
+        <v>5089</v>
       </c>
       <c r="BC93" t="n">
         <v>0</v>
       </c>
       <c r="BD93" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="BE93" t="n">
         <v>0</v>
       </c>
       <c r="BF93" t="n">
-        <v>4294</v>
+        <v>-1</v>
       </c>
       <c r="BG93" t="n">
         <v>2</v>
@@ -44189,190 +44197,190 @@
         <v>1</v>
       </c>
       <c r="BI93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BJ93" t="n">
         <v>1</v>
       </c>
       <c r="BK93" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL93" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM93" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN93" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT93" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV93" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW93" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX93" t="n">
+        <v>105</v>
+      </c>
+      <c r="BY93" t="n">
+        <v>80</v>
+      </c>
+      <c r="BZ93" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CA93" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CB93" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM93" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR93" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS93" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU93" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV93" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX93" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY93" t="n">
         <v>7</v>
       </c>
-      <c r="BL93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM93" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN93" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO93" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ93" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR93" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS93" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT93" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU93" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV93" t="n">
-        <v>63</v>
-      </c>
-      <c r="BW93" t="n">
-        <v>29</v>
-      </c>
-      <c r="BX93" t="n">
-        <v>117</v>
-      </c>
-      <c r="BY93" t="n">
-        <v>88</v>
-      </c>
-      <c r="BZ93" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CA93" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="CB93" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="CC93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR93" t="n">
+      <c r="CZ93" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA93" t="n">
+        <v>74</v>
+      </c>
+      <c r="DB93" t="n">
+        <v>37</v>
+      </c>
+      <c r="DC93" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD93" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE93" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DF93" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DG93" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH93" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DI93" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ93" t="n">
+        <v>55</v>
+      </c>
+      <c r="DK93" t="n">
+        <v>27</v>
+      </c>
+      <c r="DL93" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DM93" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DN93" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DO93" t="n">
         <v>17</v>
       </c>
-      <c r="CS93" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU93" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV93" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX93" t="n">
-        <v>2</v>
-      </c>
-      <c r="CY93" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ93" t="n">
-        <v>72</v>
-      </c>
-      <c r="DA93" t="n">
-        <v>92</v>
-      </c>
-      <c r="DB93" t="n">
-        <v>35</v>
-      </c>
-      <c r="DC93" t="n">
-        <v>64</v>
-      </c>
-      <c r="DD93" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DE93" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DF93" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG93" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DH93" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DI93" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DJ93" t="n">
-        <v>29</v>
-      </c>
-      <c r="DK93" t="n">
-        <v>9</v>
-      </c>
-      <c r="DL93" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="DM93" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="DN93" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="DO93" t="n">
-        <v>16</v>
-      </c>
       <c r="DP93" t="b">
         <v>1</v>
       </c>
       <c r="DQ93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS93" t="b">
         <v>0</v>
@@ -44384,17 +44392,17 @@
         <v>0</v>
       </c>
       <c r="DV93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW93" t="n">
-        <v>17.94</v>
+        <v>18.59</v>
       </c>
       <c r="DX93" t="n">
-        <v>6.89</v>
+        <v>5.81</v>
       </c>
       <c r="DY93" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="DZ93" t="inlineStr">
@@ -44404,52 +44412,52 @@
       </c>
       <c r="EA93" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EB93" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EC93" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="ED93" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EE93" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EF93" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EG93" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EH93" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="EI93" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EJ93" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EK93" t="inlineStr">
@@ -44459,27 +44467,27 @@
       </c>
       <c r="EL93" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EM93" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="EN93" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EO93" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EP93" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
@@ -44499,12 +44507,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
@@ -44514,25 +44522,25 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K94" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N94" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -44541,326 +44549,318 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S94" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T94" t="n">
         <v>4</v>
       </c>
       <c r="U94" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="V94" t="n">
+        <v>5</v>
+      </c>
+      <c r="W94" t="n">
+        <v>13</v>
+      </c>
+      <c r="X94" t="n">
         <v>11</v>
       </c>
-      <c r="W94" t="n">
-        <v>8</v>
-      </c>
-      <c r="X94" t="n">
-        <v>12</v>
-      </c>
       <c r="Y94" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="Z94" t="n">
-        <v>49</v>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>Prince Turki bin Abdul Aziz Stadium</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>, Riyadh</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD94" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE94" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>5074</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>72</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF94" t="n">
+        <v>4294</v>
+      </c>
+      <c r="BG94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI94" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK94" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN94" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV94" t="n">
+        <v>63</v>
+      </c>
+      <c r="BW94" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX94" t="n">
+        <v>117</v>
+      </c>
+      <c r="BY94" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ94" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CA94" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="CB94" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR94" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS94" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU94" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV94" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX94" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY94" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ94" t="n">
+        <v>72</v>
+      </c>
+      <c r="DA94" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB94" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC94" t="n">
+        <v>64</v>
+      </c>
+      <c r="DD94" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DE94" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DF94" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG94" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DH94" t="n">
         <v>2.5</v>
       </c>
-      <c r="AF94" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG94" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH94" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI94" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AJ94" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AK94" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL94" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AM94" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AN94" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO94" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AP94" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AQ94" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR94" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AS94" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AT94" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU94" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV94" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW94" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX94" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY94" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ94" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB94" t="n">
-        <v>5089</v>
-      </c>
-      <c r="BC94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD94" t="n">
-        <v>64</v>
-      </c>
-      <c r="BE94" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF94" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG94" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI94" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK94" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL94" t="n">
-        <v>4</v>
-      </c>
-      <c r="BM94" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN94" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP94" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR94" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS94" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT94" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV94" t="n">
-        <v>45</v>
-      </c>
-      <c r="BW94" t="n">
-        <v>48</v>
-      </c>
-      <c r="BX94" t="n">
-        <v>105</v>
-      </c>
-      <c r="BY94" t="n">
-        <v>80</v>
-      </c>
-      <c r="BZ94" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CA94" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CB94" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="CC94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM94" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO94" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR94" t="n">
-        <v>28</v>
-      </c>
-      <c r="CS94" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU94" t="n">
-        <v>12</v>
-      </c>
-      <c r="CV94" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX94" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY94" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ94" t="n">
-        <v>45</v>
-      </c>
-      <c r="DA94" t="n">
-        <v>74</v>
-      </c>
-      <c r="DB94" t="n">
-        <v>37</v>
-      </c>
-      <c r="DC94" t="n">
-        <v>65</v>
-      </c>
-      <c r="DD94" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE94" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DF94" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DG94" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DH94" t="n">
-        <v>0.8</v>
-      </c>
       <c r="DI94" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="DJ94" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="DK94" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="DL94" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="DM94" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="DN94" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="DO94" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
       </c>
       <c r="DQ94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS94" t="b">
         <v>0</v>
@@ -44872,17 +44872,17 @@
         <v>0</v>
       </c>
       <c r="DV94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW94" t="n">
-        <v>18.59</v>
+        <v>17.94</v>
       </c>
       <c r="DX94" t="n">
-        <v>5.81</v>
+        <v>6.89</v>
       </c>
       <c r="DY94" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="DZ94" t="inlineStr">
@@ -44892,52 +44892,52 @@
       </c>
       <c r="EA94" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EB94" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EC94" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="ED94" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EE94" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="EF94" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="EG94" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EH94" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="EI94" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EJ94" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EK94" t="inlineStr">
@@ -44947,27 +44947,27 @@
       </c>
       <c r="EL94" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EM94" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="EN94" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EO94" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="EP94" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.28</t>
         </is>
       </c>
     </row>
@@ -45783,7 +45783,7 @@
         <v>3.12</v>
       </c>
       <c r="DO96" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -46205,7 +46205,7 @@
         <v>0.89</v>
       </c>
       <c r="DE97" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF97" t="n">
         <v>0.8</v>
@@ -46235,7 +46235,7 @@
         <v>2.15</v>
       </c>
       <c r="DO97" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -46699,7 +46699,7 @@
         <v>3.06</v>
       </c>
       <c r="DO98" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46807,76 +46807,76 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
         <v>46022.72916666666</v>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
         <v>3</v>
       </c>
       <c r="I99" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J99" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K99" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L99" t="n">
         <v>12</v>
       </c>
       <c r="M99" t="n">
+        <v>2</v>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" t="n">
+        <v>1</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
         <v>4</v>
       </c>
-      <c r="N99" t="n">
-        <v>1</v>
-      </c>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>6</v>
-      </c>
       <c r="R99" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S99" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T99" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="U99" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V99" t="n">
+        <v>24</v>
+      </c>
+      <c r="W99" t="n">
         <v>11</v>
       </c>
-      <c r="W99" t="n">
-        <v>9</v>
-      </c>
       <c r="X99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y99" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z99" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr"/>
@@ -46887,88 +46887,88 @@
         <v>1</v>
       </c>
       <c r="AE99" t="n">
-        <v>5.59</v>
+        <v>10</v>
       </c>
       <c r="AF99" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AT99" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AU99" t="n">
         <v>4</v>
       </c>
-      <c r="AG99" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI99" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AJ99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK99" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL99" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU99" t="n">
-        <v>5</v>
-      </c>
       <c r="AV99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ99" t="n">
         <v>2</v>
       </c>
       <c r="BA99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB99" t="n">
-        <v>5068</v>
+        <v>5066</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BE99" t="n">
         <v>0</v>
       </c>
       <c r="BF99" t="n">
-        <v>2556</v>
+        <v>9253</v>
       </c>
       <c r="BG99" t="n">
         <v>2</v>
@@ -46977,178 +46977,178 @@
         <v>1</v>
       </c>
       <c r="BI99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL99" t="n">
+        <v>8</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV99" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW99" t="n">
+        <v>68</v>
+      </c>
+      <c r="BX99" t="n">
+        <v>57</v>
+      </c>
+      <c r="BY99" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ99" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CA99" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="CB99" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="CC99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR99" t="n">
         <v>6</v>
       </c>
-      <c r="BL99" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM99" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN99" t="n">
+      <c r="CS99" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU99" t="n">
         <v>9</v>
       </c>
-      <c r="BO99" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ99" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR99" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS99" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT99" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU99" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV99" t="n">
-        <v>59</v>
-      </c>
-      <c r="BW99" t="n">
-        <v>61</v>
-      </c>
-      <c r="BX99" t="n">
-        <v>99</v>
-      </c>
-      <c r="BY99" t="n">
-        <v>116</v>
-      </c>
-      <c r="BZ99" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="CA99" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CB99" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="CC99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR99" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS99" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU99" t="n">
-        <v>14</v>
-      </c>
       <c r="CV99" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CW99" t="n">
         <v>1</v>
       </c>
       <c r="CX99" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="CY99" t="n">
         <v>9</v>
       </c>
       <c r="CZ99" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="DA99" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="DB99" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="DC99" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.13</v>
+        <v>0.67</v>
       </c>
       <c r="DE99" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="DF99" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DG99" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="DH99" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="DI99" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="DJ99" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="DK99" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="DL99" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="DM99" t="n">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="DN99" t="n">
-        <v>3.04</v>
+        <v>3.24</v>
       </c>
       <c r="DO99" t="n">
         <v>17</v>
@@ -47166,7 +47166,7 @@
         <v>1</v>
       </c>
       <c r="DT99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU99" t="b">
         <v>0</v>
@@ -47175,14 +47175,14 @@
         <v>1</v>
       </c>
       <c r="DW99" t="n">
-        <v>13.4</v>
+        <v>15.88</v>
       </c>
       <c r="DX99" t="n">
-        <v>4.76</v>
+        <v>5.15</v>
       </c>
       <c r="DY99" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="DZ99" t="inlineStr">
@@ -47190,32 +47190,68 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA99" t="inlineStr"/>
-      <c r="EB99" t="inlineStr"/>
+      <c r="EA99" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EB99" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
       <c r="EC99" t="inlineStr"/>
       <c r="ED99" t="inlineStr"/>
       <c r="EE99" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EF99" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="EG99" t="inlineStr">
         <is>
-          <t>5.07</t>
-        </is>
-      </c>
-      <c r="EH99" t="inlineStr"/>
-      <c r="EI99" t="inlineStr"/>
-      <c r="EJ99" t="inlineStr"/>
-      <c r="EK99" t="inlineStr"/>
-      <c r="EL99" t="inlineStr"/>
-      <c r="EM99" t="inlineStr"/>
-      <c r="EN99" t="inlineStr"/>
+          <t>8.72</t>
+        </is>
+      </c>
+      <c r="EH99" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EI99" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EJ99" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="EK99" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EL99" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EM99" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EN99" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
       <c r="EO99" t="inlineStr"/>
       <c r="EP99" t="inlineStr"/>
     </row>
@@ -47235,76 +47271,76 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
         <v>46022.72916666666</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" t="n">
         <v>3</v>
       </c>
       <c r="I100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J100" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K100" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L100" t="n">
         <v>12</v>
       </c>
       <c r="M100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N100" t="n">
         <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R100" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T100" t="n">
+        <v>5</v>
+      </c>
+      <c r="U100" t="n">
         <v>14</v>
       </c>
-      <c r="U100" t="n">
+      <c r="V100" t="n">
         <v>11</v>
       </c>
-      <c r="V100" t="n">
-        <v>24</v>
-      </c>
       <c r="W100" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y100" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z100" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr"/>
@@ -47315,88 +47351,88 @@
         <v>1</v>
       </c>
       <c r="AE100" t="n">
-        <v>10</v>
+        <v>5.59</v>
       </c>
       <c r="AF100" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="AG100" t="n">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI100" t="n">
-        <v>1.31</v>
+        <v>1.72</v>
       </c>
       <c r="AJ100" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AK100" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AL100" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AM100" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN100" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO100" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AS100" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AU100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ100" t="n">
         <v>2</v>
       </c>
       <c r="BA100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB100" t="n">
-        <v>5066</v>
+        <v>5068</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
       </c>
       <c r="BF100" t="n">
-        <v>9253</v>
+        <v>2556</v>
       </c>
       <c r="BG100" t="n">
         <v>2</v>
@@ -47405,178 +47441,178 @@
         <v>1</v>
       </c>
       <c r="BI100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK100" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BL100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV100" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW100" t="n">
+        <v>61</v>
+      </c>
+      <c r="BX100" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY100" t="n">
+        <v>116</v>
+      </c>
+      <c r="BZ100" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CC100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR100" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS100" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU100" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV100" t="n">
         <v>8</v>
       </c>
-      <c r="BM100" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN100" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO100" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ100" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR100" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS100" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT100" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU100" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV100" t="n">
-        <v>18</v>
-      </c>
-      <c r="BW100" t="n">
-        <v>68</v>
-      </c>
-      <c r="BX100" t="n">
-        <v>57</v>
-      </c>
-      <c r="BY100" t="n">
-        <v>110</v>
-      </c>
-      <c r="BZ100" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="CA100" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="CB100" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="CC100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR100" t="n">
-        <v>6</v>
-      </c>
-      <c r="CS100" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU100" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV100" t="n">
-        <v>11</v>
-      </c>
       <c r="CW100" t="n">
         <v>1</v>
       </c>
       <c r="CX100" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="CY100" t="n">
         <v>9</v>
       </c>
       <c r="CZ100" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="DA100" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="DB100" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="DC100" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="DD100" t="n">
-        <v>0.67</v>
+        <v>1.13</v>
       </c>
       <c r="DE100" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="DF100" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DG100" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="DH100" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="DI100" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="DJ100" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="DK100" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="DL100" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="DM100" t="n">
-        <v>1.88</v>
+        <v>1.41</v>
       </c>
       <c r="DN100" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="DO100" t="n">
         <v>17</v>
@@ -47594,7 +47630,7 @@
         <v>1</v>
       </c>
       <c r="DT100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU100" t="b">
         <v>0</v>
@@ -47603,14 +47639,14 @@
         <v>1</v>
       </c>
       <c r="DW100" t="n">
-        <v>15.88</v>
+        <v>13.4</v>
       </c>
       <c r="DX100" t="n">
-        <v>5.15</v>
+        <v>4.76</v>
       </c>
       <c r="DY100" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="DZ100" t="inlineStr">
@@ -47618,68 +47654,32 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="EA100" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EB100" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
+      <c r="EA100" t="inlineStr"/>
+      <c r="EB100" t="inlineStr"/>
       <c r="EC100" t="inlineStr"/>
       <c r="ED100" t="inlineStr"/>
       <c r="EE100" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EF100" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="EG100" t="inlineStr">
         <is>
-          <t>8.72</t>
-        </is>
-      </c>
-      <c r="EH100" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EI100" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EJ100" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="EK100" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EL100" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EM100" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EN100" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="EH100" t="inlineStr"/>
+      <c r="EI100" t="inlineStr"/>
+      <c r="EJ100" t="inlineStr"/>
+      <c r="EK100" t="inlineStr"/>
+      <c r="EL100" t="inlineStr"/>
+      <c r="EM100" t="inlineStr"/>
+      <c r="EN100" t="inlineStr"/>
       <c r="EO100" t="inlineStr"/>
       <c r="EP100" t="inlineStr"/>
     </row>
@@ -48493,7 +48493,7 @@
         <v>1.44</v>
       </c>
       <c r="DE102" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF102" t="n">
         <v>1.5</v>
@@ -48523,7 +48523,7 @@
         <v>1.44</v>
       </c>
       <c r="DO102" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48959,7 +48959,7 @@
         <v>3.97</v>
       </c>
       <c r="DO103" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -50306,10 +50306,10 @@
         <v>82</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE106" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF106" t="n">
         <v>1.5</v>
@@ -50339,7 +50339,7 @@
         <v>3.01</v>
       </c>
       <c r="DO106" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -50754,7 +50754,7 @@
         <v>65</v>
       </c>
       <c r="DD107" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="DE107" t="n">
         <v>1.75</v>
@@ -50787,7 +50787,7 @@
         <v>2.44</v>
       </c>
       <c r="DO107" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50923,40 +50923,40 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
         <v>46026.72916666666</v>
       </c>
       <c r="G108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I108" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J108" t="n">
+        <v>2</v>
+      </c>
+      <c r="K108" t="n">
         <v>9</v>
       </c>
-      <c r="K108" t="n">
-        <v>4</v>
-      </c>
       <c r="L108" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -50965,114 +50965,122 @@
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S108" t="n">
         <v>8</v>
       </c>
       <c r="T108" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U108" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="V108" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="W108" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="X108" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="Y108" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="Z108" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA108" t="inlineStr"/>
-      <c r="AB108" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>Dhamak Club Stadium</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>, Khamis Mushait</t>
+        </is>
+      </c>
       <c r="AC108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.3</v>
+        <v>12.2</v>
       </c>
       <c r="AF108" t="n">
-        <v>5.2</v>
+        <v>6.15</v>
       </c>
       <c r="AG108" t="n">
-        <v>9.140000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="AH108" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI108" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AJ108" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AK108" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AL108" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AM108" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN108" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AO108" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AP108" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR108" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS108" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AU108" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB108" t="n">
-        <v>5068</v>
+        <v>5066</v>
       </c>
       <c r="BC108" t="n">
         <v>0</v>
@@ -51084,7 +51092,7 @@
         <v>0</v>
       </c>
       <c r="BF108" t="n">
-        <v>6160</v>
+        <v>14873</v>
       </c>
       <c r="BG108" t="n">
         <v>2</v>
@@ -51093,133 +51101,133 @@
         <v>1</v>
       </c>
       <c r="BI108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ108" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL108" t="n">
         <v>6</v>
       </c>
-      <c r="BJ108" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK108" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL108" t="n">
-        <v>2</v>
-      </c>
       <c r="BM108" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN108" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV108" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW108" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX108" t="n">
+        <v>71</v>
+      </c>
+      <c r="BY108" t="n">
+        <v>119</v>
+      </c>
+      <c r="BZ108" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CA108" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CB108" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR108" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS108" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU108" t="n">
         <v>8</v>
       </c>
-      <c r="BN108" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ108" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT108" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV108" t="n">
-        <v>49</v>
-      </c>
-      <c r="BW108" t="n">
-        <v>52</v>
-      </c>
-      <c r="BX108" t="n">
-        <v>90</v>
-      </c>
-      <c r="BY108" t="n">
-        <v>79</v>
-      </c>
-      <c r="BZ108" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CA108" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CB108" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="CC108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR108" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS108" t="n">
-        <v>18</v>
-      </c>
-      <c r="CT108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU108" t="n">
-        <v>19</v>
-      </c>
       <c r="CV108" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CW108" t="n">
         <v>1</v>
       </c>
       <c r="CX108" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CY108" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CZ108" t="n">
         <v>60</v>
@@ -51228,28 +51236,28 @@
         <v>90</v>
       </c>
       <c r="DB108" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="DC108" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="DD108" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE108" t="n">
         <v>2.5</v>
       </c>
-      <c r="DE108" t="n">
-        <v>0.25</v>
-      </c>
       <c r="DF108" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="DG108" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="DH108" t="n">
-        <v>1.91</v>
+        <v>0.82</v>
       </c>
       <c r="DI108" t="n">
-        <v>0.73</v>
+        <v>2.64</v>
       </c>
       <c r="DJ108" t="n">
         <v>40</v>
@@ -51258,13 +51266,13 @@
         <v>10</v>
       </c>
       <c r="DL108" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="DM108" t="n">
-        <v>1.05</v>
+        <v>2.04</v>
       </c>
       <c r="DN108" t="n">
-        <v>2.86</v>
+        <v>3.29</v>
       </c>
       <c r="DO108" t="n">
         <v>17</v>
@@ -51276,10 +51284,10 @@
         <v>1</v>
       </c>
       <c r="DR108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT108" t="b">
         <v>0</v>
@@ -51291,47 +51299,83 @@
         <v>0</v>
       </c>
       <c r="DW108" t="n">
-        <v>19.18</v>
+        <v>20.33</v>
       </c>
       <c r="DX108" t="n">
-        <v>12.01</v>
+        <v>4</v>
       </c>
       <c r="DY108" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="DZ108" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="EA108" t="inlineStr"/>
-      <c r="EB108" t="inlineStr"/>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="EA108" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EB108" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
       <c r="EC108" t="inlineStr"/>
       <c r="ED108" t="inlineStr"/>
       <c r="EE108" t="inlineStr">
         <is>
-          <t>10.72</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EF108" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="EG108" t="inlineStr">
         <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="EH108" t="inlineStr"/>
-      <c r="EI108" t="inlineStr"/>
-      <c r="EJ108" t="inlineStr"/>
-      <c r="EK108" t="inlineStr"/>
-      <c r="EL108" t="inlineStr"/>
-      <c r="EM108" t="inlineStr"/>
-      <c r="EN108" t="inlineStr"/>
+          <t>9.85</t>
+        </is>
+      </c>
+      <c r="EH108" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EI108" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EJ108" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EK108" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EL108" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EM108" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EN108" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
       <c r="EO108" t="inlineStr"/>
       <c r="EP108" t="inlineStr"/>
     </row>
@@ -51351,40 +51395,40 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
         <v>46026.72916666666</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J109" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K109" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L109" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -51393,122 +51437,114 @@
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R109" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S109" t="n">
         <v>8</v>
       </c>
       <c r="T109" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="U109" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="V109" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="W109" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="X109" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="Y109" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="Z109" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>Dhamak Club Stadium</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>, Khamis Mushait</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr"/>
       <c r="AC109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>12.2</v>
+        <v>1.3</v>
       </c>
       <c r="AF109" t="n">
-        <v>6.15</v>
+        <v>5.2</v>
       </c>
       <c r="AG109" t="n">
-        <v>1.11</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AH109" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI109" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ109" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AK109" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AL109" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AM109" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN109" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AO109" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR109" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS109" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AT109" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AU109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB109" t="n">
-        <v>5066</v>
+        <v>5068</v>
       </c>
       <c r="BC109" t="n">
         <v>0</v>
@@ -51520,7 +51556,7 @@
         <v>0</v>
       </c>
       <c r="BF109" t="n">
-        <v>14873</v>
+        <v>6160</v>
       </c>
       <c r="BG109" t="n">
         <v>2</v>
@@ -51529,133 +51565,133 @@
         <v>1</v>
       </c>
       <c r="BI109" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BJ109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV109" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW109" t="n">
+        <v>52</v>
+      </c>
+      <c r="BX109" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY109" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ109" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CA109" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CB109" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CC109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR109" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS109" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU109" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV109" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX109" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY109" t="n">
         <v>6</v>
-      </c>
-      <c r="BM109" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN109" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP109" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS109" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT109" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV109" t="n">
-        <v>22</v>
-      </c>
-      <c r="BW109" t="n">
-        <v>56</v>
-      </c>
-      <c r="BX109" t="n">
-        <v>71</v>
-      </c>
-      <c r="BY109" t="n">
-        <v>119</v>
-      </c>
-      <c r="BZ109" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="CA109" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CB109" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="CC109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP109" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR109" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS109" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU109" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV109" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX109" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY109" t="n">
-        <v>9</v>
       </c>
       <c r="CZ109" t="n">
         <v>60</v>
@@ -51664,28 +51700,28 @@
         <v>90</v>
       </c>
       <c r="DB109" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="DC109" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="DD109" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="DE109" t="n">
-        <v>2.5</v>
+        <v>0.25</v>
       </c>
       <c r="DF109" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="DG109" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="DH109" t="n">
-        <v>0.82</v>
+        <v>1.91</v>
       </c>
       <c r="DI109" t="n">
-        <v>2.64</v>
+        <v>0.73</v>
       </c>
       <c r="DJ109" t="n">
         <v>40</v>
@@ -51694,16 +51730,16 @@
         <v>10</v>
       </c>
       <c r="DL109" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="DM109" t="n">
-        <v>2.04</v>
+        <v>1.05</v>
       </c>
       <c r="DN109" t="n">
-        <v>3.29</v>
+        <v>2.86</v>
       </c>
       <c r="DO109" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51712,10 +51748,10 @@
         <v>1</v>
       </c>
       <c r="DR109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT109" t="b">
         <v>0</v>
@@ -51727,83 +51763,47 @@
         <v>0</v>
       </c>
       <c r="DW109" t="n">
-        <v>20.33</v>
+        <v>19.18</v>
       </c>
       <c r="DX109" t="n">
-        <v>4</v>
+        <v>12.01</v>
       </c>
       <c r="DY109" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="DZ109" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="EA109" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="EB109" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA109" t="inlineStr"/>
+      <c r="EB109" t="inlineStr"/>
       <c r="EC109" t="inlineStr"/>
       <c r="ED109" t="inlineStr"/>
       <c r="EE109" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="EF109" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="EG109" t="inlineStr">
         <is>
-          <t>9.85</t>
-        </is>
-      </c>
-      <c r="EH109" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="EI109" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EJ109" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="EK109" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="EL109" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EM109" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="EN109" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EH109" t="inlineStr"/>
+      <c r="EI109" t="inlineStr"/>
+      <c r="EJ109" t="inlineStr"/>
+      <c r="EK109" t="inlineStr"/>
+      <c r="EL109" t="inlineStr"/>
+      <c r="EM109" t="inlineStr"/>
+      <c r="EN109" t="inlineStr"/>
       <c r="EO109" t="inlineStr"/>
       <c r="EP109" t="inlineStr"/>
     </row>
@@ -52167,7 +52167,7 @@
         <v>3.4</v>
       </c>
       <c r="DO110" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -52606,7 +52606,7 @@
         <v>75</v>
       </c>
       <c r="DD111" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE111" t="n">
         <v>2.11</v>
@@ -52639,7 +52639,7 @@
         <v>3.84</v>
       </c>
       <c r="DO111" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -53509,7 +53509,7 @@
         <v>1.75</v>
       </c>
       <c r="DE113" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF113" t="n">
         <v>1.4</v>
@@ -53539,7 +53539,7 @@
         <v>2.25</v>
       </c>
       <c r="DO113" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP113" t="b">
         <v>1</v>
@@ -53987,7 +53987,7 @@
         <v>2.21</v>
       </c>
       <c r="DO114" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -54467,7 +54467,7 @@
         <v>2.96</v>
       </c>
       <c r="DO115" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -55851,7 +55851,7 @@
         <v>3.01</v>
       </c>
       <c r="DO118" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -56298,7 +56298,7 @@
         <v>49</v>
       </c>
       <c r="DD119" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="DE119" t="n">
         <v>0.22</v>
@@ -56331,7 +56331,7 @@
         <v>2.19</v>
       </c>
       <c r="DO119" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -57275,7 +57275,7 @@
         <v>4.5</v>
       </c>
       <c r="DO121" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -57731,7 +57731,7 @@
         <v>2.24</v>
       </c>
       <c r="DO122" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -58203,7 +58203,7 @@
         <v>2.99</v>
       </c>
       <c r="DO123" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP123" t="b">
         <v>1</v>
@@ -59239,146 +59239,146 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F126" s="2" t="n">
         <v>46036.72916666666</v>
       </c>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J126" t="n">
+        <v>2</v>
+      </c>
+      <c r="K126" t="n">
+        <v>4</v>
+      </c>
+      <c r="L126" t="n">
+        <v>6</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1</v>
+      </c>
+      <c r="N126" t="n">
+        <v>2</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>9</v>
+      </c>
+      <c r="R126" t="n">
+        <v>4</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="n">
         <v>7</v>
       </c>
-      <c r="K126" t="n">
-        <v>1</v>
-      </c>
-      <c r="L126" t="n">
-        <v>8</v>
-      </c>
-      <c r="M126" t="n">
-        <v>3</v>
-      </c>
-      <c r="N126" t="n">
-        <v>4</v>
-      </c>
-      <c r="O126" t="n">
-        <v>1</v>
-      </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
+      <c r="U126" t="n">
+        <v>19</v>
+      </c>
+      <c r="V126" t="n">
+        <v>11</v>
+      </c>
+      <c r="W126" t="n">
+        <v>13</v>
+      </c>
+      <c r="X126" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>King Saud University Stadium</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
+        </is>
+      </c>
+      <c r="AC126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU126" t="n">
         <v>5</v>
       </c>
-      <c r="R126" t="n">
-        <v>5</v>
-      </c>
-      <c r="S126" t="n">
-        <v>6</v>
-      </c>
-      <c r="T126" t="n">
-        <v>0</v>
-      </c>
-      <c r="U126" t="n">
-        <v>11</v>
-      </c>
-      <c r="V126" t="n">
-        <v>5</v>
-      </c>
-      <c r="W126" t="n">
-        <v>18</v>
-      </c>
-      <c r="X126" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>49</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>King Abdullah Sports City</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>, Jeddah</t>
-        </is>
-      </c>
-      <c r="AC126" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD126" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE126" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF126" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="AG126" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI126" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AJ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU126" t="n">
-        <v>3</v>
-      </c>
       <c r="AV126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW126" t="n">
         <v>1</v>
@@ -59387,22 +59387,22 @@
         <v>2</v>
       </c>
       <c r="AY126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB126" t="n">
-        <v>5062</v>
+        <v>5067</v>
       </c>
       <c r="BC126" t="n">
         <v>0</v>
       </c>
       <c r="BD126" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="BE126" t="n">
         <v>0</v>
@@ -59417,76 +59417,76 @@
         <v>1</v>
       </c>
       <c r="BI126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK126" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BL126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM126" t="n">
         <v>3</v>
       </c>
       <c r="BN126" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BO126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT126" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU126" t="n">
         <v>1</v>
       </c>
       <c r="BV126" t="n">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="BW126" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="BX126" t="n">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="BY126" t="n">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="BZ126" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="CA126" t="n">
-        <v>0.96</v>
+        <v>1.17</v>
       </c>
       <c r="CB126" t="n">
-        <v>2.56</v>
+        <v>3.19</v>
       </c>
       <c r="CC126" t="n">
         <v>1</v>
       </c>
       <c r="CD126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE126" t="n">
         <v>1</v>
       </c>
       <c r="CF126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG126" t="n">
         <v>0</v>
@@ -59501,10 +59501,10 @@
         <v>1</v>
       </c>
       <c r="CK126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM126" t="n">
         <v>0</v>
@@ -59522,76 +59522,76 @@
         <v>1</v>
       </c>
       <c r="CR126" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CS126" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="CT126" t="n">
         <v>1</v>
       </c>
       <c r="CU126" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CV126" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX126" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY126" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ126" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA126" t="n">
+        <v>83</v>
+      </c>
+      <c r="DB126" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC126" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD126" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DE126" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DF126" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DG126" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DH126" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="DI126" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DJ126" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK126" t="n">
         <v>17</v>
       </c>
-      <c r="CW126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX126" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY126" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ126" t="n">
-        <v>47</v>
-      </c>
-      <c r="DA126" t="n">
-        <v>77</v>
-      </c>
-      <c r="DB126" t="n">
-        <v>40</v>
-      </c>
-      <c r="DC126" t="n">
-        <v>77</v>
-      </c>
-      <c r="DD126" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="DE126" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="DF126" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DG126" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DH126" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="DI126" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="DJ126" t="n">
-        <v>54</v>
-      </c>
-      <c r="DK126" t="n">
-        <v>24</v>
-      </c>
       <c r="DL126" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="DM126" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="DN126" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="DO126" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -59603,10 +59603,10 @@
         <v>1</v>
       </c>
       <c r="DS126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU126" t="b">
         <v>0</v>
@@ -59615,49 +59615,101 @@
         <v>1</v>
       </c>
       <c r="DW126" t="n">
-        <v>24.12</v>
+        <v>19.91</v>
       </c>
       <c r="DX126" t="n">
-        <v>7.98</v>
+        <v>6.1</v>
       </c>
       <c r="DY126" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="DZ126" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="EA126" t="inlineStr"/>
-      <c r="EB126" t="inlineStr"/>
-      <c r="EC126" t="inlineStr"/>
-      <c r="ED126" t="inlineStr"/>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="EA126" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EB126" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EC126" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="ED126" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
       <c r="EE126" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="EF126" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="EG126" t="inlineStr">
         <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EH126" t="inlineStr"/>
-      <c r="EI126" t="inlineStr"/>
-      <c r="EJ126" t="inlineStr"/>
-      <c r="EK126" t="inlineStr"/>
-      <c r="EL126" t="inlineStr"/>
-      <c r="EM126" t="inlineStr"/>
-      <c r="EN126" t="inlineStr"/>
-      <c r="EO126" t="inlineStr"/>
-      <c r="EP126" t="inlineStr"/>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="EH126" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EI126" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EJ126" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EK126" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EL126" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EM126" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="EN126" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EO126" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EP126" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -59675,146 +59727,146 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F127" s="2" t="n">
         <v>46036.72916666666</v>
       </c>
       <c r="G127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I127" t="n">
+        <v>3</v>
+      </c>
+      <c r="J127" t="n">
+        <v>7</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1</v>
+      </c>
+      <c r="L127" t="n">
+        <v>8</v>
+      </c>
+      <c r="M127" t="n">
+        <v>3</v>
+      </c>
+      <c r="N127" t="n">
+        <v>4</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
         <v>5</v>
       </c>
-      <c r="J127" t="n">
-        <v>2</v>
-      </c>
-      <c r="K127" t="n">
+      <c r="R127" t="n">
+        <v>5</v>
+      </c>
+      <c r="S127" t="n">
+        <v>6</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="n">
+        <v>11</v>
+      </c>
+      <c r="V127" t="n">
+        <v>5</v>
+      </c>
+      <c r="W127" t="n">
+        <v>18</v>
+      </c>
+      <c r="X127" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>King Abdullah Sports City</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>, Jeddah</t>
+        </is>
+      </c>
+      <c r="AC127" t="n">
         <v>4</v>
       </c>
-      <c r="L127" t="n">
-        <v>6</v>
-      </c>
-      <c r="M127" t="n">
-        <v>1</v>
-      </c>
-      <c r="N127" t="n">
-        <v>2</v>
-      </c>
-      <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>9</v>
-      </c>
-      <c r="R127" t="n">
+      <c r="AD127" t="n">
         <v>4</v>
       </c>
-      <c r="S127" t="n">
-        <v>10</v>
-      </c>
-      <c r="T127" t="n">
-        <v>7</v>
-      </c>
-      <c r="U127" t="n">
-        <v>19</v>
-      </c>
-      <c r="V127" t="n">
-        <v>11</v>
-      </c>
-      <c r="W127" t="n">
-        <v>13</v>
-      </c>
-      <c r="X127" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y127" t="n">
-        <v>42</v>
-      </c>
-      <c r="Z127" t="n">
-        <v>58</v>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>King Saud University Stadium</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
-        </is>
-      </c>
-      <c r="AC127" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD127" t="n">
-        <v>2</v>
-      </c>
       <c r="AE127" t="n">
-        <v>2.68</v>
+        <v>1.57</v>
       </c>
       <c r="AF127" t="n">
-        <v>3.4</v>
+        <v>4.37</v>
       </c>
       <c r="AG127" t="n">
-        <v>2.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH127" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI127" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AJ127" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AK127" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AL127" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AM127" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AN127" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AO127" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR127" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AS127" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AT127" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AU127" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW127" t="n">
         <v>1</v>
@@ -59823,22 +59875,22 @@
         <v>2</v>
       </c>
       <c r="AY127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB127" t="n">
-        <v>5067</v>
+        <v>5062</v>
       </c>
       <c r="BC127" t="n">
         <v>0</v>
       </c>
       <c r="BD127" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="BE127" t="n">
         <v>0</v>
@@ -59853,76 +59905,76 @@
         <v>1</v>
       </c>
       <c r="BI127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK127" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM127" t="n">
         <v>3</v>
       </c>
       <c r="BN127" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BO127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT127" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU127" t="n">
         <v>1</v>
       </c>
       <c r="BV127" t="n">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="BW127" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="BX127" t="n">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="BY127" t="n">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="BZ127" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="CA127" t="n">
-        <v>1.17</v>
+        <v>0.96</v>
       </c>
       <c r="CB127" t="n">
-        <v>3.19</v>
+        <v>2.56</v>
       </c>
       <c r="CC127" t="n">
         <v>1</v>
       </c>
       <c r="CD127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE127" t="n">
         <v>1</v>
       </c>
       <c r="CF127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG127" t="n">
         <v>0</v>
@@ -59937,10 +59989,10 @@
         <v>1</v>
       </c>
       <c r="CK127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM127" t="n">
         <v>0</v>
@@ -59958,73 +60010,73 @@
         <v>1</v>
       </c>
       <c r="CR127" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CS127" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="CT127" t="n">
         <v>1</v>
       </c>
       <c r="CU127" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CV127" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="CW127" t="n">
         <v>1</v>
       </c>
       <c r="CX127" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="CY127" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CZ127" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="DA127" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="DB127" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="DC127" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="DD127" t="n">
-        <v>1.13</v>
+        <v>2.33</v>
       </c>
       <c r="DE127" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DF127" t="n">
-        <v>0.83</v>
+        <v>2.14</v>
       </c>
       <c r="DG127" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="DH127" t="n">
-        <v>0.62</v>
+        <v>2.15</v>
       </c>
       <c r="DI127" t="n">
-        <v>1.54</v>
+        <v>2.38</v>
       </c>
       <c r="DJ127" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="DK127" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="DL127" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="DM127" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="DN127" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="DO127" t="n">
         <v>17</v>
@@ -60039,10 +60091,10 @@
         <v>1</v>
       </c>
       <c r="DS127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU127" t="b">
         <v>0</v>
@@ -60051,101 +60103,49 @@
         <v>1</v>
       </c>
       <c r="DW127" t="n">
-        <v>19.91</v>
+        <v>24.12</v>
       </c>
       <c r="DX127" t="n">
-        <v>6.1</v>
+        <v>7.98</v>
       </c>
       <c r="DY127" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="DZ127" t="inlineStr">
         <is>
-          <t>13%</t>
-        </is>
-      </c>
-      <c r="EA127" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EB127" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EC127" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="ED127" t="inlineStr">
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA127" t="inlineStr"/>
+      <c r="EB127" t="inlineStr"/>
+      <c r="EC127" t="inlineStr"/>
+      <c r="ED127" t="inlineStr"/>
+      <c r="EE127" t="inlineStr">
+        <is>
+          <t>5.44</t>
+        </is>
+      </c>
+      <c r="EF127" t="inlineStr">
+        <is>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="EG127" t="inlineStr">
         <is>
           <t>1.52</t>
         </is>
       </c>
-      <c r="EE127" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
-      <c r="EF127" t="inlineStr">
-        <is>
-          <t>3.48</t>
-        </is>
-      </c>
-      <c r="EG127" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="EH127" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
-      </c>
-      <c r="EI127" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="EJ127" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="EK127" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EL127" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="EM127" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="EN127" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EO127" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EP127" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
+      <c r="EH127" t="inlineStr"/>
+      <c r="EI127" t="inlineStr"/>
+      <c r="EJ127" t="inlineStr"/>
+      <c r="EK127" t="inlineStr"/>
+      <c r="EL127" t="inlineStr"/>
+      <c r="EM127" t="inlineStr"/>
+      <c r="EN127" t="inlineStr"/>
+      <c r="EO127" t="inlineStr"/>
+      <c r="EP127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -60941,7 +60941,7 @@
         <v>1.75</v>
       </c>
       <c r="DE129" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF129" t="n">
         <v>1.67</v>
@@ -60971,7 +60971,7 @@
         <v>2.11</v>
       </c>
       <c r="DO129" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP129" t="b">
         <v>1</v>
@@ -61426,7 +61426,7 @@
         <v>77</v>
       </c>
       <c r="DD130" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE130" t="n">
         <v>2</v>
@@ -61459,7 +61459,7 @@
         <v>3.23</v>
       </c>
       <c r="DO130" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -61893,7 +61893,7 @@
         <v>1.25</v>
       </c>
       <c r="DE131" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DF131" t="n">
         <v>1</v>
@@ -61923,7 +61923,7 @@
         <v>1.9</v>
       </c>
       <c r="DO131" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -62798,7 +62798,7 @@
         <v>79</v>
       </c>
       <c r="DD133" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="DE133" t="n">
         <v>0.44</v>
@@ -62831,7 +62831,7 @@
         <v>3.35</v>
       </c>
       <c r="DO133" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -63262,7 +63262,7 @@
         <v>54</v>
       </c>
       <c r="DD134" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="DE134" t="n">
         <v>2.11</v>
@@ -63295,7 +63295,7 @@
         <v>2.77</v>
       </c>
       <c r="DO134" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP134" t="b">
         <v>1</v>
@@ -63753,7 +63753,7 @@
         <v>1</v>
       </c>
       <c r="DE135" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DF135" t="n">
         <v>1.14</v>
@@ -63783,7 +63783,7 @@
         <v>2.59</v>
       </c>
       <c r="DO135" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -66131,7 +66131,7 @@
         <v>2.36</v>
       </c>
       <c r="DO140" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP140" t="b">
         <v>1</v>
@@ -66603,7 +66603,7 @@
         <v>3.25</v>
       </c>
       <c r="DO141" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -67523,7 +67523,7 @@
         <v>2.43</v>
       </c>
       <c r="DO143" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP143" t="b">
         <v>1</v>
@@ -67987,7 +67987,7 @@
         <v>3.66</v>
       </c>
       <c r="DO144" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP144" t="b">
         <v>1</v>
@@ -68724,7 +68724,7 @@
         <v>0</v>
       </c>
       <c r="BF146" t="n">
-        <v>-1</v>
+        <v>2519</v>
       </c>
       <c r="BG146" t="n">
         <v>2</v>
@@ -69196,7 +69196,7 @@
         <v>0</v>
       </c>
       <c r="BF147" t="n">
-        <v>-1</v>
+        <v>1596</v>
       </c>
       <c r="BG147" t="n">
         <v>2</v>
@@ -69684,7 +69684,7 @@
         <v>0</v>
       </c>
       <c r="BF148" t="n">
-        <v>-1</v>
+        <v>6967</v>
       </c>
       <c r="BG148" t="n">
         <v>2</v>
@@ -70172,7 +70172,7 @@
         <v>0</v>
       </c>
       <c r="BF149" t="n">
-        <v>-1</v>
+        <v>3107</v>
       </c>
       <c r="BG149" t="n">
         <v>2</v>
@@ -70475,140 +70475,132 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
         <v>46047.72916666666</v>
       </c>
       <c r="G150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" t="n">
         <v>2</v>
       </c>
       <c r="J150" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K150" t="n">
+        <v>8</v>
+      </c>
+      <c r="L150" t="n">
+        <v>12</v>
+      </c>
+      <c r="M150" t="n">
+        <v>2</v>
+      </c>
+      <c r="N150" t="n">
+        <v>2</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
         <v>6</v>
       </c>
-      <c r="L150" t="n">
+      <c r="R150" t="n">
+        <v>5</v>
+      </c>
+      <c r="S150" t="n">
         <v>8</v>
       </c>
-      <c r="M150" t="n">
-        <v>2</v>
-      </c>
-      <c r="N150" t="n">
-        <v>2</v>
-      </c>
-      <c r="O150" t="n">
-        <v>1</v>
-      </c>
-      <c r="P150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>2</v>
-      </c>
-      <c r="R150" t="n">
-        <v>4</v>
-      </c>
-      <c r="S150" t="n">
-        <v>2</v>
-      </c>
       <c r="T150" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U150" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="V150" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="W150" t="n">
+        <v>8</v>
+      </c>
+      <c r="X150" t="n">
         <v>12</v>
       </c>
-      <c r="X150" t="n">
-        <v>8</v>
-      </c>
       <c r="Y150" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Z150" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA150" t="inlineStr">
-        <is>
-          <t>Prince Turki bin Abdul Aziz Stadium</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>, Riyadh</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="AA150" t="inlineStr"/>
+      <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD150" t="n">
         <v>2</v>
       </c>
       <c r="AE150" t="n">
-        <v>12</v>
+        <v>2.4</v>
       </c>
       <c r="AF150" t="n">
-        <v>8</v>
+        <v>3.45</v>
       </c>
       <c r="AG150" t="n">
-        <v>1.16</v>
+        <v>3</v>
       </c>
       <c r="AH150" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AI150" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="AJ150" t="n">
-        <v>1.8</v>
+        <v>3.14</v>
       </c>
       <c r="AK150" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL150" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AM150" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AN150" t="n">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="AO150" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AP150" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="AR150" t="n">
-        <v>2.01</v>
+        <v>2.78</v>
       </c>
       <c r="AS150" t="n">
-        <v>4.8</v>
+        <v>2.99</v>
       </c>
       <c r="AT150" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AU150" t="n">
         <v>2</v>
@@ -70617,28 +70609,28 @@
         <v>0</v>
       </c>
       <c r="AW150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY150" t="n">
         <v>0</v>
       </c>
       <c r="AZ150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB150" t="n">
-        <v>-1</v>
+        <v>5071</v>
       </c>
       <c r="BC150" t="n">
         <v>0</v>
       </c>
       <c r="BD150" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="BE150" t="n">
         <v>0</v>
@@ -70653,64 +70645,64 @@
         <v>1</v>
       </c>
       <c r="BI150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ150" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BK150" t="n">
         <v>1</v>
       </c>
       <c r="BL150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM150" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BN150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BO150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP150" t="n">
         <v>1</v>
       </c>
       <c r="BQ150" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR150" t="n">
         <v>1</v>
       </c>
       <c r="BS150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT150" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BU150" t="n">
         <v>1</v>
       </c>
       <c r="BV150" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="BW150" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="BX150" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="BY150" t="n">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="BZ150" t="n">
-        <v>0.59</v>
+        <v>1.69</v>
       </c>
       <c r="CA150" t="n">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="CB150" t="n">
-        <v>2.16</v>
+        <v>2.88</v>
       </c>
       <c r="CC150" t="n">
         <v>0</v>
@@ -70746,7 +70738,7 @@
         <v>0</v>
       </c>
       <c r="CN150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CO150" t="n">
         <v>0</v>
@@ -70758,73 +70750,73 @@
         <v>1</v>
       </c>
       <c r="CR150" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="CS150" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CT150" t="n">
         <v>1</v>
       </c>
       <c r="CU150" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV150" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX150" t="n">
         <v>7</v>
       </c>
-      <c r="CV150" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW150" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX150" t="n">
-        <v>9</v>
-      </c>
       <c r="CY150" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CZ150" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="DA150" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="DB150" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="DC150" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="DD150" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE150" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="DF150" t="n">
         <v>1</v>
       </c>
       <c r="DG150" t="n">
-        <v>2.71</v>
+        <v>1.13</v>
       </c>
       <c r="DH150" t="n">
-        <v>0.63</v>
+        <v>0.88</v>
       </c>
       <c r="DI150" t="n">
-        <v>2.75</v>
+        <v>1.31</v>
       </c>
       <c r="DJ150" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="DK150" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="DL150" t="n">
-        <v>1.54</v>
+        <v>1.1</v>
       </c>
       <c r="DM150" t="n">
-        <v>1.98</v>
+        <v>1.29</v>
       </c>
       <c r="DN150" t="n">
-        <v>3.52</v>
+        <v>2.39</v>
       </c>
       <c r="DO150" t="n">
         <v>17</v>
@@ -70848,17 +70840,17 @@
         <v>0</v>
       </c>
       <c r="DV150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW150" t="n">
-        <v>18.26</v>
+        <v>14.15</v>
       </c>
       <c r="DX150" t="n">
-        <v>10.93</v>
+        <v>11.69</v>
       </c>
       <c r="DY150" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="DZ150" t="inlineStr">
@@ -70868,68 +70860,84 @@
       </c>
       <c r="EA150" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EB150" t="inlineStr">
         <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="EC150" t="inlineStr"/>
-      <c r="ED150" t="inlineStr"/>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EC150" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="ED150" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
       <c r="EE150" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EF150" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="EG150" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EH150" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EI150" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EJ150" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="EK150" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EL150" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EM150" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="EN150" t="inlineStr">
         <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EO150" t="inlineStr"/>
-      <c r="EP150" t="inlineStr"/>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EO150" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EP150" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -70947,348 +70955,356 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F151" s="2" t="n">
         <v>46047.72916666666</v>
       </c>
       <c r="G151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151" t="n">
         <v>2</v>
       </c>
       <c r="J151" t="n">
+        <v>2</v>
+      </c>
+      <c r="K151" t="n">
+        <v>6</v>
+      </c>
+      <c r="L151" t="n">
+        <v>8</v>
+      </c>
+      <c r="M151" t="n">
+        <v>2</v>
+      </c>
+      <c r="N151" t="n">
+        <v>2</v>
+      </c>
+      <c r="O151" t="n">
+        <v>1</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>2</v>
+      </c>
+      <c r="R151" t="n">
         <v>4</v>
       </c>
-      <c r="K151" t="n">
+      <c r="S151" t="n">
+        <v>2</v>
+      </c>
+      <c r="T151" t="n">
+        <v>9</v>
+      </c>
+      <c r="U151" t="n">
+        <v>4</v>
+      </c>
+      <c r="V151" t="n">
+        <v>13</v>
+      </c>
+      <c r="W151" t="n">
+        <v>12</v>
+      </c>
+      <c r="X151" t="n">
         <v>8</v>
       </c>
-      <c r="L151" t="n">
+      <c r="Y151" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>66</v>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>Prince Turki bin Abdul Aziz Stadium</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>, Riyadh</t>
+        </is>
+      </c>
+      <c r="AC151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE151" t="n">
         <v>12</v>
       </c>
-      <c r="M151" t="n">
-        <v>2</v>
-      </c>
-      <c r="N151" t="n">
-        <v>2</v>
-      </c>
-      <c r="O151" t="n">
-        <v>0</v>
-      </c>
-      <c r="P151" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q151" t="n">
+      <c r="AF151" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>66</v>
+      </c>
+      <c r="BE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF151" t="n">
+        <v>4480</v>
+      </c>
+      <c r="BG151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ151" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM151" t="n">
         <v>6</v>
       </c>
-      <c r="R151" t="n">
+      <c r="BN151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ151" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT151" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV151" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW151" t="n">
+        <v>64</v>
+      </c>
+      <c r="BX151" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY151" t="n">
+        <v>135</v>
+      </c>
+      <c r="BZ151" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="CA151" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CB151" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR151" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS151" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU151" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV151" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX151" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY151" t="n">
         <v>5</v>
       </c>
-      <c r="S151" t="n">
-        <v>8</v>
-      </c>
-      <c r="T151" t="n">
-        <v>3</v>
-      </c>
-      <c r="U151" t="n">
-        <v>14</v>
-      </c>
-      <c r="V151" t="n">
-        <v>8</v>
-      </c>
-      <c r="W151" t="n">
-        <v>8</v>
-      </c>
-      <c r="X151" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y151" t="n">
-        <v>56</v>
-      </c>
-      <c r="Z151" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA151" t="inlineStr"/>
-      <c r="AB151" t="inlineStr"/>
-      <c r="AC151" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD151" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE151" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF151" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AG151" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH151" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI151" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ151" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AK151" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL151" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM151" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AN151" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AO151" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AP151" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ151" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR151" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AS151" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AT151" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU151" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX151" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ151" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB151" t="n">
-        <v>5071</v>
-      </c>
-      <c r="BC151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD151" t="n">
-        <v>53</v>
-      </c>
-      <c r="BE151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF151" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG151" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH151" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI151" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ151" t="n">
-        <v>6</v>
-      </c>
-      <c r="BK151" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL151" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM151" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN151" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO151" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP151" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR151" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS151" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT151" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU151" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV151" t="n">
-        <v>54</v>
-      </c>
-      <c r="BW151" t="n">
-        <v>46</v>
-      </c>
-      <c r="BX151" t="n">
-        <v>93</v>
-      </c>
-      <c r="BY151" t="n">
-        <v>73</v>
-      </c>
-      <c r="BZ151" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CA151" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="CB151" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="CC151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI151" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ151" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN151" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ151" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR151" t="n">
-        <v>28</v>
-      </c>
-      <c r="CS151" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT151" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU151" t="n">
-        <v>12</v>
-      </c>
-      <c r="CV151" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW151" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX151" t="n">
+      <c r="CZ151" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA151" t="n">
+        <v>94</v>
+      </c>
+      <c r="DB151" t="n">
+        <v>48</v>
+      </c>
+      <c r="DC151" t="n">
+        <v>94</v>
+      </c>
+      <c r="DD151" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE151" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DF151" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG151" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DH151" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DI151" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DJ151" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK151" t="n">
         <v>7</v>
       </c>
-      <c r="CY151" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ151" t="n">
-        <v>34</v>
-      </c>
-      <c r="DA151" t="n">
-        <v>67</v>
-      </c>
-      <c r="DB151" t="n">
-        <v>34</v>
-      </c>
-      <c r="DC151" t="n">
-        <v>66</v>
-      </c>
-      <c r="DD151" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DE151" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF151" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG151" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="DH151" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="DI151" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="DJ151" t="n">
-        <v>67</v>
-      </c>
-      <c r="DK151" t="n">
-        <v>34</v>
-      </c>
       <c r="DL151" t="n">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="DM151" t="n">
-        <v>1.29</v>
+        <v>1.98</v>
       </c>
       <c r="DN151" t="n">
-        <v>2.39</v>
+        <v>3.52</v>
       </c>
       <c r="DO151" t="n">
         <v>17</v>
@@ -71312,104 +71328,1480 @@
         <v>0</v>
       </c>
       <c r="DV151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW151" t="n">
-        <v>14.15</v>
+        <v>18.26</v>
       </c>
       <c r="DX151" t="n">
-        <v>11.69</v>
+        <v>10.93</v>
       </c>
       <c r="DY151" t="inlineStr">
         <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="DZ151" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="EA151" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EB151" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EC151" t="inlineStr"/>
+      <c r="ED151" t="inlineStr"/>
+      <c r="EE151" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EF151" t="inlineStr">
+        <is>
+          <t>8.51</t>
+        </is>
+      </c>
+      <c r="EG151" t="inlineStr">
+        <is>
+          <t>11.38</t>
+        </is>
+      </c>
+      <c r="EH151" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EI151" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EJ151" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="EK151" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EL151" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EM151" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EN151" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EO151" t="inlineStr"/>
+      <c r="EP151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>18</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Al Hazm</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Dhamk</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>46048.63888888889</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2</v>
+      </c>
+      <c r="H152" t="n">
+        <v>1</v>
+      </c>
+      <c r="I152" t="n">
+        <v>3</v>
+      </c>
+      <c r="J152" t="n">
+        <v>5</v>
+      </c>
+      <c r="K152" t="n">
+        <v>3</v>
+      </c>
+      <c r="L152" t="n">
+        <v>8</v>
+      </c>
+      <c r="M152" t="n">
+        <v>2</v>
+      </c>
+      <c r="N152" t="n">
+        <v>5</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>3</v>
+      </c>
+      <c r="R152" t="n">
+        <v>4</v>
+      </c>
+      <c r="S152" t="n">
+        <v>5</v>
+      </c>
+      <c r="T152" t="n">
+        <v>6</v>
+      </c>
+      <c r="U152" t="n">
+        <v>8</v>
+      </c>
+      <c r="V152" t="n">
+        <v>10</v>
+      </c>
+      <c r="W152" t="n">
+        <v>10</v>
+      </c>
+      <c r="X152" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA152" t="inlineStr"/>
+      <c r="AB152" t="inlineStr"/>
+      <c r="AC152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>5089</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>66</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>1114</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI152" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL152" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN152" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP152" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ152" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS152" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV152" t="n">
+        <v>70</v>
+      </c>
+      <c r="BW152" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX152" t="n">
+        <v>119</v>
+      </c>
+      <c r="BY152" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ152" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA152" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CB152" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP152" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR152" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS152" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU152" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV152" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW152" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX152" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY152" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ152" t="n">
+        <v>48</v>
+      </c>
+      <c r="DA152" t="n">
+        <v>87</v>
+      </c>
+      <c r="DB152" t="n">
+        <v>52</v>
+      </c>
+      <c r="DC152" t="n">
+        <v>72</v>
+      </c>
+      <c r="DD152" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DE152" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DF152" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DG152" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DH152" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DI152" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="DJ152" t="n">
+        <v>53</v>
+      </c>
+      <c r="DK152" t="n">
+        <v>14</v>
+      </c>
+      <c r="DL152" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DM152" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DN152" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DO152" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP152" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ152" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR152" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU152" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV152" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW152" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="DX152" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="DY152" t="inlineStr">
+        <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="DZ151" t="inlineStr">
+      <c r="DZ152" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="EA152" t="inlineStr"/>
+      <c r="EB152" t="inlineStr"/>
+      <c r="EC152" t="inlineStr"/>
+      <c r="ED152" t="inlineStr"/>
+      <c r="EE152" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="EF152" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EG152" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EH152" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="EI152" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EJ152" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EK152" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EL152" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EM152" t="inlineStr"/>
+      <c r="EN152" t="inlineStr"/>
+      <c r="EO152" t="inlineStr"/>
+      <c r="EP152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>18</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Al Taawon</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>46048.72916666666</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" t="n">
+        <v>8</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>8</v>
+      </c>
+      <c r="M153" t="n">
+        <v>5</v>
+      </c>
+      <c r="N153" t="n">
+        <v>5</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>9</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="n">
+        <v>11</v>
+      </c>
+      <c r="T153" t="n">
+        <v>3</v>
+      </c>
+      <c r="U153" t="n">
+        <v>20</v>
+      </c>
+      <c r="V153" t="n">
+        <v>3</v>
+      </c>
+      <c r="W153" t="n">
+        <v>24</v>
+      </c>
+      <c r="X153" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>King Saud University Stadium</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>Ash Shaikh Hasan Ibn Abdullah Al Ash Shaikh, King Saud University, Riyadh</t>
+        </is>
+      </c>
+      <c r="AC153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>5069</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD153" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF153" t="n">
+        <v>15425</v>
+      </c>
+      <c r="BG153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI153" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK153" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM153" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN153" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO153" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ153" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR153" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS153" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT153" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV153" t="n">
+        <v>75</v>
+      </c>
+      <c r="BW153" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX153" t="n">
+        <v>121</v>
+      </c>
+      <c r="BY153" t="n">
+        <v>61</v>
+      </c>
+      <c r="BZ153" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CA153" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CB153" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="CC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP153" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR153" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS153" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU153" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV153" t="n">
+        <v>24</v>
+      </c>
+      <c r="CW153" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX153" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY153" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ153" t="n">
+        <v>76</v>
+      </c>
+      <c r="DA153" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB153" t="n">
+        <v>57</v>
+      </c>
+      <c r="DC153" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD153" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DE153" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF153" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DG153" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DH153" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DI153" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="DJ153" t="n">
+        <v>26</v>
+      </c>
+      <c r="DK153" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL153" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DM153" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DN153" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="DO153" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP153" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV153" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW153" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="DX153" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="DY153" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="DZ153" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="EA151" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EB151" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EC151" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="ED151" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EE151" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="EF151" t="inlineStr">
-        <is>
-          <t>3.58</t>
-        </is>
-      </c>
-      <c r="EG151" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EH151" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="EI151" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EJ151" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="EK151" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EL151" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="EM151" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="EN151" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EO151" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EP151" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
+      <c r="EA153" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EB153" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EC153" t="inlineStr"/>
+      <c r="ED153" t="inlineStr"/>
+      <c r="EE153" t="inlineStr">
+        <is>
+          <t>9.65</t>
+        </is>
+      </c>
+      <c r="EF153" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="EG153" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EH153" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EI153" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EJ153" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="EK153" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EL153" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EM153" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EN153" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EO153" t="inlineStr"/>
+      <c r="EP153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Saudi_Pro_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>18</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Al Akhdoud</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>46048.72916666666</v>
+      </c>
+      <c r="G154" t="n">
+        <v>2</v>
+      </c>
+      <c r="H154" t="n">
+        <v>1</v>
+      </c>
+      <c r="I154" t="n">
+        <v>3</v>
+      </c>
+      <c r="J154" t="n">
+        <v>10</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>10</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>2</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>9</v>
+      </c>
+      <c r="R154" t="n">
+        <v>2</v>
+      </c>
+      <c r="S154" t="n">
+        <v>9</v>
+      </c>
+      <c r="T154" t="n">
+        <v>4</v>
+      </c>
+      <c r="U154" t="n">
+        <v>18</v>
+      </c>
+      <c r="V154" t="n">
+        <v>6</v>
+      </c>
+      <c r="W154" t="n">
+        <v>15</v>
+      </c>
+      <c r="X154" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>72</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>King Abdullah Sports City</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>, Jeddah</t>
+        </is>
+      </c>
+      <c r="AC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>5070</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>8102</v>
+      </c>
+      <c r="BG154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI154" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK154" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM154" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN154" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV154" t="n">
+        <v>86</v>
+      </c>
+      <c r="BW154" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX154" t="n">
+        <v>135</v>
+      </c>
+      <c r="BY154" t="n">
+        <v>37</v>
+      </c>
+      <c r="BZ154" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CA154" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="CB154" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="CC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR154" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS154" t="n">
+        <v>8</v>
+      </c>
+      <c r="CT154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU154" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV154" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX154" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY154" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ154" t="n">
+        <v>34</v>
+      </c>
+      <c r="DA154" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB154" t="n">
+        <v>34</v>
+      </c>
+      <c r="DC154" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD154" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE154" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DF154" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG154" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DH154" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DI154" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DJ154" t="n">
+        <v>66</v>
+      </c>
+      <c r="DK154" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL154" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DM154" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="DN154" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DO154" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW154" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="DX154" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="DY154" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="DZ154" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="EA154" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EB154" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EC154" t="inlineStr"/>
+      <c r="ED154" t="inlineStr"/>
+      <c r="EE154" t="inlineStr">
+        <is>
+          <t>15.14</t>
+        </is>
+      </c>
+      <c r="EF154" t="inlineStr">
+        <is>
+          <t>9.44</t>
+        </is>
+      </c>
+      <c r="EG154" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="EH154" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EI154" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EJ154" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="EK154" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EL154" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EM154" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EN154" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EO154" t="inlineStr"/>
+      <c r="EP154" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
@@ -81381,10 +81381,10 @@
         <v>12</v>
       </c>
       <c r="Y179" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Z179" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA179" t="inlineStr"/>
       <c r="AB179" t="inlineStr"/>
@@ -82233,7 +82233,7 @@
         <v>0</v>
       </c>
       <c r="Q181" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R181" t="n">
         <v>1</v>
@@ -82245,7 +82245,7 @@
         <v>4</v>
       </c>
       <c r="U181" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V181" t="n">
         <v>5</v>
@@ -82412,13 +82412,13 @@
         <v>74</v>
       </c>
       <c r="BZ181" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="CA181" t="n">
         <v>0.61</v>
       </c>
       <c r="CB181" t="n">
-        <v>2.73</v>
+        <v>2.86</v>
       </c>
       <c r="CC181" t="n">
         <v>0</v>

--- a/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
@@ -86694,8 +86694,16 @@
           <t>2.39</t>
         </is>
       </c>
-      <c r="EI190" t="inlineStr"/>
-      <c r="EJ190" t="inlineStr"/>
+      <c r="EI190" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EJ190" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
       <c r="EK190" t="inlineStr"/>
       <c r="EL190" t="inlineStr"/>
     </row>

--- a/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
+++ b/data/matches/leagues/Saudi_Pro_League_2025-2026.xlsx
@@ -96333,13 +96333,13 @@
         <v>1</v>
       </c>
       <c r="Q212" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R212" t="n">
         <v>3</v>
       </c>
       <c r="S212" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T212" t="n">
         <v>5</v>
@@ -96512,13 +96512,13 @@
         <v>82</v>
       </c>
       <c r="BZ212" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="CA212" t="n">
         <v>1.07</v>
       </c>
       <c r="CB212" t="n">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="CC212" t="n">
         <v>1</v>
@@ -97219,13 +97219,13 @@
         <v>1</v>
       </c>
       <c r="S214" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T214" t="n">
         <v>1</v>
       </c>
       <c r="U214" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V214" t="n">
         <v>2</v>
@@ -97392,13 +97392,13 @@
         <v>57</v>
       </c>
       <c r="BZ214" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="CA214" t="n">
         <v>0.33</v>
       </c>
       <c r="CB214" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="CC214" t="n">
         <v>1</v>
@@ -98113,10 +98113,10 @@
         <v>8</v>
       </c>
       <c r="M216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -98149,18 +98149,18 @@
         <v>13</v>
       </c>
       <c r="Y216" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Z216" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AA216" t="inlineStr"/>
       <c r="AB216" t="inlineStr"/>
       <c r="AC216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE216" t="n">
         <v>8.82</v>
@@ -98274,19 +98274,19 @@
         <v>1</v>
       </c>
       <c r="BP216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR216" t="n">
         <v>0</v>
       </c>
       <c r="BS216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU216" t="n">
         <v>1</v>
